--- a/doc/시스템사업부_프로젝트 개발 일정표.xlsx
+++ b/doc/시스템사업부_프로젝트 개발 일정표.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\web_git\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EFD838A-E9F1-4971-B841-A42A2D276BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADE4CC1-1C29-479F-96CF-233DB4BAB4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4725" yWindow="4170" windowWidth="21435" windowHeight="15600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="개발 일정표" sheetId="1" r:id="rId1"/>
@@ -442,8 +442,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="177" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="mm\/dd"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="mm\/dd"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1325,11 +1325,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1395,127 +1395,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1538,108 +1426,90 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1654,59 +1524,47 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
@@ -1724,20 +1582,14 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1755,13 +1607,13 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="51" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1769,26 +1621,26 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1799,6 +1651,147 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="48" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2091,136 +2084,136 @@
   <sheetData>
     <row r="3" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F4" s="50" t="s">
+      <c r="F4" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="51"/>
-      <c r="P4" s="51"/>
-      <c r="Q4" s="51"/>
-      <c r="R4" s="51"/>
-      <c r="S4" s="51"/>
-      <c r="T4" s="51"/>
-      <c r="U4" s="51"/>
-      <c r="V4" s="51"/>
-      <c r="W4" s="52"/>
+      <c r="G4" s="137"/>
+      <c r="H4" s="137"/>
+      <c r="I4" s="137"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137"/>
+      <c r="M4" s="137"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="137"/>
+      <c r="P4" s="137"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="137"/>
+      <c r="S4" s="137"/>
+      <c r="T4" s="137"/>
+      <c r="U4" s="137"/>
+      <c r="V4" s="137"/>
+      <c r="W4" s="138"/>
     </row>
     <row r="5" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F5" s="53"/>
-      <c r="G5" s="54"/>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="54"/>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="54"/>
-      <c r="Q5" s="54"/>
-      <c r="R5" s="54"/>
-      <c r="S5" s="54"/>
-      <c r="T5" s="54"/>
-      <c r="U5" s="54"/>
-      <c r="V5" s="54"/>
-      <c r="W5" s="55"/>
+      <c r="F5" s="139"/>
+      <c r="G5" s="140"/>
+      <c r="H5" s="140"/>
+      <c r="I5" s="140"/>
+      <c r="J5" s="140"/>
+      <c r="K5" s="140"/>
+      <c r="L5" s="140"/>
+      <c r="M5" s="140"/>
+      <c r="N5" s="140"/>
+      <c r="O5" s="140"/>
+      <c r="P5" s="140"/>
+      <c r="Q5" s="140"/>
+      <c r="R5" s="140"/>
+      <c r="S5" s="140"/>
+      <c r="T5" s="140"/>
+      <c r="U5" s="140"/>
+      <c r="V5" s="140"/>
+      <c r="W5" s="141"/>
     </row>
     <row r="6" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F6" s="56"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
-      <c r="O6" s="57"/>
-      <c r="P6" s="57"/>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="57"/>
-      <c r="S6" s="57"/>
-      <c r="T6" s="57"/>
-      <c r="U6" s="57"/>
-      <c r="V6" s="57"/>
-      <c r="W6" s="58"/>
+      <c r="F6" s="142"/>
+      <c r="G6" s="143"/>
+      <c r="H6" s="143"/>
+      <c r="I6" s="143"/>
+      <c r="J6" s="143"/>
+      <c r="K6" s="143"/>
+      <c r="L6" s="143"/>
+      <c r="M6" s="143"/>
+      <c r="N6" s="143"/>
+      <c r="O6" s="143"/>
+      <c r="P6" s="143"/>
+      <c r="Q6" s="143"/>
+      <c r="R6" s="143"/>
+      <c r="S6" s="143"/>
+      <c r="T6" s="143"/>
+      <c r="U6" s="143"/>
+      <c r="V6" s="143"/>
+      <c r="W6" s="144"/>
     </row>
     <row r="7" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F7" s="59" t="s">
+      <c r="F7" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
-      <c r="J7" s="60"/>
-      <c r="K7" s="60"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="60"/>
-      <c r="N7" s="60"/>
-      <c r="O7" s="60"/>
-      <c r="P7" s="60"/>
-      <c r="Q7" s="60"/>
-      <c r="R7" s="60"/>
-      <c r="S7" s="60"/>
-      <c r="T7" s="60"/>
-      <c r="U7" s="60"/>
-      <c r="V7" s="60"/>
-      <c r="W7" s="61"/>
+      <c r="G7" s="146"/>
+      <c r="H7" s="146"/>
+      <c r="I7" s="146"/>
+      <c r="J7" s="146"/>
+      <c r="K7" s="146"/>
+      <c r="L7" s="146"/>
+      <c r="M7" s="146"/>
+      <c r="N7" s="146"/>
+      <c r="O7" s="146"/>
+      <c r="P7" s="146"/>
+      <c r="Q7" s="146"/>
+      <c r="R7" s="146"/>
+      <c r="S7" s="146"/>
+      <c r="T7" s="146"/>
+      <c r="U7" s="146"/>
+      <c r="V7" s="146"/>
+      <c r="W7" s="147"/>
     </row>
     <row r="8" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F8" s="62"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
-      <c r="J8" s="63"/>
-      <c r="K8" s="63"/>
-      <c r="L8" s="63"/>
-      <c r="M8" s="63"/>
-      <c r="N8" s="63"/>
-      <c r="O8" s="63"/>
-      <c r="P8" s="63"/>
-      <c r="Q8" s="63"/>
-      <c r="R8" s="63"/>
-      <c r="S8" s="63"/>
-      <c r="T8" s="63"/>
-      <c r="U8" s="63"/>
-      <c r="V8" s="63"/>
-      <c r="W8" s="64"/>
+      <c r="F8" s="148"/>
+      <c r="G8" s="149"/>
+      <c r="H8" s="149"/>
+      <c r="I8" s="149"/>
+      <c r="J8" s="149"/>
+      <c r="K8" s="149"/>
+      <c r="L8" s="149"/>
+      <c r="M8" s="149"/>
+      <c r="N8" s="149"/>
+      <c r="O8" s="149"/>
+      <c r="P8" s="149"/>
+      <c r="Q8" s="149"/>
+      <c r="R8" s="149"/>
+      <c r="S8" s="149"/>
+      <c r="T8" s="149"/>
+      <c r="U8" s="149"/>
+      <c r="V8" s="149"/>
+      <c r="W8" s="150"/>
     </row>
     <row r="9" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F9" s="35" t="s">
+      <c r="F9" s="151" t="s">
         <v>0</v>
       </c>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="35" t="s">
+      <c r="G9" s="152"/>
+      <c r="H9" s="152"/>
+      <c r="I9" s="152"/>
+      <c r="J9" s="152"/>
+      <c r="K9" s="151" t="s">
         <v>1</v>
       </c>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="37"/>
-      <c r="O9" s="35" t="s">
+      <c r="L9" s="152"/>
+      <c r="M9" s="152"/>
+      <c r="N9" s="153"/>
+      <c r="O9" s="151" t="s">
         <v>12</v>
       </c>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="37"/>
-      <c r="S9" s="35" t="s">
+      <c r="P9" s="152"/>
+      <c r="Q9" s="152"/>
+      <c r="R9" s="153"/>
+      <c r="S9" s="151" t="s">
         <v>13</v>
       </c>
-      <c r="T9" s="36"/>
-      <c r="U9" s="36"/>
-      <c r="V9" s="36"/>
-      <c r="W9" s="37"/>
+      <c r="T9" s="152"/>
+      <c r="U9" s="152"/>
+      <c r="V9" s="152"/>
+      <c r="W9" s="153"/>
     </row>
     <row r="10" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F10" s="3" t="s">
@@ -2294,7 +2287,7 @@
       <c r="W11" s="7"/>
     </row>
     <row r="12" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F12" s="81" t="s">
+      <c r="F12" s="43" t="s">
         <v>14</v>
       </c>
       <c r="K12" s="4"/>
@@ -2306,14 +2299,14 @@
       <c r="W12" s="7"/>
     </row>
     <row r="13" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F13" s="77" t="s">
+      <c r="F13" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="41" t="s">
+      <c r="G13" s="159" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="42"/>
-      <c r="I13" s="43"/>
+      <c r="H13" s="160"/>
+      <c r="I13" s="161"/>
       <c r="K13" s="4"/>
       <c r="L13" s="17"/>
       <c r="N13" s="7"/>
@@ -2327,7 +2320,7 @@
       <c r="G14" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="84"/>
+      <c r="H14" s="46"/>
       <c r="I14" s="7"/>
       <c r="K14" s="4"/>
       <c r="L14" s="17"/>
@@ -2339,8 +2332,8 @@
     </row>
     <row r="15" spans="2:23" x14ac:dyDescent="0.3">
       <c r="F15" s="4"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="84"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="46"/>
       <c r="I15" s="7"/>
       <c r="K15" s="4"/>
       <c r="L15" s="17"/>
@@ -2351,11 +2344,11 @@
       <c r="W15" s="7"/>
     </row>
     <row r="16" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B16" s="83"/>
-      <c r="C16" s="83"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="45"/>
       <c r="F16" s="4"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="84"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="46"/>
       <c r="I16" s="7"/>
       <c r="K16" s="4"/>
       <c r="L16" s="17"/>
@@ -2366,11 +2359,11 @@
       <c r="W16" s="7"/>
     </row>
     <row r="17" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B17" s="83"/>
-      <c r="C17" s="83"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
       <c r="F17" s="4"/>
       <c r="G17" s="20"/>
-      <c r="H17" s="84"/>
+      <c r="H17" s="46"/>
       <c r="I17" s="7"/>
       <c r="K17" s="4"/>
       <c r="L17" s="17"/>
@@ -2381,11 +2374,11 @@
       <c r="W17" s="7"/>
     </row>
     <row r="18" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B18" s="83"/>
-      <c r="C18" s="83"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
       <c r="F18" s="4"/>
       <c r="G18" s="20"/>
-      <c r="H18" s="84"/>
+      <c r="H18" s="46"/>
       <c r="I18" s="7"/>
       <c r="K18" s="4"/>
       <c r="L18" s="17"/>
@@ -2396,11 +2389,11 @@
       <c r="W18" s="7"/>
     </row>
     <row r="19" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B19" s="83"/>
-      <c r="C19" s="83"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="45"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
-      <c r="H19" s="70" t="s">
+      <c r="H19" s="23" t="s">
         <v>51</v>
       </c>
       <c r="I19" s="7"/>
@@ -2413,11 +2406,11 @@
       <c r="W19" s="7"/>
     </row>
     <row r="20" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B20" s="83"/>
-      <c r="C20" s="83"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
-      <c r="H20" s="70"/>
+      <c r="H20" s="23"/>
       <c r="I20" s="7"/>
       <c r="K20" s="4"/>
       <c r="L20" s="17"/>
@@ -2428,11 +2421,11 @@
       <c r="W20" s="7"/>
     </row>
     <row r="21" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B21" s="83"/>
-      <c r="C21" s="83"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="70"/>
+      <c r="H21" s="23"/>
       <c r="I21" s="7"/>
       <c r="K21" s="4"/>
       <c r="L21" s="17"/>
@@ -2443,11 +2436,11 @@
       <c r="W21" s="7"/>
     </row>
     <row r="22" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B22" s="83"/>
-      <c r="C22" s="83"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="70"/>
+      <c r="H22" s="23"/>
       <c r="I22" s="7"/>
       <c r="K22" s="4"/>
       <c r="L22" s="17"/>
@@ -2458,12 +2451,12 @@
       <c r="W22" s="7"/>
     </row>
     <row r="23" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B23" s="83"/>
-      <c r="C23" s="83"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
-      <c r="H23" s="84"/>
-      <c r="I23" s="69" t="s">
+      <c r="H23" s="46"/>
+      <c r="I23" s="33" t="s">
         <v>52</v>
       </c>
       <c r="K23" s="4"/>
@@ -2475,14 +2468,14 @@
       <c r="W23" s="7"/>
     </row>
     <row r="24" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B24" s="83"/>
-      <c r="C24" s="83"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
-      <c r="H24" s="85" t="s">
+      <c r="H24" s="47" t="s">
         <v>50</v>
       </c>
-      <c r="I24" s="82" t="s">
+      <c r="I24" s="44" t="s">
         <v>50</v>
       </c>
       <c r="K24" s="4"/>
@@ -2494,12 +2487,12 @@
       <c r="W24" s="7"/>
     </row>
     <row r="25" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="B25" s="83"/>
-      <c r="C25" s="83"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
-      <c r="H25" s="84"/>
-      <c r="I25" s="69"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="33"/>
       <c r="K25" s="4"/>
       <c r="L25" s="17"/>
       <c r="N25" s="7"/>
@@ -2509,11 +2502,11 @@
       <c r="W25" s="7"/>
     </row>
     <row r="26" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="83"/>
-      <c r="C26" s="83"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
       <c r="F26" s="4"/>
       <c r="G26" s="11"/>
-      <c r="H26" s="86"/>
+      <c r="H26" s="48"/>
       <c r="I26" s="22"/>
       <c r="K26" s="4"/>
       <c r="L26" s="17"/>
@@ -2572,74 +2565,74 @@
       <c r="W29" s="14"/>
     </row>
     <row r="30" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F30" s="44" t="s">
+      <c r="F30" s="162" t="s">
         <v>11</v>
       </c>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="45"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="45"/>
-      <c r="M30" s="45"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="45"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="45"/>
-      <c r="R30" s="45"/>
-      <c r="S30" s="45"/>
-      <c r="T30" s="45"/>
-      <c r="U30" s="45"/>
-      <c r="V30" s="45"/>
-      <c r="W30" s="46"/>
+      <c r="G30" s="163"/>
+      <c r="H30" s="163"/>
+      <c r="I30" s="163"/>
+      <c r="J30" s="163"/>
+      <c r="K30" s="163"/>
+      <c r="L30" s="163"/>
+      <c r="M30" s="163"/>
+      <c r="N30" s="163"/>
+      <c r="O30" s="163"/>
+      <c r="P30" s="163"/>
+      <c r="Q30" s="163"/>
+      <c r="R30" s="163"/>
+      <c r="S30" s="163"/>
+      <c r="T30" s="163"/>
+      <c r="U30" s="163"/>
+      <c r="V30" s="163"/>
+      <c r="W30" s="164"/>
     </row>
     <row r="31" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F31" s="47"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="48"/>
-      <c r="K31" s="48"/>
-      <c r="L31" s="48"/>
-      <c r="M31" s="48"/>
-      <c r="N31" s="48"/>
-      <c r="O31" s="48"/>
-      <c r="P31" s="48"/>
-      <c r="Q31" s="48"/>
-      <c r="R31" s="48"/>
-      <c r="S31" s="48"/>
-      <c r="T31" s="48"/>
-      <c r="U31" s="48"/>
-      <c r="V31" s="48"/>
-      <c r="W31" s="49"/>
+      <c r="F31" s="165"/>
+      <c r="G31" s="166"/>
+      <c r="H31" s="166"/>
+      <c r="I31" s="166"/>
+      <c r="J31" s="166"/>
+      <c r="K31" s="166"/>
+      <c r="L31" s="166"/>
+      <c r="M31" s="166"/>
+      <c r="N31" s="166"/>
+      <c r="O31" s="166"/>
+      <c r="P31" s="166"/>
+      <c r="Q31" s="166"/>
+      <c r="R31" s="166"/>
+      <c r="S31" s="166"/>
+      <c r="T31" s="166"/>
+      <c r="U31" s="166"/>
+      <c r="V31" s="166"/>
+      <c r="W31" s="167"/>
     </row>
     <row r="32" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F32" s="35" t="s">
+      <c r="F32" s="151" t="s">
         <v>0</v>
       </c>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="35" t="s">
+      <c r="G32" s="152"/>
+      <c r="H32" s="152"/>
+      <c r="I32" s="152"/>
+      <c r="J32" s="152"/>
+      <c r="K32" s="151" t="s">
         <v>1</v>
       </c>
-      <c r="L32" s="36"/>
-      <c r="M32" s="36"/>
-      <c r="N32" s="37"/>
-      <c r="O32" s="35" t="s">
+      <c r="L32" s="152"/>
+      <c r="M32" s="152"/>
+      <c r="N32" s="153"/>
+      <c r="O32" s="151" t="s">
         <v>12</v>
       </c>
-      <c r="P32" s="36"/>
-      <c r="Q32" s="36"/>
-      <c r="R32" s="37"/>
-      <c r="S32" s="35" t="s">
+      <c r="P32" s="152"/>
+      <c r="Q32" s="152"/>
+      <c r="R32" s="153"/>
+      <c r="S32" s="151" t="s">
         <v>13</v>
       </c>
-      <c r="T32" s="36"/>
-      <c r="U32" s="36"/>
-      <c r="V32" s="36"/>
-      <c r="W32" s="37"/>
+      <c r="T32" s="152"/>
+      <c r="U32" s="152"/>
+      <c r="V32" s="152"/>
+      <c r="W32" s="153"/>
     </row>
     <row r="33" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F33" s="3" t="s">
@@ -2716,7 +2709,7 @@
     <row r="35" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F35" s="4"/>
       <c r="G35" s="10"/>
-      <c r="K35" s="76" t="s">
+      <c r="K35" s="38" t="s">
         <v>14</v>
       </c>
       <c r="L35" s="17"/>
@@ -2727,17 +2720,17 @@
       <c r="W35" s="7"/>
     </row>
     <row r="36" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="83"/>
-      <c r="C36" s="83"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
       <c r="F36" s="4"/>
-      <c r="K36" s="77" t="s">
+      <c r="K36" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="L36" s="92"/>
-      <c r="M36" s="91" t="s">
+      <c r="L36" s="54"/>
+      <c r="M36" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="N36" s="93"/>
+      <c r="N36" s="55"/>
       <c r="O36" s="4"/>
       <c r="R36" s="7"/>
       <c r="S36" s="4"/>
@@ -2746,7 +2739,7 @@
     <row r="37" spans="2:23" x14ac:dyDescent="0.3">
       <c r="F37" s="4"/>
       <c r="J37" s="6"/>
-      <c r="L37" s="73"/>
+      <c r="L37" s="17"/>
       <c r="M37" s="20" t="s">
         <v>42</v>
       </c>
@@ -2757,11 +2750,11 @@
       <c r="W37" s="7"/>
     </row>
     <row r="38" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="C38" s="83"/>
+      <c r="C38" s="45"/>
       <c r="F38" s="4"/>
       <c r="J38" s="6"/>
-      <c r="L38" s="73"/>
-      <c r="M38" s="72" t="s">
+      <c r="L38" s="17"/>
+      <c r="M38" s="35" t="s">
         <v>45</v>
       </c>
       <c r="N38" s="7"/>
@@ -2771,11 +2764,11 @@
       <c r="W38" s="7"/>
     </row>
     <row r="39" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="C39" s="83"/>
+      <c r="C39" s="45"/>
       <c r="F39" s="4"/>
       <c r="J39" s="6"/>
-      <c r="L39" s="73"/>
-      <c r="M39" s="72" t="s">
+      <c r="L39" s="17"/>
+      <c r="M39" s="35" t="s">
         <v>43</v>
       </c>
       <c r="N39" s="7"/>
@@ -2785,11 +2778,11 @@
       <c r="W39" s="7"/>
     </row>
     <row r="40" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="C40" s="83"/>
+      <c r="C40" s="45"/>
       <c r="F40" s="4"/>
       <c r="J40" s="6"/>
-      <c r="L40" s="73"/>
-      <c r="M40" s="72" t="s">
+      <c r="L40" s="17"/>
+      <c r="M40" s="35" t="s">
         <v>44</v>
       </c>
       <c r="N40" s="7"/>
@@ -2799,12 +2792,12 @@
       <c r="W40" s="7"/>
     </row>
     <row r="41" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="C41" s="83"/>
+      <c r="C41" s="45"/>
       <c r="F41" s="4"/>
       <c r="J41" s="6"/>
-      <c r="L41" s="73"/>
+      <c r="L41" s="17"/>
       <c r="M41" s="4"/>
-      <c r="N41" s="69" t="s">
+      <c r="N41" s="33" t="s">
         <v>18</v>
       </c>
       <c r="O41" s="4"/>
@@ -2813,12 +2806,12 @@
       <c r="W41" s="7"/>
     </row>
     <row r="42" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="C42" s="83"/>
+      <c r="C42" s="45"/>
       <c r="F42" s="4"/>
       <c r="J42" s="6"/>
-      <c r="L42" s="73"/>
+      <c r="L42" s="17"/>
       <c r="M42" s="4"/>
-      <c r="N42" s="74" t="s">
+      <c r="N42" s="36" t="s">
         <v>45</v>
       </c>
       <c r="O42" s="4"/>
@@ -2827,12 +2820,12 @@
       <c r="W42" s="7"/>
     </row>
     <row r="43" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="C43" s="83"/>
+      <c r="C43" s="45"/>
       <c r="F43" s="4"/>
       <c r="J43" s="6"/>
-      <c r="L43" s="73"/>
+      <c r="L43" s="17"/>
       <c r="M43" s="4"/>
-      <c r="N43" s="74" t="s">
+      <c r="N43" s="36" t="s">
         <v>43</v>
       </c>
       <c r="O43" s="4"/>
@@ -2845,7 +2838,7 @@
       <c r="J44" s="6"/>
       <c r="L44" s="18"/>
       <c r="M44" s="11"/>
-      <c r="N44" s="75" t="s">
+      <c r="N44" s="37" t="s">
         <v>44</v>
       </c>
       <c r="O44" s="4"/>
@@ -2873,10 +2866,10 @@
       <c r="J46" s="6"/>
       <c r="K46" s="4"/>
       <c r="L46" s="17"/>
-      <c r="O46" s="79" t="s">
+      <c r="O46" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="P46" s="78"/>
+      <c r="P46" s="40"/>
       <c r="R46" s="7"/>
       <c r="S46" s="4"/>
       <c r="W46" s="7"/>
@@ -2886,10 +2879,10 @@
       <c r="J47" s="6"/>
       <c r="K47" s="4"/>
       <c r="L47" s="17"/>
-      <c r="O47" s="79" t="s">
+      <c r="O47" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="P47" s="78"/>
+      <c r="P47" s="40"/>
       <c r="R47" s="7"/>
       <c r="S47" s="4"/>
       <c r="W47" s="7"/>
@@ -2899,7 +2892,7 @@
       <c r="J48" s="6"/>
       <c r="K48" s="4"/>
       <c r="L48" s="17"/>
-      <c r="O48" s="80" t="s">
+      <c r="O48" s="42" t="s">
         <v>48</v>
       </c>
       <c r="P48" s="26"/>
@@ -2928,74 +2921,74 @@
       <c r="W49" s="14"/>
     </row>
     <row r="50" spans="6:23" x14ac:dyDescent="0.3">
-      <c r="F50" s="44" t="s">
+      <c r="F50" s="162" t="s">
         <v>20</v>
       </c>
-      <c r="G50" s="45"/>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45"/>
-      <c r="J50" s="45"/>
-      <c r="K50" s="45"/>
-      <c r="L50" s="45"/>
-      <c r="M50" s="45"/>
-      <c r="N50" s="45"/>
-      <c r="O50" s="45"/>
-      <c r="P50" s="45"/>
-      <c r="Q50" s="45"/>
-      <c r="R50" s="45"/>
-      <c r="S50" s="45"/>
-      <c r="T50" s="45"/>
-      <c r="U50" s="45"/>
-      <c r="V50" s="45"/>
-      <c r="W50" s="46"/>
+      <c r="G50" s="163"/>
+      <c r="H50" s="163"/>
+      <c r="I50" s="163"/>
+      <c r="J50" s="163"/>
+      <c r="K50" s="163"/>
+      <c r="L50" s="163"/>
+      <c r="M50" s="163"/>
+      <c r="N50" s="163"/>
+      <c r="O50" s="163"/>
+      <c r="P50" s="163"/>
+      <c r="Q50" s="163"/>
+      <c r="R50" s="163"/>
+      <c r="S50" s="163"/>
+      <c r="T50" s="163"/>
+      <c r="U50" s="163"/>
+      <c r="V50" s="163"/>
+      <c r="W50" s="164"/>
     </row>
     <row r="51" spans="6:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F51" s="47"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="48"/>
-      <c r="J51" s="48"/>
-      <c r="K51" s="48"/>
-      <c r="L51" s="48"/>
-      <c r="M51" s="48"/>
-      <c r="N51" s="48"/>
-      <c r="O51" s="48"/>
-      <c r="P51" s="48"/>
-      <c r="Q51" s="48"/>
-      <c r="R51" s="48"/>
-      <c r="S51" s="48"/>
-      <c r="T51" s="48"/>
-      <c r="U51" s="48"/>
-      <c r="V51" s="48"/>
-      <c r="W51" s="49"/>
+      <c r="F51" s="165"/>
+      <c r="G51" s="166"/>
+      <c r="H51" s="166"/>
+      <c r="I51" s="166"/>
+      <c r="J51" s="166"/>
+      <c r="K51" s="166"/>
+      <c r="L51" s="166"/>
+      <c r="M51" s="166"/>
+      <c r="N51" s="166"/>
+      <c r="O51" s="166"/>
+      <c r="P51" s="166"/>
+      <c r="Q51" s="166"/>
+      <c r="R51" s="166"/>
+      <c r="S51" s="166"/>
+      <c r="T51" s="166"/>
+      <c r="U51" s="166"/>
+      <c r="V51" s="166"/>
+      <c r="W51" s="167"/>
     </row>
     <row r="52" spans="6:23" x14ac:dyDescent="0.3">
-      <c r="F52" s="35" t="s">
+      <c r="F52" s="151" t="s">
         <v>0</v>
       </c>
-      <c r="G52" s="36"/>
-      <c r="H52" s="36"/>
-      <c r="I52" s="36"/>
-      <c r="J52" s="36"/>
-      <c r="K52" s="35" t="s">
+      <c r="G52" s="152"/>
+      <c r="H52" s="152"/>
+      <c r="I52" s="152"/>
+      <c r="J52" s="152"/>
+      <c r="K52" s="151" t="s">
         <v>1</v>
       </c>
-      <c r="L52" s="36"/>
-      <c r="M52" s="36"/>
-      <c r="N52" s="37"/>
-      <c r="O52" s="35" t="s">
+      <c r="L52" s="152"/>
+      <c r="M52" s="152"/>
+      <c r="N52" s="153"/>
+      <c r="O52" s="151" t="s">
         <v>12</v>
       </c>
-      <c r="P52" s="36"/>
-      <c r="Q52" s="36"/>
-      <c r="R52" s="37"/>
-      <c r="S52" s="35" t="s">
+      <c r="P52" s="152"/>
+      <c r="Q52" s="152"/>
+      <c r="R52" s="153"/>
+      <c r="S52" s="151" t="s">
         <v>13</v>
       </c>
-      <c r="T52" s="36"/>
-      <c r="U52" s="36"/>
-      <c r="V52" s="36"/>
-      <c r="W52" s="37"/>
+      <c r="T52" s="152"/>
+      <c r="U52" s="152"/>
+      <c r="V52" s="152"/>
+      <c r="W52" s="153"/>
     </row>
     <row r="53" spans="6:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F53" s="3" t="s">
@@ -3091,12 +3084,12 @@
       <c r="L56" s="17"/>
       <c r="N56" s="7"/>
       <c r="O56" s="4"/>
-      <c r="P56" s="38" t="s">
+      <c r="P56" s="156" t="s">
         <v>16</v>
       </c>
-      <c r="Q56" s="39"/>
-      <c r="R56" s="39"/>
-      <c r="S56" s="40"/>
+      <c r="Q56" s="157"/>
+      <c r="R56" s="157"/>
+      <c r="S56" s="158"/>
       <c r="W56" s="7"/>
     </row>
     <row r="57" spans="6:23" x14ac:dyDescent="0.3">
@@ -3143,10 +3136,10 @@
       <c r="O59" s="4"/>
       <c r="R59" s="7"/>
       <c r="S59" s="4"/>
-      <c r="T59" s="33" t="s">
+      <c r="T59" s="154" t="s">
         <v>23</v>
       </c>
-      <c r="U59" s="34"/>
+      <c r="U59" s="155"/>
       <c r="W59" s="7"/>
     </row>
     <row r="60" spans="6:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3184,12 +3177,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="F4:W6"/>
-    <mergeCell ref="F7:W8"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="S9:W9"/>
     <mergeCell ref="T59:U59"/>
     <mergeCell ref="S52:W52"/>
     <mergeCell ref="P56:S56"/>
@@ -3203,6 +3190,12 @@
     <mergeCell ref="K32:N32"/>
     <mergeCell ref="O32:R32"/>
     <mergeCell ref="S32:W32"/>
+    <mergeCell ref="F4:W6"/>
+    <mergeCell ref="F7:W8"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="S9:W9"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3221,748 +3214,748 @@
   <sheetData>
     <row r="3" spans="4:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="4:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G4" s="98" t="s">
+      <c r="G4" s="168" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="100"/>
-      <c r="L4" s="98" t="s">
+      <c r="H4" s="169"/>
+      <c r="I4" s="169"/>
+      <c r="J4" s="169"/>
+      <c r="K4" s="170"/>
+      <c r="L4" s="168" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="99"/>
-      <c r="N4" s="99"/>
-      <c r="O4" s="100"/>
-      <c r="P4" s="89"/>
+      <c r="M4" s="169"/>
+      <c r="N4" s="169"/>
+      <c r="O4" s="170"/>
+      <c r="P4" s="51"/>
     </row>
     <row r="5" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D5" s="90"/>
-      <c r="E5" s="124"/>
-      <c r="F5" s="136" t="s">
+      <c r="D5" s="52"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="89" t="s">
         <v>91</v>
       </c>
-      <c r="G5" s="146" t="s">
+      <c r="G5" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="125" t="s">
+      <c r="H5" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="I5" s="125" t="s">
+      <c r="I5" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="J5" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="127" t="s">
+      <c r="K5" s="83" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="146" t="s">
+      <c r="L5" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="M5" s="126" t="s">
+      <c r="M5" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="N5" s="125" t="s">
+      <c r="N5" s="81" t="s">
         <v>7</v>
       </c>
-      <c r="O5" s="127" t="s">
+      <c r="O5" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="96"/>
+      <c r="P5" s="58"/>
     </row>
     <row r="6" spans="4:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="90"/>
-      <c r="E6" s="131" t="s">
+      <c r="D6" s="52"/>
+      <c r="E6" s="173" t="s">
         <v>96</v>
       </c>
-      <c r="F6" s="137" t="s">
+      <c r="F6" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="G6" s="102" t="s">
+      <c r="G6" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="107"/>
-      <c r="I6" s="104"/>
-      <c r="J6" s="104"/>
-      <c r="K6" s="103"/>
-      <c r="L6" s="149"/>
-      <c r="M6" s="133"/>
-      <c r="N6" s="129"/>
-      <c r="O6" s="134"/>
-      <c r="P6" s="97"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="101"/>
+      <c r="M6" s="86"/>
+      <c r="N6" s="84"/>
+      <c r="O6" s="87"/>
+      <c r="P6" s="59"/>
     </row>
     <row r="7" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D7" s="90"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="138" t="s">
+      <c r="D7" s="52"/>
+      <c r="E7" s="174"/>
+      <c r="F7" s="91" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="152"/>
-      <c r="H7" s="144"/>
-      <c r="I7" s="110"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="115"/>
-      <c r="L7" s="150"/>
-      <c r="M7" s="112"/>
-      <c r="N7" s="111"/>
-      <c r="O7" s="114"/>
-      <c r="P7" s="97"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="96"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="102"/>
+      <c r="M7" s="71"/>
+      <c r="N7" s="70"/>
+      <c r="O7" s="73"/>
+      <c r="P7" s="59"/>
     </row>
     <row r="8" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D8" s="90"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="138" t="s">
+      <c r="D8" s="52"/>
+      <c r="E8" s="174"/>
+      <c r="F8" s="91" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="152"/>
-      <c r="H8" s="144"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="110"/>
-      <c r="K8" s="115"/>
-      <c r="L8" s="150"/>
-      <c r="M8" s="112"/>
-      <c r="N8" s="111"/>
-      <c r="O8" s="114"/>
-      <c r="P8" s="97"/>
+      <c r="G8" s="104"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="74"/>
+      <c r="L8" s="102"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="70"/>
+      <c r="O8" s="73"/>
+      <c r="P8" s="59"/>
     </row>
     <row r="9" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D9" s="90"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="138" t="s">
+      <c r="D9" s="52"/>
+      <c r="E9" s="174"/>
+      <c r="F9" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="153"/>
-      <c r="H9" s="144"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="110"/>
-      <c r="K9" s="115"/>
-      <c r="L9" s="150"/>
-      <c r="M9" s="112"/>
-      <c r="N9" s="111"/>
-      <c r="O9" s="114"/>
-      <c r="P9" s="97"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="69"/>
+      <c r="K9" s="74"/>
+      <c r="L9" s="102"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="70"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="59"/>
     </row>
     <row r="10" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D10" s="90"/>
-      <c r="E10" s="120"/>
-      <c r="F10" s="139" t="s">
+      <c r="D10" s="52"/>
+      <c r="E10" s="174"/>
+      <c r="F10" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="154" t="s">
+      <c r="G10" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="144"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="110"/>
-      <c r="K10" s="115"/>
-      <c r="L10" s="150"/>
-      <c r="M10" s="112"/>
-      <c r="N10" s="111"/>
-      <c r="O10" s="114"/>
-      <c r="P10" s="97"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="69"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="102"/>
+      <c r="M10" s="71"/>
+      <c r="N10" s="70"/>
+      <c r="O10" s="73"/>
+      <c r="P10" s="59"/>
     </row>
     <row r="11" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D11" s="90"/>
-      <c r="E11" s="120"/>
-      <c r="F11" s="140" t="s">
+      <c r="D11" s="52"/>
+      <c r="E11" s="174"/>
+      <c r="F11" s="93" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="152"/>
-      <c r="H11" s="144"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="110"/>
-      <c r="K11" s="115"/>
-      <c r="L11" s="150"/>
-      <c r="M11" s="112"/>
-      <c r="N11" s="111"/>
-      <c r="O11" s="114"/>
-      <c r="P11" s="97"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="69"/>
+      <c r="K11" s="74"/>
+      <c r="L11" s="102"/>
+      <c r="M11" s="71"/>
+      <c r="N11" s="70"/>
+      <c r="O11" s="73"/>
+      <c r="P11" s="59"/>
     </row>
     <row r="12" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D12" s="90"/>
-      <c r="E12" s="120"/>
-      <c r="F12" s="140" t="s">
+      <c r="D12" s="52"/>
+      <c r="E12" s="174"/>
+      <c r="F12" s="93" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="152"/>
-      <c r="H12" s="144"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="110"/>
-      <c r="K12" s="115"/>
-      <c r="L12" s="150"/>
-      <c r="M12" s="112"/>
-      <c r="N12" s="111"/>
-      <c r="O12" s="114"/>
-      <c r="P12" s="97"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="96"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="69"/>
+      <c r="K12" s="74"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="71"/>
+      <c r="N12" s="70"/>
+      <c r="O12" s="73"/>
+      <c r="P12" s="59"/>
     </row>
     <row r="13" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D13" s="90"/>
-      <c r="E13" s="120"/>
-      <c r="F13" s="140" t="s">
+      <c r="D13" s="52"/>
+      <c r="E13" s="174"/>
+      <c r="F13" s="93" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="152"/>
-      <c r="H13" s="144"/>
-      <c r="I13" s="110"/>
-      <c r="J13" s="110"/>
-      <c r="K13" s="115"/>
-      <c r="L13" s="150"/>
-      <c r="M13" s="112"/>
-      <c r="N13" s="111"/>
-      <c r="O13" s="114"/>
-      <c r="P13" s="97"/>
+      <c r="G13" s="104"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="74"/>
+      <c r="L13" s="102"/>
+      <c r="M13" s="71"/>
+      <c r="N13" s="70"/>
+      <c r="O13" s="73"/>
+      <c r="P13" s="59"/>
     </row>
     <row r="14" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D14" s="90"/>
-      <c r="E14" s="120"/>
-      <c r="F14" s="140" t="s">
+      <c r="D14" s="52"/>
+      <c r="E14" s="174"/>
+      <c r="F14" s="93" t="s">
         <v>56</v>
       </c>
-      <c r="G14" s="152"/>
-      <c r="H14" s="144"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="110"/>
-      <c r="K14" s="115"/>
-      <c r="L14" s="150"/>
-      <c r="M14" s="112"/>
-      <c r="N14" s="111"/>
-      <c r="O14" s="114"/>
-      <c r="P14" s="97"/>
+      <c r="G14" s="104"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="74"/>
+      <c r="L14" s="102"/>
+      <c r="M14" s="71"/>
+      <c r="N14" s="70"/>
+      <c r="O14" s="73"/>
+      <c r="P14" s="59"/>
     </row>
     <row r="15" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D15" s="90"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="141" t="s">
+      <c r="D15" s="52"/>
+      <c r="E15" s="175"/>
+      <c r="F15" s="94" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="155"/>
-      <c r="H15" s="145"/>
-      <c r="I15" s="116"/>
-      <c r="J15" s="116"/>
-      <c r="K15" s="119"/>
-      <c r="L15" s="151"/>
-      <c r="M15" s="117"/>
-      <c r="N15" s="118"/>
-      <c r="O15" s="135"/>
-      <c r="P15" s="97"/>
+      <c r="G15" s="107"/>
+      <c r="H15" s="97"/>
+      <c r="I15" s="75"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="78"/>
+      <c r="L15" s="103"/>
+      <c r="M15" s="76"/>
+      <c r="N15" s="77"/>
+      <c r="O15" s="88"/>
+      <c r="P15" s="59"/>
     </row>
     <row r="16" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D16" s="90"/>
-      <c r="E16" s="131" t="s">
+      <c r="D16" s="52"/>
+      <c r="E16" s="173" t="s">
         <v>62</v>
       </c>
-      <c r="F16" s="137" t="s">
+      <c r="F16" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="G16" s="156"/>
-      <c r="H16" s="159" t="s">
+      <c r="G16" s="108"/>
+      <c r="H16" s="171" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="160"/>
-      <c r="J16" s="107"/>
-      <c r="K16" s="103"/>
-      <c r="L16" s="105"/>
-      <c r="M16" s="133"/>
-      <c r="N16" s="129"/>
-      <c r="O16" s="134"/>
-      <c r="P16" s="97"/>
+      <c r="I16" s="172"/>
+      <c r="J16" s="66"/>
+      <c r="K16" s="62"/>
+      <c r="L16" s="64"/>
+      <c r="M16" s="86"/>
+      <c r="N16" s="84"/>
+      <c r="O16" s="87"/>
+      <c r="P16" s="59"/>
     </row>
     <row r="17" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D17" s="90"/>
-      <c r="E17" s="120"/>
-      <c r="F17" s="138" t="s">
+      <c r="D17" s="52"/>
+      <c r="E17" s="174"/>
+      <c r="F17" s="91" t="s">
         <v>65</v>
       </c>
-      <c r="G17" s="157"/>
-      <c r="H17" s="161"/>
-      <c r="I17" s="114"/>
-      <c r="J17" s="144"/>
-      <c r="K17" s="115"/>
-      <c r="L17" s="147"/>
-      <c r="M17" s="112"/>
-      <c r="N17" s="111"/>
-      <c r="O17" s="114"/>
-      <c r="P17" s="97"/>
+      <c r="G17" s="109"/>
+      <c r="H17" s="111"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="74"/>
+      <c r="L17" s="99"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="70"/>
+      <c r="O17" s="73"/>
+      <c r="P17" s="59"/>
     </row>
     <row r="18" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D18" s="90"/>
-      <c r="E18" s="132"/>
-      <c r="F18" s="142" t="s">
+      <c r="D18" s="52"/>
+      <c r="E18" s="175"/>
+      <c r="F18" s="95" t="s">
         <v>66</v>
       </c>
-      <c r="G18" s="158"/>
-      <c r="H18" s="151"/>
-      <c r="I18" s="162"/>
-      <c r="J18" s="145"/>
-      <c r="K18" s="119"/>
-      <c r="L18" s="148"/>
-      <c r="M18" s="117"/>
-      <c r="N18" s="118"/>
-      <c r="O18" s="135"/>
-      <c r="P18" s="97"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="112"/>
+      <c r="J18" s="97"/>
+      <c r="K18" s="78"/>
+      <c r="L18" s="100"/>
+      <c r="M18" s="76"/>
+      <c r="N18" s="77"/>
+      <c r="O18" s="88"/>
+      <c r="P18" s="59"/>
     </row>
     <row r="19" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D19" s="90"/>
-      <c r="E19" s="131" t="s">
+      <c r="D19" s="52"/>
+      <c r="E19" s="173" t="s">
         <v>97</v>
       </c>
-      <c r="F19" s="137" t="s">
+      <c r="F19" s="90" t="s">
         <v>74</v>
       </c>
-      <c r="G19" s="156"/>
-      <c r="H19" s="159" t="s">
+      <c r="G19" s="108"/>
+      <c r="H19" s="171" t="s">
         <v>51</v>
       </c>
-      <c r="I19" s="160"/>
-      <c r="J19" s="107"/>
-      <c r="K19" s="103"/>
-      <c r="L19" s="105"/>
-      <c r="M19" s="133"/>
-      <c r="N19" s="129"/>
-      <c r="O19" s="134"/>
-      <c r="P19" s="97"/>
+      <c r="I19" s="172"/>
+      <c r="J19" s="66"/>
+      <c r="K19" s="62"/>
+      <c r="L19" s="64"/>
+      <c r="M19" s="86"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="87"/>
+      <c r="P19" s="59"/>
     </row>
     <row r="20" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D20" s="90"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="138" t="s">
+      <c r="D20" s="52"/>
+      <c r="E20" s="174"/>
+      <c r="F20" s="91" t="s">
         <v>76</v>
       </c>
-      <c r="G20" s="157"/>
-      <c r="H20" s="163"/>
-      <c r="I20" s="114"/>
-      <c r="J20" s="144"/>
-      <c r="K20" s="115"/>
-      <c r="L20" s="147"/>
-      <c r="M20" s="112"/>
-      <c r="N20" s="111"/>
-      <c r="O20" s="114"/>
-      <c r="P20" s="97"/>
+      <c r="G20" s="109"/>
+      <c r="H20" s="113"/>
+      <c r="I20" s="73"/>
+      <c r="J20" s="96"/>
+      <c r="K20" s="74"/>
+      <c r="L20" s="99"/>
+      <c r="M20" s="71"/>
+      <c r="N20" s="70"/>
+      <c r="O20" s="73"/>
+      <c r="P20" s="59"/>
     </row>
     <row r="21" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D21" s="90"/>
-      <c r="E21" s="132"/>
-      <c r="F21" s="142" t="s">
+      <c r="D21" s="52"/>
+      <c r="E21" s="175"/>
+      <c r="F21" s="95" t="s">
         <v>75</v>
       </c>
-      <c r="G21" s="158"/>
-      <c r="H21" s="151"/>
-      <c r="I21" s="164"/>
-      <c r="J21" s="145"/>
-      <c r="K21" s="119"/>
-      <c r="L21" s="148"/>
-      <c r="M21" s="117"/>
-      <c r="N21" s="118"/>
-      <c r="O21" s="135"/>
-      <c r="P21" s="97"/>
+      <c r="G21" s="110"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="114"/>
+      <c r="J21" s="97"/>
+      <c r="K21" s="78"/>
+      <c r="L21" s="100"/>
+      <c r="M21" s="76"/>
+      <c r="N21" s="77"/>
+      <c r="O21" s="88"/>
+      <c r="P21" s="59"/>
     </row>
     <row r="22" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D22" s="90"/>
-      <c r="E22" s="131" t="s">
+      <c r="D22" s="52"/>
+      <c r="E22" s="173" t="s">
         <v>98</v>
       </c>
-      <c r="F22" s="137" t="s">
+      <c r="F22" s="90" t="s">
         <v>68</v>
       </c>
-      <c r="G22" s="156"/>
-      <c r="H22" s="159" t="s">
+      <c r="G22" s="108"/>
+      <c r="H22" s="171" t="s">
         <v>52</v>
       </c>
-      <c r="I22" s="160"/>
-      <c r="J22" s="107"/>
-      <c r="K22" s="103"/>
-      <c r="L22" s="105"/>
-      <c r="M22" s="133"/>
-      <c r="N22" s="129"/>
-      <c r="O22" s="103"/>
-      <c r="P22" s="96"/>
+      <c r="I22" s="172"/>
+      <c r="J22" s="66"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="64"/>
+      <c r="M22" s="86"/>
+      <c r="N22" s="84"/>
+      <c r="O22" s="62"/>
+      <c r="P22" s="58"/>
     </row>
     <row r="23" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D23" s="90"/>
-      <c r="E23" s="120"/>
-      <c r="F23" s="138" t="s">
+      <c r="D23" s="52"/>
+      <c r="E23" s="174"/>
+      <c r="F23" s="91" t="s">
         <v>63</v>
       </c>
-      <c r="G23" s="157"/>
-      <c r="H23" s="165"/>
-      <c r="I23" s="114"/>
-      <c r="J23" s="144"/>
-      <c r="K23" s="115"/>
-      <c r="L23" s="147"/>
-      <c r="M23" s="112"/>
-      <c r="N23" s="111"/>
-      <c r="O23" s="115"/>
-      <c r="P23" s="96"/>
+      <c r="G23" s="109"/>
+      <c r="H23" s="115"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="74"/>
+      <c r="L23" s="99"/>
+      <c r="M23" s="71"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="74"/>
+      <c r="P23" s="58"/>
     </row>
     <row r="24" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D24" s="90"/>
-      <c r="E24" s="132"/>
-      <c r="F24" s="142" t="s">
+      <c r="D24" s="52"/>
+      <c r="E24" s="175"/>
+      <c r="F24" s="95" t="s">
         <v>64</v>
       </c>
-      <c r="G24" s="158"/>
-      <c r="H24" s="151"/>
-      <c r="I24" s="166"/>
-      <c r="J24" s="145"/>
-      <c r="K24" s="119"/>
-      <c r="L24" s="148"/>
-      <c r="M24" s="117"/>
-      <c r="N24" s="118"/>
-      <c r="O24" s="119"/>
-      <c r="P24" s="96"/>
+      <c r="G24" s="110"/>
+      <c r="H24" s="103"/>
+      <c r="I24" s="116"/>
+      <c r="J24" s="97"/>
+      <c r="K24" s="78"/>
+      <c r="L24" s="100"/>
+      <c r="M24" s="76"/>
+      <c r="N24" s="77"/>
+      <c r="O24" s="78"/>
+      <c r="P24" s="58"/>
     </row>
     <row r="25" spans="4:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D25" s="90"/>
-      <c r="E25" s="131" t="s">
+      <c r="D25" s="52"/>
+      <c r="E25" s="173" t="s">
         <v>71</v>
       </c>
-      <c r="F25" s="137" t="s">
+      <c r="F25" s="90" t="s">
         <v>77</v>
       </c>
-      <c r="G25" s="156"/>
-      <c r="H25" s="102" t="s">
+      <c r="G25" s="108"/>
+      <c r="H25" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="I25" s="107"/>
-      <c r="J25" s="104"/>
-      <c r="K25" s="103"/>
-      <c r="L25" s="149"/>
-      <c r="M25" s="106"/>
-      <c r="N25" s="104"/>
-      <c r="O25" s="103"/>
-      <c r="P25" s="96"/>
+      <c r="I25" s="66"/>
+      <c r="J25" s="63"/>
+      <c r="K25" s="62"/>
+      <c r="L25" s="101"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="63"/>
+      <c r="O25" s="62"/>
+      <c r="P25" s="58"/>
     </row>
     <row r="26" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D26" s="90"/>
-      <c r="E26" s="120"/>
-      <c r="F26" s="138" t="s">
+      <c r="D26" s="52"/>
+      <c r="E26" s="174"/>
+      <c r="F26" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="G26" s="157"/>
-      <c r="H26" s="167"/>
-      <c r="I26" s="144"/>
-      <c r="J26" s="110"/>
-      <c r="K26" s="115"/>
-      <c r="L26" s="150"/>
-      <c r="M26" s="113"/>
-      <c r="N26" s="110"/>
-      <c r="O26" s="115"/>
-      <c r="P26" s="96"/>
+      <c r="G26" s="109"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="96"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="74"/>
+      <c r="L26" s="102"/>
+      <c r="M26" s="72"/>
+      <c r="N26" s="69"/>
+      <c r="O26" s="74"/>
+      <c r="P26" s="58"/>
     </row>
     <row r="27" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D27" s="90"/>
-      <c r="E27" s="120"/>
-      <c r="F27" s="138" t="s">
+      <c r="D27" s="52"/>
+      <c r="E27" s="174"/>
+      <c r="F27" s="91" t="s">
         <v>72</v>
       </c>
-      <c r="G27" s="157"/>
-      <c r="H27" s="167"/>
-      <c r="I27" s="144"/>
-      <c r="J27" s="110"/>
-      <c r="K27" s="115"/>
-      <c r="L27" s="150"/>
-      <c r="M27" s="113"/>
-      <c r="N27" s="110"/>
-      <c r="O27" s="115"/>
-      <c r="P27" s="96"/>
+      <c r="G27" s="109"/>
+      <c r="H27" s="117"/>
+      <c r="I27" s="96"/>
+      <c r="J27" s="69"/>
+      <c r="K27" s="74"/>
+      <c r="L27" s="102"/>
+      <c r="M27" s="72"/>
+      <c r="N27" s="69"/>
+      <c r="O27" s="74"/>
+      <c r="P27" s="58"/>
     </row>
     <row r="28" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D28" s="90"/>
-      <c r="E28" s="120"/>
-      <c r="F28" s="138" t="s">
+      <c r="D28" s="52"/>
+      <c r="E28" s="174"/>
+      <c r="F28" s="91" t="s">
         <v>73</v>
       </c>
-      <c r="G28" s="157"/>
-      <c r="H28" s="167"/>
-      <c r="I28" s="144"/>
-      <c r="J28" s="110"/>
-      <c r="K28" s="115"/>
-      <c r="L28" s="150"/>
-      <c r="M28" s="113"/>
-      <c r="N28" s="110"/>
-      <c r="O28" s="115"/>
-      <c r="P28" s="96"/>
+      <c r="G28" s="109"/>
+      <c r="H28" s="117"/>
+      <c r="I28" s="96"/>
+      <c r="J28" s="69"/>
+      <c r="K28" s="74"/>
+      <c r="L28" s="102"/>
+      <c r="M28" s="72"/>
+      <c r="N28" s="69"/>
+      <c r="O28" s="74"/>
+      <c r="P28" s="58"/>
     </row>
     <row r="29" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D29" s="90"/>
-      <c r="E29" s="120"/>
-      <c r="F29" s="138" t="s">
+      <c r="D29" s="52"/>
+      <c r="E29" s="174"/>
+      <c r="F29" s="91" t="s">
         <v>85</v>
       </c>
-      <c r="G29" s="157"/>
-      <c r="H29" s="168"/>
-      <c r="I29" s="182"/>
-      <c r="J29" s="123"/>
-      <c r="K29" s="115"/>
-      <c r="L29" s="150"/>
-      <c r="M29" s="113"/>
-      <c r="N29" s="110"/>
-      <c r="O29" s="115"/>
-      <c r="P29" s="96"/>
+      <c r="G29" s="109"/>
+      <c r="H29" s="118"/>
+      <c r="I29" s="132"/>
+      <c r="J29" s="79"/>
+      <c r="K29" s="74"/>
+      <c r="L29" s="102"/>
+      <c r="M29" s="72"/>
+      <c r="N29" s="69"/>
+      <c r="O29" s="74"/>
+      <c r="P29" s="58"/>
     </row>
     <row r="30" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D30" s="90"/>
-      <c r="E30" s="120"/>
-      <c r="F30" s="143" t="s">
+      <c r="D30" s="52"/>
+      <c r="E30" s="174"/>
+      <c r="F30" s="92" t="s">
         <v>80</v>
       </c>
-      <c r="G30" s="147"/>
-      <c r="H30" s="108"/>
-      <c r="I30" s="159" t="s">
+      <c r="G30" s="99"/>
+      <c r="H30" s="67"/>
+      <c r="I30" s="171" t="s">
         <v>69</v>
       </c>
-      <c r="J30" s="160"/>
-      <c r="K30" s="178"/>
-      <c r="L30" s="150"/>
-      <c r="M30" s="113"/>
-      <c r="N30" s="110"/>
-      <c r="O30" s="115"/>
-      <c r="P30" s="96"/>
+      <c r="J30" s="172"/>
+      <c r="K30" s="128"/>
+      <c r="L30" s="102"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="69"/>
+      <c r="O30" s="74"/>
+      <c r="P30" s="58"/>
     </row>
     <row r="31" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D31" s="90"/>
-      <c r="E31" s="120"/>
-      <c r="F31" s="138" t="s">
+      <c r="D31" s="52"/>
+      <c r="E31" s="174"/>
+      <c r="F31" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="G31" s="147"/>
-      <c r="H31" s="170"/>
-      <c r="I31" s="183"/>
-      <c r="J31" s="115"/>
-      <c r="K31" s="178"/>
-      <c r="L31" s="150"/>
-      <c r="M31" s="113"/>
-      <c r="N31" s="110"/>
-      <c r="O31" s="115"/>
-      <c r="P31" s="96"/>
+      <c r="G31" s="99"/>
+      <c r="H31" s="120"/>
+      <c r="I31" s="133"/>
+      <c r="J31" s="74"/>
+      <c r="K31" s="128"/>
+      <c r="L31" s="102"/>
+      <c r="M31" s="72"/>
+      <c r="N31" s="69"/>
+      <c r="O31" s="74"/>
+      <c r="P31" s="58"/>
     </row>
     <row r="32" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D32" s="90"/>
-      <c r="E32" s="120"/>
-      <c r="F32" s="138" t="s">
+      <c r="D32" s="52"/>
+      <c r="E32" s="174"/>
+      <c r="F32" s="91" t="s">
         <v>78</v>
       </c>
-      <c r="G32" s="147"/>
-      <c r="H32" s="170"/>
-      <c r="I32" s="147"/>
-      <c r="J32" s="184"/>
-      <c r="K32" s="178"/>
-      <c r="L32" s="150"/>
-      <c r="M32" s="113"/>
-      <c r="N32" s="110"/>
-      <c r="O32" s="115"/>
-      <c r="P32" s="96"/>
+      <c r="G32" s="99"/>
+      <c r="H32" s="120"/>
+      <c r="I32" s="99"/>
+      <c r="J32" s="134"/>
+      <c r="K32" s="128"/>
+      <c r="L32" s="102"/>
+      <c r="M32" s="72"/>
+      <c r="N32" s="69"/>
+      <c r="O32" s="74"/>
+      <c r="P32" s="58"/>
     </row>
     <row r="33" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D33" s="90"/>
-      <c r="E33" s="120"/>
-      <c r="F33" s="138" t="s">
+      <c r="D33" s="52"/>
+      <c r="E33" s="174"/>
+      <c r="F33" s="91" t="s">
         <v>84</v>
       </c>
-      <c r="G33" s="147"/>
-      <c r="H33" s="170"/>
-      <c r="I33" s="147"/>
-      <c r="J33" s="184"/>
-      <c r="K33" s="178"/>
-      <c r="L33" s="150"/>
-      <c r="M33" s="113"/>
-      <c r="N33" s="110"/>
-      <c r="O33" s="115"/>
-      <c r="P33" s="96"/>
+      <c r="G33" s="99"/>
+      <c r="H33" s="120"/>
+      <c r="I33" s="99"/>
+      <c r="J33" s="134"/>
+      <c r="K33" s="128"/>
+      <c r="L33" s="102"/>
+      <c r="M33" s="72"/>
+      <c r="N33" s="69"/>
+      <c r="O33" s="74"/>
+      <c r="P33" s="58"/>
     </row>
     <row r="34" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D34" s="90"/>
-      <c r="E34" s="132"/>
-      <c r="F34" s="142" t="s">
+      <c r="D34" s="52"/>
+      <c r="E34" s="175"/>
+      <c r="F34" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="G34" s="148"/>
-      <c r="H34" s="171"/>
-      <c r="I34" s="148"/>
-      <c r="J34" s="185"/>
-      <c r="K34" s="181"/>
-      <c r="L34" s="151"/>
-      <c r="M34" s="130"/>
-      <c r="N34" s="116"/>
-      <c r="O34" s="119"/>
-      <c r="P34" s="96"/>
+      <c r="G34" s="100"/>
+      <c r="H34" s="121"/>
+      <c r="I34" s="100"/>
+      <c r="J34" s="135"/>
+      <c r="K34" s="131"/>
+      <c r="L34" s="103"/>
+      <c r="M34" s="85"/>
+      <c r="N34" s="75"/>
+      <c r="O34" s="78"/>
+      <c r="P34" s="58"/>
     </row>
     <row r="35" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D35" s="90"/>
-      <c r="E35" s="128" t="s">
+      <c r="D35" s="52"/>
+      <c r="E35" s="176" t="s">
         <v>47</v>
       </c>
-      <c r="F35" s="137" t="s">
+      <c r="F35" s="90" t="s">
         <v>88</v>
       </c>
-      <c r="G35" s="105"/>
-      <c r="H35" s="104"/>
-      <c r="I35" s="104"/>
-      <c r="J35" s="169"/>
-      <c r="K35" s="172" t="s">
+      <c r="G35" s="64"/>
+      <c r="H35" s="63"/>
+      <c r="I35" s="63"/>
+      <c r="J35" s="119"/>
+      <c r="K35" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="L35" s="149"/>
-      <c r="M35" s="106"/>
-      <c r="N35" s="104"/>
-      <c r="O35" s="103"/>
-      <c r="P35" s="96"/>
+      <c r="L35" s="101"/>
+      <c r="M35" s="65"/>
+      <c r="N35" s="63"/>
+      <c r="O35" s="62"/>
+      <c r="P35" s="58"/>
     </row>
     <row r="36" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D36" s="90"/>
-      <c r="E36" s="121"/>
-      <c r="F36" s="138" t="s">
+      <c r="D36" s="52"/>
+      <c r="E36" s="177"/>
+      <c r="F36" s="91" t="s">
         <v>83</v>
       </c>
-      <c r="G36" s="147"/>
-      <c r="H36" s="110"/>
-      <c r="I36" s="110"/>
-      <c r="J36" s="170"/>
-      <c r="K36" s="173"/>
-      <c r="L36" s="150"/>
-      <c r="M36" s="113"/>
-      <c r="N36" s="110"/>
-      <c r="O36" s="115"/>
-      <c r="P36" s="96"/>
+      <c r="G36" s="99"/>
+      <c r="H36" s="69"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="120"/>
+      <c r="K36" s="123"/>
+      <c r="L36" s="102"/>
+      <c r="M36" s="72"/>
+      <c r="N36" s="69"/>
+      <c r="O36" s="74"/>
+      <c r="P36" s="58"/>
     </row>
     <row r="37" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D37" s="90"/>
-      <c r="E37" s="122"/>
-      <c r="F37" s="142" t="s">
+      <c r="D37" s="52"/>
+      <c r="E37" s="178"/>
+      <c r="F37" s="95" t="s">
         <v>82</v>
       </c>
-      <c r="G37" s="148"/>
-      <c r="H37" s="116"/>
-      <c r="I37" s="116"/>
-      <c r="J37" s="171"/>
-      <c r="K37" s="174"/>
-      <c r="L37" s="151"/>
-      <c r="M37" s="130"/>
-      <c r="N37" s="116"/>
-      <c r="O37" s="119"/>
-      <c r="P37" s="96"/>
+      <c r="G37" s="100"/>
+      <c r="H37" s="75"/>
+      <c r="I37" s="75"/>
+      <c r="J37" s="121"/>
+      <c r="K37" s="124"/>
+      <c r="L37" s="103"/>
+      <c r="M37" s="85"/>
+      <c r="N37" s="75"/>
+      <c r="O37" s="78"/>
+      <c r="P37" s="58"/>
     </row>
     <row r="38" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D38" s="90"/>
-      <c r="E38" s="128" t="s">
+      <c r="D38" s="52"/>
+      <c r="E38" s="176" t="s">
         <v>87</v>
       </c>
-      <c r="F38" s="137" t="s">
+      <c r="F38" s="90" t="s">
         <v>89</v>
       </c>
-      <c r="G38" s="105"/>
-      <c r="H38" s="104"/>
-      <c r="I38" s="104"/>
-      <c r="J38" s="104"/>
-      <c r="K38" s="103"/>
-      <c r="L38" s="172" t="s">
+      <c r="G38" s="64"/>
+      <c r="H38" s="63"/>
+      <c r="I38" s="63"/>
+      <c r="J38" s="63"/>
+      <c r="K38" s="62"/>
+      <c r="L38" s="122" t="s">
         <v>21</v>
       </c>
-      <c r="M38" s="175"/>
-      <c r="N38" s="179"/>
-      <c r="O38" s="103"/>
-      <c r="P38" s="96"/>
+      <c r="M38" s="125"/>
+      <c r="N38" s="129"/>
+      <c r="O38" s="62"/>
+      <c r="P38" s="58"/>
     </row>
     <row r="39" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D39" s="90"/>
-      <c r="E39" s="121"/>
-      <c r="F39" s="138" t="s">
+      <c r="D39" s="52"/>
+      <c r="E39" s="177"/>
+      <c r="F39" s="91" t="s">
         <v>90</v>
       </c>
-      <c r="G39" s="147"/>
-      <c r="H39" s="110"/>
-      <c r="I39" s="110"/>
-      <c r="J39" s="110"/>
-      <c r="K39" s="115"/>
-      <c r="L39" s="174"/>
-      <c r="M39" s="176"/>
-      <c r="N39" s="172" t="s">
+      <c r="G39" s="99"/>
+      <c r="H39" s="69"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="69"/>
+      <c r="K39" s="74"/>
+      <c r="L39" s="124"/>
+      <c r="M39" s="126"/>
+      <c r="N39" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="O39" s="178"/>
-      <c r="P39" s="96"/>
+      <c r="O39" s="128"/>
+      <c r="P39" s="58"/>
     </row>
     <row r="40" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D40" s="90"/>
-      <c r="E40" s="121"/>
-      <c r="F40" s="138" t="s">
+      <c r="D40" s="52"/>
+      <c r="E40" s="177"/>
+      <c r="F40" s="91" t="s">
         <v>93</v>
       </c>
-      <c r="G40" s="147"/>
-      <c r="H40" s="110"/>
-      <c r="I40" s="110"/>
-      <c r="J40" s="110"/>
-      <c r="K40" s="115"/>
-      <c r="L40" s="101"/>
-      <c r="M40" s="177"/>
-      <c r="N40" s="174"/>
-      <c r="O40" s="172" t="s">
+      <c r="G40" s="99"/>
+      <c r="H40" s="69"/>
+      <c r="I40" s="69"/>
+      <c r="J40" s="69"/>
+      <c r="K40" s="74"/>
+      <c r="L40" s="60"/>
+      <c r="M40" s="127"/>
+      <c r="N40" s="124"/>
+      <c r="O40" s="122" t="s">
         <v>95</v>
       </c>
-      <c r="P40" s="96"/>
+      <c r="P40" s="58"/>
     </row>
     <row r="41" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D41" s="90"/>
-      <c r="E41" s="122"/>
-      <c r="F41" s="142" t="s">
+      <c r="D41" s="52"/>
+      <c r="E41" s="178"/>
+      <c r="F41" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="G41" s="148"/>
-      <c r="H41" s="116"/>
-      <c r="I41" s="116"/>
-      <c r="J41" s="116"/>
-      <c r="K41" s="119"/>
-      <c r="L41" s="148"/>
-      <c r="M41" s="117"/>
-      <c r="N41" s="180"/>
-      <c r="O41" s="174"/>
-      <c r="P41" s="96"/>
+      <c r="G41" s="100"/>
+      <c r="H41" s="75"/>
+      <c r="I41" s="75"/>
+      <c r="J41" s="75"/>
+      <c r="K41" s="78"/>
+      <c r="L41" s="100"/>
+      <c r="M41" s="76"/>
+      <c r="N41" s="130"/>
+      <c r="O41" s="124"/>
+      <c r="P41" s="58"/>
     </row>
     <row r="42" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D42" s="108"/>
-      <c r="E42" s="109"/>
-      <c r="F42" s="95" t="s">
+      <c r="D42" s="67"/>
+      <c r="E42" s="68"/>
+      <c r="F42" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="G42" s="95"/>
-      <c r="H42" s="95"/>
-      <c r="I42" s="95"/>
-      <c r="J42" s="95"/>
-      <c r="K42" s="95"/>
-      <c r="L42" s="95"/>
-      <c r="M42" s="95"/>
-      <c r="N42" s="95"/>
-      <c r="O42" s="95"/>
-      <c r="P42" s="94"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57"/>
+      <c r="K42" s="57"/>
+      <c r="L42" s="57"/>
+      <c r="M42" s="57"/>
+      <c r="N42" s="57"/>
+      <c r="O42" s="57"/>
+      <c r="P42" s="56"/>
     </row>
     <row r="43" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="F43" s="87" t="s">
+      <c r="F43" s="49" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="44" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="F44" s="88" t="s">
+      <c r="F44" s="50" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="45" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="F45" s="88" t="s">
+      <c r="F45" s="50" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="46" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="F46" s="88" t="s">
+      <c r="F46" s="50" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="47" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="F47" s="88" t="s">
+      <c r="F47" s="50" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="48" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="F48" s="88" t="s">
+      <c r="F48" s="50" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3973,19 +3966,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="L4:O4"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="E35:E37"/>
+    <mergeCell ref="E38:E41"/>
     <mergeCell ref="I30:J30"/>
     <mergeCell ref="E6:E15"/>
     <mergeCell ref="E16:E18"/>
     <mergeCell ref="E19:E21"/>
     <mergeCell ref="E22:E24"/>
     <mergeCell ref="E25:E34"/>
-    <mergeCell ref="E35:E37"/>
-    <mergeCell ref="E38:E41"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="L4:O4"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H19:I19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4002,50 +3995,50 @@
   <sheetData>
     <row r="3" spans="2:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="145" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="61"/>
+      <c r="C4" s="146"/>
+      <c r="D4" s="146"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="146"/>
+      <c r="M4" s="146"/>
+      <c r="N4" s="146"/>
+      <c r="O4" s="146"/>
+      <c r="P4" s="146"/>
+      <c r="Q4" s="146"/>
+      <c r="R4" s="146"/>
+      <c r="S4" s="147"/>
     </row>
     <row r="5" spans="2:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="62"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
-      <c r="L5" s="63"/>
-      <c r="M5" s="63"/>
-      <c r="N5" s="63"/>
-      <c r="O5" s="63"/>
-      <c r="P5" s="63"/>
-      <c r="Q5" s="63"/>
-      <c r="R5" s="63"/>
-      <c r="S5" s="64"/>
+      <c r="B5" s="148"/>
+      <c r="C5" s="149"/>
+      <c r="D5" s="149"/>
+      <c r="E5" s="149"/>
+      <c r="F5" s="149"/>
+      <c r="G5" s="149"/>
+      <c r="H5" s="149"/>
+      <c r="I5" s="149"/>
+      <c r="J5" s="149"/>
+      <c r="K5" s="149"/>
+      <c r="L5" s="149"/>
+      <c r="M5" s="149"/>
+      <c r="N5" s="149"/>
+      <c r="O5" s="149"/>
+      <c r="P5" s="149"/>
+      <c r="Q5" s="149"/>
+      <c r="R5" s="149"/>
+      <c r="S5" s="150"/>
     </row>
     <row r="6" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="65"/>
-      <c r="C6" s="68" t="s">
+      <c r="B6" s="179"/>
+      <c r="C6" s="182" t="s">
         <v>24</v>
       </c>
       <c r="D6" t="s">
@@ -4068,8 +4061,8 @@
       <c r="S6" s="32"/>
     </row>
     <row r="7" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="66"/>
-      <c r="C7" s="67"/>
+      <c r="B7" s="180"/>
+      <c r="C7" s="181"/>
       <c r="D7" t="s">
         <v>26</v>
       </c>
@@ -4078,8 +4071,8 @@
       </c>
     </row>
     <row r="8" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="66"/>
-      <c r="C8" s="67"/>
+      <c r="B8" s="180"/>
+      <c r="C8" s="181"/>
       <c r="D8" t="s">
         <v>28</v>
       </c>
@@ -4088,7 +4081,7 @@
       </c>
     </row>
     <row r="9" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="66"/>
+      <c r="B9" s="180"/>
       <c r="C9" s="10" t="s">
         <v>19</v>
       </c>
@@ -4100,8 +4093,8 @@
       </c>
     </row>
     <row r="10" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="66"/>
-      <c r="C10" s="67" t="s">
+      <c r="B10" s="180"/>
+      <c r="C10" s="181" t="s">
         <v>17</v>
       </c>
       <c r="D10" t="s">
@@ -4109,15 +4102,15 @@
       </c>
     </row>
     <row r="11" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="66"/>
-      <c r="C11" s="67"/>
+      <c r="B11" s="180"/>
+      <c r="C11" s="181"/>
       <c r="D11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="66"/>
-      <c r="C12" s="67" t="s">
+      <c r="B12" s="180"/>
+      <c r="C12" s="181" t="s">
         <v>18</v>
       </c>
       <c r="D12" t="s">
@@ -4128,8 +4121,8 @@
       </c>
     </row>
     <row r="13" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="66"/>
-      <c r="C13" s="67"/>
+      <c r="B13" s="180"/>
+      <c r="C13" s="181"/>
       <c r="D13" t="s">
         <v>30</v>
       </c>
@@ -4138,8 +4131,8 @@
       </c>
     </row>
     <row r="14" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="66"/>
-      <c r="C14" s="67"/>
+      <c r="B14" s="180"/>
+      <c r="C14" s="181"/>
       <c r="D14" t="s">
         <v>29</v>
       </c>
@@ -4148,8 +4141,8 @@
       </c>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B15" s="66"/>
-      <c r="C15" s="67"/>
+      <c r="B15" s="180"/>
+      <c r="C15" s="181"/>
       <c r="D15" t="s">
         <v>33</v>
       </c>

--- a/doc/시스템사업부_프로젝트 개발 일정표.xlsx
+++ b/doc/시스템사업부_프로젝트 개발 일정표.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\web_git\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADE4CC1-1C29-479F-96CF-233DB4BAB4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91186A0-61CC-46AF-BAB3-E5FDCAEA0FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4725" yWindow="4170" windowWidth="21435" windowHeight="15600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="38640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="개발 일정표" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="105">
   <si>
     <t>09월</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -377,10 +377,6 @@
   </si>
   <si>
     <t xml:space="preserve"> &gt; 기타 페이지 작업중 안내(Progress circular)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>제어(Snackbars)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -434,6 +430,35 @@
   <si>
     <t>F/E
 (Vue)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 데이터베이스 제어 기능 개발</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 제어장비(방송, 문자, 전광판, 차단기) 제어이력 입력 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 제어장비(방송, 문자, 전광판, 차단기) 제어 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 일반 센싱 상태정보 (방송, 문자, 전광판, 차단기)  입력 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>셋업
+(DB 설계)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 장비(방송, 문자, 전광판, 차단기) 제어연동 테이블 설계</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 장비(방송, 문자, 전광판, 차단기) 상태연동 테이블 설계</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -592,7 +617,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="58">
+  <borders count="64">
     <border>
       <left/>
       <right/>
@@ -971,15 +996,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="hair">
         <color indexed="64"/>
       </right>
@@ -1314,6 +1330,93 @@
       <top style="hair">
         <color indexed="64"/>
       </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1329,7 +1432,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="192">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1457,28 +1560,25 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
@@ -1488,7 +1588,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1497,160 +1596,211 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="46" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="49" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="50" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="44" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="44" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="44" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="49" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="45" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="48" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="45" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="48" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="50" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="51" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="49" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="44" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="38" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="47" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="45" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="39" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="48" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1697,56 +1847,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1757,30 +1880,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1792,6 +1891,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2084,136 +2216,136 @@
   <sheetData>
     <row r="3" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F4" s="136" t="s">
+      <c r="F4" s="151" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137"/>
-      <c r="I4" s="137"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="137"/>
-      <c r="L4" s="137"/>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137"/>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="137"/>
-      <c r="S4" s="137"/>
-      <c r="T4" s="137"/>
-      <c r="U4" s="137"/>
-      <c r="V4" s="137"/>
-      <c r="W4" s="138"/>
+      <c r="G4" s="152"/>
+      <c r="H4" s="152"/>
+      <c r="I4" s="152"/>
+      <c r="J4" s="152"/>
+      <c r="K4" s="152"/>
+      <c r="L4" s="152"/>
+      <c r="M4" s="152"/>
+      <c r="N4" s="152"/>
+      <c r="O4" s="152"/>
+      <c r="P4" s="152"/>
+      <c r="Q4" s="152"/>
+      <c r="R4" s="152"/>
+      <c r="S4" s="152"/>
+      <c r="T4" s="152"/>
+      <c r="U4" s="152"/>
+      <c r="V4" s="152"/>
+      <c r="W4" s="153"/>
     </row>
     <row r="5" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F5" s="139"/>
-      <c r="G5" s="140"/>
-      <c r="H5" s="140"/>
-      <c r="I5" s="140"/>
-      <c r="J5" s="140"/>
-      <c r="K5" s="140"/>
-      <c r="L5" s="140"/>
-      <c r="M5" s="140"/>
-      <c r="N5" s="140"/>
-      <c r="O5" s="140"/>
-      <c r="P5" s="140"/>
-      <c r="Q5" s="140"/>
-      <c r="R5" s="140"/>
-      <c r="S5" s="140"/>
-      <c r="T5" s="140"/>
-      <c r="U5" s="140"/>
-      <c r="V5" s="140"/>
-      <c r="W5" s="141"/>
+      <c r="F5" s="154"/>
+      <c r="G5" s="155"/>
+      <c r="H5" s="155"/>
+      <c r="I5" s="155"/>
+      <c r="J5" s="155"/>
+      <c r="K5" s="155"/>
+      <c r="L5" s="155"/>
+      <c r="M5" s="155"/>
+      <c r="N5" s="155"/>
+      <c r="O5" s="155"/>
+      <c r="P5" s="155"/>
+      <c r="Q5" s="155"/>
+      <c r="R5" s="155"/>
+      <c r="S5" s="155"/>
+      <c r="T5" s="155"/>
+      <c r="U5" s="155"/>
+      <c r="V5" s="155"/>
+      <c r="W5" s="156"/>
     </row>
     <row r="6" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F6" s="142"/>
-      <c r="G6" s="143"/>
-      <c r="H6" s="143"/>
-      <c r="I6" s="143"/>
-      <c r="J6" s="143"/>
-      <c r="K6" s="143"/>
-      <c r="L6" s="143"/>
-      <c r="M6" s="143"/>
-      <c r="N6" s="143"/>
-      <c r="O6" s="143"/>
-      <c r="P6" s="143"/>
-      <c r="Q6" s="143"/>
-      <c r="R6" s="143"/>
-      <c r="S6" s="143"/>
-      <c r="T6" s="143"/>
-      <c r="U6" s="143"/>
-      <c r="V6" s="143"/>
-      <c r="W6" s="144"/>
+      <c r="F6" s="157"/>
+      <c r="G6" s="158"/>
+      <c r="H6" s="158"/>
+      <c r="I6" s="158"/>
+      <c r="J6" s="158"/>
+      <c r="K6" s="158"/>
+      <c r="L6" s="158"/>
+      <c r="M6" s="158"/>
+      <c r="N6" s="158"/>
+      <c r="O6" s="158"/>
+      <c r="P6" s="158"/>
+      <c r="Q6" s="158"/>
+      <c r="R6" s="158"/>
+      <c r="S6" s="158"/>
+      <c r="T6" s="158"/>
+      <c r="U6" s="158"/>
+      <c r="V6" s="158"/>
+      <c r="W6" s="159"/>
     </row>
     <row r="7" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F7" s="145" t="s">
+      <c r="F7" s="160" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="146"/>
-      <c r="H7" s="146"/>
-      <c r="I7" s="146"/>
-      <c r="J7" s="146"/>
-      <c r="K7" s="146"/>
-      <c r="L7" s="146"/>
-      <c r="M7" s="146"/>
-      <c r="N7" s="146"/>
-      <c r="O7" s="146"/>
-      <c r="P7" s="146"/>
-      <c r="Q7" s="146"/>
-      <c r="R7" s="146"/>
-      <c r="S7" s="146"/>
-      <c r="T7" s="146"/>
-      <c r="U7" s="146"/>
-      <c r="V7" s="146"/>
-      <c r="W7" s="147"/>
+      <c r="G7" s="161"/>
+      <c r="H7" s="161"/>
+      <c r="I7" s="161"/>
+      <c r="J7" s="161"/>
+      <c r="K7" s="161"/>
+      <c r="L7" s="161"/>
+      <c r="M7" s="161"/>
+      <c r="N7" s="161"/>
+      <c r="O7" s="161"/>
+      <c r="P7" s="161"/>
+      <c r="Q7" s="161"/>
+      <c r="R7" s="161"/>
+      <c r="S7" s="161"/>
+      <c r="T7" s="161"/>
+      <c r="U7" s="161"/>
+      <c r="V7" s="161"/>
+      <c r="W7" s="162"/>
     </row>
     <row r="8" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F8" s="148"/>
-      <c r="G8" s="149"/>
-      <c r="H8" s="149"/>
-      <c r="I8" s="149"/>
-      <c r="J8" s="149"/>
-      <c r="K8" s="149"/>
-      <c r="L8" s="149"/>
-      <c r="M8" s="149"/>
-      <c r="N8" s="149"/>
-      <c r="O8" s="149"/>
-      <c r="P8" s="149"/>
-      <c r="Q8" s="149"/>
-      <c r="R8" s="149"/>
-      <c r="S8" s="149"/>
-      <c r="T8" s="149"/>
-      <c r="U8" s="149"/>
-      <c r="V8" s="149"/>
-      <c r="W8" s="150"/>
+      <c r="F8" s="163"/>
+      <c r="G8" s="164"/>
+      <c r="H8" s="164"/>
+      <c r="I8" s="164"/>
+      <c r="J8" s="164"/>
+      <c r="K8" s="164"/>
+      <c r="L8" s="164"/>
+      <c r="M8" s="164"/>
+      <c r="N8" s="164"/>
+      <c r="O8" s="164"/>
+      <c r="P8" s="164"/>
+      <c r="Q8" s="164"/>
+      <c r="R8" s="164"/>
+      <c r="S8" s="164"/>
+      <c r="T8" s="164"/>
+      <c r="U8" s="164"/>
+      <c r="V8" s="164"/>
+      <c r="W8" s="165"/>
     </row>
     <row r="9" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F9" s="151" t="s">
+      <c r="F9" s="136" t="s">
         <v>0</v>
       </c>
-      <c r="G9" s="152"/>
-      <c r="H9" s="152"/>
-      <c r="I9" s="152"/>
-      <c r="J9" s="152"/>
-      <c r="K9" s="151" t="s">
+      <c r="G9" s="137"/>
+      <c r="H9" s="137"/>
+      <c r="I9" s="137"/>
+      <c r="J9" s="137"/>
+      <c r="K9" s="136" t="s">
         <v>1</v>
       </c>
-      <c r="L9" s="152"/>
-      <c r="M9" s="152"/>
-      <c r="N9" s="153"/>
-      <c r="O9" s="151" t="s">
+      <c r="L9" s="137"/>
+      <c r="M9" s="137"/>
+      <c r="N9" s="138"/>
+      <c r="O9" s="136" t="s">
         <v>12</v>
       </c>
-      <c r="P9" s="152"/>
-      <c r="Q9" s="152"/>
-      <c r="R9" s="153"/>
-      <c r="S9" s="151" t="s">
+      <c r="P9" s="137"/>
+      <c r="Q9" s="137"/>
+      <c r="R9" s="138"/>
+      <c r="S9" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="T9" s="152"/>
-      <c r="U9" s="152"/>
-      <c r="V9" s="152"/>
-      <c r="W9" s="153"/>
+      <c r="T9" s="137"/>
+      <c r="U9" s="137"/>
+      <c r="V9" s="137"/>
+      <c r="W9" s="138"/>
     </row>
     <row r="10" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F10" s="3" t="s">
@@ -2302,11 +2434,11 @@
       <c r="F13" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="159" t="s">
+      <c r="G13" s="142" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="160"/>
-      <c r="I13" s="161"/>
+      <c r="H13" s="143"/>
+      <c r="I13" s="144"/>
       <c r="K13" s="4"/>
       <c r="L13" s="17"/>
       <c r="N13" s="7"/>
@@ -2565,74 +2697,74 @@
       <c r="W29" s="14"/>
     </row>
     <row r="30" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F30" s="162" t="s">
+      <c r="F30" s="145" t="s">
         <v>11</v>
       </c>
-      <c r="G30" s="163"/>
-      <c r="H30" s="163"/>
-      <c r="I30" s="163"/>
-      <c r="J30" s="163"/>
-      <c r="K30" s="163"/>
-      <c r="L30" s="163"/>
-      <c r="M30" s="163"/>
-      <c r="N30" s="163"/>
-      <c r="O30" s="163"/>
-      <c r="P30" s="163"/>
-      <c r="Q30" s="163"/>
-      <c r="R30" s="163"/>
-      <c r="S30" s="163"/>
-      <c r="T30" s="163"/>
-      <c r="U30" s="163"/>
-      <c r="V30" s="163"/>
-      <c r="W30" s="164"/>
+      <c r="G30" s="146"/>
+      <c r="H30" s="146"/>
+      <c r="I30" s="146"/>
+      <c r="J30" s="146"/>
+      <c r="K30" s="146"/>
+      <c r="L30" s="146"/>
+      <c r="M30" s="146"/>
+      <c r="N30" s="146"/>
+      <c r="O30" s="146"/>
+      <c r="P30" s="146"/>
+      <c r="Q30" s="146"/>
+      <c r="R30" s="146"/>
+      <c r="S30" s="146"/>
+      <c r="T30" s="146"/>
+      <c r="U30" s="146"/>
+      <c r="V30" s="146"/>
+      <c r="W30" s="147"/>
     </row>
     <row r="31" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F31" s="165"/>
-      <c r="G31" s="166"/>
-      <c r="H31" s="166"/>
-      <c r="I31" s="166"/>
-      <c r="J31" s="166"/>
-      <c r="K31" s="166"/>
-      <c r="L31" s="166"/>
-      <c r="M31" s="166"/>
-      <c r="N31" s="166"/>
-      <c r="O31" s="166"/>
-      <c r="P31" s="166"/>
-      <c r="Q31" s="166"/>
-      <c r="R31" s="166"/>
-      <c r="S31" s="166"/>
-      <c r="T31" s="166"/>
-      <c r="U31" s="166"/>
-      <c r="V31" s="166"/>
-      <c r="W31" s="167"/>
+      <c r="F31" s="148"/>
+      <c r="G31" s="149"/>
+      <c r="H31" s="149"/>
+      <c r="I31" s="149"/>
+      <c r="J31" s="149"/>
+      <c r="K31" s="149"/>
+      <c r="L31" s="149"/>
+      <c r="M31" s="149"/>
+      <c r="N31" s="149"/>
+      <c r="O31" s="149"/>
+      <c r="P31" s="149"/>
+      <c r="Q31" s="149"/>
+      <c r="R31" s="149"/>
+      <c r="S31" s="149"/>
+      <c r="T31" s="149"/>
+      <c r="U31" s="149"/>
+      <c r="V31" s="149"/>
+      <c r="W31" s="150"/>
     </row>
     <row r="32" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F32" s="151" t="s">
+      <c r="F32" s="136" t="s">
         <v>0</v>
       </c>
-      <c r="G32" s="152"/>
-      <c r="H32" s="152"/>
-      <c r="I32" s="152"/>
-      <c r="J32" s="152"/>
-      <c r="K32" s="151" t="s">
+      <c r="G32" s="137"/>
+      <c r="H32" s="137"/>
+      <c r="I32" s="137"/>
+      <c r="J32" s="137"/>
+      <c r="K32" s="136" t="s">
         <v>1</v>
       </c>
-      <c r="L32" s="152"/>
-      <c r="M32" s="152"/>
-      <c r="N32" s="153"/>
-      <c r="O32" s="151" t="s">
+      <c r="L32" s="137"/>
+      <c r="M32" s="137"/>
+      <c r="N32" s="138"/>
+      <c r="O32" s="136" t="s">
         <v>12</v>
       </c>
-      <c r="P32" s="152"/>
-      <c r="Q32" s="152"/>
-      <c r="R32" s="153"/>
-      <c r="S32" s="151" t="s">
+      <c r="P32" s="137"/>
+      <c r="Q32" s="137"/>
+      <c r="R32" s="138"/>
+      <c r="S32" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="T32" s="152"/>
-      <c r="U32" s="152"/>
-      <c r="V32" s="152"/>
-      <c r="W32" s="153"/>
+      <c r="T32" s="137"/>
+      <c r="U32" s="137"/>
+      <c r="V32" s="137"/>
+      <c r="W32" s="138"/>
     </row>
     <row r="33" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F33" s="3" t="s">
@@ -2921,74 +3053,74 @@
       <c r="W49" s="14"/>
     </row>
     <row r="50" spans="6:23" x14ac:dyDescent="0.3">
-      <c r="F50" s="162" t="s">
+      <c r="F50" s="145" t="s">
         <v>20</v>
       </c>
-      <c r="G50" s="163"/>
-      <c r="H50" s="163"/>
-      <c r="I50" s="163"/>
-      <c r="J50" s="163"/>
-      <c r="K50" s="163"/>
-      <c r="L50" s="163"/>
-      <c r="M50" s="163"/>
-      <c r="N50" s="163"/>
-      <c r="O50" s="163"/>
-      <c r="P50" s="163"/>
-      <c r="Q50" s="163"/>
-      <c r="R50" s="163"/>
-      <c r="S50" s="163"/>
-      <c r="T50" s="163"/>
-      <c r="U50" s="163"/>
-      <c r="V50" s="163"/>
-      <c r="W50" s="164"/>
+      <c r="G50" s="146"/>
+      <c r="H50" s="146"/>
+      <c r="I50" s="146"/>
+      <c r="J50" s="146"/>
+      <c r="K50" s="146"/>
+      <c r="L50" s="146"/>
+      <c r="M50" s="146"/>
+      <c r="N50" s="146"/>
+      <c r="O50" s="146"/>
+      <c r="P50" s="146"/>
+      <c r="Q50" s="146"/>
+      <c r="R50" s="146"/>
+      <c r="S50" s="146"/>
+      <c r="T50" s="146"/>
+      <c r="U50" s="146"/>
+      <c r="V50" s="146"/>
+      <c r="W50" s="147"/>
     </row>
     <row r="51" spans="6:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F51" s="165"/>
-      <c r="G51" s="166"/>
-      <c r="H51" s="166"/>
-      <c r="I51" s="166"/>
-      <c r="J51" s="166"/>
-      <c r="K51" s="166"/>
-      <c r="L51" s="166"/>
-      <c r="M51" s="166"/>
-      <c r="N51" s="166"/>
-      <c r="O51" s="166"/>
-      <c r="P51" s="166"/>
-      <c r="Q51" s="166"/>
-      <c r="R51" s="166"/>
-      <c r="S51" s="166"/>
-      <c r="T51" s="166"/>
-      <c r="U51" s="166"/>
-      <c r="V51" s="166"/>
-      <c r="W51" s="167"/>
+      <c r="F51" s="148"/>
+      <c r="G51" s="149"/>
+      <c r="H51" s="149"/>
+      <c r="I51" s="149"/>
+      <c r="J51" s="149"/>
+      <c r="K51" s="149"/>
+      <c r="L51" s="149"/>
+      <c r="M51" s="149"/>
+      <c r="N51" s="149"/>
+      <c r="O51" s="149"/>
+      <c r="P51" s="149"/>
+      <c r="Q51" s="149"/>
+      <c r="R51" s="149"/>
+      <c r="S51" s="149"/>
+      <c r="T51" s="149"/>
+      <c r="U51" s="149"/>
+      <c r="V51" s="149"/>
+      <c r="W51" s="150"/>
     </row>
     <row r="52" spans="6:23" x14ac:dyDescent="0.3">
-      <c r="F52" s="151" t="s">
+      <c r="F52" s="136" t="s">
         <v>0</v>
       </c>
-      <c r="G52" s="152"/>
-      <c r="H52" s="152"/>
-      <c r="I52" s="152"/>
-      <c r="J52" s="152"/>
-      <c r="K52" s="151" t="s">
+      <c r="G52" s="137"/>
+      <c r="H52" s="137"/>
+      <c r="I52" s="137"/>
+      <c r="J52" s="137"/>
+      <c r="K52" s="136" t="s">
         <v>1</v>
       </c>
-      <c r="L52" s="152"/>
-      <c r="M52" s="152"/>
-      <c r="N52" s="153"/>
-      <c r="O52" s="151" t="s">
+      <c r="L52" s="137"/>
+      <c r="M52" s="137"/>
+      <c r="N52" s="138"/>
+      <c r="O52" s="136" t="s">
         <v>12</v>
       </c>
-      <c r="P52" s="152"/>
-      <c r="Q52" s="152"/>
-      <c r="R52" s="153"/>
-      <c r="S52" s="151" t="s">
+      <c r="P52" s="137"/>
+      <c r="Q52" s="137"/>
+      <c r="R52" s="138"/>
+      <c r="S52" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="T52" s="152"/>
-      <c r="U52" s="152"/>
-      <c r="V52" s="152"/>
-      <c r="W52" s="153"/>
+      <c r="T52" s="137"/>
+      <c r="U52" s="137"/>
+      <c r="V52" s="137"/>
+      <c r="W52" s="138"/>
     </row>
     <row r="53" spans="6:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F53" s="3" t="s">
@@ -3084,12 +3216,12 @@
       <c r="L56" s="17"/>
       <c r="N56" s="7"/>
       <c r="O56" s="4"/>
-      <c r="P56" s="156" t="s">
+      <c r="P56" s="139" t="s">
         <v>16</v>
       </c>
-      <c r="Q56" s="157"/>
-      <c r="R56" s="157"/>
-      <c r="S56" s="158"/>
+      <c r="Q56" s="140"/>
+      <c r="R56" s="140"/>
+      <c r="S56" s="141"/>
       <c r="W56" s="7"/>
     </row>
     <row r="57" spans="6:23" x14ac:dyDescent="0.3">
@@ -3136,10 +3268,10 @@
       <c r="O59" s="4"/>
       <c r="R59" s="7"/>
       <c r="S59" s="4"/>
-      <c r="T59" s="154" t="s">
+      <c r="T59" s="134" t="s">
         <v>23</v>
       </c>
-      <c r="U59" s="155"/>
+      <c r="U59" s="135"/>
       <c r="W59" s="7"/>
     </row>
     <row r="60" spans="6:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3177,6 +3309,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="F4:W6"/>
+    <mergeCell ref="F7:W8"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="S9:W9"/>
     <mergeCell ref="T59:U59"/>
     <mergeCell ref="S52:W52"/>
     <mergeCell ref="P56:S56"/>
@@ -3190,12 +3328,6 @@
     <mergeCell ref="K32:N32"/>
     <mergeCell ref="O32:R32"/>
     <mergeCell ref="S32:W32"/>
-    <mergeCell ref="F4:W6"/>
-    <mergeCell ref="F7:W8"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="S9:W9"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3205,7 +3337,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019D5629-DDAE-4958-87CA-0890F9F624F4}">
-  <dimension ref="D3:P64"/>
+  <dimension ref="D3:P52"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -3214,758 +3346,821 @@
   <sheetData>
     <row r="3" spans="4:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="4:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G4" s="168" t="s">
+      <c r="G4" s="174" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="169"/>
-      <c r="I4" s="169"/>
-      <c r="J4" s="169"/>
-      <c r="K4" s="170"/>
-      <c r="L4" s="168" t="s">
+      <c r="H4" s="175"/>
+      <c r="I4" s="175"/>
+      <c r="J4" s="175"/>
+      <c r="K4" s="176"/>
+      <c r="L4" s="174" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="169"/>
-      <c r="N4" s="169"/>
-      <c r="O4" s="170"/>
+      <c r="M4" s="175"/>
+      <c r="N4" s="175"/>
+      <c r="O4" s="176"/>
       <c r="P4" s="51"/>
     </row>
     <row r="5" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D5" s="52"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="89" t="s">
-        <v>91</v>
-      </c>
-      <c r="G5" s="98" t="s">
+      <c r="E5" s="78"/>
+      <c r="F5" s="87" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="81" t="s">
+      <c r="H5" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="I5" s="81" t="s">
+      <c r="I5" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="81" t="s">
+      <c r="J5" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="83" t="s">
+      <c r="K5" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="98" t="s">
+      <c r="L5" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="M5" s="82" t="s">
+      <c r="M5" s="80" t="s">
         <v>3</v>
       </c>
-      <c r="N5" s="81" t="s">
+      <c r="N5" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="O5" s="83" t="s">
+      <c r="O5" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="58"/>
+      <c r="P5" s="57"/>
     </row>
     <row r="6" spans="4:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D6" s="52"/>
-      <c r="E6" s="173" t="s">
-        <v>96</v>
-      </c>
-      <c r="F6" s="90" t="s">
+      <c r="E6" s="171" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="G6" s="61" t="s">
+      <c r="G6" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="66"/>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="101"/>
-      <c r="M6" s="86"/>
-      <c r="N6" s="84"/>
-      <c r="O6" s="87"/>
-      <c r="P6" s="59"/>
+      <c r="H6" s="65"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="99"/>
+      <c r="M6" s="84"/>
+      <c r="N6" s="82"/>
+      <c r="O6" s="85"/>
+      <c r="P6" s="58"/>
     </row>
     <row r="7" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D7" s="52"/>
-      <c r="E7" s="174"/>
-      <c r="F7" s="91" t="s">
+      <c r="E7" s="172"/>
+      <c r="F7" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="104"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="69"/>
-      <c r="J7" s="69"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="71"/>
-      <c r="N7" s="70"/>
-      <c r="O7" s="73"/>
-      <c r="P7" s="59"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="67"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="72"/>
+      <c r="L7" s="100"/>
+      <c r="M7" s="69"/>
+      <c r="N7" s="68"/>
+      <c r="O7" s="71"/>
+      <c r="P7" s="58"/>
     </row>
     <row r="8" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D8" s="52"/>
-      <c r="E8" s="174"/>
-      <c r="F8" s="91" t="s">
+      <c r="E8" s="172"/>
+      <c r="F8" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="104"/>
-      <c r="H8" s="96"/>
-      <c r="I8" s="69"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="74"/>
-      <c r="L8" s="102"/>
-      <c r="M8" s="71"/>
-      <c r="N8" s="70"/>
-      <c r="O8" s="73"/>
-      <c r="P8" s="59"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="72"/>
+      <c r="L8" s="100"/>
+      <c r="M8" s="69"/>
+      <c r="N8" s="68"/>
+      <c r="O8" s="71"/>
+      <c r="P8" s="58"/>
     </row>
     <row r="9" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D9" s="52"/>
-      <c r="E9" s="174"/>
-      <c r="F9" s="91" t="s">
+      <c r="E9" s="172"/>
+      <c r="F9" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="105"/>
-      <c r="H9" s="96"/>
-      <c r="I9" s="69"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="74"/>
-      <c r="L9" s="102"/>
-      <c r="M9" s="71"/>
-      <c r="N9" s="70"/>
-      <c r="O9" s="73"/>
-      <c r="P9" s="59"/>
+      <c r="G9" s="103"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="67"/>
+      <c r="K9" s="72"/>
+      <c r="L9" s="100"/>
+      <c r="M9" s="69"/>
+      <c r="N9" s="68"/>
+      <c r="O9" s="71"/>
+      <c r="P9" s="58"/>
     </row>
     <row r="10" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D10" s="52"/>
-      <c r="E10" s="174"/>
-      <c r="F10" s="92" t="s">
+      <c r="E10" s="172"/>
+      <c r="F10" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="106" t="s">
+      <c r="G10" s="104" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="96"/>
-      <c r="I10" s="69"/>
-      <c r="J10" s="69"/>
-      <c r="K10" s="74"/>
-      <c r="L10" s="102"/>
-      <c r="M10" s="71"/>
-      <c r="N10" s="70"/>
-      <c r="O10" s="73"/>
-      <c r="P10" s="59"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="67"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="100"/>
+      <c r="M10" s="69"/>
+      <c r="N10" s="68"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="58"/>
     </row>
     <row r="11" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D11" s="52"/>
-      <c r="E11" s="174"/>
-      <c r="F11" s="93" t="s">
+      <c r="E11" s="172"/>
+      <c r="F11" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="104"/>
-      <c r="H11" s="96"/>
-      <c r="I11" s="69"/>
-      <c r="J11" s="69"/>
-      <c r="K11" s="74"/>
-      <c r="L11" s="102"/>
-      <c r="M11" s="71"/>
-      <c r="N11" s="70"/>
-      <c r="O11" s="73"/>
-      <c r="P11" s="59"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="72"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="69"/>
+      <c r="N11" s="68"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="58"/>
     </row>
     <row r="12" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D12" s="52"/>
-      <c r="E12" s="174"/>
-      <c r="F12" s="93" t="s">
+      <c r="E12" s="172"/>
+      <c r="F12" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="G12" s="104"/>
-      <c r="H12" s="96"/>
-      <c r="I12" s="69"/>
-      <c r="J12" s="69"/>
-      <c r="K12" s="74"/>
-      <c r="L12" s="102"/>
-      <c r="M12" s="71"/>
-      <c r="N12" s="70"/>
-      <c r="O12" s="73"/>
-      <c r="P12" s="59"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="72"/>
+      <c r="L12" s="100"/>
+      <c r="M12" s="69"/>
+      <c r="N12" s="68"/>
+      <c r="O12" s="71"/>
+      <c r="P12" s="58"/>
     </row>
     <row r="13" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D13" s="52"/>
-      <c r="E13" s="174"/>
-      <c r="F13" s="93" t="s">
+      <c r="E13" s="172"/>
+      <c r="F13" s="91" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="104"/>
-      <c r="H13" s="96"/>
-      <c r="I13" s="69"/>
-      <c r="J13" s="69"/>
-      <c r="K13" s="74"/>
-      <c r="L13" s="102"/>
-      <c r="M13" s="71"/>
-      <c r="N13" s="70"/>
-      <c r="O13" s="73"/>
-      <c r="P13" s="59"/>
+      <c r="G13" s="102"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="67"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="100"/>
+      <c r="M13" s="69"/>
+      <c r="N13" s="68"/>
+      <c r="O13" s="71"/>
+      <c r="P13" s="58"/>
     </row>
     <row r="14" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D14" s="52"/>
-      <c r="E14" s="174"/>
-      <c r="F14" s="93" t="s">
+      <c r="E14" s="172"/>
+      <c r="F14" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="G14" s="104"/>
-      <c r="H14" s="96"/>
-      <c r="I14" s="69"/>
-      <c r="J14" s="69"/>
-      <c r="K14" s="74"/>
-      <c r="L14" s="102"/>
-      <c r="M14" s="71"/>
-      <c r="N14" s="70"/>
-      <c r="O14" s="73"/>
-      <c r="P14" s="59"/>
+      <c r="G14" s="102"/>
+      <c r="H14" s="94"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="67"/>
+      <c r="K14" s="72"/>
+      <c r="L14" s="100"/>
+      <c r="M14" s="69"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="71"/>
+      <c r="P14" s="58"/>
     </row>
     <row r="15" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D15" s="52"/>
-      <c r="E15" s="175"/>
-      <c r="F15" s="94" t="s">
+      <c r="E15" s="173"/>
+      <c r="F15" s="92" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="107"/>
-      <c r="H15" s="97"/>
-      <c r="I15" s="75"/>
-      <c r="J15" s="75"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="103"/>
-      <c r="M15" s="76"/>
-      <c r="N15" s="77"/>
-      <c r="O15" s="88"/>
-      <c r="P15" s="59"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="73"/>
+      <c r="J15" s="73"/>
+      <c r="K15" s="76"/>
+      <c r="L15" s="101"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="86"/>
+      <c r="P15" s="58"/>
     </row>
     <row r="16" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D16" s="52"/>
-      <c r="E16" s="173" t="s">
+      <c r="E16" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="F16" s="90" t="s">
+      <c r="F16" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="G16" s="108"/>
-      <c r="H16" s="171" t="s">
+      <c r="G16" s="106"/>
+      <c r="H16" s="169" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="172"/>
-      <c r="J16" s="66"/>
-      <c r="K16" s="62"/>
-      <c r="L16" s="64"/>
-      <c r="M16" s="86"/>
-      <c r="N16" s="84"/>
-      <c r="O16" s="87"/>
-      <c r="P16" s="59"/>
+      <c r="I16" s="170"/>
+      <c r="J16" s="65"/>
+      <c r="K16" s="61"/>
+      <c r="L16" s="63"/>
+      <c r="M16" s="84"/>
+      <c r="N16" s="82"/>
+      <c r="O16" s="85"/>
+      <c r="P16" s="58"/>
     </row>
     <row r="17" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D17" s="52"/>
-      <c r="E17" s="174"/>
-      <c r="F17" s="91" t="s">
+      <c r="E17" s="172"/>
+      <c r="F17" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="G17" s="109"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="73"/>
-      <c r="J17" s="96"/>
-      <c r="K17" s="74"/>
-      <c r="L17" s="99"/>
-      <c r="M17" s="71"/>
-      <c r="N17" s="70"/>
-      <c r="O17" s="73"/>
-      <c r="P17" s="59"/>
+      <c r="G17" s="107"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="94"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="97"/>
+      <c r="M17" s="69"/>
+      <c r="N17" s="68"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="58"/>
     </row>
     <row r="18" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D18" s="52"/>
-      <c r="E18" s="175"/>
-      <c r="F18" s="95" t="s">
+      <c r="E18" s="173"/>
+      <c r="F18" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="G18" s="110"/>
-      <c r="H18" s="103"/>
-      <c r="I18" s="112"/>
-      <c r="J18" s="97"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="100"/>
-      <c r="M18" s="76"/>
-      <c r="N18" s="77"/>
-      <c r="O18" s="88"/>
-      <c r="P18" s="59"/>
+      <c r="G18" s="108"/>
+      <c r="H18" s="101"/>
+      <c r="I18" s="110"/>
+      <c r="J18" s="95"/>
+      <c r="K18" s="76"/>
+      <c r="L18" s="98"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="75"/>
+      <c r="O18" s="86"/>
+      <c r="P18" s="58"/>
     </row>
     <row r="19" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D19" s="52"/>
-      <c r="E19" s="173" t="s">
-        <v>97</v>
-      </c>
-      <c r="F19" s="90" t="s">
+      <c r="E19" s="171" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="88" t="s">
         <v>74</v>
       </c>
-      <c r="G19" s="108"/>
-      <c r="H19" s="171" t="s">
+      <c r="G19" s="106"/>
+      <c r="H19" s="169" t="s">
         <v>51</v>
       </c>
-      <c r="I19" s="172"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="62"/>
-      <c r="L19" s="64"/>
-      <c r="M19" s="86"/>
-      <c r="N19" s="84"/>
-      <c r="O19" s="87"/>
-      <c r="P19" s="59"/>
+      <c r="I19" s="170"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="82"/>
+      <c r="O19" s="85"/>
+      <c r="P19" s="58"/>
     </row>
     <row r="20" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D20" s="52"/>
-      <c r="E20" s="174"/>
-      <c r="F20" s="91" t="s">
+      <c r="E20" s="172"/>
+      <c r="F20" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="G20" s="109"/>
-      <c r="H20" s="113"/>
-      <c r="I20" s="73"/>
-      <c r="J20" s="96"/>
-      <c r="K20" s="74"/>
-      <c r="L20" s="99"/>
-      <c r="M20" s="71"/>
-      <c r="N20" s="70"/>
-      <c r="O20" s="73"/>
-      <c r="P20" s="59"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="111"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="94"/>
+      <c r="K20" s="72"/>
+      <c r="L20" s="97"/>
+      <c r="M20" s="69"/>
+      <c r="N20" s="68"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="58"/>
     </row>
     <row r="21" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D21" s="52"/>
-      <c r="E21" s="175"/>
-      <c r="F21" s="95" t="s">
+      <c r="E21" s="173"/>
+      <c r="F21" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="G21" s="110"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="114"/>
-      <c r="J21" s="97"/>
-      <c r="K21" s="78"/>
-      <c r="L21" s="100"/>
-      <c r="M21" s="76"/>
-      <c r="N21" s="77"/>
-      <c r="O21" s="88"/>
-      <c r="P21" s="59"/>
+      <c r="G21" s="108"/>
+      <c r="H21" s="101"/>
+      <c r="I21" s="112"/>
+      <c r="J21" s="95"/>
+      <c r="K21" s="76"/>
+      <c r="L21" s="98"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="75"/>
+      <c r="O21" s="86"/>
+      <c r="P21" s="58"/>
     </row>
     <row r="22" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D22" s="52"/>
-      <c r="E22" s="173" t="s">
-        <v>98</v>
-      </c>
-      <c r="F22" s="90" t="s">
+      <c r="E22" s="171" t="s">
+        <v>97</v>
+      </c>
+      <c r="F22" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="G22" s="108"/>
-      <c r="H22" s="171" t="s">
+      <c r="G22" s="106"/>
+      <c r="H22" s="169" t="s">
         <v>52</v>
       </c>
-      <c r="I22" s="172"/>
-      <c r="J22" s="66"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="64"/>
-      <c r="M22" s="86"/>
-      <c r="N22" s="84"/>
-      <c r="O22" s="62"/>
-      <c r="P22" s="58"/>
+      <c r="I22" s="170"/>
+      <c r="J22" s="65"/>
+      <c r="K22" s="61"/>
+      <c r="L22" s="63"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="82"/>
+      <c r="O22" s="61"/>
+      <c r="P22" s="57"/>
     </row>
     <row r="23" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D23" s="52"/>
-      <c r="E23" s="174"/>
-      <c r="F23" s="91" t="s">
+      <c r="E23" s="172"/>
+      <c r="F23" s="89" t="s">
         <v>63</v>
       </c>
-      <c r="G23" s="109"/>
-      <c r="H23" s="115"/>
-      <c r="I23" s="73"/>
-      <c r="J23" s="96"/>
-      <c r="K23" s="74"/>
-      <c r="L23" s="99"/>
-      <c r="M23" s="71"/>
-      <c r="N23" s="70"/>
-      <c r="O23" s="74"/>
-      <c r="P23" s="58"/>
+      <c r="G23" s="107"/>
+      <c r="H23" s="113"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="94"/>
+      <c r="K23" s="72"/>
+      <c r="L23" s="97"/>
+      <c r="M23" s="69"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="72"/>
+      <c r="P23" s="57"/>
     </row>
     <row r="24" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D24" s="52"/>
-      <c r="E24" s="175"/>
-      <c r="F24" s="95" t="s">
+      <c r="E24" s="173"/>
+      <c r="F24" s="93" t="s">
         <v>64</v>
       </c>
-      <c r="G24" s="110"/>
-      <c r="H24" s="103"/>
-      <c r="I24" s="116"/>
-      <c r="J24" s="97"/>
-      <c r="K24" s="78"/>
-      <c r="L24" s="100"/>
-      <c r="M24" s="76"/>
-      <c r="N24" s="77"/>
-      <c r="O24" s="78"/>
-      <c r="P24" s="58"/>
+      <c r="G24" s="108"/>
+      <c r="H24" s="101"/>
+      <c r="I24" s="114"/>
+      <c r="J24" s="95"/>
+      <c r="K24" s="76"/>
+      <c r="L24" s="98"/>
+      <c r="M24" s="74"/>
+      <c r="N24" s="75"/>
+      <c r="O24" s="76"/>
+      <c r="P24" s="57"/>
     </row>
     <row r="25" spans="4:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D25" s="52"/>
-      <c r="E25" s="173" t="s">
+      <c r="E25" s="171" t="s">
         <v>71</v>
       </c>
-      <c r="F25" s="90" t="s">
+      <c r="F25" s="88" t="s">
         <v>77</v>
       </c>
-      <c r="G25" s="108"/>
-      <c r="H25" s="61" t="s">
+      <c r="G25" s="106"/>
+      <c r="H25" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="I25" s="66"/>
-      <c r="J25" s="63"/>
-      <c r="K25" s="62"/>
-      <c r="L25" s="101"/>
-      <c r="M25" s="65"/>
-      <c r="N25" s="63"/>
-      <c r="O25" s="62"/>
-      <c r="P25" s="58"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="62"/>
+      <c r="K25" s="61"/>
+      <c r="L25" s="99"/>
+      <c r="M25" s="64"/>
+      <c r="N25" s="62"/>
+      <c r="O25" s="61"/>
+      <c r="P25" s="57"/>
     </row>
     <row r="26" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D26" s="52"/>
-      <c r="E26" s="174"/>
-      <c r="F26" s="91" t="s">
+      <c r="E26" s="172"/>
+      <c r="F26" s="89" t="s">
         <v>70</v>
       </c>
-      <c r="G26" s="109"/>
-      <c r="H26" s="117"/>
-      <c r="I26" s="96"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="74"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="72"/>
-      <c r="N26" s="69"/>
-      <c r="O26" s="74"/>
-      <c r="P26" s="58"/>
+      <c r="G26" s="107"/>
+      <c r="H26" s="115"/>
+      <c r="I26" s="94"/>
+      <c r="J26" s="67"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="100"/>
+      <c r="M26" s="70"/>
+      <c r="N26" s="67"/>
+      <c r="O26" s="72"/>
+      <c r="P26" s="57"/>
     </row>
     <row r="27" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D27" s="52"/>
-      <c r="E27" s="174"/>
-      <c r="F27" s="91" t="s">
+      <c r="E27" s="172"/>
+      <c r="F27" s="89" t="s">
         <v>72</v>
       </c>
-      <c r="G27" s="109"/>
-      <c r="H27" s="117"/>
-      <c r="I27" s="96"/>
-      <c r="J27" s="69"/>
-      <c r="K27" s="74"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="72"/>
-      <c r="N27" s="69"/>
-      <c r="O27" s="74"/>
-      <c r="P27" s="58"/>
+      <c r="G27" s="107"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="94"/>
+      <c r="J27" s="67"/>
+      <c r="K27" s="72"/>
+      <c r="L27" s="100"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="67"/>
+      <c r="O27" s="72"/>
+      <c r="P27" s="57"/>
     </row>
     <row r="28" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D28" s="52"/>
-      <c r="E28" s="174"/>
-      <c r="F28" s="91" t="s">
+      <c r="E28" s="172"/>
+      <c r="F28" s="89" t="s">
         <v>73</v>
       </c>
-      <c r="G28" s="109"/>
-      <c r="H28" s="117"/>
-      <c r="I28" s="96"/>
-      <c r="J28" s="69"/>
-      <c r="K28" s="74"/>
-      <c r="L28" s="102"/>
-      <c r="M28" s="72"/>
-      <c r="N28" s="69"/>
-      <c r="O28" s="74"/>
-      <c r="P28" s="58"/>
+      <c r="G28" s="107"/>
+      <c r="H28" s="115"/>
+      <c r="I28" s="94"/>
+      <c r="J28" s="67"/>
+      <c r="K28" s="72"/>
+      <c r="L28" s="100"/>
+      <c r="M28" s="70"/>
+      <c r="N28" s="67"/>
+      <c r="O28" s="72"/>
+      <c r="P28" s="57"/>
     </row>
     <row r="29" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D29" s="52"/>
-      <c r="E29" s="174"/>
-      <c r="F29" s="91" t="s">
+      <c r="E29" s="172"/>
+      <c r="F29" s="89" t="s">
         <v>85</v>
       </c>
-      <c r="G29" s="109"/>
-      <c r="H29" s="118"/>
-      <c r="I29" s="132"/>
-      <c r="J29" s="79"/>
-      <c r="K29" s="74"/>
-      <c r="L29" s="102"/>
-      <c r="M29" s="72"/>
-      <c r="N29" s="69"/>
-      <c r="O29" s="74"/>
-      <c r="P29" s="58"/>
+      <c r="G29" s="107"/>
+      <c r="H29" s="116"/>
+      <c r="I29" s="130"/>
+      <c r="J29" s="77"/>
+      <c r="K29" s="72"/>
+      <c r="L29" s="100"/>
+      <c r="M29" s="70"/>
+      <c r="N29" s="67"/>
+      <c r="O29" s="72"/>
+      <c r="P29" s="57"/>
     </row>
     <row r="30" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D30" s="52"/>
-      <c r="E30" s="174"/>
-      <c r="F30" s="92" t="s">
+      <c r="E30" s="172"/>
+      <c r="F30" s="90" t="s">
         <v>80</v>
       </c>
-      <c r="G30" s="99"/>
-      <c r="H30" s="67"/>
-      <c r="I30" s="171" t="s">
+      <c r="G30" s="97"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="169" t="s">
         <v>69</v>
       </c>
-      <c r="J30" s="172"/>
-      <c r="K30" s="128"/>
-      <c r="L30" s="102"/>
-      <c r="M30" s="72"/>
-      <c r="N30" s="69"/>
-      <c r="O30" s="74"/>
-      <c r="P30" s="58"/>
+      <c r="J30" s="170"/>
+      <c r="K30" s="126"/>
+      <c r="L30" s="100"/>
+      <c r="M30" s="70"/>
+      <c r="N30" s="67"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="57"/>
     </row>
     <row r="31" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D31" s="52"/>
-      <c r="E31" s="174"/>
-      <c r="F31" s="91" t="s">
+      <c r="E31" s="172"/>
+      <c r="F31" s="89" t="s">
         <v>81</v>
       </c>
-      <c r="G31" s="99"/>
-      <c r="H31" s="120"/>
-      <c r="I31" s="133"/>
-      <c r="J31" s="74"/>
-      <c r="K31" s="128"/>
-      <c r="L31" s="102"/>
-      <c r="M31" s="72"/>
-      <c r="N31" s="69"/>
-      <c r="O31" s="74"/>
-      <c r="P31" s="58"/>
+      <c r="G31" s="97"/>
+      <c r="H31" s="118"/>
+      <c r="I31" s="131"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="126"/>
+      <c r="L31" s="100"/>
+      <c r="M31" s="70"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="72"/>
+      <c r="P31" s="57"/>
     </row>
     <row r="32" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D32" s="52"/>
-      <c r="E32" s="174"/>
-      <c r="F32" s="91" t="s">
+      <c r="E32" s="172"/>
+      <c r="F32" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="G32" s="99"/>
-      <c r="H32" s="120"/>
-      <c r="I32" s="99"/>
-      <c r="J32" s="134"/>
-      <c r="K32" s="128"/>
-      <c r="L32" s="102"/>
-      <c r="M32" s="72"/>
-      <c r="N32" s="69"/>
-      <c r="O32" s="74"/>
-      <c r="P32" s="58"/>
+      <c r="G32" s="97"/>
+      <c r="H32" s="118"/>
+      <c r="I32" s="97"/>
+      <c r="J32" s="132"/>
+      <c r="K32" s="126"/>
+      <c r="L32" s="100"/>
+      <c r="M32" s="70"/>
+      <c r="N32" s="67"/>
+      <c r="O32" s="72"/>
+      <c r="P32" s="57"/>
     </row>
     <row r="33" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D33" s="52"/>
-      <c r="E33" s="174"/>
-      <c r="F33" s="91" t="s">
+      <c r="E33" s="172"/>
+      <c r="F33" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="G33" s="99"/>
-      <c r="H33" s="120"/>
-      <c r="I33" s="99"/>
-      <c r="J33" s="134"/>
-      <c r="K33" s="128"/>
-      <c r="L33" s="102"/>
-      <c r="M33" s="72"/>
-      <c r="N33" s="69"/>
-      <c r="O33" s="74"/>
-      <c r="P33" s="58"/>
+      <c r="G33" s="97"/>
+      <c r="H33" s="118"/>
+      <c r="I33" s="97"/>
+      <c r="J33" s="132"/>
+      <c r="K33" s="126"/>
+      <c r="L33" s="100"/>
+      <c r="M33" s="70"/>
+      <c r="N33" s="67"/>
+      <c r="O33" s="72"/>
+      <c r="P33" s="57"/>
     </row>
     <row r="34" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D34" s="52"/>
-      <c r="E34" s="175"/>
-      <c r="F34" s="95" t="s">
+      <c r="E34" s="173"/>
+      <c r="F34" s="93" t="s">
         <v>79</v>
       </c>
-      <c r="G34" s="100"/>
-      <c r="H34" s="121"/>
-      <c r="I34" s="100"/>
-      <c r="J34" s="135"/>
-      <c r="K34" s="131"/>
-      <c r="L34" s="103"/>
-      <c r="M34" s="85"/>
-      <c r="N34" s="75"/>
-      <c r="O34" s="78"/>
-      <c r="P34" s="58"/>
+      <c r="G34" s="98"/>
+      <c r="H34" s="119"/>
+      <c r="I34" s="98"/>
+      <c r="J34" s="133"/>
+      <c r="K34" s="129"/>
+      <c r="L34" s="101"/>
+      <c r="M34" s="83"/>
+      <c r="N34" s="73"/>
+      <c r="O34" s="76"/>
+      <c r="P34" s="57"/>
     </row>
     <row r="35" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D35" s="52"/>
-      <c r="E35" s="176" t="s">
+      <c r="E35" s="166" t="s">
         <v>47</v>
       </c>
-      <c r="F35" s="90" t="s">
-        <v>88</v>
-      </c>
-      <c r="G35" s="64"/>
-      <c r="H35" s="63"/>
-      <c r="I35" s="63"/>
-      <c r="J35" s="119"/>
-      <c r="K35" s="122" t="s">
+      <c r="F35" s="88" t="s">
+        <v>87</v>
+      </c>
+      <c r="G35" s="63"/>
+      <c r="H35" s="62"/>
+      <c r="I35" s="62"/>
+      <c r="J35" s="117"/>
+      <c r="K35" s="120" t="s">
         <v>47</v>
       </c>
-      <c r="L35" s="101"/>
-      <c r="M35" s="65"/>
-      <c r="N35" s="63"/>
-      <c r="O35" s="62"/>
-      <c r="P35" s="58"/>
+      <c r="L35" s="99"/>
+      <c r="M35" s="64"/>
+      <c r="N35" s="62"/>
+      <c r="O35" s="61"/>
+      <c r="P35" s="57"/>
     </row>
     <row r="36" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D36" s="52"/>
-      <c r="E36" s="177"/>
-      <c r="F36" s="91" t="s">
+      <c r="E36" s="167"/>
+      <c r="F36" s="89" t="s">
         <v>83</v>
       </c>
-      <c r="G36" s="99"/>
-      <c r="H36" s="69"/>
-      <c r="I36" s="69"/>
-      <c r="J36" s="120"/>
-      <c r="K36" s="123"/>
-      <c r="L36" s="102"/>
-      <c r="M36" s="72"/>
-      <c r="N36" s="69"/>
-      <c r="O36" s="74"/>
-      <c r="P36" s="58"/>
+      <c r="G36" s="97"/>
+      <c r="H36" s="67"/>
+      <c r="I36" s="67"/>
+      <c r="J36" s="118"/>
+      <c r="K36" s="121"/>
+      <c r="L36" s="100"/>
+      <c r="M36" s="70"/>
+      <c r="N36" s="67"/>
+      <c r="O36" s="72"/>
+      <c r="P36" s="57"/>
     </row>
     <row r="37" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D37" s="52"/>
-      <c r="E37" s="178"/>
-      <c r="F37" s="95" t="s">
+      <c r="E37" s="168"/>
+      <c r="F37" s="93" t="s">
         <v>82</v>
       </c>
-      <c r="G37" s="100"/>
-      <c r="H37" s="75"/>
-      <c r="I37" s="75"/>
-      <c r="J37" s="121"/>
-      <c r="K37" s="124"/>
-      <c r="L37" s="103"/>
-      <c r="M37" s="85"/>
-      <c r="N37" s="75"/>
-      <c r="O37" s="78"/>
-      <c r="P37" s="58"/>
+      <c r="G37" s="98"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73"/>
+      <c r="J37" s="119"/>
+      <c r="K37" s="122"/>
+      <c r="L37" s="101"/>
+      <c r="M37" s="83"/>
+      <c r="N37" s="73"/>
+      <c r="O37" s="76"/>
+      <c r="P37" s="57"/>
     </row>
     <row r="38" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D38" s="52"/>
-      <c r="E38" s="176" t="s">
-        <v>87</v>
-      </c>
-      <c r="F38" s="90" t="s">
-        <v>89</v>
-      </c>
-      <c r="G38" s="64"/>
-      <c r="H38" s="63"/>
-      <c r="I38" s="63"/>
-      <c r="J38" s="63"/>
-      <c r="K38" s="62"/>
-      <c r="L38" s="122" t="s">
+      <c r="E38" s="166" t="s">
+        <v>86</v>
+      </c>
+      <c r="F38" s="88" t="s">
+        <v>88</v>
+      </c>
+      <c r="G38" s="63"/>
+      <c r="H38" s="62"/>
+      <c r="I38" s="62"/>
+      <c r="J38" s="62"/>
+      <c r="K38" s="61"/>
+      <c r="L38" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="M38" s="125"/>
-      <c r="N38" s="129"/>
-      <c r="O38" s="62"/>
-      <c r="P38" s="58"/>
+      <c r="M38" s="123"/>
+      <c r="N38" s="127"/>
+      <c r="O38" s="61"/>
+      <c r="P38" s="57"/>
     </row>
     <row r="39" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D39" s="52"/>
-      <c r="E39" s="177"/>
-      <c r="F39" s="91" t="s">
-        <v>90</v>
-      </c>
-      <c r="G39" s="99"/>
-      <c r="H39" s="69"/>
-      <c r="I39" s="69"/>
-      <c r="J39" s="69"/>
-      <c r="K39" s="74"/>
-      <c r="L39" s="124"/>
-      <c r="M39" s="126"/>
-      <c r="N39" s="122" t="s">
+      <c r="E39" s="167"/>
+      <c r="F39" s="89" t="s">
+        <v>89</v>
+      </c>
+      <c r="G39" s="97"/>
+      <c r="H39" s="67"/>
+      <c r="I39" s="67"/>
+      <c r="J39" s="67"/>
+      <c r="K39" s="72"/>
+      <c r="L39" s="122"/>
+      <c r="M39" s="124"/>
+      <c r="N39" s="120" t="s">
         <v>22</v>
       </c>
-      <c r="O39" s="128"/>
-      <c r="P39" s="58"/>
+      <c r="O39" s="126"/>
+      <c r="P39" s="57"/>
     </row>
     <row r="40" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D40" s="52"/>
-      <c r="E40" s="177"/>
-      <c r="F40" s="91" t="s">
-        <v>93</v>
-      </c>
-      <c r="G40" s="99"/>
-      <c r="H40" s="69"/>
-      <c r="I40" s="69"/>
-      <c r="J40" s="69"/>
-      <c r="K40" s="74"/>
-      <c r="L40" s="60"/>
-      <c r="M40" s="127"/>
-      <c r="N40" s="124"/>
-      <c r="O40" s="122" t="s">
-        <v>95</v>
-      </c>
-      <c r="P40" s="58"/>
+      <c r="E40" s="167"/>
+      <c r="F40" s="89" t="s">
+        <v>92</v>
+      </c>
+      <c r="G40" s="97"/>
+      <c r="H40" s="67"/>
+      <c r="I40" s="67"/>
+      <c r="J40" s="67"/>
+      <c r="K40" s="72"/>
+      <c r="L40" s="59"/>
+      <c r="M40" s="125"/>
+      <c r="N40" s="122"/>
+      <c r="O40" s="120" t="s">
+        <v>94</v>
+      </c>
+      <c r="P40" s="57"/>
     </row>
     <row r="41" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D41" s="52"/>
-      <c r="E41" s="178"/>
-      <c r="F41" s="95" t="s">
-        <v>94</v>
-      </c>
-      <c r="G41" s="100"/>
-      <c r="H41" s="75"/>
-      <c r="I41" s="75"/>
-      <c r="J41" s="75"/>
-      <c r="K41" s="78"/>
-      <c r="L41" s="100"/>
-      <c r="M41" s="76"/>
-      <c r="N41" s="130"/>
-      <c r="O41" s="124"/>
-      <c r="P41" s="58"/>
-    </row>
-    <row r="42" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D42" s="67"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="57" t="s">
-        <v>92</v>
-      </c>
-      <c r="G42" s="57"/>
-      <c r="H42" s="57"/>
-      <c r="I42" s="57"/>
-      <c r="J42" s="57"/>
-      <c r="K42" s="57"/>
-      <c r="L42" s="57"/>
-      <c r="M42" s="57"/>
-      <c r="N42" s="57"/>
-      <c r="O42" s="57"/>
-      <c r="P42" s="56"/>
-    </row>
-    <row r="43" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="F43" s="49" t="s">
+      <c r="E41" s="168"/>
+      <c r="F41" s="93" t="s">
+        <v>93</v>
+      </c>
+      <c r="G41" s="98"/>
+      <c r="H41" s="73"/>
+      <c r="I41" s="73"/>
+      <c r="J41" s="73"/>
+      <c r="K41" s="76"/>
+      <c r="L41" s="98"/>
+      <c r="M41" s="74"/>
+      <c r="N41" s="128"/>
+      <c r="O41" s="122"/>
+      <c r="P41" s="57"/>
+    </row>
+    <row r="42" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D42" s="181"/>
+      <c r="F42" s="182"/>
+      <c r="G42" s="174" t="s">
+        <v>0</v>
+      </c>
+      <c r="H42" s="175"/>
+      <c r="I42" s="175"/>
+      <c r="J42" s="175"/>
+      <c r="K42" s="176"/>
+      <c r="L42" s="174" t="s">
+        <v>1</v>
+      </c>
+      <c r="M42" s="175"/>
+      <c r="N42" s="175"/>
+      <c r="O42" s="176"/>
+      <c r="P42" s="58"/>
+    </row>
+    <row r="43" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D43" s="66"/>
+      <c r="E43" s="183"/>
+      <c r="F43" s="184" t="s">
+        <v>91</v>
+      </c>
+      <c r="G43" s="185" t="s">
+        <v>2</v>
+      </c>
+      <c r="H43" s="186" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="186" t="s">
+        <v>4</v>
+      </c>
+      <c r="J43" s="186" t="s">
+        <v>5</v>
+      </c>
+      <c r="K43" s="187" t="s">
+        <v>6</v>
+      </c>
+      <c r="L43" s="185" t="s">
+        <v>2</v>
+      </c>
+      <c r="M43" s="188" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="186" t="s">
+        <v>7</v>
+      </c>
+      <c r="O43" s="187" t="s">
+        <v>8</v>
+      </c>
+      <c r="P43" s="56"/>
+    </row>
+    <row r="44" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="E44" s="189" t="s">
+        <v>102</v>
+      </c>
+      <c r="F44" s="49" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="44" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="F44" s="50" t="s">
-        <v>54</v>
-      </c>
-    </row>
     <row r="45" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="E45" s="191"/>
       <c r="F45" s="50" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="4:16" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" spans="4:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E46" s="190"/>
       <c r="F46" s="50" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="F47" s="50" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="48" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="F48" s="50" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="64" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F64" t="s">
-        <v>86</v>
-      </c>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="47" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E47" s="171" t="s">
+        <v>62</v>
+      </c>
+      <c r="F47" s="88" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E48" s="172"/>
+      <c r="F48" s="89" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="49" spans="5:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E49" s="173"/>
+      <c r="F49" s="89" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="5:6" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="F50" s="88" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="5:6" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="F51" s="89" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="5:6" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="F52" s="89"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="17">
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="L42:O42"/>
+    <mergeCell ref="E44:E46"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="L4:O4"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H19:I19"/>
     <mergeCell ref="E35:E37"/>
     <mergeCell ref="E38:E41"/>
     <mergeCell ref="I30:J30"/>
@@ -3974,11 +4169,6 @@
     <mergeCell ref="E19:E21"/>
     <mergeCell ref="E22:E24"/>
     <mergeCell ref="E25:E34"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="L4:O4"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H19:I19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3995,50 +4185,50 @@
   <sheetData>
     <row r="3" spans="2:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B4" s="145" t="s">
+      <c r="B4" s="160" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="146"/>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="146"/>
-      <c r="K4" s="146"/>
-      <c r="L4" s="146"/>
-      <c r="M4" s="146"/>
-      <c r="N4" s="146"/>
-      <c r="O4" s="146"/>
-      <c r="P4" s="146"/>
-      <c r="Q4" s="146"/>
-      <c r="R4" s="146"/>
-      <c r="S4" s="147"/>
+      <c r="C4" s="161"/>
+      <c r="D4" s="161"/>
+      <c r="E4" s="161"/>
+      <c r="F4" s="161"/>
+      <c r="G4" s="161"/>
+      <c r="H4" s="161"/>
+      <c r="I4" s="161"/>
+      <c r="J4" s="161"/>
+      <c r="K4" s="161"/>
+      <c r="L4" s="161"/>
+      <c r="M4" s="161"/>
+      <c r="N4" s="161"/>
+      <c r="O4" s="161"/>
+      <c r="P4" s="161"/>
+      <c r="Q4" s="161"/>
+      <c r="R4" s="161"/>
+      <c r="S4" s="162"/>
     </row>
     <row r="5" spans="2:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="148"/>
-      <c r="C5" s="149"/>
-      <c r="D5" s="149"/>
-      <c r="E5" s="149"/>
-      <c r="F5" s="149"/>
-      <c r="G5" s="149"/>
-      <c r="H5" s="149"/>
-      <c r="I5" s="149"/>
-      <c r="J5" s="149"/>
-      <c r="K5" s="149"/>
-      <c r="L5" s="149"/>
-      <c r="M5" s="149"/>
-      <c r="N5" s="149"/>
-      <c r="O5" s="149"/>
-      <c r="P5" s="149"/>
-      <c r="Q5" s="149"/>
-      <c r="R5" s="149"/>
-      <c r="S5" s="150"/>
+      <c r="B5" s="163"/>
+      <c r="C5" s="164"/>
+      <c r="D5" s="164"/>
+      <c r="E5" s="164"/>
+      <c r="F5" s="164"/>
+      <c r="G5" s="164"/>
+      <c r="H5" s="164"/>
+      <c r="I5" s="164"/>
+      <c r="J5" s="164"/>
+      <c r="K5" s="164"/>
+      <c r="L5" s="164"/>
+      <c r="M5" s="164"/>
+      <c r="N5" s="164"/>
+      <c r="O5" s="164"/>
+      <c r="P5" s="164"/>
+      <c r="Q5" s="164"/>
+      <c r="R5" s="164"/>
+      <c r="S5" s="165"/>
     </row>
     <row r="6" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="179"/>
-      <c r="C6" s="182" t="s">
+      <c r="B6" s="177"/>
+      <c r="C6" s="180" t="s">
         <v>24</v>
       </c>
       <c r="D6" t="s">
@@ -4061,8 +4251,8 @@
       <c r="S6" s="32"/>
     </row>
     <row r="7" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="180"/>
-      <c r="C7" s="181"/>
+      <c r="B7" s="178"/>
+      <c r="C7" s="179"/>
       <c r="D7" t="s">
         <v>26</v>
       </c>
@@ -4071,8 +4261,8 @@
       </c>
     </row>
     <row r="8" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="180"/>
-      <c r="C8" s="181"/>
+      <c r="B8" s="178"/>
+      <c r="C8" s="179"/>
       <c r="D8" t="s">
         <v>28</v>
       </c>
@@ -4081,7 +4271,7 @@
       </c>
     </row>
     <row r="9" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="180"/>
+      <c r="B9" s="178"/>
       <c r="C9" s="10" t="s">
         <v>19</v>
       </c>
@@ -4093,8 +4283,8 @@
       </c>
     </row>
     <row r="10" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="180"/>
-      <c r="C10" s="181" t="s">
+      <c r="B10" s="178"/>
+      <c r="C10" s="179" t="s">
         <v>17</v>
       </c>
       <c r="D10" t="s">
@@ -4102,15 +4292,15 @@
       </c>
     </row>
     <row r="11" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="180"/>
-      <c r="C11" s="181"/>
+      <c r="B11" s="178"/>
+      <c r="C11" s="179"/>
       <c r="D11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="180"/>
-      <c r="C12" s="181" t="s">
+      <c r="B12" s="178"/>
+      <c r="C12" s="179" t="s">
         <v>18</v>
       </c>
       <c r="D12" t="s">
@@ -4121,8 +4311,8 @@
       </c>
     </row>
     <row r="13" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="180"/>
-      <c r="C13" s="181"/>
+      <c r="B13" s="178"/>
+      <c r="C13" s="179"/>
       <c r="D13" t="s">
         <v>30</v>
       </c>
@@ -4131,8 +4321,8 @@
       </c>
     </row>
     <row r="14" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="180"/>
-      <c r="C14" s="181"/>
+      <c r="B14" s="178"/>
+      <c r="C14" s="179"/>
       <c r="D14" t="s">
         <v>29</v>
       </c>
@@ -4141,8 +4331,8 @@
       </c>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B15" s="180"/>
-      <c r="C15" s="181"/>
+      <c r="B15" s="178"/>
+      <c r="C15" s="179"/>
       <c r="D15" t="s">
         <v>33</v>
       </c>

--- a/doc/시스템사업부_프로젝트 개발 일정표.xlsx
+++ b/doc/시스템사업부_프로젝트 개발 일정표.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\web_git\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JUNG\Desktop\web_git\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91186A0-61CC-46AF-BAB3-E5FDCAEA0FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="38640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="38640"/>
   </bookViews>
   <sheets>
-    <sheet name="개발 일정표" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
+    <sheet name="개발일정표" sheetId="4" r:id="rId1"/>
+    <sheet name="개발 일정표" sheetId="1" state="hidden" r:id="rId2"/>
     <sheet name="장비모니터링" sheetId="2" state="hidden" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="160">
   <si>
     <t>09월</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -291,10 +290,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> &gt; 일반 센싱 계측정보(강우, 수위, 변위, 적설, 경사, 침수) 조회 기능</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> &gt; 센싱정보 관리기관 정보, 프로젝트 코드, 계측센서 기본정보 입력 기능</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -307,10 +302,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>- 데이터베이스 조회 기능 개발</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>UI</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -319,11 +310,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>UI
-(Vuetify)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> &gt; router 기능 개발(모니터링, 제어, 관리, 계정)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -356,10 +342,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>- 데이터 표출 기능 개발</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve"> &gt;&gt; 센싱정보 관리기관 정보 표출(Treeview)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -409,10 +391,6 @@
   </si>
   <si>
     <t xml:space="preserve"> &gt; 3차 배포(무상 유지보수지역, 설치 1년 이내)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>배포(3차)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -437,35 +415,277 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> &gt; 제어장비(방송, 문자, 전광판, 차단기) 제어이력 입력 기능</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> &gt; 제어장비(방송, 문자, 전광판, 차단기) 제어 기능</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> &gt; 일반 센싱 상태정보 (방송, 문자, 전광판, 차단기)  입력 기능</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>셋업
 (DB 설계)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> &gt; 장비(방송, 문자, 전광판, 차단기) 제어연동 테이블 설계</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> &gt; 장비(방송, 문자, 전광판, 차단기) 상태연동 테이블 설계</t>
+    <t>UI</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>F/E</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>B/E</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>S/W</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 경보 장비(방송, 문자, 전광판, 차단기) 원격제어 테이블 설계</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 경보 장비(방송, 문자, 전광판, 차단기) 동작이력 테이블 설계</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 경보 장비 (방송, 문자, 전광판, 차단기) 동작이력 연계 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 경보 장비 (방송, 문자, 전광판, 차단기) 상태정보 연계 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 경보 장비(방송, 문자, 전광판, 차단기) 상태정보 테이블 설계</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1차</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>배포</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 경보 장비 (방송, 문자, 전광판, 차단기) 동작이력 표출 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 경보 장비 (방송, 문자, 전광판, 차단기) 원격제어 명령 및 결과 연계 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 경보 장비 원격제어 (방송, 문자, 전광판, 차단기) 명령 및 결과 입력 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 데이터베이스 명령 기능 개발</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 테스트 운영중 수정 및 개선 내용 반영</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI
+(Vuetify)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI
+(Vuetify)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 데이터 표출 기능 개발</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 데이터베이스 조회 기능 개발</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 일반 센싱 계측정보(강우, 수위, 변위, 적설, 경사, 침수) 조회 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 경보 장비 (방송, 문자, 전광판, 차단기) 동작이력 조회 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 경보 장비 (방송, 문자, 전광판, 차단기) 상태정보 조회 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 경보 장비 동작이력 (방송, 문자, 전광판, 차단기) 입력 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 경보 장비 상태정보 (방송, 문자, 전광판, 차단기) 입력 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 경보 장비 (방송, 문자, 전광판, 차단기) 상태정보 표출 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 경보 장비 (방송, 문자, 전광판, 차단기) 원격제어 결과 조회 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 경보 장비 (방송, 문자, 전광판, 차단기) 원격제어 명령 입력 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 로그인 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>▷ 소하천 보고서 시스템</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 1차 배포(계약 유력지역)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 2차 배포(관심도 높은 지역)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>설계</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>설계</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 일반 센싱 계측정보 테이블 ( 법정동코드, 프로젝트코드, 소하천 명칭, 계측일시, 계측값)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 일반 센싱 계측정보(수위, 유량, 유속) 입력 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; API 연계정보 테이블 (기상특보, 날씨예보)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 센싱정보 관리기관 정보 테이블 설계 (지역별 법정동코드 5자리, 부서, 소속, 담당자, 연락처)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> &gt; 계측센서 기본정보 테이블 설계 (법정동코드, 프로젝트코드, 소하천 명칭, 주소, 위경도, 임계치 정보, CCTV 정보)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 데이터베이스 조회 기능 개발</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 보고서 표출 기능 개발</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 보고서 데이터 조회 기능 개발</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; 레이아웃(보고서 양식)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; 24시간 예보 정보 API 연계 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; 기상 특보 목록 API 연계 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; 24시간 예보 정보 조회 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; 기상 특보 목록 조회 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; 24시간 예보 정보 표출 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; 기상 특보 목록 표출 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; 계측시설 정보 표출 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; 관리기관 정보 표출 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; 관리기관 정보 조회 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; 계측시설 정보 조회 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>- 보고서 데이터 연계 기능 개발</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; 관리기관 정보 연계 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; 계측시설 정보 연계 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; 소하천 데이터 정보(수위, 유량, 유속) 연계 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; 소하천 데이터 정보(수위, 유량, 유속) 조회 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; 소하천 데이터 정보 그래프 및 테이블(수위, 유량, 유속) 표출 기능</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; CCTV 영상 연계 기능(RTSP)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; CCTV 영상 조회 기능(IMG)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt; CCTV 영상 표출 기능(IMG)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>3차</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="mm\/dd"/>
@@ -555,7 +775,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -616,8 +836,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="64">
+  <borders count="86">
     <border>
       <left/>
       <right/>
@@ -1297,7 +1523,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="hair">
         <color indexed="64"/>
       </left>
       <right/>
@@ -1310,16 +1536,202 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
       <top style="hair">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1330,9 +1742,7 @@
       <top style="hair">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1340,13 +1750,65 @@
       <right style="hair">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -1356,15 +1818,37 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="hair">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1374,12 +1858,8 @@
       <left style="hair">
         <color indexed="64"/>
       </left>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1392,28 +1872,28 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <top/>
+      <bottom style="hair">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="hair">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -1432,7 +1912,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="192">
+  <cellXfs count="348">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1542,15 +2022,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1675,9 +2146,6 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="49" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1685,9 +2153,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="44" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1712,33 +2177,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="49" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1751,21 +2199,90 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="47" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="56" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1802,50 +2319,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1856,30 +2349,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1892,44 +2361,413 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="71" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="75" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="75" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="50" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="81" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="82" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="49" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="44" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="67" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="84" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="83" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="54" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="75" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="71" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="47" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="84" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="50" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="64" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="81" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="49" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="76" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0] 2" xfId="2" xr:uid="{C9BB0B92-1ABE-461B-91B2-3799103E1004}"/>
+    <cellStyle name="쉼표 [0] 2" xfId="2"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="1" xr:uid="{55AAD021-65B1-490C-8DD8-B5D0B1E8C5EA}"/>
+    <cellStyle name="표준 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2206,7 +3044,3223 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="D3:X127"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="118" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="4:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G4" s="164" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="165"/>
+      <c r="I4" s="165"/>
+      <c r="J4" s="165"/>
+      <c r="K4" s="165"/>
+      <c r="L4" s="164" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="165"/>
+      <c r="N4" s="165"/>
+      <c r="O4" s="166"/>
+      <c r="P4" s="165" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q4" s="165"/>
+      <c r="R4" s="165"/>
+      <c r="S4" s="165"/>
+      <c r="T4" s="194" t="s">
+        <v>13</v>
+      </c>
+      <c r="U4" s="195"/>
+      <c r="V4" s="195"/>
+      <c r="W4" s="196"/>
+    </row>
+    <row r="5" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D5" s="49"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="84" t="s">
+        <v>86</v>
+      </c>
+      <c r="G5" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="J5" s="76" t="s">
+        <v>5</v>
+      </c>
+      <c r="K5" s="197" t="s">
+        <v>6</v>
+      </c>
+      <c r="L5" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="M5" s="77" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="76" t="s">
+        <v>7</v>
+      </c>
+      <c r="O5" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="P5" s="249" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="R5" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="S5" s="197" t="s">
+        <v>5</v>
+      </c>
+      <c r="T5" s="262" t="s">
+        <v>2</v>
+      </c>
+      <c r="U5" s="233" t="s">
+        <v>3</v>
+      </c>
+      <c r="V5" s="233" t="s">
+        <v>4</v>
+      </c>
+      <c r="W5" s="263" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="4:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="49"/>
+      <c r="E6" s="162" t="s">
+        <v>90</v>
+      </c>
+      <c r="F6" s="85" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="62"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="112"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="79"/>
+      <c r="O6" s="82"/>
+      <c r="P6" s="250"/>
+      <c r="Q6" s="79"/>
+      <c r="R6" s="79"/>
+      <c r="S6" s="198"/>
+      <c r="T6" s="96"/>
+      <c r="U6" s="79"/>
+      <c r="V6" s="79"/>
+      <c r="W6" s="82"/>
+    </row>
+    <row r="7" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D7" s="49"/>
+      <c r="E7" s="163"/>
+      <c r="F7" s="86" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="99"/>
+      <c r="H7" s="91"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="113"/>
+      <c r="L7" s="97"/>
+      <c r="M7" s="66"/>
+      <c r="N7" s="65"/>
+      <c r="O7" s="68"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="65"/>
+      <c r="R7" s="65"/>
+      <c r="S7" s="199"/>
+      <c r="T7" s="97"/>
+      <c r="U7" s="65"/>
+      <c r="V7" s="65"/>
+      <c r="W7" s="68"/>
+    </row>
+    <row r="8" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D8" s="49"/>
+      <c r="E8" s="163"/>
+      <c r="F8" s="86" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="99"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+      <c r="K8" s="113"/>
+      <c r="L8" s="97"/>
+      <c r="M8" s="66"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="68"/>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="65"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="199"/>
+      <c r="T8" s="97"/>
+      <c r="U8" s="65"/>
+      <c r="V8" s="65"/>
+      <c r="W8" s="68"/>
+    </row>
+    <row r="9" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D9" s="49"/>
+      <c r="E9" s="163"/>
+      <c r="F9" s="86" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="193"/>
+      <c r="H9" s="92"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="114"/>
+      <c r="L9" s="98"/>
+      <c r="M9" s="71"/>
+      <c r="N9" s="72"/>
+      <c r="O9" s="83"/>
+      <c r="P9" s="208"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="248"/>
+      <c r="T9" s="98"/>
+      <c r="U9" s="72"/>
+      <c r="V9" s="72"/>
+      <c r="W9" s="83"/>
+    </row>
+    <row r="10" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D10" s="49"/>
+      <c r="E10" s="163"/>
+      <c r="F10" s="87" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="H10" s="62"/>
+      <c r="I10" s="59"/>
+      <c r="J10" s="59"/>
+      <c r="K10" s="112"/>
+      <c r="L10" s="96"/>
+      <c r="M10" s="81"/>
+      <c r="N10" s="79"/>
+      <c r="O10" s="82"/>
+      <c r="P10" s="250"/>
+      <c r="Q10" s="79"/>
+      <c r="R10" s="79"/>
+      <c r="S10" s="198"/>
+      <c r="T10" s="96"/>
+      <c r="U10" s="79"/>
+      <c r="V10" s="79"/>
+      <c r="W10" s="82"/>
+    </row>
+    <row r="11" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D11" s="49"/>
+      <c r="E11" s="163"/>
+      <c r="F11" s="88" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11" s="99"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="64"/>
+      <c r="K11" s="113"/>
+      <c r="L11" s="97"/>
+      <c r="M11" s="66"/>
+      <c r="N11" s="65"/>
+      <c r="O11" s="68"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="65"/>
+      <c r="R11" s="65"/>
+      <c r="S11" s="199"/>
+      <c r="T11" s="97"/>
+      <c r="U11" s="65"/>
+      <c r="V11" s="65"/>
+      <c r="W11" s="68"/>
+    </row>
+    <row r="12" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D12" s="49"/>
+      <c r="E12" s="163"/>
+      <c r="F12" s="88" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="99"/>
+      <c r="H12" s="91"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
+      <c r="K12" s="113"/>
+      <c r="L12" s="97"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="68"/>
+      <c r="P12" s="54"/>
+      <c r="Q12" s="65"/>
+      <c r="R12" s="65"/>
+      <c r="S12" s="199"/>
+      <c r="T12" s="97"/>
+      <c r="U12" s="65"/>
+      <c r="V12" s="65"/>
+      <c r="W12" s="68"/>
+    </row>
+    <row r="13" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D13" s="49"/>
+      <c r="E13" s="163"/>
+      <c r="F13" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="99"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="64"/>
+      <c r="J13" s="64"/>
+      <c r="K13" s="113"/>
+      <c r="L13" s="97"/>
+      <c r="M13" s="66"/>
+      <c r="N13" s="65"/>
+      <c r="O13" s="68"/>
+      <c r="P13" s="54"/>
+      <c r="Q13" s="65"/>
+      <c r="R13" s="65"/>
+      <c r="S13" s="199"/>
+      <c r="T13" s="97"/>
+      <c r="U13" s="65"/>
+      <c r="V13" s="65"/>
+      <c r="W13" s="68"/>
+    </row>
+    <row r="14" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D14" s="49"/>
+      <c r="E14" s="163"/>
+      <c r="F14" s="88" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" s="101"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="114"/>
+      <c r="L14" s="98"/>
+      <c r="M14" s="71"/>
+      <c r="N14" s="72"/>
+      <c r="O14" s="83"/>
+      <c r="P14" s="208"/>
+      <c r="Q14" s="72"/>
+      <c r="R14" s="72"/>
+      <c r="S14" s="248"/>
+      <c r="T14" s="98"/>
+      <c r="U14" s="72"/>
+      <c r="V14" s="72"/>
+      <c r="W14" s="83"/>
+    </row>
+    <row r="15" spans="4:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D15" s="49"/>
+      <c r="E15" s="178" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="85" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15" s="102"/>
+      <c r="H15" s="167" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="168"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="112"/>
+      <c r="L15" s="60"/>
+      <c r="M15" s="81"/>
+      <c r="N15" s="79"/>
+      <c r="O15" s="82"/>
+      <c r="P15" s="250"/>
+      <c r="Q15" s="79"/>
+      <c r="R15" s="79"/>
+      <c r="S15" s="198"/>
+      <c r="T15" s="96"/>
+      <c r="U15" s="79"/>
+      <c r="V15" s="79"/>
+      <c r="W15" s="82"/>
+    </row>
+    <row r="16" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D16" s="49"/>
+      <c r="E16" s="179"/>
+      <c r="F16" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="103"/>
+      <c r="H16" s="104"/>
+      <c r="I16" s="68"/>
+      <c r="J16" s="91"/>
+      <c r="K16" s="185"/>
+      <c r="L16" s="94"/>
+      <c r="M16" s="66"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="68"/>
+      <c r="P16" s="54"/>
+      <c r="Q16" s="65"/>
+      <c r="R16" s="65"/>
+      <c r="S16" s="199"/>
+      <c r="T16" s="97"/>
+      <c r="U16" s="65"/>
+      <c r="V16" s="65"/>
+      <c r="W16" s="68"/>
+    </row>
+    <row r="17" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D17" s="49"/>
+      <c r="E17" s="179"/>
+      <c r="F17" s="219" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" s="103"/>
+      <c r="H17" s="98"/>
+      <c r="I17" s="105"/>
+      <c r="J17" s="290"/>
+      <c r="K17" s="291" t="s">
+        <v>98</v>
+      </c>
+      <c r="L17" s="91"/>
+      <c r="M17" s="66"/>
+      <c r="N17" s="65"/>
+      <c r="O17" s="68"/>
+      <c r="P17" s="54"/>
+      <c r="Q17" s="65"/>
+      <c r="R17" s="65"/>
+      <c r="S17" s="199"/>
+      <c r="T17" s="97"/>
+      <c r="U17" s="65"/>
+      <c r="V17" s="65"/>
+      <c r="W17" s="68"/>
+    </row>
+    <row r="18" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D18" s="49"/>
+      <c r="E18" s="180"/>
+      <c r="F18" s="213" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="95"/>
+      <c r="H18" s="176"/>
+      <c r="I18" s="176"/>
+      <c r="J18" s="114"/>
+      <c r="K18" s="293"/>
+      <c r="L18" s="92"/>
+      <c r="M18" s="71"/>
+      <c r="N18" s="72"/>
+      <c r="O18" s="83"/>
+      <c r="P18" s="208"/>
+      <c r="Q18" s="72"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="248"/>
+      <c r="T18" s="98"/>
+      <c r="U18" s="72"/>
+      <c r="V18" s="72"/>
+      <c r="W18" s="83"/>
+    </row>
+    <row r="19" spans="4:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D19" s="49"/>
+      <c r="E19" s="178" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="102"/>
+      <c r="H19" s="167" t="s">
+        <v>51</v>
+      </c>
+      <c r="I19" s="168"/>
+      <c r="J19" s="62"/>
+      <c r="K19" s="243"/>
+      <c r="L19" s="60"/>
+      <c r="M19" s="81"/>
+      <c r="N19" s="79"/>
+      <c r="O19" s="82"/>
+      <c r="P19" s="250"/>
+      <c r="Q19" s="79"/>
+      <c r="R19" s="79"/>
+      <c r="S19" s="198"/>
+      <c r="T19" s="96"/>
+      <c r="U19" s="79"/>
+      <c r="V19" s="79"/>
+      <c r="W19" s="82"/>
+    </row>
+    <row r="20" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D20" s="49"/>
+      <c r="E20" s="179"/>
+      <c r="F20" s="86" t="s">
+        <v>73</v>
+      </c>
+      <c r="G20" s="103"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="68"/>
+      <c r="J20" s="91"/>
+      <c r="K20" s="185"/>
+      <c r="L20" s="94"/>
+      <c r="M20" s="66"/>
+      <c r="N20" s="65"/>
+      <c r="O20" s="68"/>
+      <c r="P20" s="54"/>
+      <c r="Q20" s="65"/>
+      <c r="R20" s="65"/>
+      <c r="S20" s="199"/>
+      <c r="T20" s="97"/>
+      <c r="U20" s="65"/>
+      <c r="V20" s="65"/>
+      <c r="W20" s="68"/>
+    </row>
+    <row r="21" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D21" s="49"/>
+      <c r="E21" s="179"/>
+      <c r="F21" s="219" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="103"/>
+      <c r="H21" s="98"/>
+      <c r="I21" s="107"/>
+      <c r="J21" s="290"/>
+      <c r="K21" s="291" t="s">
+        <v>97</v>
+      </c>
+      <c r="L21" s="91"/>
+      <c r="M21" s="66"/>
+      <c r="N21" s="65"/>
+      <c r="O21" s="68"/>
+      <c r="P21" s="54"/>
+      <c r="Q21" s="65"/>
+      <c r="R21" s="65"/>
+      <c r="S21" s="199"/>
+      <c r="T21" s="97"/>
+      <c r="U21" s="65"/>
+      <c r="V21" s="65"/>
+      <c r="W21" s="68"/>
+    </row>
+    <row r="22" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D22" s="49"/>
+      <c r="E22" s="180"/>
+      <c r="F22" s="213" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="95"/>
+      <c r="H22" s="176"/>
+      <c r="I22" s="176"/>
+      <c r="J22" s="114"/>
+      <c r="K22" s="205"/>
+      <c r="L22" s="92"/>
+      <c r="M22" s="71"/>
+      <c r="N22" s="72"/>
+      <c r="O22" s="83"/>
+      <c r="P22" s="208"/>
+      <c r="Q22" s="72"/>
+      <c r="R22" s="72"/>
+      <c r="S22" s="248"/>
+      <c r="T22" s="98"/>
+      <c r="U22" s="72"/>
+      <c r="V22" s="72"/>
+      <c r="W22" s="83"/>
+    </row>
+    <row r="23" spans="4:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D23" s="49"/>
+      <c r="E23" s="178" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" s="85" t="s">
+        <v>115</v>
+      </c>
+      <c r="G23" s="288"/>
+      <c r="H23" s="167" t="s">
+        <v>52</v>
+      </c>
+      <c r="I23" s="168"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="243"/>
+      <c r="L23" s="56"/>
+      <c r="M23" s="231"/>
+      <c r="N23" s="228"/>
+      <c r="O23" s="255"/>
+      <c r="P23" s="55"/>
+      <c r="Q23" s="228"/>
+      <c r="R23" s="228"/>
+      <c r="S23" s="63"/>
+      <c r="T23" s="96"/>
+      <c r="U23" s="79"/>
+      <c r="V23" s="79"/>
+      <c r="W23" s="82"/>
+    </row>
+    <row r="24" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D24" s="49"/>
+      <c r="E24" s="179"/>
+      <c r="F24" s="86" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24" s="103"/>
+      <c r="H24" s="108"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="91"/>
+      <c r="K24" s="185"/>
+      <c r="L24" s="94"/>
+      <c r="M24" s="66"/>
+      <c r="N24" s="65"/>
+      <c r="O24" s="69"/>
+      <c r="P24" s="54"/>
+      <c r="Q24" s="65"/>
+      <c r="R24" s="65"/>
+      <c r="S24" s="199"/>
+      <c r="T24" s="97"/>
+      <c r="U24" s="65"/>
+      <c r="V24" s="65"/>
+      <c r="W24" s="68"/>
+    </row>
+    <row r="25" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D25" s="49"/>
+      <c r="E25" s="179"/>
+      <c r="F25" s="181" t="s">
+        <v>116</v>
+      </c>
+      <c r="G25" s="103"/>
+      <c r="H25" s="98"/>
+      <c r="I25" s="109"/>
+      <c r="J25" s="290"/>
+      <c r="K25" s="291" t="s">
+        <v>96</v>
+      </c>
+      <c r="L25" s="91"/>
+      <c r="M25" s="66"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="69"/>
+      <c r="P25" s="54"/>
+      <c r="Q25" s="65"/>
+      <c r="R25" s="65"/>
+      <c r="S25" s="199"/>
+      <c r="T25" s="97"/>
+      <c r="U25" s="65"/>
+      <c r="V25" s="65"/>
+      <c r="W25" s="68"/>
+    </row>
+    <row r="26" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D26" s="49"/>
+      <c r="E26" s="180"/>
+      <c r="F26" s="213" t="s">
+        <v>111</v>
+      </c>
+      <c r="G26" s="95"/>
+      <c r="H26" s="176"/>
+      <c r="I26" s="117"/>
+      <c r="J26" s="114"/>
+      <c r="K26" s="292"/>
+      <c r="L26" s="92"/>
+      <c r="M26" s="71"/>
+      <c r="N26" s="72"/>
+      <c r="O26" s="73"/>
+      <c r="P26" s="208"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="248"/>
+      <c r="T26" s="98"/>
+      <c r="U26" s="72"/>
+      <c r="V26" s="72"/>
+      <c r="W26" s="83"/>
+    </row>
+    <row r="27" spans="4:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D27" s="49"/>
+      <c r="E27" s="178" t="s">
+        <v>112</v>
+      </c>
+      <c r="F27" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" s="102"/>
+      <c r="H27" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="I27" s="62"/>
+      <c r="J27" s="59"/>
+      <c r="K27" s="243"/>
+      <c r="L27" s="96"/>
+      <c r="M27" s="61"/>
+      <c r="N27" s="59"/>
+      <c r="O27" s="58"/>
+      <c r="P27" s="250"/>
+      <c r="Q27" s="79"/>
+      <c r="R27" s="79"/>
+      <c r="S27" s="198"/>
+      <c r="T27" s="96"/>
+      <c r="U27" s="79"/>
+      <c r="V27" s="79"/>
+      <c r="W27" s="82"/>
+    </row>
+    <row r="28" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D28" s="49"/>
+      <c r="E28" s="179"/>
+      <c r="F28" s="86" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="103"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="91"/>
+      <c r="J28" s="64"/>
+      <c r="K28" s="113"/>
+      <c r="L28" s="97"/>
+      <c r="M28" s="67"/>
+      <c r="N28" s="64"/>
+      <c r="O28" s="69"/>
+      <c r="P28" s="54"/>
+      <c r="Q28" s="65"/>
+      <c r="R28" s="65"/>
+      <c r="S28" s="199"/>
+      <c r="T28" s="97"/>
+      <c r="U28" s="65"/>
+      <c r="V28" s="65"/>
+      <c r="W28" s="68"/>
+    </row>
+    <row r="29" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D29" s="49"/>
+      <c r="E29" s="179"/>
+      <c r="F29" s="86" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" s="103"/>
+      <c r="H29" s="110"/>
+      <c r="I29" s="91"/>
+      <c r="J29" s="64"/>
+      <c r="K29" s="113"/>
+      <c r="L29" s="97"/>
+      <c r="M29" s="67"/>
+      <c r="N29" s="64"/>
+      <c r="O29" s="69"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="65"/>
+      <c r="R29" s="65"/>
+      <c r="S29" s="199"/>
+      <c r="T29" s="97"/>
+      <c r="U29" s="65"/>
+      <c r="V29" s="65"/>
+      <c r="W29" s="68"/>
+    </row>
+    <row r="30" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D30" s="49"/>
+      <c r="E30" s="179"/>
+      <c r="F30" s="86" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="103"/>
+      <c r="H30" s="110"/>
+      <c r="I30" s="91"/>
+      <c r="J30" s="64"/>
+      <c r="K30" s="113"/>
+      <c r="L30" s="97"/>
+      <c r="M30" s="67"/>
+      <c r="N30" s="64"/>
+      <c r="O30" s="69"/>
+      <c r="P30" s="54"/>
+      <c r="Q30" s="65"/>
+      <c r="R30" s="65"/>
+      <c r="S30" s="199"/>
+      <c r="T30" s="97"/>
+      <c r="U30" s="65"/>
+      <c r="V30" s="65"/>
+      <c r="W30" s="68"/>
+    </row>
+    <row r="31" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D31" s="49"/>
+      <c r="E31" s="179"/>
+      <c r="F31" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31" s="103"/>
+      <c r="H31" s="111"/>
+      <c r="I31" s="118"/>
+      <c r="J31" s="74"/>
+      <c r="K31" s="113"/>
+      <c r="L31" s="97"/>
+      <c r="M31" s="67"/>
+      <c r="N31" s="64"/>
+      <c r="O31" s="69"/>
+      <c r="P31" s="54"/>
+      <c r="Q31" s="65"/>
+      <c r="R31" s="65"/>
+      <c r="S31" s="199"/>
+      <c r="T31" s="97"/>
+      <c r="U31" s="65"/>
+      <c r="V31" s="65"/>
+      <c r="W31" s="68"/>
+    </row>
+    <row r="32" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D32" s="49"/>
+      <c r="E32" s="179"/>
+      <c r="F32" s="87" t="s">
+        <v>114</v>
+      </c>
+      <c r="G32" s="94"/>
+      <c r="H32" s="63"/>
+      <c r="I32" s="167" t="s">
+        <v>67</v>
+      </c>
+      <c r="J32" s="168"/>
+      <c r="K32" s="290"/>
+      <c r="L32" s="97"/>
+      <c r="M32" s="67"/>
+      <c r="N32" s="64"/>
+      <c r="O32" s="69"/>
+      <c r="P32" s="54"/>
+      <c r="Q32" s="65"/>
+      <c r="R32" s="65"/>
+      <c r="S32" s="199"/>
+      <c r="T32" s="97"/>
+      <c r="U32" s="65"/>
+      <c r="V32" s="65"/>
+      <c r="W32" s="68"/>
+    </row>
+    <row r="33" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D33" s="49"/>
+      <c r="E33" s="179"/>
+      <c r="F33" s="86" t="s">
+        <v>77</v>
+      </c>
+      <c r="G33" s="94"/>
+      <c r="H33" s="113"/>
+      <c r="I33" s="119"/>
+      <c r="J33" s="69"/>
+      <c r="K33" s="290"/>
+      <c r="L33" s="97"/>
+      <c r="M33" s="67"/>
+      <c r="N33" s="64"/>
+      <c r="O33" s="69"/>
+      <c r="P33" s="54"/>
+      <c r="Q33" s="65"/>
+      <c r="R33" s="65"/>
+      <c r="S33" s="199"/>
+      <c r="T33" s="97"/>
+      <c r="U33" s="65"/>
+      <c r="V33" s="65"/>
+      <c r="W33" s="68"/>
+    </row>
+    <row r="34" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D34" s="49"/>
+      <c r="E34" s="179"/>
+      <c r="F34" s="86" t="s">
+        <v>75</v>
+      </c>
+      <c r="G34" s="94"/>
+      <c r="H34" s="113"/>
+      <c r="I34" s="94"/>
+      <c r="J34" s="120"/>
+      <c r="K34" s="290"/>
+      <c r="L34" s="97"/>
+      <c r="M34" s="67"/>
+      <c r="N34" s="64"/>
+      <c r="O34" s="69"/>
+      <c r="P34" s="54"/>
+      <c r="Q34" s="65"/>
+      <c r="R34" s="65"/>
+      <c r="S34" s="199"/>
+      <c r="T34" s="97"/>
+      <c r="U34" s="65"/>
+      <c r="V34" s="65"/>
+      <c r="W34" s="68"/>
+    </row>
+    <row r="35" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D35" s="49"/>
+      <c r="E35" s="179"/>
+      <c r="F35" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="G35" s="94"/>
+      <c r="H35" s="113"/>
+      <c r="I35" s="94"/>
+      <c r="J35" s="120"/>
+      <c r="K35" s="186"/>
+      <c r="L35" s="97"/>
+      <c r="M35" s="67"/>
+      <c r="N35" s="64"/>
+      <c r="O35" s="69"/>
+      <c r="P35" s="54"/>
+      <c r="Q35" s="65"/>
+      <c r="R35" s="65"/>
+      <c r="S35" s="199"/>
+      <c r="T35" s="97"/>
+      <c r="U35" s="65"/>
+      <c r="V35" s="65"/>
+      <c r="W35" s="68"/>
+    </row>
+    <row r="36" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D36" s="49"/>
+      <c r="E36" s="179"/>
+      <c r="F36" s="181" t="s">
+        <v>76</v>
+      </c>
+      <c r="G36" s="94"/>
+      <c r="H36" s="113"/>
+      <c r="I36" s="95"/>
+      <c r="J36" s="121"/>
+      <c r="K36" s="291" t="s">
+        <v>95</v>
+      </c>
+      <c r="L36" s="253"/>
+      <c r="M36" s="67"/>
+      <c r="N36" s="64"/>
+      <c r="O36" s="69"/>
+      <c r="P36" s="54"/>
+      <c r="Q36" s="65"/>
+      <c r="R36" s="65"/>
+      <c r="S36" s="199"/>
+      <c r="T36" s="97"/>
+      <c r="U36" s="65"/>
+      <c r="V36" s="65"/>
+      <c r="W36" s="68"/>
+    </row>
+    <row r="37" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D37" s="49"/>
+      <c r="E37" s="180"/>
+      <c r="F37" s="213" t="s">
+        <v>111</v>
+      </c>
+      <c r="G37" s="95"/>
+      <c r="H37" s="70"/>
+      <c r="I37" s="212"/>
+      <c r="J37" s="207"/>
+      <c r="K37" s="111"/>
+      <c r="L37" s="254"/>
+      <c r="M37" s="80"/>
+      <c r="N37" s="70"/>
+      <c r="O37" s="73"/>
+      <c r="P37" s="208"/>
+      <c r="Q37" s="72"/>
+      <c r="R37" s="72"/>
+      <c r="S37" s="248"/>
+      <c r="T37" s="98"/>
+      <c r="U37" s="72"/>
+      <c r="V37" s="72"/>
+      <c r="W37" s="83"/>
+    </row>
+    <row r="38" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D38" s="49"/>
+      <c r="E38" s="169" t="s">
+        <v>47</v>
+      </c>
+      <c r="F38" s="85" t="s">
+        <v>83</v>
+      </c>
+      <c r="G38" s="60"/>
+      <c r="H38" s="59"/>
+      <c r="I38" s="59"/>
+      <c r="J38" s="112"/>
+      <c r="K38" s="115" t="s">
+        <v>47</v>
+      </c>
+      <c r="L38" s="252"/>
+      <c r="M38" s="61"/>
+      <c r="N38" s="59"/>
+      <c r="O38" s="58"/>
+      <c r="P38" s="250"/>
+      <c r="Q38" s="79"/>
+      <c r="R38" s="79"/>
+      <c r="S38" s="198"/>
+      <c r="T38" s="96"/>
+      <c r="U38" s="79"/>
+      <c r="V38" s="79"/>
+      <c r="W38" s="82"/>
+    </row>
+    <row r="39" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D39" s="49"/>
+      <c r="E39" s="170"/>
+      <c r="F39" s="86" t="s">
+        <v>79</v>
+      </c>
+      <c r="G39" s="94"/>
+      <c r="H39" s="64"/>
+      <c r="I39" s="64"/>
+      <c r="J39" s="113"/>
+      <c r="K39" s="215"/>
+      <c r="L39" s="253"/>
+      <c r="M39" s="67"/>
+      <c r="N39" s="64"/>
+      <c r="O39" s="69"/>
+      <c r="P39" s="54"/>
+      <c r="Q39" s="65"/>
+      <c r="R39" s="65"/>
+      <c r="S39" s="199"/>
+      <c r="T39" s="97"/>
+      <c r="U39" s="65"/>
+      <c r="V39" s="65"/>
+      <c r="W39" s="68"/>
+    </row>
+    <row r="40" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D40" s="49"/>
+      <c r="E40" s="171"/>
+      <c r="F40" s="90" t="s">
+        <v>78</v>
+      </c>
+      <c r="G40" s="95"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="114"/>
+      <c r="K40" s="216"/>
+      <c r="L40" s="276"/>
+      <c r="M40" s="80"/>
+      <c r="N40" s="70"/>
+      <c r="O40" s="73"/>
+      <c r="P40" s="208"/>
+      <c r="Q40" s="72"/>
+      <c r="R40" s="72"/>
+      <c r="S40" s="248"/>
+      <c r="T40" s="98"/>
+      <c r="U40" s="72"/>
+      <c r="V40" s="72"/>
+      <c r="W40" s="83"/>
+    </row>
+    <row r="41" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="D41" s="49"/>
+      <c r="E41" s="169" t="s">
+        <v>82</v>
+      </c>
+      <c r="F41" s="85" t="s">
+        <v>84</v>
+      </c>
+      <c r="G41" s="60"/>
+      <c r="H41" s="59"/>
+      <c r="I41" s="59"/>
+      <c r="J41" s="59"/>
+      <c r="K41" s="243"/>
+      <c r="L41" s="115" t="s">
+        <v>106</v>
+      </c>
+      <c r="M41" s="116"/>
+      <c r="N41" s="59"/>
+      <c r="O41" s="58"/>
+      <c r="P41" s="250"/>
+      <c r="Q41" s="79"/>
+      <c r="R41" s="79"/>
+      <c r="S41" s="198"/>
+      <c r="T41" s="96"/>
+      <c r="U41" s="79"/>
+      <c r="V41" s="79"/>
+      <c r="W41" s="82"/>
+    </row>
+    <row r="42" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D42" s="49"/>
+      <c r="E42" s="170"/>
+      <c r="F42" s="86" t="s">
+        <v>85</v>
+      </c>
+      <c r="G42" s="94"/>
+      <c r="H42" s="64"/>
+      <c r="I42" s="64"/>
+      <c r="J42" s="64"/>
+      <c r="K42" s="113"/>
+      <c r="L42" s="283" t="s">
+        <v>105</v>
+      </c>
+      <c r="M42" s="289"/>
+      <c r="N42" s="64"/>
+      <c r="O42" s="69"/>
+      <c r="P42" s="54"/>
+      <c r="Q42" s="65"/>
+      <c r="R42" s="65"/>
+      <c r="S42" s="199"/>
+      <c r="T42" s="97"/>
+      <c r="U42" s="65"/>
+      <c r="V42" s="65"/>
+      <c r="W42" s="68"/>
+    </row>
+    <row r="43" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D43" s="49"/>
+      <c r="E43" s="170"/>
+      <c r="F43" s="86" t="s">
+        <v>88</v>
+      </c>
+      <c r="G43" s="94"/>
+      <c r="H43" s="64"/>
+      <c r="I43" s="64"/>
+      <c r="J43" s="64"/>
+      <c r="K43" s="113"/>
+      <c r="L43" s="192" t="s">
+        <v>104</v>
+      </c>
+      <c r="M43" s="289"/>
+      <c r="N43" s="64"/>
+      <c r="O43" s="69"/>
+      <c r="P43" s="54"/>
+      <c r="Q43" s="65"/>
+      <c r="R43" s="65"/>
+      <c r="S43" s="199"/>
+      <c r="T43" s="97"/>
+      <c r="U43" s="65"/>
+      <c r="V43" s="65"/>
+      <c r="W43" s="68"/>
+      <c r="X43" s="115" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D44" s="49"/>
+      <c r="E44" s="171"/>
+      <c r="F44" s="90" t="s">
+        <v>89</v>
+      </c>
+      <c r="G44" s="95"/>
+      <c r="H44" s="70"/>
+      <c r="I44" s="70"/>
+      <c r="J44" s="70"/>
+      <c r="K44" s="114"/>
+      <c r="L44" s="206"/>
+      <c r="M44" s="71"/>
+      <c r="N44" s="72"/>
+      <c r="O44" s="73"/>
+      <c r="P44" s="208"/>
+      <c r="Q44" s="72"/>
+      <c r="R44" s="72"/>
+      <c r="S44" s="248"/>
+      <c r="T44" s="98"/>
+      <c r="U44" s="72"/>
+      <c r="V44" s="72"/>
+      <c r="W44" s="83"/>
+      <c r="X44" s="192" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="45" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D45" s="122"/>
+      <c r="F45" s="123"/>
+      <c r="G45" s="240" t="s">
+        <v>0</v>
+      </c>
+      <c r="H45" s="241"/>
+      <c r="I45" s="241"/>
+      <c r="J45" s="241"/>
+      <c r="K45" s="244"/>
+      <c r="L45" s="240" t="s">
+        <v>1</v>
+      </c>
+      <c r="M45" s="241"/>
+      <c r="N45" s="241"/>
+      <c r="O45" s="242"/>
+      <c r="P45" s="251" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q45" s="241"/>
+      <c r="R45" s="241"/>
+      <c r="S45" s="244"/>
+      <c r="T45" s="194" t="s">
+        <v>13</v>
+      </c>
+      <c r="U45" s="195"/>
+      <c r="V45" s="195"/>
+      <c r="W45" s="196"/>
+    </row>
+    <row r="46" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D46" s="63"/>
+      <c r="E46" s="124"/>
+      <c r="F46" s="125" t="s">
+        <v>87</v>
+      </c>
+      <c r="G46" s="126" t="s">
+        <v>2</v>
+      </c>
+      <c r="H46" s="127" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="127" t="s">
+        <v>4</v>
+      </c>
+      <c r="J46" s="127" t="s">
+        <v>5</v>
+      </c>
+      <c r="K46" s="201" t="s">
+        <v>6</v>
+      </c>
+      <c r="L46" s="126" t="s">
+        <v>2</v>
+      </c>
+      <c r="M46" s="129" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="127" t="s">
+        <v>7</v>
+      </c>
+      <c r="O46" s="128" t="s">
+        <v>8</v>
+      </c>
+      <c r="P46" s="209" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q46" s="127" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="127" t="s">
+        <v>4</v>
+      </c>
+      <c r="S46" s="201" t="s">
+        <v>5</v>
+      </c>
+      <c r="T46" s="262" t="s">
+        <v>2</v>
+      </c>
+      <c r="U46" s="233" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="233" t="s">
+        <v>4</v>
+      </c>
+      <c r="W46" s="263" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="4:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E47" s="188" t="s">
+        <v>94</v>
+      </c>
+      <c r="F47" s="85" t="s">
+        <v>49</v>
+      </c>
+      <c r="G47" s="235"/>
+      <c r="H47" s="236"/>
+      <c r="I47" s="236"/>
+      <c r="J47" s="236"/>
+      <c r="K47" s="245"/>
+      <c r="L47" s="57" t="s">
+        <v>129</v>
+      </c>
+      <c r="M47" s="285"/>
+      <c r="N47" s="236"/>
+      <c r="O47" s="256"/>
+      <c r="P47" s="252"/>
+      <c r="Q47" s="79"/>
+      <c r="R47" s="79"/>
+      <c r="S47" s="198"/>
+      <c r="T47" s="96"/>
+      <c r="U47" s="79"/>
+      <c r="V47" s="79"/>
+      <c r="W47" s="82"/>
+    </row>
+    <row r="48" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E48" s="189"/>
+      <c r="F48" s="187" t="s">
+        <v>100</v>
+      </c>
+      <c r="G48" s="237"/>
+      <c r="H48" s="226"/>
+      <c r="I48" s="226"/>
+      <c r="J48" s="226"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="99"/>
+      <c r="M48" s="286"/>
+      <c r="N48" s="226"/>
+      <c r="O48" s="257"/>
+      <c r="P48" s="253"/>
+      <c r="Q48" s="65"/>
+      <c r="R48" s="65"/>
+      <c r="S48" s="199"/>
+      <c r="T48" s="97"/>
+      <c r="U48" s="65"/>
+      <c r="V48" s="65"/>
+      <c r="W48" s="68"/>
+    </row>
+    <row r="49" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E49" s="189"/>
+      <c r="F49" s="187" t="s">
+        <v>103</v>
+      </c>
+      <c r="G49" s="237"/>
+      <c r="H49" s="226"/>
+      <c r="I49" s="226"/>
+      <c r="J49" s="226"/>
+      <c r="K49" s="246"/>
+      <c r="L49" s="99"/>
+      <c r="M49" s="286"/>
+      <c r="N49" s="226"/>
+      <c r="O49" s="257"/>
+      <c r="P49" s="253"/>
+      <c r="Q49" s="65"/>
+      <c r="R49" s="65"/>
+      <c r="S49" s="199"/>
+      <c r="T49" s="97"/>
+      <c r="U49" s="65"/>
+      <c r="V49" s="65"/>
+      <c r="W49" s="68"/>
+    </row>
+    <row r="50" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E50" s="189"/>
+      <c r="F50" s="187" t="s">
+        <v>99</v>
+      </c>
+      <c r="G50" s="237"/>
+      <c r="H50" s="226"/>
+      <c r="I50" s="226"/>
+      <c r="J50" s="226"/>
+      <c r="K50" s="246"/>
+      <c r="L50" s="100"/>
+      <c r="M50" s="286"/>
+      <c r="N50" s="226"/>
+      <c r="O50" s="257"/>
+      <c r="P50" s="253"/>
+      <c r="Q50" s="65"/>
+      <c r="R50" s="65"/>
+      <c r="S50" s="199"/>
+      <c r="T50" s="97"/>
+      <c r="U50" s="65"/>
+      <c r="V50" s="65"/>
+      <c r="W50" s="68"/>
+    </row>
+    <row r="51" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E51" s="190"/>
+      <c r="F51" s="89" t="s">
+        <v>57</v>
+      </c>
+      <c r="G51" s="238"/>
+      <c r="H51" s="239"/>
+      <c r="I51" s="239"/>
+      <c r="J51" s="239"/>
+      <c r="K51" s="247"/>
+      <c r="L51" s="193"/>
+      <c r="M51" s="287"/>
+      <c r="N51" s="230"/>
+      <c r="O51" s="278"/>
+      <c r="P51" s="254"/>
+      <c r="Q51" s="72"/>
+      <c r="R51" s="72"/>
+      <c r="S51" s="248"/>
+      <c r="T51" s="182"/>
+      <c r="U51" s="183"/>
+      <c r="V51" s="183"/>
+      <c r="W51" s="184"/>
+    </row>
+    <row r="52" spans="5:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E52" s="178" t="s">
+        <v>62</v>
+      </c>
+      <c r="F52" s="85" t="s">
+        <v>66</v>
+      </c>
+      <c r="G52" s="96"/>
+      <c r="H52" s="79"/>
+      <c r="I52" s="79"/>
+      <c r="J52" s="79"/>
+      <c r="K52" s="198"/>
+      <c r="L52" s="96"/>
+      <c r="M52" s="264"/>
+      <c r="N52" s="167" t="s">
+        <v>17</v>
+      </c>
+      <c r="O52" s="168"/>
+      <c r="P52" s="211"/>
+      <c r="Q52" s="79"/>
+      <c r="R52" s="79"/>
+      <c r="S52" s="198"/>
+      <c r="T52" s="96"/>
+      <c r="U52" s="79"/>
+      <c r="V52" s="79"/>
+      <c r="W52" s="82"/>
+    </row>
+    <row r="53" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E53" s="179"/>
+      <c r="F53" s="86" t="s">
+        <v>119</v>
+      </c>
+      <c r="G53" s="97"/>
+      <c r="H53" s="65"/>
+      <c r="I53" s="65"/>
+      <c r="J53" s="65"/>
+      <c r="K53" s="199"/>
+      <c r="L53" s="97"/>
+      <c r="M53" s="265"/>
+      <c r="N53" s="104"/>
+      <c r="O53" s="68"/>
+      <c r="P53" s="253"/>
+      <c r="Q53" s="65"/>
+      <c r="R53" s="65"/>
+      <c r="S53" s="199"/>
+      <c r="T53" s="97"/>
+      <c r="U53" s="65"/>
+      <c r="V53" s="65"/>
+      <c r="W53" s="68"/>
+    </row>
+    <row r="54" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E54" s="179"/>
+      <c r="F54" s="181" t="s">
+        <v>120</v>
+      </c>
+      <c r="G54" s="97"/>
+      <c r="H54" s="65"/>
+      <c r="I54" s="65"/>
+      <c r="J54" s="65"/>
+      <c r="K54" s="199"/>
+      <c r="L54" s="97"/>
+      <c r="M54" s="265"/>
+      <c r="N54" s="98"/>
+      <c r="O54" s="284"/>
+      <c r="P54" s="276"/>
+      <c r="Q54" s="183"/>
+      <c r="R54" s="65"/>
+      <c r="S54" s="199"/>
+      <c r="T54" s="97"/>
+      <c r="U54" s="65"/>
+      <c r="V54" s="65"/>
+      <c r="W54" s="68"/>
+    </row>
+    <row r="55" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E55" s="179"/>
+      <c r="F55" s="220" t="s">
+        <v>93</v>
+      </c>
+      <c r="G55" s="97"/>
+      <c r="H55" s="65"/>
+      <c r="I55" s="65"/>
+      <c r="J55" s="65"/>
+      <c r="K55" s="199"/>
+      <c r="L55" s="97"/>
+      <c r="M55" s="66"/>
+      <c r="N55" s="232"/>
+      <c r="O55" s="282"/>
+      <c r="P55" s="167" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q55" s="168"/>
+      <c r="R55" s="253"/>
+      <c r="S55" s="199"/>
+      <c r="T55" s="97"/>
+      <c r="U55" s="65"/>
+      <c r="V55" s="65"/>
+      <c r="W55" s="68"/>
+    </row>
+    <row r="56" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E56" s="179"/>
+      <c r="F56" s="219" t="s">
+        <v>109</v>
+      </c>
+      <c r="G56" s="97"/>
+      <c r="H56" s="65"/>
+      <c r="I56" s="65"/>
+      <c r="J56" s="65"/>
+      <c r="K56" s="199"/>
+      <c r="L56" s="97"/>
+      <c r="M56" s="66"/>
+      <c r="N56" s="65"/>
+      <c r="O56" s="271"/>
+      <c r="P56" s="104"/>
+      <c r="Q56" s="68"/>
+      <c r="R56" s="253"/>
+      <c r="S56" s="199"/>
+      <c r="T56" s="97"/>
+      <c r="U56" s="65"/>
+      <c r="V56" s="65"/>
+      <c r="W56" s="68"/>
+    </row>
+    <row r="57" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E57" s="180"/>
+      <c r="F57" s="213" t="s">
+        <v>111</v>
+      </c>
+      <c r="G57" s="98"/>
+      <c r="H57" s="72"/>
+      <c r="I57" s="72"/>
+      <c r="J57" s="72"/>
+      <c r="K57" s="248"/>
+      <c r="L57" s="98"/>
+      <c r="M57" s="71"/>
+      <c r="N57" s="183"/>
+      <c r="O57" s="277"/>
+      <c r="P57" s="98"/>
+      <c r="Q57" s="284"/>
+      <c r="R57" s="254"/>
+      <c r="S57" s="248"/>
+      <c r="T57" s="98"/>
+      <c r="U57" s="72"/>
+      <c r="V57" s="72"/>
+      <c r="W57" s="83"/>
+    </row>
+    <row r="58" spans="5:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E58" s="178" t="s">
+        <v>91</v>
+      </c>
+      <c r="F58" s="221" t="s">
+        <v>71</v>
+      </c>
+      <c r="G58" s="96"/>
+      <c r="H58" s="79"/>
+      <c r="I58" s="79"/>
+      <c r="J58" s="79"/>
+      <c r="K58" s="198"/>
+      <c r="L58" s="96"/>
+      <c r="M58" s="264"/>
+      <c r="N58" s="167" t="s">
+        <v>51</v>
+      </c>
+      <c r="O58" s="168"/>
+      <c r="P58" s="281"/>
+      <c r="Q58" s="228"/>
+      <c r="R58" s="79"/>
+      <c r="S58" s="198"/>
+      <c r="T58" s="96"/>
+      <c r="U58" s="79"/>
+      <c r="V58" s="79"/>
+      <c r="W58" s="82"/>
+    </row>
+    <row r="59" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E59" s="179"/>
+      <c r="F59" s="222" t="s">
+        <v>101</v>
+      </c>
+      <c r="G59" s="97"/>
+      <c r="H59" s="65"/>
+      <c r="I59" s="65"/>
+      <c r="J59" s="65"/>
+      <c r="K59" s="199"/>
+      <c r="L59" s="97"/>
+      <c r="M59" s="265"/>
+      <c r="N59" s="106"/>
+      <c r="O59" s="68"/>
+      <c r="P59" s="276"/>
+      <c r="Q59" s="183"/>
+      <c r="R59" s="65"/>
+      <c r="S59" s="199"/>
+      <c r="T59" s="97"/>
+      <c r="U59" s="65"/>
+      <c r="V59" s="65"/>
+      <c r="W59" s="68"/>
+    </row>
+    <row r="60" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E60" s="179"/>
+      <c r="F60" s="222" t="s">
+        <v>102</v>
+      </c>
+      <c r="G60" s="97"/>
+      <c r="H60" s="65"/>
+      <c r="I60" s="65"/>
+      <c r="J60" s="65"/>
+      <c r="K60" s="199"/>
+      <c r="L60" s="97"/>
+      <c r="M60" s="265"/>
+      <c r="N60" s="98"/>
+      <c r="O60" s="107"/>
+      <c r="P60" s="167" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q60" s="168"/>
+      <c r="R60" s="253"/>
+      <c r="S60" s="199"/>
+      <c r="T60" s="97"/>
+      <c r="U60" s="65"/>
+      <c r="V60" s="65"/>
+      <c r="W60" s="68"/>
+    </row>
+    <row r="61" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E61" s="179"/>
+      <c r="F61" s="181" t="s">
+        <v>125</v>
+      </c>
+      <c r="G61" s="97"/>
+      <c r="H61" s="65"/>
+      <c r="I61" s="65"/>
+      <c r="J61" s="65"/>
+      <c r="K61" s="199"/>
+      <c r="L61" s="97"/>
+      <c r="M61" s="265"/>
+      <c r="N61" s="295"/>
+      <c r="O61" s="280"/>
+      <c r="P61" s="106"/>
+      <c r="Q61" s="294"/>
+      <c r="R61" s="253"/>
+      <c r="S61" s="199"/>
+      <c r="T61" s="97"/>
+      <c r="U61" s="65"/>
+      <c r="V61" s="65"/>
+      <c r="W61" s="68"/>
+    </row>
+    <row r="62" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E62" s="179"/>
+      <c r="F62" s="219" t="s">
+        <v>108</v>
+      </c>
+      <c r="G62" s="97"/>
+      <c r="H62" s="65"/>
+      <c r="I62" s="65"/>
+      <c r="J62" s="65"/>
+      <c r="K62" s="199"/>
+      <c r="L62" s="97"/>
+      <c r="M62" s="66"/>
+      <c r="N62" s="228"/>
+      <c r="O62" s="63"/>
+      <c r="P62" s="106"/>
+      <c r="Q62" s="68"/>
+      <c r="R62" s="253"/>
+      <c r="S62" s="199"/>
+      <c r="T62" s="97"/>
+      <c r="U62" s="65"/>
+      <c r="V62" s="65"/>
+      <c r="W62" s="68"/>
+    </row>
+    <row r="63" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E63" s="180"/>
+      <c r="F63" s="213" t="s">
+        <v>111</v>
+      </c>
+      <c r="G63" s="98"/>
+      <c r="H63" s="72"/>
+      <c r="I63" s="72"/>
+      <c r="J63" s="72"/>
+      <c r="K63" s="248"/>
+      <c r="L63" s="98"/>
+      <c r="M63" s="71"/>
+      <c r="N63" s="183"/>
+      <c r="O63" s="200"/>
+      <c r="P63" s="98"/>
+      <c r="Q63" s="107"/>
+      <c r="R63" s="254"/>
+      <c r="S63" s="248"/>
+      <c r="T63" s="98"/>
+      <c r="U63" s="72"/>
+      <c r="V63" s="72"/>
+      <c r="W63" s="83"/>
+    </row>
+    <row r="64" spans="5:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E64" s="178" t="s">
+        <v>92</v>
+      </c>
+      <c r="F64" s="85" t="s">
+        <v>136</v>
+      </c>
+      <c r="G64" s="60"/>
+      <c r="H64" s="79"/>
+      <c r="I64" s="79"/>
+      <c r="J64" s="59"/>
+      <c r="K64" s="112"/>
+      <c r="L64" s="60"/>
+      <c r="M64" s="264"/>
+      <c r="N64" s="167" t="s">
+        <v>52</v>
+      </c>
+      <c r="O64" s="168"/>
+      <c r="P64" s="281"/>
+      <c r="Q64" s="228"/>
+      <c r="R64" s="79"/>
+      <c r="S64" s="198"/>
+      <c r="T64" s="96"/>
+      <c r="U64" s="79"/>
+      <c r="V64" s="79"/>
+      <c r="W64" s="82"/>
+    </row>
+    <row r="65" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E65" s="179"/>
+      <c r="F65" s="86" t="s">
+        <v>117</v>
+      </c>
+      <c r="G65" s="94"/>
+      <c r="H65" s="65"/>
+      <c r="I65" s="65"/>
+      <c r="J65" s="64"/>
+      <c r="K65" s="113"/>
+      <c r="L65" s="94"/>
+      <c r="M65" s="265"/>
+      <c r="N65" s="108"/>
+      <c r="O65" s="68"/>
+      <c r="P65" s="253"/>
+      <c r="Q65" s="65"/>
+      <c r="R65" s="65"/>
+      <c r="S65" s="199"/>
+      <c r="T65" s="97"/>
+      <c r="U65" s="65"/>
+      <c r="V65" s="65"/>
+      <c r="W65" s="68"/>
+    </row>
+    <row r="66" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E66" s="179"/>
+      <c r="F66" s="86" t="s">
+        <v>118</v>
+      </c>
+      <c r="G66" s="94"/>
+      <c r="H66" s="65"/>
+      <c r="I66" s="65"/>
+      <c r="J66" s="64"/>
+      <c r="K66" s="199"/>
+      <c r="L66" s="94"/>
+      <c r="M66" s="265"/>
+      <c r="N66" s="98"/>
+      <c r="O66" s="109"/>
+      <c r="P66" s="276"/>
+      <c r="Q66" s="183"/>
+      <c r="R66" s="65"/>
+      <c r="S66" s="199"/>
+      <c r="T66" s="97"/>
+      <c r="U66" s="65"/>
+      <c r="V66" s="65"/>
+      <c r="W66" s="68"/>
+    </row>
+    <row r="67" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E67" s="179"/>
+      <c r="F67" s="87" t="s">
+        <v>110</v>
+      </c>
+      <c r="G67" s="94"/>
+      <c r="H67" s="65"/>
+      <c r="I67" s="65"/>
+      <c r="J67" s="64"/>
+      <c r="K67" s="199"/>
+      <c r="L67" s="94"/>
+      <c r="M67" s="66"/>
+      <c r="N67" s="228"/>
+      <c r="O67" s="280"/>
+      <c r="P67" s="167" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q67" s="168"/>
+      <c r="R67" s="253"/>
+      <c r="S67" s="199"/>
+      <c r="T67" s="97"/>
+      <c r="U67" s="65"/>
+      <c r="V67" s="65"/>
+      <c r="W67" s="68"/>
+    </row>
+    <row r="68" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E68" s="179"/>
+      <c r="F68" s="181" t="s">
+        <v>125</v>
+      </c>
+      <c r="G68" s="94"/>
+      <c r="H68" s="65"/>
+      <c r="I68" s="65"/>
+      <c r="J68" s="64"/>
+      <c r="K68" s="199"/>
+      <c r="L68" s="94"/>
+      <c r="M68" s="66"/>
+      <c r="N68" s="228"/>
+      <c r="O68" s="280"/>
+      <c r="P68" s="108"/>
+      <c r="Q68" s="294"/>
+      <c r="R68" s="253"/>
+      <c r="S68" s="199"/>
+      <c r="T68" s="97"/>
+      <c r="U68" s="65"/>
+      <c r="V68" s="65"/>
+      <c r="W68" s="68"/>
+    </row>
+    <row r="69" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E69" s="179"/>
+      <c r="F69" s="181" t="s">
+        <v>122</v>
+      </c>
+      <c r="G69" s="94"/>
+      <c r="H69" s="65"/>
+      <c r="I69" s="65"/>
+      <c r="J69" s="64"/>
+      <c r="K69" s="199"/>
+      <c r="L69" s="94"/>
+      <c r="M69" s="66"/>
+      <c r="N69" s="64"/>
+      <c r="O69" s="266"/>
+      <c r="P69" s="108"/>
+      <c r="Q69" s="68"/>
+      <c r="R69" s="253"/>
+      <c r="S69" s="199"/>
+      <c r="T69" s="97"/>
+      <c r="U69" s="65"/>
+      <c r="V69" s="65"/>
+      <c r="W69" s="68"/>
+    </row>
+    <row r="70" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E70" s="179"/>
+      <c r="F70" s="213" t="s">
+        <v>111</v>
+      </c>
+      <c r="G70" s="95"/>
+      <c r="H70" s="72"/>
+      <c r="I70" s="72"/>
+      <c r="J70" s="70"/>
+      <c r="K70" s="248"/>
+      <c r="L70" s="95"/>
+      <c r="M70" s="71"/>
+      <c r="N70" s="74"/>
+      <c r="O70" s="275"/>
+      <c r="P70" s="98"/>
+      <c r="Q70" s="109"/>
+      <c r="R70" s="254"/>
+      <c r="S70" s="248"/>
+      <c r="T70" s="98"/>
+      <c r="U70" s="72"/>
+      <c r="V70" s="72"/>
+      <c r="W70" s="83"/>
+    </row>
+    <row r="71" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E71" s="178" t="s">
+        <v>113</v>
+      </c>
+      <c r="F71" s="85" t="s">
+        <v>114</v>
+      </c>
+      <c r="G71" s="60"/>
+      <c r="H71" s="79"/>
+      <c r="I71" s="79"/>
+      <c r="J71" s="59"/>
+      <c r="K71" s="198"/>
+      <c r="L71" s="60"/>
+      <c r="M71" s="264"/>
+      <c r="N71" s="167" t="s">
+        <v>67</v>
+      </c>
+      <c r="O71" s="168"/>
+      <c r="P71" s="272"/>
+      <c r="Q71" s="228"/>
+      <c r="R71" s="79"/>
+      <c r="S71" s="198"/>
+      <c r="T71" s="96"/>
+      <c r="U71" s="79"/>
+      <c r="V71" s="79"/>
+      <c r="W71" s="82"/>
+    </row>
+    <row r="72" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E72" s="179"/>
+      <c r="F72" s="86" t="s">
+        <v>107</v>
+      </c>
+      <c r="G72" s="94"/>
+      <c r="H72" s="65"/>
+      <c r="I72" s="65"/>
+      <c r="J72" s="64"/>
+      <c r="K72" s="199"/>
+      <c r="L72" s="94"/>
+      <c r="M72" s="265"/>
+      <c r="N72" s="217"/>
+      <c r="O72" s="68"/>
+      <c r="P72" s="253"/>
+      <c r="Q72" s="65"/>
+      <c r="R72" s="65"/>
+      <c r="S72" s="199"/>
+      <c r="T72" s="97"/>
+      <c r="U72" s="65"/>
+      <c r="V72" s="65"/>
+      <c r="W72" s="68"/>
+    </row>
+    <row r="73" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E73" s="179"/>
+      <c r="F73" s="86" t="s">
+        <v>121</v>
+      </c>
+      <c r="G73" s="94"/>
+      <c r="H73" s="65"/>
+      <c r="I73" s="65"/>
+      <c r="J73" s="64"/>
+      <c r="K73" s="199"/>
+      <c r="L73" s="94"/>
+      <c r="M73" s="265"/>
+      <c r="N73" s="98"/>
+      <c r="O73" s="218"/>
+      <c r="P73" s="276"/>
+      <c r="Q73" s="183"/>
+      <c r="R73" s="65"/>
+      <c r="S73" s="199"/>
+      <c r="T73" s="97"/>
+      <c r="U73" s="65"/>
+      <c r="V73" s="65"/>
+      <c r="W73" s="68"/>
+    </row>
+    <row r="74" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E74" s="179"/>
+      <c r="F74" s="87" t="s">
+        <v>110</v>
+      </c>
+      <c r="G74" s="94"/>
+      <c r="H74" s="65"/>
+      <c r="I74" s="65"/>
+      <c r="J74" s="64"/>
+      <c r="K74" s="199"/>
+      <c r="L74" s="94"/>
+      <c r="M74" s="66"/>
+      <c r="N74" s="227"/>
+      <c r="O74" s="279"/>
+      <c r="P74" s="167" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q74" s="168"/>
+      <c r="R74" s="253"/>
+      <c r="S74" s="199"/>
+      <c r="T74" s="97"/>
+      <c r="U74" s="65"/>
+      <c r="V74" s="65"/>
+      <c r="W74" s="68"/>
+    </row>
+    <row r="75" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E75" s="179"/>
+      <c r="F75" s="181" t="s">
+        <v>125</v>
+      </c>
+      <c r="G75" s="94"/>
+      <c r="H75" s="65"/>
+      <c r="I75" s="65"/>
+      <c r="J75" s="64"/>
+      <c r="K75" s="199"/>
+      <c r="L75" s="94"/>
+      <c r="M75" s="66"/>
+      <c r="N75" s="227"/>
+      <c r="O75" s="279"/>
+      <c r="P75" s="217"/>
+      <c r="Q75" s="294"/>
+      <c r="R75" s="253"/>
+      <c r="S75" s="199"/>
+      <c r="T75" s="97"/>
+      <c r="U75" s="65"/>
+      <c r="V75" s="65"/>
+      <c r="W75" s="68"/>
+    </row>
+    <row r="76" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E76" s="179"/>
+      <c r="F76" s="181" t="s">
+        <v>123</v>
+      </c>
+      <c r="G76" s="94"/>
+      <c r="H76" s="65"/>
+      <c r="I76" s="65"/>
+      <c r="J76" s="64"/>
+      <c r="K76" s="199"/>
+      <c r="L76" s="94"/>
+      <c r="M76" s="66"/>
+      <c r="N76" s="64"/>
+      <c r="O76" s="266"/>
+      <c r="P76" s="217"/>
+      <c r="Q76" s="68"/>
+      <c r="R76" s="253"/>
+      <c r="S76" s="199"/>
+      <c r="T76" s="97"/>
+      <c r="U76" s="65"/>
+      <c r="V76" s="65"/>
+      <c r="W76" s="68"/>
+    </row>
+    <row r="77" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E77" s="180"/>
+      <c r="F77" s="214" t="s">
+        <v>111</v>
+      </c>
+      <c r="G77" s="95"/>
+      <c r="H77" s="72"/>
+      <c r="I77" s="72"/>
+      <c r="J77" s="70"/>
+      <c r="K77" s="248"/>
+      <c r="L77" s="95"/>
+      <c r="M77" s="71"/>
+      <c r="N77" s="70"/>
+      <c r="O77" s="267"/>
+      <c r="P77" s="98"/>
+      <c r="Q77" s="218"/>
+      <c r="R77" s="254"/>
+      <c r="S77" s="248"/>
+      <c r="T77" s="98"/>
+      <c r="U77" s="72"/>
+      <c r="V77" s="72"/>
+      <c r="W77" s="83"/>
+    </row>
+    <row r="78" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E78" s="169" t="s">
+        <v>47</v>
+      </c>
+      <c r="F78" s="85" t="s">
+        <v>83</v>
+      </c>
+      <c r="G78" s="56"/>
+      <c r="H78" s="227"/>
+      <c r="I78" s="227"/>
+      <c r="J78" s="227"/>
+      <c r="K78" s="243"/>
+      <c r="L78" s="261"/>
+      <c r="M78" s="229"/>
+      <c r="N78" s="227"/>
+      <c r="O78" s="255"/>
+      <c r="P78" s="268"/>
+      <c r="Q78" s="115" t="s">
+        <v>47</v>
+      </c>
+      <c r="R78" s="272"/>
+      <c r="S78" s="63"/>
+      <c r="T78" s="96"/>
+      <c r="U78" s="79"/>
+      <c r="V78" s="79"/>
+      <c r="W78" s="82"/>
+    </row>
+    <row r="79" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E79" s="170"/>
+      <c r="F79" s="86" t="s">
+        <v>79</v>
+      </c>
+      <c r="G79" s="94"/>
+      <c r="H79" s="64"/>
+      <c r="I79" s="64"/>
+      <c r="J79" s="64"/>
+      <c r="K79" s="113"/>
+      <c r="L79" s="97"/>
+      <c r="M79" s="67"/>
+      <c r="N79" s="64"/>
+      <c r="O79" s="69"/>
+      <c r="P79" s="269"/>
+      <c r="Q79" s="215"/>
+      <c r="R79" s="253"/>
+      <c r="S79" s="199"/>
+      <c r="T79" s="97"/>
+      <c r="U79" s="65"/>
+      <c r="V79" s="65"/>
+      <c r="W79" s="68"/>
+    </row>
+    <row r="80" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E80" s="171"/>
+      <c r="F80" s="90" t="s">
+        <v>78</v>
+      </c>
+      <c r="G80" s="95"/>
+      <c r="H80" s="70"/>
+      <c r="I80" s="70"/>
+      <c r="J80" s="70"/>
+      <c r="K80" s="114"/>
+      <c r="L80" s="98"/>
+      <c r="M80" s="80"/>
+      <c r="N80" s="70"/>
+      <c r="O80" s="73"/>
+      <c r="P80" s="270"/>
+      <c r="Q80" s="216"/>
+      <c r="R80" s="276"/>
+      <c r="S80" s="248"/>
+      <c r="T80" s="98"/>
+      <c r="U80" s="72"/>
+      <c r="V80" s="72"/>
+      <c r="W80" s="83"/>
+    </row>
+    <row r="81" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E81" s="169" t="s">
+        <v>82</v>
+      </c>
+      <c r="F81" s="85" t="s">
+        <v>84</v>
+      </c>
+      <c r="G81" s="60"/>
+      <c r="H81" s="59"/>
+      <c r="I81" s="59"/>
+      <c r="J81" s="59"/>
+      <c r="K81" s="112"/>
+      <c r="L81" s="96"/>
+      <c r="M81" s="61"/>
+      <c r="N81" s="59"/>
+      <c r="O81" s="58"/>
+      <c r="P81" s="250"/>
+      <c r="Q81" s="63"/>
+      <c r="R81" s="115" t="s">
+        <v>106</v>
+      </c>
+      <c r="S81" s="273"/>
+      <c r="T81" s="96"/>
+      <c r="U81" s="79"/>
+      <c r="V81" s="79"/>
+      <c r="W81" s="82"/>
+    </row>
+    <row r="82" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E82" s="170"/>
+      <c r="F82" s="86" t="s">
+        <v>85</v>
+      </c>
+      <c r="G82" s="94"/>
+      <c r="H82" s="64"/>
+      <c r="I82" s="64"/>
+      <c r="J82" s="64"/>
+      <c r="K82" s="113"/>
+      <c r="L82" s="97"/>
+      <c r="M82" s="67"/>
+      <c r="N82" s="64"/>
+      <c r="O82" s="69"/>
+      <c r="P82" s="54"/>
+      <c r="Q82" s="199"/>
+      <c r="R82" s="283" t="s">
+        <v>105</v>
+      </c>
+      <c r="S82" s="274"/>
+      <c r="T82" s="97"/>
+      <c r="U82" s="65"/>
+      <c r="V82" s="65"/>
+      <c r="W82" s="68"/>
+    </row>
+    <row r="83" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E83" s="170"/>
+      <c r="F83" s="86" t="s">
+        <v>88</v>
+      </c>
+      <c r="G83" s="94"/>
+      <c r="H83" s="64"/>
+      <c r="I83" s="64"/>
+      <c r="J83" s="64"/>
+      <c r="K83" s="113"/>
+      <c r="L83" s="97"/>
+      <c r="M83" s="67"/>
+      <c r="N83" s="64"/>
+      <c r="O83" s="69"/>
+      <c r="P83" s="54"/>
+      <c r="Q83" s="199"/>
+      <c r="R83" s="192" t="s">
+        <v>104</v>
+      </c>
+      <c r="S83" s="274"/>
+      <c r="T83" s="97"/>
+      <c r="U83" s="65"/>
+      <c r="V83" s="65"/>
+      <c r="W83" s="68"/>
+      <c r="X83" s="115" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="84" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E84" s="171"/>
+      <c r="F84" s="90" t="s">
+        <v>89</v>
+      </c>
+      <c r="G84" s="95"/>
+      <c r="H84" s="70"/>
+      <c r="I84" s="70"/>
+      <c r="J84" s="70"/>
+      <c r="K84" s="114"/>
+      <c r="L84" s="95"/>
+      <c r="M84" s="71"/>
+      <c r="N84" s="72"/>
+      <c r="O84" s="73"/>
+      <c r="P84" s="208"/>
+      <c r="Q84" s="72"/>
+      <c r="R84" s="117"/>
+      <c r="S84" s="248"/>
+      <c r="T84" s="98"/>
+      <c r="U84" s="72"/>
+      <c r="V84" s="72"/>
+      <c r="W84" s="83"/>
+      <c r="X84" s="192" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="85" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F85" s="123"/>
+      <c r="G85" s="240" t="s">
+        <v>0</v>
+      </c>
+      <c r="H85" s="241"/>
+      <c r="I85" s="241"/>
+      <c r="J85" s="241"/>
+      <c r="K85" s="244"/>
+      <c r="L85" s="240" t="s">
+        <v>1</v>
+      </c>
+      <c r="M85" s="241"/>
+      <c r="N85" s="241"/>
+      <c r="O85" s="242"/>
+      <c r="P85" s="251" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q85" s="241"/>
+      <c r="R85" s="241"/>
+      <c r="S85" s="244"/>
+      <c r="T85" s="194" t="s">
+        <v>13</v>
+      </c>
+      <c r="U85" s="195"/>
+      <c r="V85" s="195"/>
+      <c r="W85" s="196"/>
+    </row>
+    <row r="86" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E86" s="124"/>
+      <c r="F86" s="125" t="s">
+        <v>126</v>
+      </c>
+      <c r="G86" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="H86" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="I86" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="J86" s="76" t="s">
+        <v>5</v>
+      </c>
+      <c r="K86" s="197" t="s">
+        <v>6</v>
+      </c>
+      <c r="L86" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="M86" s="77" t="s">
+        <v>3</v>
+      </c>
+      <c r="N86" s="76" t="s">
+        <v>7</v>
+      </c>
+      <c r="O86" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="P86" s="249" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q86" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="R86" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="S86" s="197" t="s">
+        <v>5</v>
+      </c>
+      <c r="T86" s="262" t="s">
+        <v>2</v>
+      </c>
+      <c r="U86" s="233" t="s">
+        <v>3</v>
+      </c>
+      <c r="V86" s="233" t="s">
+        <v>4</v>
+      </c>
+      <c r="W86" s="263" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="4:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E87" s="188" t="s">
+        <v>94</v>
+      </c>
+      <c r="F87" s="87" t="s">
+        <v>49</v>
+      </c>
+      <c r="G87" s="298"/>
+      <c r="H87" s="299"/>
+      <c r="I87" s="299"/>
+      <c r="J87" s="299"/>
+      <c r="K87" s="300"/>
+      <c r="L87" s="298"/>
+      <c r="M87" s="317"/>
+      <c r="N87" s="299"/>
+      <c r="O87" s="300"/>
+      <c r="P87" s="298"/>
+      <c r="Q87" s="312"/>
+      <c r="R87" s="57" t="s">
+        <v>130</v>
+      </c>
+      <c r="S87" s="315"/>
+      <c r="T87" s="320"/>
+      <c r="U87" s="299"/>
+      <c r="V87" s="299"/>
+      <c r="W87" s="300"/>
+    </row>
+    <row r="88" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E88" s="189"/>
+      <c r="F88" s="88" t="s">
+        <v>134</v>
+      </c>
+      <c r="G88" s="301"/>
+      <c r="H88" s="297"/>
+      <c r="I88" s="297"/>
+      <c r="J88" s="297"/>
+      <c r="K88" s="302"/>
+      <c r="L88" s="301"/>
+      <c r="M88" s="318"/>
+      <c r="N88" s="297"/>
+      <c r="O88" s="302"/>
+      <c r="P88" s="301"/>
+      <c r="Q88" s="313"/>
+      <c r="R88" s="99"/>
+      <c r="S88" s="316"/>
+      <c r="T88" s="321"/>
+      <c r="U88" s="297"/>
+      <c r="V88" s="297"/>
+      <c r="W88" s="302"/>
+    </row>
+    <row r="89" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E89" s="189"/>
+      <c r="F89" s="88" t="s">
+        <v>53</v>
+      </c>
+      <c r="G89" s="301"/>
+      <c r="H89" s="297"/>
+      <c r="I89" s="297"/>
+      <c r="J89" s="297"/>
+      <c r="K89" s="302"/>
+      <c r="L89" s="301"/>
+      <c r="M89" s="318"/>
+      <c r="N89" s="297"/>
+      <c r="O89" s="302"/>
+      <c r="P89" s="301"/>
+      <c r="Q89" s="313"/>
+      <c r="R89" s="99"/>
+      <c r="S89" s="316"/>
+      <c r="T89" s="321"/>
+      <c r="U89" s="297"/>
+      <c r="V89" s="297"/>
+      <c r="W89" s="302"/>
+    </row>
+    <row r="90" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E90" s="189"/>
+      <c r="F90" s="88" t="s">
+        <v>135</v>
+      </c>
+      <c r="G90" s="301"/>
+      <c r="H90" s="297"/>
+      <c r="I90" s="297"/>
+      <c r="J90" s="297"/>
+      <c r="K90" s="302"/>
+      <c r="L90" s="301"/>
+      <c r="M90" s="318"/>
+      <c r="N90" s="297"/>
+      <c r="O90" s="302"/>
+      <c r="P90" s="301"/>
+      <c r="Q90" s="313"/>
+      <c r="R90" s="99"/>
+      <c r="S90" s="316"/>
+      <c r="T90" s="321"/>
+      <c r="U90" s="297"/>
+      <c r="V90" s="297"/>
+      <c r="W90" s="302"/>
+    </row>
+    <row r="91" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E91" s="189"/>
+      <c r="F91" s="88" t="s">
+        <v>131</v>
+      </c>
+      <c r="G91" s="305"/>
+      <c r="H91" s="303"/>
+      <c r="I91" s="303"/>
+      <c r="J91" s="303"/>
+      <c r="K91" s="304"/>
+      <c r="L91" s="305"/>
+      <c r="M91" s="331"/>
+      <c r="N91" s="303"/>
+      <c r="O91" s="304"/>
+      <c r="P91" s="305"/>
+      <c r="Q91" s="335"/>
+      <c r="R91" s="332"/>
+      <c r="S91" s="336"/>
+      <c r="T91" s="333"/>
+      <c r="U91" s="303"/>
+      <c r="V91" s="303"/>
+      <c r="W91" s="304"/>
+    </row>
+    <row r="92" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E92" s="190"/>
+      <c r="F92" s="191" t="s">
+        <v>133</v>
+      </c>
+      <c r="G92" s="323"/>
+      <c r="H92" s="324"/>
+      <c r="I92" s="324"/>
+      <c r="J92" s="324"/>
+      <c r="K92" s="330"/>
+      <c r="L92" s="323"/>
+      <c r="M92" s="326"/>
+      <c r="N92" s="324"/>
+      <c r="O92" s="325"/>
+      <c r="P92" s="338"/>
+      <c r="Q92" s="339"/>
+      <c r="R92" s="337"/>
+      <c r="S92" s="296"/>
+      <c r="T92" s="98"/>
+      <c r="U92" s="72"/>
+      <c r="V92" s="324"/>
+      <c r="W92" s="325"/>
+    </row>
+    <row r="93" spans="4:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D93" s="49"/>
+      <c r="E93" s="178" t="s">
+        <v>62</v>
+      </c>
+      <c r="F93" s="85" t="s">
+        <v>66</v>
+      </c>
+      <c r="G93" s="60"/>
+      <c r="H93" s="59"/>
+      <c r="I93" s="59"/>
+      <c r="J93" s="59"/>
+      <c r="K93" s="112"/>
+      <c r="L93" s="60"/>
+      <c r="M93" s="81"/>
+      <c r="N93" s="79"/>
+      <c r="O93" s="82"/>
+      <c r="P93" s="250"/>
+      <c r="Q93" s="79"/>
+      <c r="R93" s="198"/>
+      <c r="S93" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="T93" s="329"/>
+      <c r="U93" s="306"/>
+      <c r="V93" s="79"/>
+      <c r="W93" s="82"/>
+    </row>
+    <row r="94" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D94" s="49"/>
+      <c r="E94" s="179"/>
+      <c r="F94" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="G94" s="94"/>
+      <c r="H94" s="64"/>
+      <c r="I94" s="64"/>
+      <c r="J94" s="64"/>
+      <c r="K94" s="113"/>
+      <c r="L94" s="301"/>
+      <c r="M94" s="66"/>
+      <c r="N94" s="65"/>
+      <c r="O94" s="68"/>
+      <c r="P94" s="54"/>
+      <c r="Q94" s="65"/>
+      <c r="R94" s="199"/>
+      <c r="S94" s="340"/>
+      <c r="T94" s="329"/>
+      <c r="U94" s="306"/>
+      <c r="V94" s="65"/>
+      <c r="W94" s="302"/>
+    </row>
+    <row r="95" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D95" s="49"/>
+      <c r="E95" s="179"/>
+      <c r="F95" s="219" t="s">
+        <v>132</v>
+      </c>
+      <c r="G95" s="94"/>
+      <c r="H95" s="64"/>
+      <c r="I95" s="64"/>
+      <c r="J95" s="64"/>
+      <c r="K95" s="113"/>
+      <c r="L95" s="301"/>
+      <c r="M95" s="66"/>
+      <c r="N95" s="65"/>
+      <c r="O95" s="68"/>
+      <c r="P95" s="54"/>
+      <c r="Q95" s="65"/>
+      <c r="R95" s="199"/>
+      <c r="S95" s="293"/>
+      <c r="T95" s="321"/>
+      <c r="U95" s="297"/>
+      <c r="W95" s="291" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="96" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D96" s="49"/>
+      <c r="E96" s="180"/>
+      <c r="F96" s="214" t="s">
+        <v>111</v>
+      </c>
+      <c r="G96" s="95"/>
+      <c r="H96" s="70"/>
+      <c r="I96" s="70"/>
+      <c r="J96" s="70"/>
+      <c r="K96" s="114"/>
+      <c r="L96" s="311"/>
+      <c r="M96" s="71"/>
+      <c r="N96" s="72"/>
+      <c r="O96" s="83"/>
+      <c r="P96" s="208"/>
+      <c r="Q96" s="72"/>
+      <c r="R96" s="72"/>
+      <c r="S96" s="200"/>
+      <c r="T96" s="182"/>
+      <c r="U96" s="183"/>
+      <c r="V96" s="183"/>
+      <c r="W96" s="293"/>
+    </row>
+    <row r="97" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E97" s="179" t="s">
+        <v>91</v>
+      </c>
+      <c r="F97" s="85" t="s">
+        <v>150</v>
+      </c>
+      <c r="G97" s="308"/>
+      <c r="H97" s="306"/>
+      <c r="I97" s="306"/>
+      <c r="J97" s="306"/>
+      <c r="K97" s="307"/>
+      <c r="L97" s="308"/>
+      <c r="M97" s="328"/>
+      <c r="N97" s="306"/>
+      <c r="O97" s="307"/>
+      <c r="P97" s="308"/>
+      <c r="Q97" s="306"/>
+      <c r="R97" s="341"/>
+      <c r="S97" s="167" t="s">
+        <v>51</v>
+      </c>
+      <c r="T97" s="234"/>
+      <c r="U97" s="234"/>
+      <c r="V97" s="168"/>
+      <c r="W97" s="342"/>
+    </row>
+    <row r="98" spans="5:23" x14ac:dyDescent="0.3">
+      <c r="E98" s="179"/>
+      <c r="F98" s="334" t="s">
+        <v>151</v>
+      </c>
+      <c r="G98" s="308"/>
+      <c r="H98" s="306"/>
+      <c r="I98" s="306"/>
+      <c r="J98" s="306"/>
+      <c r="K98" s="307"/>
+      <c r="L98" s="308"/>
+      <c r="M98" s="328"/>
+      <c r="N98" s="306"/>
+      <c r="O98" s="307"/>
+      <c r="P98" s="308"/>
+      <c r="Q98" s="306"/>
+      <c r="R98" s="341"/>
+      <c r="S98" s="106"/>
+      <c r="T98" s="65"/>
+      <c r="U98" s="65"/>
+      <c r="V98" s="302"/>
+      <c r="W98" s="342"/>
+    </row>
+    <row r="99" spans="5:23" x14ac:dyDescent="0.3">
+      <c r="E99" s="179"/>
+      <c r="F99" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G99" s="301"/>
+      <c r="H99" s="297"/>
+      <c r="I99" s="297"/>
+      <c r="J99" s="297"/>
+      <c r="K99" s="302"/>
+      <c r="L99" s="301"/>
+      <c r="M99" s="318"/>
+      <c r="N99" s="297"/>
+      <c r="O99" s="302"/>
+      <c r="P99" s="301"/>
+      <c r="Q99" s="297"/>
+      <c r="R99" s="313"/>
+      <c r="S99" s="106"/>
+      <c r="T99" s="65"/>
+      <c r="U99" s="65"/>
+      <c r="V99" s="302"/>
+      <c r="W99" s="316"/>
+    </row>
+    <row r="100" spans="5:23" x14ac:dyDescent="0.3">
+      <c r="E100" s="179"/>
+      <c r="F100" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G100" s="301"/>
+      <c r="H100" s="297"/>
+      <c r="I100" s="297"/>
+      <c r="J100" s="297"/>
+      <c r="K100" s="302"/>
+      <c r="L100" s="301"/>
+      <c r="M100" s="318"/>
+      <c r="N100" s="297"/>
+      <c r="O100" s="302"/>
+      <c r="P100" s="301"/>
+      <c r="Q100" s="297"/>
+      <c r="R100" s="313"/>
+      <c r="S100" s="97"/>
+      <c r="T100" s="223"/>
+      <c r="U100" s="65"/>
+      <c r="V100" s="302"/>
+      <c r="W100" s="316"/>
+    </row>
+    <row r="101" spans="5:23" x14ac:dyDescent="0.3">
+      <c r="E101" s="179"/>
+      <c r="F101" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="G101" s="301"/>
+      <c r="H101" s="297"/>
+      <c r="I101" s="297"/>
+      <c r="J101" s="297"/>
+      <c r="K101" s="302"/>
+      <c r="L101" s="301"/>
+      <c r="M101" s="318"/>
+      <c r="N101" s="297"/>
+      <c r="O101" s="302"/>
+      <c r="P101" s="301"/>
+      <c r="Q101" s="297"/>
+      <c r="R101" s="313"/>
+      <c r="S101" s="301"/>
+      <c r="T101" s="297"/>
+      <c r="U101" s="223"/>
+      <c r="V101" s="302"/>
+      <c r="W101" s="316"/>
+    </row>
+    <row r="102" spans="5:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E102" s="179"/>
+      <c r="F102" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G102" s="301"/>
+      <c r="H102" s="297"/>
+      <c r="I102" s="297"/>
+      <c r="J102" s="297"/>
+      <c r="K102" s="302"/>
+      <c r="L102" s="301"/>
+      <c r="M102" s="318"/>
+      <c r="N102" s="297"/>
+      <c r="O102" s="302"/>
+      <c r="P102" s="301"/>
+      <c r="Q102" s="297"/>
+      <c r="R102" s="313"/>
+      <c r="S102" s="301"/>
+      <c r="T102" s="297"/>
+      <c r="U102" s="297"/>
+      <c r="V102" s="258"/>
+      <c r="W102" s="316"/>
+    </row>
+    <row r="103" spans="5:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E103" s="179"/>
+      <c r="F103" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G103" s="301"/>
+      <c r="H103" s="297"/>
+      <c r="I103" s="297"/>
+      <c r="J103" s="297"/>
+      <c r="K103" s="302"/>
+      <c r="L103" s="301"/>
+      <c r="M103" s="318"/>
+      <c r="N103" s="297"/>
+      <c r="O103" s="302"/>
+      <c r="P103" s="301"/>
+      <c r="Q103" s="297"/>
+      <c r="R103" s="313"/>
+      <c r="S103" s="311"/>
+      <c r="T103" s="309"/>
+      <c r="U103" s="309"/>
+      <c r="V103" s="107"/>
+      <c r="W103" s="343" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="104" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E104" s="180"/>
+      <c r="F104" s="214" t="s">
+        <v>111</v>
+      </c>
+      <c r="G104" s="311"/>
+      <c r="H104" s="309"/>
+      <c r="I104" s="309"/>
+      <c r="J104" s="309"/>
+      <c r="K104" s="310"/>
+      <c r="L104" s="311"/>
+      <c r="M104" s="319"/>
+      <c r="N104" s="309"/>
+      <c r="O104" s="310"/>
+      <c r="P104" s="311"/>
+      <c r="Q104" s="309"/>
+      <c r="R104" s="309"/>
+      <c r="S104" s="330"/>
+      <c r="T104" s="327"/>
+      <c r="U104" s="324"/>
+      <c r="V104" s="177"/>
+      <c r="W104" s="205"/>
+    </row>
+    <row r="105" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E105" s="178" t="s">
+        <v>92</v>
+      </c>
+      <c r="F105" s="85" t="s">
+        <v>138</v>
+      </c>
+      <c r="G105" s="298"/>
+      <c r="H105" s="299"/>
+      <c r="I105" s="299"/>
+      <c r="J105" s="299"/>
+      <c r="K105" s="300"/>
+      <c r="L105" s="298"/>
+      <c r="M105" s="317"/>
+      <c r="N105" s="299"/>
+      <c r="O105" s="300"/>
+      <c r="P105" s="298"/>
+      <c r="Q105" s="299"/>
+      <c r="R105" s="312"/>
+      <c r="S105" s="167" t="s">
+        <v>52</v>
+      </c>
+      <c r="T105" s="234"/>
+      <c r="U105" s="234"/>
+      <c r="V105" s="168"/>
+      <c r="W105" s="315"/>
+    </row>
+    <row r="106" spans="5:23" x14ac:dyDescent="0.3">
+      <c r="E106" s="179"/>
+      <c r="F106" s="334" t="s">
+        <v>148</v>
+      </c>
+      <c r="G106" s="301"/>
+      <c r="H106" s="297"/>
+      <c r="I106" s="297"/>
+      <c r="J106" s="297"/>
+      <c r="K106" s="302"/>
+      <c r="L106" s="301"/>
+      <c r="M106" s="318"/>
+      <c r="N106" s="297"/>
+      <c r="O106" s="302"/>
+      <c r="P106" s="301"/>
+      <c r="Q106" s="297"/>
+      <c r="R106" s="313"/>
+      <c r="S106" s="108"/>
+      <c r="T106" s="65"/>
+      <c r="U106" s="297"/>
+      <c r="V106" s="302"/>
+      <c r="W106" s="316"/>
+    </row>
+    <row r="107" spans="5:23" x14ac:dyDescent="0.3">
+      <c r="E107" s="179"/>
+      <c r="F107" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G107" s="97"/>
+      <c r="H107" s="65"/>
+      <c r="I107" s="65"/>
+      <c r="J107" s="65"/>
+      <c r="K107" s="68"/>
+      <c r="L107" s="97"/>
+      <c r="M107" s="66"/>
+      <c r="N107" s="65"/>
+      <c r="O107" s="68"/>
+      <c r="P107" s="97"/>
+      <c r="Q107" s="65"/>
+      <c r="R107" s="199"/>
+      <c r="S107" s="108"/>
+      <c r="T107" s="65"/>
+      <c r="U107" s="297"/>
+      <c r="V107" s="302"/>
+      <c r="W107" s="316"/>
+    </row>
+    <row r="108" spans="5:23" x14ac:dyDescent="0.3">
+      <c r="E108" s="179"/>
+      <c r="F108" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G108" s="97"/>
+      <c r="H108" s="65"/>
+      <c r="I108" s="65"/>
+      <c r="J108" s="65"/>
+      <c r="K108" s="68"/>
+      <c r="L108" s="97"/>
+      <c r="M108" s="66"/>
+      <c r="N108" s="65"/>
+      <c r="O108" s="68"/>
+      <c r="P108" s="97"/>
+      <c r="Q108" s="65"/>
+      <c r="R108" s="199"/>
+      <c r="S108" s="97"/>
+      <c r="T108" s="224"/>
+      <c r="U108" s="297"/>
+      <c r="V108" s="302"/>
+      <c r="W108" s="316"/>
+    </row>
+    <row r="109" spans="5:23" x14ac:dyDescent="0.3">
+      <c r="E109" s="179"/>
+      <c r="F109" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G109" s="97"/>
+      <c r="H109" s="65"/>
+      <c r="I109" s="65"/>
+      <c r="J109" s="65"/>
+      <c r="K109" s="68"/>
+      <c r="L109" s="97"/>
+      <c r="M109" s="66"/>
+      <c r="N109" s="65"/>
+      <c r="O109" s="68"/>
+      <c r="P109" s="97"/>
+      <c r="Q109" s="65"/>
+      <c r="R109" s="199"/>
+      <c r="S109" s="97"/>
+      <c r="T109" s="297"/>
+      <c r="U109" s="224"/>
+      <c r="V109" s="302"/>
+      <c r="W109" s="316"/>
+    </row>
+    <row r="110" spans="5:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E110" s="179"/>
+      <c r="F110" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G110" s="97"/>
+      <c r="H110" s="65"/>
+      <c r="I110" s="65"/>
+      <c r="J110" s="65"/>
+      <c r="K110" s="68"/>
+      <c r="L110" s="97"/>
+      <c r="M110" s="66"/>
+      <c r="N110" s="65"/>
+      <c r="O110" s="68"/>
+      <c r="P110" s="97"/>
+      <c r="Q110" s="65"/>
+      <c r="R110" s="199"/>
+      <c r="S110" s="97"/>
+      <c r="T110" s="65"/>
+      <c r="U110" s="65"/>
+      <c r="V110" s="259"/>
+      <c r="W110" s="316"/>
+    </row>
+    <row r="111" spans="5:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E111" s="179"/>
+      <c r="F111" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G111" s="97"/>
+      <c r="H111" s="65"/>
+      <c r="I111" s="65"/>
+      <c r="J111" s="65"/>
+      <c r="K111" s="68"/>
+      <c r="L111" s="97"/>
+      <c r="M111" s="66"/>
+      <c r="N111" s="65"/>
+      <c r="O111" s="68"/>
+      <c r="P111" s="97"/>
+      <c r="Q111" s="65"/>
+      <c r="R111" s="199"/>
+      <c r="S111" s="98"/>
+      <c r="T111" s="309"/>
+      <c r="U111" s="309"/>
+      <c r="V111" s="109"/>
+      <c r="W111" s="343" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="112" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E112" s="179"/>
+      <c r="F112" s="214" t="s">
+        <v>111</v>
+      </c>
+      <c r="G112" s="98"/>
+      <c r="H112" s="72"/>
+      <c r="I112" s="72"/>
+      <c r="J112" s="72"/>
+      <c r="K112" s="83"/>
+      <c r="L112" s="98"/>
+      <c r="M112" s="71"/>
+      <c r="N112" s="72"/>
+      <c r="O112" s="83"/>
+      <c r="P112" s="98"/>
+      <c r="Q112" s="72"/>
+      <c r="R112" s="72"/>
+      <c r="S112" s="210"/>
+      <c r="T112" s="344"/>
+      <c r="U112" s="345"/>
+      <c r="V112" s="117"/>
+      <c r="W112" s="292"/>
+    </row>
+    <row r="113" spans="5:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E113" s="178" t="s">
+        <v>113</v>
+      </c>
+      <c r="F113" s="85" t="s">
+        <v>137</v>
+      </c>
+      <c r="G113" s="96"/>
+      <c r="H113" s="79"/>
+      <c r="I113" s="79"/>
+      <c r="J113" s="79"/>
+      <c r="K113" s="82"/>
+      <c r="L113" s="96"/>
+      <c r="M113" s="81"/>
+      <c r="N113" s="79"/>
+      <c r="O113" s="82"/>
+      <c r="P113" s="96"/>
+      <c r="Q113" s="79"/>
+      <c r="R113" s="198"/>
+      <c r="S113" s="150" t="s">
+        <v>67</v>
+      </c>
+      <c r="T113" s="151"/>
+      <c r="U113" s="151"/>
+      <c r="V113" s="152"/>
+      <c r="W113" s="315"/>
+    </row>
+    <row r="114" spans="5:24" x14ac:dyDescent="0.3">
+      <c r="E114" s="179"/>
+      <c r="F114" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G114" s="97"/>
+      <c r="H114" s="65"/>
+      <c r="I114" s="65"/>
+      <c r="J114" s="65"/>
+      <c r="K114" s="68"/>
+      <c r="L114" s="97"/>
+      <c r="M114" s="66"/>
+      <c r="N114" s="65"/>
+      <c r="O114" s="68"/>
+      <c r="P114" s="97"/>
+      <c r="Q114" s="65"/>
+      <c r="R114" s="199"/>
+      <c r="S114" s="347"/>
+      <c r="T114" s="59"/>
+      <c r="U114" s="299"/>
+      <c r="V114" s="300"/>
+      <c r="W114" s="316"/>
+    </row>
+    <row r="115" spans="5:24" x14ac:dyDescent="0.3">
+      <c r="E115" s="179"/>
+      <c r="F115" s="334" t="s">
+        <v>147</v>
+      </c>
+      <c r="G115" s="97"/>
+      <c r="H115" s="65"/>
+      <c r="I115" s="65"/>
+      <c r="J115" s="65"/>
+      <c r="K115" s="68"/>
+      <c r="L115" s="97"/>
+      <c r="M115" s="66"/>
+      <c r="N115" s="65"/>
+      <c r="O115" s="68"/>
+      <c r="P115" s="97"/>
+      <c r="Q115" s="65"/>
+      <c r="R115" s="199"/>
+      <c r="S115" s="119"/>
+      <c r="T115" s="65"/>
+      <c r="U115" s="297"/>
+      <c r="V115" s="302"/>
+      <c r="W115" s="316"/>
+    </row>
+    <row r="116" spans="5:24" x14ac:dyDescent="0.3">
+      <c r="E116" s="179"/>
+      <c r="F116" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G116" s="97"/>
+      <c r="H116" s="65"/>
+      <c r="I116" s="65"/>
+      <c r="J116" s="65"/>
+      <c r="K116" s="68"/>
+      <c r="L116" s="97"/>
+      <c r="M116" s="66"/>
+      <c r="N116" s="65"/>
+      <c r="O116" s="68"/>
+      <c r="P116" s="97"/>
+      <c r="Q116" s="65"/>
+      <c r="R116" s="199"/>
+      <c r="S116" s="119"/>
+      <c r="T116" s="297"/>
+      <c r="U116" s="297"/>
+      <c r="V116" s="302"/>
+      <c r="W116" s="316"/>
+    </row>
+    <row r="117" spans="5:24" x14ac:dyDescent="0.3">
+      <c r="E117" s="179"/>
+      <c r="F117" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G117" s="97"/>
+      <c r="H117" s="65"/>
+      <c r="I117" s="65"/>
+      <c r="J117" s="65"/>
+      <c r="K117" s="68"/>
+      <c r="L117" s="97"/>
+      <c r="M117" s="66"/>
+      <c r="N117" s="65"/>
+      <c r="O117" s="68"/>
+      <c r="P117" s="97"/>
+      <c r="Q117" s="65"/>
+      <c r="R117" s="199"/>
+      <c r="S117" s="97"/>
+      <c r="T117" s="225"/>
+      <c r="U117" s="297"/>
+      <c r="V117" s="302"/>
+      <c r="W117" s="316"/>
+    </row>
+    <row r="118" spans="5:24" x14ac:dyDescent="0.3">
+      <c r="E118" s="179"/>
+      <c r="F118" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G118" s="97"/>
+      <c r="H118" s="65"/>
+      <c r="I118" s="65"/>
+      <c r="J118" s="65"/>
+      <c r="K118" s="68"/>
+      <c r="L118" s="97"/>
+      <c r="M118" s="66"/>
+      <c r="N118" s="65"/>
+      <c r="O118" s="68"/>
+      <c r="P118" s="97"/>
+      <c r="Q118" s="65"/>
+      <c r="R118" s="199"/>
+      <c r="S118" s="97"/>
+      <c r="T118" s="297"/>
+      <c r="U118" s="225"/>
+      <c r="V118" s="302"/>
+      <c r="W118" s="316"/>
+    </row>
+    <row r="119" spans="5:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E119" s="179"/>
+      <c r="F119" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G119" s="97"/>
+      <c r="H119" s="65"/>
+      <c r="I119" s="65"/>
+      <c r="J119" s="65"/>
+      <c r="K119" s="68"/>
+      <c r="L119" s="97"/>
+      <c r="M119" s="66"/>
+      <c r="N119" s="65"/>
+      <c r="O119" s="68"/>
+      <c r="P119" s="97"/>
+      <c r="Q119" s="65"/>
+      <c r="R119" s="199"/>
+      <c r="S119" s="97"/>
+      <c r="T119" s="65"/>
+      <c r="U119" s="65"/>
+      <c r="V119" s="260"/>
+      <c r="W119" s="316"/>
+    </row>
+    <row r="120" spans="5:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E120" s="179"/>
+      <c r="F120" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G120" s="97"/>
+      <c r="H120" s="65"/>
+      <c r="I120" s="65"/>
+      <c r="J120" s="65"/>
+      <c r="K120" s="68"/>
+      <c r="L120" s="97"/>
+      <c r="M120" s="66"/>
+      <c r="N120" s="65"/>
+      <c r="O120" s="68"/>
+      <c r="P120" s="97"/>
+      <c r="Q120" s="65"/>
+      <c r="R120" s="199"/>
+      <c r="S120" s="98"/>
+      <c r="T120" s="309"/>
+      <c r="U120" s="309"/>
+      <c r="V120" s="121"/>
+      <c r="W120" s="343" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="121" spans="5:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E121" s="180"/>
+      <c r="F121" s="214" t="s">
+        <v>111</v>
+      </c>
+      <c r="G121" s="98"/>
+      <c r="H121" s="72"/>
+      <c r="I121" s="72"/>
+      <c r="J121" s="72"/>
+      <c r="K121" s="83"/>
+      <c r="L121" s="98"/>
+      <c r="M121" s="71"/>
+      <c r="N121" s="72"/>
+      <c r="O121" s="83"/>
+      <c r="P121" s="98"/>
+      <c r="Q121" s="72"/>
+      <c r="R121" s="72"/>
+      <c r="S121" s="346"/>
+      <c r="T121" s="344"/>
+      <c r="U121" s="345"/>
+      <c r="W121" s="111"/>
+    </row>
+    <row r="122" spans="5:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E122" s="169" t="s">
+        <v>47</v>
+      </c>
+      <c r="F122" s="85" t="s">
+        <v>83</v>
+      </c>
+      <c r="G122" s="60"/>
+      <c r="H122" s="59"/>
+      <c r="I122" s="59"/>
+      <c r="J122" s="59"/>
+      <c r="K122" s="58"/>
+      <c r="L122" s="96"/>
+      <c r="M122" s="61"/>
+      <c r="N122" s="59"/>
+      <c r="O122" s="58"/>
+      <c r="P122" s="96"/>
+      <c r="Q122" s="79"/>
+      <c r="R122" s="79"/>
+      <c r="S122" s="82"/>
+      <c r="T122" s="320"/>
+      <c r="U122" s="312"/>
+      <c r="V122" s="198"/>
+      <c r="W122" s="115" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="123" spans="5:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E123" s="170"/>
+      <c r="F123" s="86" t="s">
+        <v>79</v>
+      </c>
+      <c r="G123" s="94"/>
+      <c r="H123" s="64"/>
+      <c r="I123" s="64"/>
+      <c r="J123" s="64"/>
+      <c r="K123" s="69"/>
+      <c r="L123" s="97"/>
+      <c r="M123" s="67"/>
+      <c r="N123" s="64"/>
+      <c r="O123" s="69"/>
+      <c r="P123" s="97"/>
+      <c r="Q123" s="65"/>
+      <c r="R123" s="65"/>
+      <c r="S123" s="68"/>
+      <c r="T123" s="321"/>
+      <c r="U123" s="313"/>
+      <c r="W123" s="215"/>
+    </row>
+    <row r="124" spans="5:24" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E124" s="171"/>
+      <c r="F124" s="90" t="s">
+        <v>78</v>
+      </c>
+      <c r="G124" s="95"/>
+      <c r="H124" s="70"/>
+      <c r="I124" s="70"/>
+      <c r="J124" s="70"/>
+      <c r="K124" s="73"/>
+      <c r="L124" s="98"/>
+      <c r="M124" s="80"/>
+      <c r="N124" s="70"/>
+      <c r="O124" s="73"/>
+      <c r="P124" s="98"/>
+      <c r="Q124" s="72"/>
+      <c r="R124" s="72"/>
+      <c r="S124" s="83"/>
+      <c r="T124" s="322"/>
+      <c r="U124" s="314"/>
+      <c r="W124" s="216"/>
+    </row>
+    <row r="125" spans="5:24" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E125" s="169" t="s">
+        <v>82</v>
+      </c>
+      <c r="F125" s="85" t="s">
+        <v>84</v>
+      </c>
+      <c r="G125" s="60"/>
+      <c r="H125" s="59"/>
+      <c r="I125" s="59"/>
+      <c r="J125" s="59"/>
+      <c r="K125" s="58"/>
+      <c r="L125" s="96"/>
+      <c r="M125" s="61"/>
+      <c r="N125" s="59"/>
+      <c r="O125" s="58"/>
+      <c r="P125" s="203"/>
+      <c r="Q125" s="79"/>
+      <c r="R125" s="79"/>
+      <c r="S125" s="82"/>
+      <c r="T125" s="96"/>
+      <c r="U125" s="79"/>
+      <c r="V125" s="198"/>
+      <c r="W125" s="82"/>
+      <c r="X125" s="115" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="126" spans="5:24" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="E126" s="170"/>
+      <c r="F126" s="86" t="s">
+        <v>127</v>
+      </c>
+      <c r="G126" s="94"/>
+      <c r="H126" s="64"/>
+      <c r="I126" s="64"/>
+      <c r="J126" s="64"/>
+      <c r="K126" s="69"/>
+      <c r="L126" s="97"/>
+      <c r="M126" s="67"/>
+      <c r="N126" s="64"/>
+      <c r="O126" s="69"/>
+      <c r="P126" s="202"/>
+      <c r="Q126" s="65"/>
+      <c r="R126" s="65"/>
+      <c r="S126" s="68"/>
+      <c r="T126" s="97"/>
+      <c r="U126" s="65"/>
+      <c r="V126" s="199"/>
+      <c r="W126" s="68"/>
+      <c r="X126" s="283" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="127" spans="5:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E127" s="171"/>
+      <c r="F127" s="90" t="s">
+        <v>128</v>
+      </c>
+      <c r="G127" s="95"/>
+      <c r="H127" s="70"/>
+      <c r="I127" s="70"/>
+      <c r="J127" s="70"/>
+      <c r="K127" s="73"/>
+      <c r="L127" s="98"/>
+      <c r="M127" s="80"/>
+      <c r="N127" s="70"/>
+      <c r="O127" s="73"/>
+      <c r="P127" s="204"/>
+      <c r="Q127" s="72"/>
+      <c r="R127" s="72"/>
+      <c r="S127" s="83"/>
+      <c r="T127" s="98"/>
+      <c r="U127" s="72"/>
+      <c r="V127" s="248"/>
+      <c r="W127" s="83"/>
+      <c r="X127" s="192" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="48">
+    <mergeCell ref="S105:V105"/>
+    <mergeCell ref="S113:V113"/>
+    <mergeCell ref="S97:V97"/>
+    <mergeCell ref="E113:E121"/>
+    <mergeCell ref="E122:E124"/>
+    <mergeCell ref="E125:E127"/>
+    <mergeCell ref="E93:E96"/>
+    <mergeCell ref="G85:K85"/>
+    <mergeCell ref="L85:O85"/>
+    <mergeCell ref="P85:S85"/>
+    <mergeCell ref="T85:W85"/>
+    <mergeCell ref="E97:E104"/>
+    <mergeCell ref="E105:E112"/>
+    <mergeCell ref="E87:E92"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="T4:W4"/>
+    <mergeCell ref="T45:W45"/>
+    <mergeCell ref="E81:E84"/>
+    <mergeCell ref="N64:O64"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="E52:E57"/>
+    <mergeCell ref="E58:E63"/>
+    <mergeCell ref="E64:E70"/>
+    <mergeCell ref="E71:E77"/>
+    <mergeCell ref="N71:O71"/>
+    <mergeCell ref="E78:E80"/>
+    <mergeCell ref="P4:S4"/>
+    <mergeCell ref="P45:S45"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="E27:E37"/>
+    <mergeCell ref="E15:E18"/>
+    <mergeCell ref="E19:E22"/>
+    <mergeCell ref="E23:E26"/>
+    <mergeCell ref="E47:E51"/>
+    <mergeCell ref="G45:K45"/>
+    <mergeCell ref="L45:O45"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="L4:O4"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="E38:E40"/>
+    <mergeCell ref="E41:E44"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="E6:E14"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:W61"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2216,136 +6270,136 @@
   <sheetData>
     <row r="3" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F4" s="151" t="s">
+      <c r="F4" s="130" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="152"/>
-      <c r="H4" s="152"/>
-      <c r="I4" s="152"/>
-      <c r="J4" s="152"/>
-      <c r="K4" s="152"/>
-      <c r="L4" s="152"/>
-      <c r="M4" s="152"/>
-      <c r="N4" s="152"/>
-      <c r="O4" s="152"/>
-      <c r="P4" s="152"/>
-      <c r="Q4" s="152"/>
-      <c r="R4" s="152"/>
-      <c r="S4" s="152"/>
-      <c r="T4" s="152"/>
-      <c r="U4" s="152"/>
-      <c r="V4" s="152"/>
-      <c r="W4" s="153"/>
+      <c r="G4" s="131"/>
+      <c r="H4" s="131"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="131"/>
+      <c r="L4" s="131"/>
+      <c r="M4" s="131"/>
+      <c r="N4" s="131"/>
+      <c r="O4" s="131"/>
+      <c r="P4" s="131"/>
+      <c r="Q4" s="131"/>
+      <c r="R4" s="131"/>
+      <c r="S4" s="131"/>
+      <c r="T4" s="131"/>
+      <c r="U4" s="131"/>
+      <c r="V4" s="131"/>
+      <c r="W4" s="132"/>
     </row>
     <row r="5" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F5" s="154"/>
-      <c r="G5" s="155"/>
-      <c r="H5" s="155"/>
-      <c r="I5" s="155"/>
-      <c r="J5" s="155"/>
-      <c r="K5" s="155"/>
-      <c r="L5" s="155"/>
-      <c r="M5" s="155"/>
-      <c r="N5" s="155"/>
-      <c r="O5" s="155"/>
-      <c r="P5" s="155"/>
-      <c r="Q5" s="155"/>
-      <c r="R5" s="155"/>
-      <c r="S5" s="155"/>
-      <c r="T5" s="155"/>
-      <c r="U5" s="155"/>
-      <c r="V5" s="155"/>
-      <c r="W5" s="156"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="134"/>
+      <c r="S5" s="134"/>
+      <c r="T5" s="134"/>
+      <c r="U5" s="134"/>
+      <c r="V5" s="134"/>
+      <c r="W5" s="135"/>
     </row>
     <row r="6" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F6" s="157"/>
-      <c r="G6" s="158"/>
-      <c r="H6" s="158"/>
-      <c r="I6" s="158"/>
-      <c r="J6" s="158"/>
-      <c r="K6" s="158"/>
-      <c r="L6" s="158"/>
-      <c r="M6" s="158"/>
-      <c r="N6" s="158"/>
-      <c r="O6" s="158"/>
-      <c r="P6" s="158"/>
-      <c r="Q6" s="158"/>
-      <c r="R6" s="158"/>
-      <c r="S6" s="158"/>
-      <c r="T6" s="158"/>
-      <c r="U6" s="158"/>
-      <c r="V6" s="158"/>
-      <c r="W6" s="159"/>
+      <c r="F6" s="136"/>
+      <c r="G6" s="137"/>
+      <c r="H6" s="137"/>
+      <c r="I6" s="137"/>
+      <c r="J6" s="137"/>
+      <c r="K6" s="137"/>
+      <c r="L6" s="137"/>
+      <c r="M6" s="137"/>
+      <c r="N6" s="137"/>
+      <c r="O6" s="137"/>
+      <c r="P6" s="137"/>
+      <c r="Q6" s="137"/>
+      <c r="R6" s="137"/>
+      <c r="S6" s="137"/>
+      <c r="T6" s="137"/>
+      <c r="U6" s="137"/>
+      <c r="V6" s="137"/>
+      <c r="W6" s="138"/>
     </row>
     <row r="7" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F7" s="160" t="s">
+      <c r="F7" s="139" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="161"/>
-      <c r="H7" s="161"/>
-      <c r="I7" s="161"/>
-      <c r="J7" s="161"/>
-      <c r="K7" s="161"/>
-      <c r="L7" s="161"/>
-      <c r="M7" s="161"/>
-      <c r="N7" s="161"/>
-      <c r="O7" s="161"/>
-      <c r="P7" s="161"/>
-      <c r="Q7" s="161"/>
-      <c r="R7" s="161"/>
-      <c r="S7" s="161"/>
-      <c r="T7" s="161"/>
-      <c r="U7" s="161"/>
-      <c r="V7" s="161"/>
-      <c r="W7" s="162"/>
+      <c r="G7" s="140"/>
+      <c r="H7" s="140"/>
+      <c r="I7" s="140"/>
+      <c r="J7" s="140"/>
+      <c r="K7" s="140"/>
+      <c r="L7" s="140"/>
+      <c r="M7" s="140"/>
+      <c r="N7" s="140"/>
+      <c r="O7" s="140"/>
+      <c r="P7" s="140"/>
+      <c r="Q7" s="140"/>
+      <c r="R7" s="140"/>
+      <c r="S7" s="140"/>
+      <c r="T7" s="140"/>
+      <c r="U7" s="140"/>
+      <c r="V7" s="140"/>
+      <c r="W7" s="141"/>
     </row>
     <row r="8" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F8" s="163"/>
-      <c r="G8" s="164"/>
-      <c r="H8" s="164"/>
-      <c r="I8" s="164"/>
-      <c r="J8" s="164"/>
-      <c r="K8" s="164"/>
-      <c r="L8" s="164"/>
-      <c r="M8" s="164"/>
-      <c r="N8" s="164"/>
-      <c r="O8" s="164"/>
-      <c r="P8" s="164"/>
-      <c r="Q8" s="164"/>
-      <c r="R8" s="164"/>
-      <c r="S8" s="164"/>
-      <c r="T8" s="164"/>
-      <c r="U8" s="164"/>
-      <c r="V8" s="164"/>
-      <c r="W8" s="165"/>
+      <c r="F8" s="142"/>
+      <c r="G8" s="143"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="143"/>
+      <c r="J8" s="143"/>
+      <c r="K8" s="143"/>
+      <c r="L8" s="143"/>
+      <c r="M8" s="143"/>
+      <c r="N8" s="143"/>
+      <c r="O8" s="143"/>
+      <c r="P8" s="143"/>
+      <c r="Q8" s="143"/>
+      <c r="R8" s="143"/>
+      <c r="S8" s="143"/>
+      <c r="T8" s="143"/>
+      <c r="U8" s="143"/>
+      <c r="V8" s="143"/>
+      <c r="W8" s="144"/>
     </row>
     <row r="9" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F9" s="136" t="s">
+      <c r="F9" s="145" t="s">
         <v>0</v>
       </c>
-      <c r="G9" s="137"/>
-      <c r="H9" s="137"/>
-      <c r="I9" s="137"/>
-      <c r="J9" s="137"/>
-      <c r="K9" s="136" t="s">
+      <c r="G9" s="146"/>
+      <c r="H9" s="146"/>
+      <c r="I9" s="146"/>
+      <c r="J9" s="146"/>
+      <c r="K9" s="145" t="s">
         <v>1</v>
       </c>
-      <c r="L9" s="137"/>
-      <c r="M9" s="137"/>
-      <c r="N9" s="138"/>
-      <c r="O9" s="136" t="s">
+      <c r="L9" s="146"/>
+      <c r="M9" s="146"/>
+      <c r="N9" s="147"/>
+      <c r="O9" s="145" t="s">
         <v>12</v>
       </c>
-      <c r="P9" s="137"/>
-      <c r="Q9" s="137"/>
-      <c r="R9" s="138"/>
-      <c r="S9" s="136" t="s">
+      <c r="P9" s="146"/>
+      <c r="Q9" s="146"/>
+      <c r="R9" s="147"/>
+      <c r="S9" s="145" t="s">
         <v>13</v>
       </c>
-      <c r="T9" s="137"/>
-      <c r="U9" s="137"/>
-      <c r="V9" s="137"/>
-      <c r="W9" s="138"/>
+      <c r="T9" s="146"/>
+      <c r="U9" s="146"/>
+      <c r="V9" s="146"/>
+      <c r="W9" s="147"/>
     </row>
     <row r="10" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F10" s="3" t="s">
@@ -2434,11 +6488,11 @@
       <c r="F13" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="142" t="s">
+      <c r="G13" s="153" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="143"/>
-      <c r="I13" s="144"/>
+      <c r="H13" s="154"/>
+      <c r="I13" s="155"/>
       <c r="K13" s="4"/>
       <c r="L13" s="17"/>
       <c r="N13" s="7"/>
@@ -2697,74 +6751,74 @@
       <c r="W29" s="14"/>
     </row>
     <row r="30" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F30" s="145" t="s">
+      <c r="F30" s="156" t="s">
         <v>11</v>
       </c>
-      <c r="G30" s="146"/>
-      <c r="H30" s="146"/>
-      <c r="I30" s="146"/>
-      <c r="J30" s="146"/>
-      <c r="K30" s="146"/>
-      <c r="L30" s="146"/>
-      <c r="M30" s="146"/>
-      <c r="N30" s="146"/>
-      <c r="O30" s="146"/>
-      <c r="P30" s="146"/>
-      <c r="Q30" s="146"/>
-      <c r="R30" s="146"/>
-      <c r="S30" s="146"/>
-      <c r="T30" s="146"/>
-      <c r="U30" s="146"/>
-      <c r="V30" s="146"/>
-      <c r="W30" s="147"/>
+      <c r="G30" s="157"/>
+      <c r="H30" s="157"/>
+      <c r="I30" s="157"/>
+      <c r="J30" s="157"/>
+      <c r="K30" s="157"/>
+      <c r="L30" s="157"/>
+      <c r="M30" s="157"/>
+      <c r="N30" s="157"/>
+      <c r="O30" s="157"/>
+      <c r="P30" s="157"/>
+      <c r="Q30" s="157"/>
+      <c r="R30" s="157"/>
+      <c r="S30" s="157"/>
+      <c r="T30" s="157"/>
+      <c r="U30" s="157"/>
+      <c r="V30" s="157"/>
+      <c r="W30" s="158"/>
     </row>
     <row r="31" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F31" s="148"/>
-      <c r="G31" s="149"/>
-      <c r="H31" s="149"/>
-      <c r="I31" s="149"/>
-      <c r="J31" s="149"/>
-      <c r="K31" s="149"/>
-      <c r="L31" s="149"/>
-      <c r="M31" s="149"/>
-      <c r="N31" s="149"/>
-      <c r="O31" s="149"/>
-      <c r="P31" s="149"/>
-      <c r="Q31" s="149"/>
-      <c r="R31" s="149"/>
-      <c r="S31" s="149"/>
-      <c r="T31" s="149"/>
-      <c r="U31" s="149"/>
-      <c r="V31" s="149"/>
-      <c r="W31" s="150"/>
+      <c r="F31" s="159"/>
+      <c r="G31" s="160"/>
+      <c r="H31" s="160"/>
+      <c r="I31" s="160"/>
+      <c r="J31" s="160"/>
+      <c r="K31" s="160"/>
+      <c r="L31" s="160"/>
+      <c r="M31" s="160"/>
+      <c r="N31" s="160"/>
+      <c r="O31" s="160"/>
+      <c r="P31" s="160"/>
+      <c r="Q31" s="160"/>
+      <c r="R31" s="160"/>
+      <c r="S31" s="160"/>
+      <c r="T31" s="160"/>
+      <c r="U31" s="160"/>
+      <c r="V31" s="160"/>
+      <c r="W31" s="161"/>
     </row>
     <row r="32" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F32" s="136" t="s">
+      <c r="F32" s="145" t="s">
         <v>0</v>
       </c>
-      <c r="G32" s="137"/>
-      <c r="H32" s="137"/>
-      <c r="I32" s="137"/>
-      <c r="J32" s="137"/>
-      <c r="K32" s="136" t="s">
+      <c r="G32" s="146"/>
+      <c r="H32" s="146"/>
+      <c r="I32" s="146"/>
+      <c r="J32" s="146"/>
+      <c r="K32" s="145" t="s">
         <v>1</v>
       </c>
-      <c r="L32" s="137"/>
-      <c r="M32" s="137"/>
-      <c r="N32" s="138"/>
-      <c r="O32" s="136" t="s">
+      <c r="L32" s="146"/>
+      <c r="M32" s="146"/>
+      <c r="N32" s="147"/>
+      <c r="O32" s="145" t="s">
         <v>12</v>
       </c>
-      <c r="P32" s="137"/>
-      <c r="Q32" s="137"/>
-      <c r="R32" s="138"/>
-      <c r="S32" s="136" t="s">
+      <c r="P32" s="146"/>
+      <c r="Q32" s="146"/>
+      <c r="R32" s="147"/>
+      <c r="S32" s="145" t="s">
         <v>13</v>
       </c>
-      <c r="T32" s="137"/>
-      <c r="U32" s="137"/>
-      <c r="V32" s="137"/>
-      <c r="W32" s="138"/>
+      <c r="T32" s="146"/>
+      <c r="U32" s="146"/>
+      <c r="V32" s="146"/>
+      <c r="W32" s="147"/>
     </row>
     <row r="33" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F33" s="3" t="s">
@@ -2858,11 +6912,11 @@
       <c r="K36" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="L36" s="54"/>
-      <c r="M36" s="53" t="s">
+      <c r="L36" s="51"/>
+      <c r="M36" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="N36" s="55"/>
+      <c r="N36" s="52"/>
       <c r="O36" s="4"/>
       <c r="R36" s="7"/>
       <c r="S36" s="4"/>
@@ -3053,74 +7107,74 @@
       <c r="W49" s="14"/>
     </row>
     <row r="50" spans="6:23" x14ac:dyDescent="0.3">
-      <c r="F50" s="145" t="s">
+      <c r="F50" s="156" t="s">
         <v>20</v>
       </c>
-      <c r="G50" s="146"/>
-      <c r="H50" s="146"/>
-      <c r="I50" s="146"/>
-      <c r="J50" s="146"/>
-      <c r="K50" s="146"/>
-      <c r="L50" s="146"/>
-      <c r="M50" s="146"/>
-      <c r="N50" s="146"/>
-      <c r="O50" s="146"/>
-      <c r="P50" s="146"/>
-      <c r="Q50" s="146"/>
-      <c r="R50" s="146"/>
-      <c r="S50" s="146"/>
-      <c r="T50" s="146"/>
-      <c r="U50" s="146"/>
-      <c r="V50" s="146"/>
-      <c r="W50" s="147"/>
+      <c r="G50" s="157"/>
+      <c r="H50" s="157"/>
+      <c r="I50" s="157"/>
+      <c r="J50" s="157"/>
+      <c r="K50" s="157"/>
+      <c r="L50" s="157"/>
+      <c r="M50" s="157"/>
+      <c r="N50" s="157"/>
+      <c r="O50" s="157"/>
+      <c r="P50" s="157"/>
+      <c r="Q50" s="157"/>
+      <c r="R50" s="157"/>
+      <c r="S50" s="157"/>
+      <c r="T50" s="157"/>
+      <c r="U50" s="157"/>
+      <c r="V50" s="157"/>
+      <c r="W50" s="158"/>
     </row>
     <row r="51" spans="6:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F51" s="148"/>
-      <c r="G51" s="149"/>
-      <c r="H51" s="149"/>
-      <c r="I51" s="149"/>
-      <c r="J51" s="149"/>
-      <c r="K51" s="149"/>
-      <c r="L51" s="149"/>
-      <c r="M51" s="149"/>
-      <c r="N51" s="149"/>
-      <c r="O51" s="149"/>
-      <c r="P51" s="149"/>
-      <c r="Q51" s="149"/>
-      <c r="R51" s="149"/>
-      <c r="S51" s="149"/>
-      <c r="T51" s="149"/>
-      <c r="U51" s="149"/>
-      <c r="V51" s="149"/>
-      <c r="W51" s="150"/>
+      <c r="F51" s="159"/>
+      <c r="G51" s="160"/>
+      <c r="H51" s="160"/>
+      <c r="I51" s="160"/>
+      <c r="J51" s="160"/>
+      <c r="K51" s="160"/>
+      <c r="L51" s="160"/>
+      <c r="M51" s="160"/>
+      <c r="N51" s="160"/>
+      <c r="O51" s="160"/>
+      <c r="P51" s="160"/>
+      <c r="Q51" s="160"/>
+      <c r="R51" s="160"/>
+      <c r="S51" s="160"/>
+      <c r="T51" s="160"/>
+      <c r="U51" s="160"/>
+      <c r="V51" s="160"/>
+      <c r="W51" s="161"/>
     </row>
     <row r="52" spans="6:23" x14ac:dyDescent="0.3">
-      <c r="F52" s="136" t="s">
+      <c r="F52" s="145" t="s">
         <v>0</v>
       </c>
-      <c r="G52" s="137"/>
-      <c r="H52" s="137"/>
-      <c r="I52" s="137"/>
-      <c r="J52" s="137"/>
-      <c r="K52" s="136" t="s">
+      <c r="G52" s="146"/>
+      <c r="H52" s="146"/>
+      <c r="I52" s="146"/>
+      <c r="J52" s="146"/>
+      <c r="K52" s="145" t="s">
         <v>1</v>
       </c>
-      <c r="L52" s="137"/>
-      <c r="M52" s="137"/>
-      <c r="N52" s="138"/>
-      <c r="O52" s="136" t="s">
+      <c r="L52" s="146"/>
+      <c r="M52" s="146"/>
+      <c r="N52" s="147"/>
+      <c r="O52" s="145" t="s">
         <v>12</v>
       </c>
-      <c r="P52" s="137"/>
-      <c r="Q52" s="137"/>
-      <c r="R52" s="138"/>
-      <c r="S52" s="136" t="s">
+      <c r="P52" s="146"/>
+      <c r="Q52" s="146"/>
+      <c r="R52" s="147"/>
+      <c r="S52" s="145" t="s">
         <v>13</v>
       </c>
-      <c r="T52" s="137"/>
-      <c r="U52" s="137"/>
-      <c r="V52" s="137"/>
-      <c r="W52" s="138"/>
+      <c r="T52" s="146"/>
+      <c r="U52" s="146"/>
+      <c r="V52" s="146"/>
+      <c r="W52" s="147"/>
     </row>
     <row r="53" spans="6:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F53" s="3" t="s">
@@ -3216,12 +7270,12 @@
       <c r="L56" s="17"/>
       <c r="N56" s="7"/>
       <c r="O56" s="4"/>
-      <c r="P56" s="139" t="s">
+      <c r="P56" s="150" t="s">
         <v>16</v>
       </c>
-      <c r="Q56" s="140"/>
-      <c r="R56" s="140"/>
-      <c r="S56" s="141"/>
+      <c r="Q56" s="151"/>
+      <c r="R56" s="151"/>
+      <c r="S56" s="152"/>
       <c r="W56" s="7"/>
     </row>
     <row r="57" spans="6:23" x14ac:dyDescent="0.3">
@@ -3268,10 +7322,10 @@
       <c r="O59" s="4"/>
       <c r="R59" s="7"/>
       <c r="S59" s="4"/>
-      <c r="T59" s="134" t="s">
+      <c r="T59" s="148" t="s">
         <v>23</v>
       </c>
-      <c r="U59" s="135"/>
+      <c r="U59" s="149"/>
       <c r="W59" s="7"/>
     </row>
     <row r="60" spans="6:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3309,12 +7363,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="F4:W6"/>
-    <mergeCell ref="F7:W8"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="S9:W9"/>
     <mergeCell ref="T59:U59"/>
     <mergeCell ref="S52:W52"/>
     <mergeCell ref="P56:S56"/>
@@ -3328,6 +7376,12 @@
     <mergeCell ref="K32:N32"/>
     <mergeCell ref="O32:R32"/>
     <mergeCell ref="S32:W32"/>
+    <mergeCell ref="F4:W6"/>
+    <mergeCell ref="F7:W8"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="S9:W9"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3335,848 +7389,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019D5629-DDAE-4958-87CA-0890F9F624F4}">
-  <dimension ref="D3:P52"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="118" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="4:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="4:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G4" s="174" t="s">
-        <v>0</v>
-      </c>
-      <c r="H4" s="175"/>
-      <c r="I4" s="175"/>
-      <c r="J4" s="175"/>
-      <c r="K4" s="176"/>
-      <c r="L4" s="174" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" s="175"/>
-      <c r="N4" s="175"/>
-      <c r="O4" s="176"/>
-      <c r="P4" s="51"/>
-    </row>
-    <row r="5" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D5" s="52"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="87" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="96" t="s">
-        <v>2</v>
-      </c>
-      <c r="H5" s="79" t="s">
-        <v>3</v>
-      </c>
-      <c r="I5" s="79" t="s">
-        <v>4</v>
-      </c>
-      <c r="J5" s="79" t="s">
-        <v>5</v>
-      </c>
-      <c r="K5" s="81" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5" s="96" t="s">
-        <v>2</v>
-      </c>
-      <c r="M5" s="80" t="s">
-        <v>3</v>
-      </c>
-      <c r="N5" s="79" t="s">
-        <v>7</v>
-      </c>
-      <c r="O5" s="81" t="s">
-        <v>8</v>
-      </c>
-      <c r="P5" s="57"/>
-    </row>
-    <row r="6" spans="4:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="52"/>
-      <c r="E6" s="171" t="s">
-        <v>95</v>
-      </c>
-      <c r="F6" s="88" t="s">
-        <v>58</v>
-      </c>
-      <c r="G6" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="65"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="62"/>
-      <c r="K6" s="61"/>
-      <c r="L6" s="99"/>
-      <c r="M6" s="84"/>
-      <c r="N6" s="82"/>
-      <c r="O6" s="85"/>
-      <c r="P6" s="58"/>
-    </row>
-    <row r="7" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D7" s="52"/>
-      <c r="E7" s="172"/>
-      <c r="F7" s="89" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="102"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="67"/>
-      <c r="J7" s="67"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="100"/>
-      <c r="M7" s="69"/>
-      <c r="N7" s="68"/>
-      <c r="O7" s="71"/>
-      <c r="P7" s="58"/>
-    </row>
-    <row r="8" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D8" s="52"/>
-      <c r="E8" s="172"/>
-      <c r="F8" s="89" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="102"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="67"/>
-      <c r="K8" s="72"/>
-      <c r="L8" s="100"/>
-      <c r="M8" s="69"/>
-      <c r="N8" s="68"/>
-      <c r="O8" s="71"/>
-      <c r="P8" s="58"/>
-    </row>
-    <row r="9" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D9" s="52"/>
-      <c r="E9" s="172"/>
-      <c r="F9" s="89" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="103"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="67"/>
-      <c r="J9" s="67"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="100"/>
-      <c r="M9" s="69"/>
-      <c r="N9" s="68"/>
-      <c r="O9" s="71"/>
-      <c r="P9" s="58"/>
-    </row>
-    <row r="10" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D10" s="52"/>
-      <c r="E10" s="172"/>
-      <c r="F10" s="90" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="104" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="94"/>
-      <c r="I10" s="67"/>
-      <c r="J10" s="67"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="100"/>
-      <c r="M10" s="69"/>
-      <c r="N10" s="68"/>
-      <c r="O10" s="71"/>
-      <c r="P10" s="58"/>
-    </row>
-    <row r="11" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D11" s="52"/>
-      <c r="E11" s="172"/>
-      <c r="F11" s="91" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="102"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="67"/>
-      <c r="J11" s="67"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="100"/>
-      <c r="M11" s="69"/>
-      <c r="N11" s="68"/>
-      <c r="O11" s="71"/>
-      <c r="P11" s="58"/>
-    </row>
-    <row r="12" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D12" s="52"/>
-      <c r="E12" s="172"/>
-      <c r="F12" s="91" t="s">
-        <v>53</v>
-      </c>
-      <c r="G12" s="102"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="67"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="100"/>
-      <c r="M12" s="69"/>
-      <c r="N12" s="68"/>
-      <c r="O12" s="71"/>
-      <c r="P12" s="58"/>
-    </row>
-    <row r="13" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D13" s="52"/>
-      <c r="E13" s="172"/>
-      <c r="F13" s="91" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13" s="102"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="67"/>
-      <c r="K13" s="72"/>
-      <c r="L13" s="100"/>
-      <c r="M13" s="69"/>
-      <c r="N13" s="68"/>
-      <c r="O13" s="71"/>
-      <c r="P13" s="58"/>
-    </row>
-    <row r="14" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D14" s="52"/>
-      <c r="E14" s="172"/>
-      <c r="F14" s="91" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" s="102"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="67"/>
-      <c r="J14" s="67"/>
-      <c r="K14" s="72"/>
-      <c r="L14" s="100"/>
-      <c r="M14" s="69"/>
-      <c r="N14" s="68"/>
-      <c r="O14" s="71"/>
-      <c r="P14" s="58"/>
-    </row>
-    <row r="15" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D15" s="52"/>
-      <c r="E15" s="173"/>
-      <c r="F15" s="92" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" s="105"/>
-      <c r="H15" s="95"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="73"/>
-      <c r="K15" s="76"/>
-      <c r="L15" s="101"/>
-      <c r="M15" s="74"/>
-      <c r="N15" s="75"/>
-      <c r="O15" s="86"/>
-      <c r="P15" s="58"/>
-    </row>
-    <row r="16" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D16" s="52"/>
-      <c r="E16" s="171" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="88" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" s="106"/>
-      <c r="H16" s="169" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="170"/>
-      <c r="J16" s="65"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="63"/>
-      <c r="M16" s="84"/>
-      <c r="N16" s="82"/>
-      <c r="O16" s="85"/>
-      <c r="P16" s="58"/>
-    </row>
-    <row r="17" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D17" s="52"/>
-      <c r="E17" s="172"/>
-      <c r="F17" s="89" t="s">
-        <v>65</v>
-      </c>
-      <c r="G17" s="107"/>
-      <c r="H17" s="109"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="94"/>
-      <c r="K17" s="72"/>
-      <c r="L17" s="97"/>
-      <c r="M17" s="69"/>
-      <c r="N17" s="68"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="58"/>
-    </row>
-    <row r="18" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D18" s="52"/>
-      <c r="E18" s="173"/>
-      <c r="F18" s="93" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18" s="108"/>
-      <c r="H18" s="101"/>
-      <c r="I18" s="110"/>
-      <c r="J18" s="95"/>
-      <c r="K18" s="76"/>
-      <c r="L18" s="98"/>
-      <c r="M18" s="74"/>
-      <c r="N18" s="75"/>
-      <c r="O18" s="86"/>
-      <c r="P18" s="58"/>
-    </row>
-    <row r="19" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D19" s="52"/>
-      <c r="E19" s="171" t="s">
-        <v>96</v>
-      </c>
-      <c r="F19" s="88" t="s">
-        <v>74</v>
-      </c>
-      <c r="G19" s="106"/>
-      <c r="H19" s="169" t="s">
-        <v>51</v>
-      </c>
-      <c r="I19" s="170"/>
-      <c r="J19" s="65"/>
-      <c r="K19" s="61"/>
-      <c r="L19" s="63"/>
-      <c r="M19" s="84"/>
-      <c r="N19" s="82"/>
-      <c r="O19" s="85"/>
-      <c r="P19" s="58"/>
-    </row>
-    <row r="20" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D20" s="52"/>
-      <c r="E20" s="172"/>
-      <c r="F20" s="89" t="s">
-        <v>76</v>
-      </c>
-      <c r="G20" s="107"/>
-      <c r="H20" s="111"/>
-      <c r="I20" s="71"/>
-      <c r="J20" s="94"/>
-      <c r="K20" s="72"/>
-      <c r="L20" s="97"/>
-      <c r="M20" s="69"/>
-      <c r="N20" s="68"/>
-      <c r="O20" s="71"/>
-      <c r="P20" s="58"/>
-    </row>
-    <row r="21" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D21" s="52"/>
-      <c r="E21" s="173"/>
-      <c r="F21" s="93" t="s">
-        <v>75</v>
-      </c>
-      <c r="G21" s="108"/>
-      <c r="H21" s="101"/>
-      <c r="I21" s="112"/>
-      <c r="J21" s="95"/>
-      <c r="K21" s="76"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="74"/>
-      <c r="N21" s="75"/>
-      <c r="O21" s="86"/>
-      <c r="P21" s="58"/>
-    </row>
-    <row r="22" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D22" s="52"/>
-      <c r="E22" s="171" t="s">
-        <v>97</v>
-      </c>
-      <c r="F22" s="88" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22" s="106"/>
-      <c r="H22" s="169" t="s">
-        <v>52</v>
-      </c>
-      <c r="I22" s="170"/>
-      <c r="J22" s="65"/>
-      <c r="K22" s="61"/>
-      <c r="L22" s="63"/>
-      <c r="M22" s="84"/>
-      <c r="N22" s="82"/>
-      <c r="O22" s="61"/>
-      <c r="P22" s="57"/>
-    </row>
-    <row r="23" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D23" s="52"/>
-      <c r="E23" s="172"/>
-      <c r="F23" s="89" t="s">
-        <v>63</v>
-      </c>
-      <c r="G23" s="107"/>
-      <c r="H23" s="113"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="94"/>
-      <c r="K23" s="72"/>
-      <c r="L23" s="97"/>
-      <c r="M23" s="69"/>
-      <c r="N23" s="68"/>
-      <c r="O23" s="72"/>
-      <c r="P23" s="57"/>
-    </row>
-    <row r="24" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D24" s="52"/>
-      <c r="E24" s="173"/>
-      <c r="F24" s="93" t="s">
-        <v>64</v>
-      </c>
-      <c r="G24" s="108"/>
-      <c r="H24" s="101"/>
-      <c r="I24" s="114"/>
-      <c r="J24" s="95"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="98"/>
-      <c r="M24" s="74"/>
-      <c r="N24" s="75"/>
-      <c r="O24" s="76"/>
-      <c r="P24" s="57"/>
-    </row>
-    <row r="25" spans="4:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D25" s="52"/>
-      <c r="E25" s="171" t="s">
-        <v>71</v>
-      </c>
-      <c r="F25" s="88" t="s">
-        <v>77</v>
-      </c>
-      <c r="G25" s="106"/>
-      <c r="H25" s="60" t="s">
-        <v>69</v>
-      </c>
-      <c r="I25" s="65"/>
-      <c r="J25" s="62"/>
-      <c r="K25" s="61"/>
-      <c r="L25" s="99"/>
-      <c r="M25" s="64"/>
-      <c r="N25" s="62"/>
-      <c r="O25" s="61"/>
-      <c r="P25" s="57"/>
-    </row>
-    <row r="26" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D26" s="52"/>
-      <c r="E26" s="172"/>
-      <c r="F26" s="89" t="s">
-        <v>70</v>
-      </c>
-      <c r="G26" s="107"/>
-      <c r="H26" s="115"/>
-      <c r="I26" s="94"/>
-      <c r="J26" s="67"/>
-      <c r="K26" s="72"/>
-      <c r="L26" s="100"/>
-      <c r="M26" s="70"/>
-      <c r="N26" s="67"/>
-      <c r="O26" s="72"/>
-      <c r="P26" s="57"/>
-    </row>
-    <row r="27" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D27" s="52"/>
-      <c r="E27" s="172"/>
-      <c r="F27" s="89" t="s">
-        <v>72</v>
-      </c>
-      <c r="G27" s="107"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="94"/>
-      <c r="J27" s="67"/>
-      <c r="K27" s="72"/>
-      <c r="L27" s="100"/>
-      <c r="M27" s="70"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="72"/>
-      <c r="P27" s="57"/>
-    </row>
-    <row r="28" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D28" s="52"/>
-      <c r="E28" s="172"/>
-      <c r="F28" s="89" t="s">
-        <v>73</v>
-      </c>
-      <c r="G28" s="107"/>
-      <c r="H28" s="115"/>
-      <c r="I28" s="94"/>
-      <c r="J28" s="67"/>
-      <c r="K28" s="72"/>
-      <c r="L28" s="100"/>
-      <c r="M28" s="70"/>
-      <c r="N28" s="67"/>
-      <c r="O28" s="72"/>
-      <c r="P28" s="57"/>
-    </row>
-    <row r="29" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D29" s="52"/>
-      <c r="E29" s="172"/>
-      <c r="F29" s="89" t="s">
-        <v>85</v>
-      </c>
-      <c r="G29" s="107"/>
-      <c r="H29" s="116"/>
-      <c r="I29" s="130"/>
-      <c r="J29" s="77"/>
-      <c r="K29" s="72"/>
-      <c r="L29" s="100"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="67"/>
-      <c r="O29" s="72"/>
-      <c r="P29" s="57"/>
-    </row>
-    <row r="30" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D30" s="52"/>
-      <c r="E30" s="172"/>
-      <c r="F30" s="90" t="s">
-        <v>80</v>
-      </c>
-      <c r="G30" s="97"/>
-      <c r="H30" s="66"/>
-      <c r="I30" s="169" t="s">
-        <v>69</v>
-      </c>
-      <c r="J30" s="170"/>
-      <c r="K30" s="126"/>
-      <c r="L30" s="100"/>
-      <c r="M30" s="70"/>
-      <c r="N30" s="67"/>
-      <c r="O30" s="72"/>
-      <c r="P30" s="57"/>
-    </row>
-    <row r="31" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D31" s="52"/>
-      <c r="E31" s="172"/>
-      <c r="F31" s="89" t="s">
-        <v>81</v>
-      </c>
-      <c r="G31" s="97"/>
-      <c r="H31" s="118"/>
-      <c r="I31" s="131"/>
-      <c r="J31" s="72"/>
-      <c r="K31" s="126"/>
-      <c r="L31" s="100"/>
-      <c r="M31" s="70"/>
-      <c r="N31" s="67"/>
-      <c r="O31" s="72"/>
-      <c r="P31" s="57"/>
-    </row>
-    <row r="32" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D32" s="52"/>
-      <c r="E32" s="172"/>
-      <c r="F32" s="89" t="s">
-        <v>78</v>
-      </c>
-      <c r="G32" s="97"/>
-      <c r="H32" s="118"/>
-      <c r="I32" s="97"/>
-      <c r="J32" s="132"/>
-      <c r="K32" s="126"/>
-      <c r="L32" s="100"/>
-      <c r="M32" s="70"/>
-      <c r="N32" s="67"/>
-      <c r="O32" s="72"/>
-      <c r="P32" s="57"/>
-    </row>
-    <row r="33" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D33" s="52"/>
-      <c r="E33" s="172"/>
-      <c r="F33" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="G33" s="97"/>
-      <c r="H33" s="118"/>
-      <c r="I33" s="97"/>
-      <c r="J33" s="132"/>
-      <c r="K33" s="126"/>
-      <c r="L33" s="100"/>
-      <c r="M33" s="70"/>
-      <c r="N33" s="67"/>
-      <c r="O33" s="72"/>
-      <c r="P33" s="57"/>
-    </row>
-    <row r="34" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D34" s="52"/>
-      <c r="E34" s="173"/>
-      <c r="F34" s="93" t="s">
-        <v>79</v>
-      </c>
-      <c r="G34" s="98"/>
-      <c r="H34" s="119"/>
-      <c r="I34" s="98"/>
-      <c r="J34" s="133"/>
-      <c r="K34" s="129"/>
-      <c r="L34" s="101"/>
-      <c r="M34" s="83"/>
-      <c r="N34" s="73"/>
-      <c r="O34" s="76"/>
-      <c r="P34" s="57"/>
-    </row>
-    <row r="35" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D35" s="52"/>
-      <c r="E35" s="166" t="s">
-        <v>47</v>
-      </c>
-      <c r="F35" s="88" t="s">
-        <v>87</v>
-      </c>
-      <c r="G35" s="63"/>
-      <c r="H35" s="62"/>
-      <c r="I35" s="62"/>
-      <c r="J35" s="117"/>
-      <c r="K35" s="120" t="s">
-        <v>47</v>
-      </c>
-      <c r="L35" s="99"/>
-      <c r="M35" s="64"/>
-      <c r="N35" s="62"/>
-      <c r="O35" s="61"/>
-      <c r="P35" s="57"/>
-    </row>
-    <row r="36" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="D36" s="52"/>
-      <c r="E36" s="167"/>
-      <c r="F36" s="89" t="s">
-        <v>83</v>
-      </c>
-      <c r="G36" s="97"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="67"/>
-      <c r="J36" s="118"/>
-      <c r="K36" s="121"/>
-      <c r="L36" s="100"/>
-      <c r="M36" s="70"/>
-      <c r="N36" s="67"/>
-      <c r="O36" s="72"/>
-      <c r="P36" s="57"/>
-    </row>
-    <row r="37" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D37" s="52"/>
-      <c r="E37" s="168"/>
-      <c r="F37" s="93" t="s">
-        <v>82</v>
-      </c>
-      <c r="G37" s="98"/>
-      <c r="H37" s="73"/>
-      <c r="I37" s="73"/>
-      <c r="J37" s="119"/>
-      <c r="K37" s="122"/>
-      <c r="L37" s="101"/>
-      <c r="M37" s="83"/>
-      <c r="N37" s="73"/>
-      <c r="O37" s="76"/>
-      <c r="P37" s="57"/>
-    </row>
-    <row r="38" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D38" s="52"/>
-      <c r="E38" s="166" t="s">
-        <v>86</v>
-      </c>
-      <c r="F38" s="88" t="s">
-        <v>88</v>
-      </c>
-      <c r="G38" s="63"/>
-      <c r="H38" s="62"/>
-      <c r="I38" s="62"/>
-      <c r="J38" s="62"/>
-      <c r="K38" s="61"/>
-      <c r="L38" s="120" t="s">
-        <v>21</v>
-      </c>
-      <c r="M38" s="123"/>
-      <c r="N38" s="127"/>
-      <c r="O38" s="61"/>
-      <c r="P38" s="57"/>
-    </row>
-    <row r="39" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D39" s="52"/>
-      <c r="E39" s="167"/>
-      <c r="F39" s="89" t="s">
-        <v>89</v>
-      </c>
-      <c r="G39" s="97"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="67"/>
-      <c r="J39" s="67"/>
-      <c r="K39" s="72"/>
-      <c r="L39" s="122"/>
-      <c r="M39" s="124"/>
-      <c r="N39" s="120" t="s">
-        <v>22</v>
-      </c>
-      <c r="O39" s="126"/>
-      <c r="P39" s="57"/>
-    </row>
-    <row r="40" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D40" s="52"/>
-      <c r="E40" s="167"/>
-      <c r="F40" s="89" t="s">
-        <v>92</v>
-      </c>
-      <c r="G40" s="97"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
-      <c r="J40" s="67"/>
-      <c r="K40" s="72"/>
-      <c r="L40" s="59"/>
-      <c r="M40" s="125"/>
-      <c r="N40" s="122"/>
-      <c r="O40" s="120" t="s">
-        <v>94</v>
-      </c>
-      <c r="P40" s="57"/>
-    </row>
-    <row r="41" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D41" s="52"/>
-      <c r="E41" s="168"/>
-      <c r="F41" s="93" t="s">
-        <v>93</v>
-      </c>
-      <c r="G41" s="98"/>
-      <c r="H41" s="73"/>
-      <c r="I41" s="73"/>
-      <c r="J41" s="73"/>
-      <c r="K41" s="76"/>
-      <c r="L41" s="98"/>
-      <c r="M41" s="74"/>
-      <c r="N41" s="128"/>
-      <c r="O41" s="122"/>
-      <c r="P41" s="57"/>
-    </row>
-    <row r="42" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D42" s="181"/>
-      <c r="F42" s="182"/>
-      <c r="G42" s="174" t="s">
-        <v>0</v>
-      </c>
-      <c r="H42" s="175"/>
-      <c r="I42" s="175"/>
-      <c r="J42" s="175"/>
-      <c r="K42" s="176"/>
-      <c r="L42" s="174" t="s">
-        <v>1</v>
-      </c>
-      <c r="M42" s="175"/>
-      <c r="N42" s="175"/>
-      <c r="O42" s="176"/>
-      <c r="P42" s="58"/>
-    </row>
-    <row r="43" spans="4:16" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D43" s="66"/>
-      <c r="E43" s="183"/>
-      <c r="F43" s="184" t="s">
-        <v>91</v>
-      </c>
-      <c r="G43" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="H43" s="186" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="186" t="s">
-        <v>4</v>
-      </c>
-      <c r="J43" s="186" t="s">
-        <v>5</v>
-      </c>
-      <c r="K43" s="187" t="s">
-        <v>6</v>
-      </c>
-      <c r="L43" s="185" t="s">
-        <v>2</v>
-      </c>
-      <c r="M43" s="188" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="186" t="s">
-        <v>7</v>
-      </c>
-      <c r="O43" s="187" t="s">
-        <v>8</v>
-      </c>
-      <c r="P43" s="56"/>
-    </row>
-    <row r="44" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="E44" s="189" t="s">
-        <v>102</v>
-      </c>
-      <c r="F44" s="49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="45" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="E45" s="191"/>
-      <c r="F45" s="50" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="46" spans="4:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E46" s="190"/>
-      <c r="F46" s="50" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="47" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E47" s="171" t="s">
-        <v>62</v>
-      </c>
-      <c r="F47" s="88" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="48" spans="4:16" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E48" s="172"/>
-      <c r="F48" s="89" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="49" spans="5:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E49" s="173"/>
-      <c r="F49" s="89" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" spans="5:6" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="F50" s="88" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="51" spans="5:6" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="F51" s="89" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="5:6" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="F52" s="89"/>
-    </row>
-  </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="G42:K42"/>
-    <mergeCell ref="L42:O42"/>
-    <mergeCell ref="E44:E46"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="L4:O4"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="E35:E37"/>
-    <mergeCell ref="E38:E41"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="E6:E15"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="E25:E34"/>
-  </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{733F8EEA-04B3-4913-A378-3DE8A4DDBF71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B3:U17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4185,50 +7399,50 @@
   <sheetData>
     <row r="3" spans="2:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B4" s="160" t="s">
+      <c r="B4" s="139" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="161"/>
-      <c r="D4" s="161"/>
-      <c r="E4" s="161"/>
-      <c r="F4" s="161"/>
-      <c r="G4" s="161"/>
-      <c r="H4" s="161"/>
-      <c r="I4" s="161"/>
-      <c r="J4" s="161"/>
-      <c r="K4" s="161"/>
-      <c r="L4" s="161"/>
-      <c r="M4" s="161"/>
-      <c r="N4" s="161"/>
-      <c r="O4" s="161"/>
-      <c r="P4" s="161"/>
-      <c r="Q4" s="161"/>
-      <c r="R4" s="161"/>
-      <c r="S4" s="162"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="140"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="140"/>
+      <c r="I4" s="140"/>
+      <c r="J4" s="140"/>
+      <c r="K4" s="140"/>
+      <c r="L4" s="140"/>
+      <c r="M4" s="140"/>
+      <c r="N4" s="140"/>
+      <c r="O4" s="140"/>
+      <c r="P4" s="140"/>
+      <c r="Q4" s="140"/>
+      <c r="R4" s="140"/>
+      <c r="S4" s="141"/>
     </row>
     <row r="5" spans="2:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="163"/>
-      <c r="C5" s="164"/>
-      <c r="D5" s="164"/>
-      <c r="E5" s="164"/>
-      <c r="F5" s="164"/>
-      <c r="G5" s="164"/>
-      <c r="H5" s="164"/>
-      <c r="I5" s="164"/>
-      <c r="J5" s="164"/>
-      <c r="K5" s="164"/>
-      <c r="L5" s="164"/>
-      <c r="M5" s="164"/>
-      <c r="N5" s="164"/>
-      <c r="O5" s="164"/>
-      <c r="P5" s="164"/>
-      <c r="Q5" s="164"/>
-      <c r="R5" s="164"/>
-      <c r="S5" s="165"/>
+      <c r="B5" s="142"/>
+      <c r="C5" s="143"/>
+      <c r="D5" s="143"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="143"/>
+      <c r="G5" s="143"/>
+      <c r="H5" s="143"/>
+      <c r="I5" s="143"/>
+      <c r="J5" s="143"/>
+      <c r="K5" s="143"/>
+      <c r="L5" s="143"/>
+      <c r="M5" s="143"/>
+      <c r="N5" s="143"/>
+      <c r="O5" s="143"/>
+      <c r="P5" s="143"/>
+      <c r="Q5" s="143"/>
+      <c r="R5" s="143"/>
+      <c r="S5" s="144"/>
     </row>
     <row r="6" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="177"/>
-      <c r="C6" s="180" t="s">
+      <c r="B6" s="172"/>
+      <c r="C6" s="175" t="s">
         <v>24</v>
       </c>
       <c r="D6" t="s">
@@ -4251,8 +7465,8 @@
       <c r="S6" s="32"/>
     </row>
     <row r="7" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="178"/>
-      <c r="C7" s="179"/>
+      <c r="B7" s="173"/>
+      <c r="C7" s="174"/>
       <c r="D7" t="s">
         <v>26</v>
       </c>
@@ -4261,8 +7475,8 @@
       </c>
     </row>
     <row r="8" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="178"/>
-      <c r="C8" s="179"/>
+      <c r="B8" s="173"/>
+      <c r="C8" s="174"/>
       <c r="D8" t="s">
         <v>28</v>
       </c>
@@ -4271,7 +7485,7 @@
       </c>
     </row>
     <row r="9" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="178"/>
+      <c r="B9" s="173"/>
       <c r="C9" s="10" t="s">
         <v>19</v>
       </c>
@@ -4283,8 +7497,8 @@
       </c>
     </row>
     <row r="10" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="178"/>
-      <c r="C10" s="179" t="s">
+      <c r="B10" s="173"/>
+      <c r="C10" s="174" t="s">
         <v>17</v>
       </c>
       <c r="D10" t="s">
@@ -4292,15 +7506,15 @@
       </c>
     </row>
     <row r="11" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="178"/>
-      <c r="C11" s="179"/>
+      <c r="B11" s="173"/>
+      <c r="C11" s="174"/>
       <c r="D11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="178"/>
-      <c r="C12" s="179" t="s">
+      <c r="B12" s="173"/>
+      <c r="C12" s="174" t="s">
         <v>18</v>
       </c>
       <c r="D12" t="s">
@@ -4311,8 +7525,8 @@
       </c>
     </row>
     <row r="13" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="178"/>
-      <c r="C13" s="179"/>
+      <c r="B13" s="173"/>
+      <c r="C13" s="174"/>
       <c r="D13" t="s">
         <v>30</v>
       </c>
@@ -4321,8 +7535,8 @@
       </c>
     </row>
     <row r="14" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="178"/>
-      <c r="C14" s="179"/>
+      <c r="B14" s="173"/>
+      <c r="C14" s="174"/>
       <c r="D14" t="s">
         <v>29</v>
       </c>
@@ -4331,8 +7545,8 @@
       </c>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B15" s="178"/>
-      <c r="C15" s="179"/>
+      <c r="B15" s="173"/>
+      <c r="C15" s="174"/>
       <c r="D15" t="s">
         <v>33</v>
       </c>

--- a/doc/시스템사업부_프로젝트 개발 일정표.xlsx
+++ b/doc/시스템사업부_프로젝트 개발 일정표.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JUNG\Desktop\web_git\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\web_git\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAC0504-676C-4491-AFED-C90B99E9ACBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="-120" windowWidth="21840" windowHeight="38640"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="개발일정표" sheetId="4" r:id="rId1"/>
@@ -21,17 +22,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -685,7 +675,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="mm\/dd"/>
@@ -1912,7 +1902,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="347">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2202,7 +2192,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2223,155 +2213,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2387,15 +2230,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="75" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="75" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2404,15 +2238,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="50" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2446,11 +2271,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1">
@@ -2487,32 +2312,17 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2523,9 +2333,6 @@
     </xf>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
@@ -2562,7 +2369,7 @@
     <xf numFmtId="176" fontId="6" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
@@ -2572,16 +2379,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="71" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="6" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2763,11 +2569,194 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="36" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표 [0] 2" xfId="2"/>
+    <cellStyle name="쉼표 [0] 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="1"/>
+    <cellStyle name="표준 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3044,7 +3033,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="D3:X127"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3054,31 +3046,31 @@
   <sheetData>
     <row r="3" spans="4:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="4:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G4" s="164" t="s">
+      <c r="G4" s="310" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="165"/>
-      <c r="I4" s="165"/>
-      <c r="J4" s="165"/>
-      <c r="K4" s="165"/>
-      <c r="L4" s="164" t="s">
+      <c r="H4" s="309"/>
+      <c r="I4" s="309"/>
+      <c r="J4" s="309"/>
+      <c r="K4" s="309"/>
+      <c r="L4" s="310" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="165"/>
-      <c r="N4" s="165"/>
-      <c r="O4" s="166"/>
-      <c r="P4" s="165" t="s">
+      <c r="M4" s="309"/>
+      <c r="N4" s="309"/>
+      <c r="O4" s="311"/>
+      <c r="P4" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="Q4" s="165"/>
-      <c r="R4" s="165"/>
-      <c r="S4" s="165"/>
-      <c r="T4" s="194" t="s">
+      <c r="Q4" s="309"/>
+      <c r="R4" s="309"/>
+      <c r="S4" s="309"/>
+      <c r="T4" s="303" t="s">
         <v>13</v>
       </c>
-      <c r="U4" s="195"/>
-      <c r="V4" s="195"/>
-      <c r="W4" s="196"/>
+      <c r="U4" s="304"/>
+      <c r="V4" s="304"/>
+      <c r="W4" s="305"/>
     </row>
     <row r="5" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D5" s="49"/>
@@ -3098,7 +3090,7 @@
       <c r="J5" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="197" t="s">
+      <c r="K5" s="142" t="s">
         <v>6</v>
       </c>
       <c r="L5" s="93" t="s">
@@ -3113,7 +3105,7 @@
       <c r="O5" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="P5" s="249" t="s">
+      <c r="P5" s="189" t="s">
         <v>2</v>
       </c>
       <c r="Q5" s="76" t="s">
@@ -3122,25 +3114,25 @@
       <c r="R5" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="S5" s="197" t="s">
+      <c r="S5" s="142" t="s">
         <v>5</v>
       </c>
-      <c r="T5" s="262" t="s">
+      <c r="T5" s="201" t="s">
         <v>2</v>
       </c>
-      <c r="U5" s="233" t="s">
+      <c r="U5" s="178" t="s">
         <v>3</v>
       </c>
-      <c r="V5" s="233" t="s">
+      <c r="V5" s="178" t="s">
         <v>4</v>
       </c>
-      <c r="W5" s="263" t="s">
+      <c r="W5" s="202" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="4:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D6" s="49"/>
-      <c r="E6" s="162" t="s">
+      <c r="E6" s="312" t="s">
         <v>90</v>
       </c>
       <c r="F6" s="85" t="s">
@@ -3157,10 +3149,10 @@
       <c r="M6" s="81"/>
       <c r="N6" s="79"/>
       <c r="O6" s="82"/>
-      <c r="P6" s="250"/>
+      <c r="P6" s="190"/>
       <c r="Q6" s="79"/>
       <c r="R6" s="79"/>
-      <c r="S6" s="198"/>
+      <c r="S6" s="143"/>
       <c r="T6" s="96"/>
       <c r="U6" s="79"/>
       <c r="V6" s="79"/>
@@ -3168,7 +3160,7 @@
     </row>
     <row r="7" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D7" s="49"/>
-      <c r="E7" s="163"/>
+      <c r="E7" s="313"/>
       <c r="F7" s="86" t="s">
         <v>59</v>
       </c>
@@ -3184,7 +3176,7 @@
       <c r="P7" s="54"/>
       <c r="Q7" s="65"/>
       <c r="R7" s="65"/>
-      <c r="S7" s="199"/>
+      <c r="S7" s="144"/>
       <c r="T7" s="97"/>
       <c r="U7" s="65"/>
       <c r="V7" s="65"/>
@@ -3192,7 +3184,7 @@
     </row>
     <row r="8" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D8" s="49"/>
-      <c r="E8" s="163"/>
+      <c r="E8" s="313"/>
       <c r="F8" s="86" t="s">
         <v>60</v>
       </c>
@@ -3208,7 +3200,7 @@
       <c r="P8" s="54"/>
       <c r="Q8" s="65"/>
       <c r="R8" s="65"/>
-      <c r="S8" s="199"/>
+      <c r="S8" s="144"/>
       <c r="T8" s="97"/>
       <c r="U8" s="65"/>
       <c r="V8" s="65"/>
@@ -3216,11 +3208,11 @@
     </row>
     <row r="9" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D9" s="49"/>
-      <c r="E9" s="163"/>
+      <c r="E9" s="313"/>
       <c r="F9" s="86" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="193"/>
+      <c r="G9" s="141"/>
       <c r="H9" s="92"/>
       <c r="I9" s="70"/>
       <c r="J9" s="70"/>
@@ -3229,10 +3221,10 @@
       <c r="M9" s="71"/>
       <c r="N9" s="72"/>
       <c r="O9" s="83"/>
-      <c r="P9" s="208"/>
+      <c r="P9" s="153"/>
       <c r="Q9" s="72"/>
       <c r="R9" s="72"/>
-      <c r="S9" s="248"/>
+      <c r="S9" s="188"/>
       <c r="T9" s="98"/>
       <c r="U9" s="72"/>
       <c r="V9" s="72"/>
@@ -3240,7 +3232,7 @@
     </row>
     <row r="10" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D10" s="49"/>
-      <c r="E10" s="163"/>
+      <c r="E10" s="313"/>
       <c r="F10" s="87" t="s">
         <v>49</v>
       </c>
@@ -3255,10 +3247,10 @@
       <c r="M10" s="81"/>
       <c r="N10" s="79"/>
       <c r="O10" s="82"/>
-      <c r="P10" s="250"/>
+      <c r="P10" s="190"/>
       <c r="Q10" s="79"/>
       <c r="R10" s="79"/>
-      <c r="S10" s="198"/>
+      <c r="S10" s="143"/>
       <c r="T10" s="96"/>
       <c r="U10" s="79"/>
       <c r="V10" s="79"/>
@@ -3266,7 +3258,7 @@
     </row>
     <row r="11" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D11" s="49"/>
-      <c r="E11" s="163"/>
+      <c r="E11" s="313"/>
       <c r="F11" s="88" t="s">
         <v>54</v>
       </c>
@@ -3282,7 +3274,7 @@
       <c r="P11" s="54"/>
       <c r="Q11" s="65"/>
       <c r="R11" s="65"/>
-      <c r="S11" s="199"/>
+      <c r="S11" s="144"/>
       <c r="T11" s="97"/>
       <c r="U11" s="65"/>
       <c r="V11" s="65"/>
@@ -3290,7 +3282,7 @@
     </row>
     <row r="12" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D12" s="49"/>
-      <c r="E12" s="163"/>
+      <c r="E12" s="313"/>
       <c r="F12" s="88" t="s">
         <v>53</v>
       </c>
@@ -3306,7 +3298,7 @@
       <c r="P12" s="54"/>
       <c r="Q12" s="65"/>
       <c r="R12" s="65"/>
-      <c r="S12" s="199"/>
+      <c r="S12" s="144"/>
       <c r="T12" s="97"/>
       <c r="U12" s="65"/>
       <c r="V12" s="65"/>
@@ -3314,7 +3306,7 @@
     </row>
     <row r="13" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D13" s="49"/>
-      <c r="E13" s="163"/>
+      <c r="E13" s="313"/>
       <c r="F13" s="88" t="s">
         <v>55</v>
       </c>
@@ -3330,7 +3322,7 @@
       <c r="P13" s="54"/>
       <c r="Q13" s="65"/>
       <c r="R13" s="65"/>
-      <c r="S13" s="199"/>
+      <c r="S13" s="144"/>
       <c r="T13" s="97"/>
       <c r="U13" s="65"/>
       <c r="V13" s="65"/>
@@ -3338,7 +3330,7 @@
     </row>
     <row r="14" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D14" s="49"/>
-      <c r="E14" s="163"/>
+      <c r="E14" s="313"/>
       <c r="F14" s="88" t="s">
         <v>56</v>
       </c>
@@ -3351,10 +3343,10 @@
       <c r="M14" s="71"/>
       <c r="N14" s="72"/>
       <c r="O14" s="83"/>
-      <c r="P14" s="208"/>
+      <c r="P14" s="153"/>
       <c r="Q14" s="72"/>
       <c r="R14" s="72"/>
-      <c r="S14" s="248"/>
+      <c r="S14" s="188"/>
       <c r="T14" s="98"/>
       <c r="U14" s="72"/>
       <c r="V14" s="72"/>
@@ -3362,27 +3354,27 @@
     </row>
     <row r="15" spans="4:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D15" s="49"/>
-      <c r="E15" s="178" t="s">
+      <c r="E15" s="292" t="s">
         <v>62</v>
       </c>
       <c r="F15" s="85" t="s">
         <v>66</v>
       </c>
       <c r="G15" s="102"/>
-      <c r="H15" s="167" t="s">
+      <c r="H15" s="286" t="s">
         <v>17</v>
       </c>
-      <c r="I15" s="168"/>
+      <c r="I15" s="288"/>
       <c r="J15" s="62"/>
       <c r="K15" s="112"/>
       <c r="L15" s="60"/>
       <c r="M15" s="81"/>
       <c r="N15" s="79"/>
       <c r="O15" s="82"/>
-      <c r="P15" s="250"/>
+      <c r="P15" s="190"/>
       <c r="Q15" s="79"/>
       <c r="R15" s="79"/>
-      <c r="S15" s="198"/>
+      <c r="S15" s="143"/>
       <c r="T15" s="96"/>
       <c r="U15" s="79"/>
       <c r="V15" s="79"/>
@@ -3390,7 +3382,7 @@
     </row>
     <row r="16" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D16" s="49"/>
-      <c r="E16" s="179"/>
+      <c r="E16" s="293"/>
       <c r="F16" s="86" t="s">
         <v>64</v>
       </c>
@@ -3398,7 +3390,7 @@
       <c r="H16" s="104"/>
       <c r="I16" s="68"/>
       <c r="J16" s="91"/>
-      <c r="K16" s="185"/>
+      <c r="K16" s="136"/>
       <c r="L16" s="94"/>
       <c r="M16" s="66"/>
       <c r="N16" s="65"/>
@@ -3406,7 +3398,7 @@
       <c r="P16" s="54"/>
       <c r="Q16" s="65"/>
       <c r="R16" s="65"/>
-      <c r="S16" s="199"/>
+      <c r="S16" s="144"/>
       <c r="T16" s="97"/>
       <c r="U16" s="65"/>
       <c r="V16" s="65"/>
@@ -3414,15 +3406,15 @@
     </row>
     <row r="17" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D17" s="49"/>
-      <c r="E17" s="179"/>
-      <c r="F17" s="219" t="s">
+      <c r="E17" s="293"/>
+      <c r="F17" s="164" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="103"/>
       <c r="H17" s="98"/>
       <c r="I17" s="105"/>
-      <c r="J17" s="290"/>
-      <c r="K17" s="291" t="s">
+      <c r="J17" s="228"/>
+      <c r="K17" s="229" t="s">
         <v>98</v>
       </c>
       <c r="L17" s="91"/>
@@ -3432,7 +3424,7 @@
       <c r="P17" s="54"/>
       <c r="Q17" s="65"/>
       <c r="R17" s="65"/>
-      <c r="S17" s="199"/>
+      <c r="S17" s="144"/>
       <c r="T17" s="97"/>
       <c r="U17" s="65"/>
       <c r="V17" s="65"/>
@@ -3440,23 +3432,23 @@
     </row>
     <row r="18" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D18" s="49"/>
-      <c r="E18" s="180"/>
-      <c r="F18" s="213" t="s">
+      <c r="E18" s="294"/>
+      <c r="F18" s="158" t="s">
         <v>111</v>
       </c>
       <c r="G18" s="95"/>
-      <c r="H18" s="176"/>
-      <c r="I18" s="176"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="130"/>
       <c r="J18" s="114"/>
-      <c r="K18" s="293"/>
+      <c r="K18" s="231"/>
       <c r="L18" s="92"/>
       <c r="M18" s="71"/>
       <c r="N18" s="72"/>
       <c r="O18" s="83"/>
-      <c r="P18" s="208"/>
+      <c r="P18" s="153"/>
       <c r="Q18" s="72"/>
       <c r="R18" s="72"/>
-      <c r="S18" s="248"/>
+      <c r="S18" s="188"/>
       <c r="T18" s="98"/>
       <c r="U18" s="72"/>
       <c r="V18" s="72"/>
@@ -3464,27 +3456,27 @@
     </row>
     <row r="19" spans="4:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D19" s="49"/>
-      <c r="E19" s="178" t="s">
+      <c r="E19" s="292" t="s">
         <v>91</v>
       </c>
       <c r="F19" s="85" t="s">
         <v>71</v>
       </c>
       <c r="G19" s="102"/>
-      <c r="H19" s="167" t="s">
+      <c r="H19" s="286" t="s">
         <v>51</v>
       </c>
-      <c r="I19" s="168"/>
+      <c r="I19" s="288"/>
       <c r="J19" s="62"/>
-      <c r="K19" s="243"/>
+      <c r="K19" s="184"/>
       <c r="L19" s="60"/>
       <c r="M19" s="81"/>
       <c r="N19" s="79"/>
       <c r="O19" s="82"/>
-      <c r="P19" s="250"/>
+      <c r="P19" s="190"/>
       <c r="Q19" s="79"/>
       <c r="R19" s="79"/>
-      <c r="S19" s="198"/>
+      <c r="S19" s="143"/>
       <c r="T19" s="96"/>
       <c r="U19" s="79"/>
       <c r="V19" s="79"/>
@@ -3492,7 +3484,7 @@
     </row>
     <row r="20" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D20" s="49"/>
-      <c r="E20" s="179"/>
+      <c r="E20" s="293"/>
       <c r="F20" s="86" t="s">
         <v>73</v>
       </c>
@@ -3500,7 +3492,7 @@
       <c r="H20" s="106"/>
       <c r="I20" s="68"/>
       <c r="J20" s="91"/>
-      <c r="K20" s="185"/>
+      <c r="K20" s="136"/>
       <c r="L20" s="94"/>
       <c r="M20" s="66"/>
       <c r="N20" s="65"/>
@@ -3508,7 +3500,7 @@
       <c r="P20" s="54"/>
       <c r="Q20" s="65"/>
       <c r="R20" s="65"/>
-      <c r="S20" s="199"/>
+      <c r="S20" s="144"/>
       <c r="T20" s="97"/>
       <c r="U20" s="65"/>
       <c r="V20" s="65"/>
@@ -3516,15 +3508,15 @@
     </row>
     <row r="21" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D21" s="49"/>
-      <c r="E21" s="179"/>
-      <c r="F21" s="219" t="s">
+      <c r="E21" s="293"/>
+      <c r="F21" s="164" t="s">
         <v>72</v>
       </c>
       <c r="G21" s="103"/>
       <c r="H21" s="98"/>
       <c r="I21" s="107"/>
-      <c r="J21" s="290"/>
-      <c r="K21" s="291" t="s">
+      <c r="J21" s="228"/>
+      <c r="K21" s="229" t="s">
         <v>97</v>
       </c>
       <c r="L21" s="91"/>
@@ -3534,7 +3526,7 @@
       <c r="P21" s="54"/>
       <c r="Q21" s="65"/>
       <c r="R21" s="65"/>
-      <c r="S21" s="199"/>
+      <c r="S21" s="144"/>
       <c r="T21" s="97"/>
       <c r="U21" s="65"/>
       <c r="V21" s="65"/>
@@ -3542,23 +3534,23 @@
     </row>
     <row r="22" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D22" s="49"/>
-      <c r="E22" s="180"/>
-      <c r="F22" s="213" t="s">
+      <c r="E22" s="294"/>
+      <c r="F22" s="158" t="s">
         <v>111</v>
       </c>
       <c r="G22" s="95"/>
-      <c r="H22" s="176"/>
-      <c r="I22" s="176"/>
+      <c r="H22" s="130"/>
+      <c r="I22" s="130"/>
       <c r="J22" s="114"/>
-      <c r="K22" s="205"/>
+      <c r="K22" s="150"/>
       <c r="L22" s="92"/>
       <c r="M22" s="71"/>
       <c r="N22" s="72"/>
       <c r="O22" s="83"/>
-      <c r="P22" s="208"/>
+      <c r="P22" s="153"/>
       <c r="Q22" s="72"/>
       <c r="R22" s="72"/>
-      <c r="S22" s="248"/>
+      <c r="S22" s="188"/>
       <c r="T22" s="98"/>
       <c r="U22" s="72"/>
       <c r="V22" s="72"/>
@@ -3566,26 +3558,26 @@
     </row>
     <row r="23" spans="4:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D23" s="49"/>
-      <c r="E23" s="178" t="s">
+      <c r="E23" s="292" t="s">
         <v>92</v>
       </c>
       <c r="F23" s="85" t="s">
         <v>115</v>
       </c>
-      <c r="G23" s="288"/>
-      <c r="H23" s="167" t="s">
+      <c r="G23" s="226"/>
+      <c r="H23" s="286" t="s">
         <v>52</v>
       </c>
-      <c r="I23" s="168"/>
+      <c r="I23" s="288"/>
       <c r="J23" s="53"/>
-      <c r="K23" s="243"/>
+      <c r="K23" s="184"/>
       <c r="L23" s="56"/>
-      <c r="M23" s="231"/>
-      <c r="N23" s="228"/>
-      <c r="O23" s="255"/>
+      <c r="M23" s="176"/>
+      <c r="N23" s="173"/>
+      <c r="O23" s="194"/>
       <c r="P23" s="55"/>
-      <c r="Q23" s="228"/>
-      <c r="R23" s="228"/>
+      <c r="Q23" s="173"/>
+      <c r="R23" s="173"/>
       <c r="S23" s="63"/>
       <c r="T23" s="96"/>
       <c r="U23" s="79"/>
@@ -3594,7 +3586,7 @@
     </row>
     <row r="24" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D24" s="49"/>
-      <c r="E24" s="179"/>
+      <c r="E24" s="293"/>
       <c r="F24" s="86" t="s">
         <v>63</v>
       </c>
@@ -3602,7 +3594,7 @@
       <c r="H24" s="108"/>
       <c r="I24" s="68"/>
       <c r="J24" s="91"/>
-      <c r="K24" s="185"/>
+      <c r="K24" s="136"/>
       <c r="L24" s="94"/>
       <c r="M24" s="66"/>
       <c r="N24" s="65"/>
@@ -3610,7 +3602,7 @@
       <c r="P24" s="54"/>
       <c r="Q24" s="65"/>
       <c r="R24" s="65"/>
-      <c r="S24" s="199"/>
+      <c r="S24" s="144"/>
       <c r="T24" s="97"/>
       <c r="U24" s="65"/>
       <c r="V24" s="65"/>
@@ -3618,15 +3610,15 @@
     </row>
     <row r="25" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D25" s="49"/>
-      <c r="E25" s="179"/>
-      <c r="F25" s="181" t="s">
+      <c r="E25" s="293"/>
+      <c r="F25" s="132" t="s">
         <v>116</v>
       </c>
       <c r="G25" s="103"/>
       <c r="H25" s="98"/>
       <c r="I25" s="109"/>
-      <c r="J25" s="290"/>
-      <c r="K25" s="291" t="s">
+      <c r="J25" s="228"/>
+      <c r="K25" s="229" t="s">
         <v>96</v>
       </c>
       <c r="L25" s="91"/>
@@ -3636,7 +3628,7 @@
       <c r="P25" s="54"/>
       <c r="Q25" s="65"/>
       <c r="R25" s="65"/>
-      <c r="S25" s="199"/>
+      <c r="S25" s="144"/>
       <c r="T25" s="97"/>
       <c r="U25" s="65"/>
       <c r="V25" s="65"/>
@@ -3644,23 +3636,23 @@
     </row>
     <row r="26" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D26" s="49"/>
-      <c r="E26" s="180"/>
-      <c r="F26" s="213" t="s">
+      <c r="E26" s="294"/>
+      <c r="F26" s="158" t="s">
         <v>111</v>
       </c>
       <c r="G26" s="95"/>
-      <c r="H26" s="176"/>
+      <c r="H26" s="130"/>
       <c r="I26" s="117"/>
       <c r="J26" s="114"/>
-      <c r="K26" s="292"/>
+      <c r="K26" s="230"/>
       <c r="L26" s="92"/>
       <c r="M26" s="71"/>
       <c r="N26" s="72"/>
       <c r="O26" s="73"/>
-      <c r="P26" s="208"/>
+      <c r="P26" s="153"/>
       <c r="Q26" s="72"/>
       <c r="R26" s="72"/>
-      <c r="S26" s="248"/>
+      <c r="S26" s="188"/>
       <c r="T26" s="98"/>
       <c r="U26" s="72"/>
       <c r="V26" s="72"/>
@@ -3668,7 +3660,7 @@
     </row>
     <row r="27" spans="4:23" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D27" s="49"/>
-      <c r="E27" s="178" t="s">
+      <c r="E27" s="292" t="s">
         <v>112</v>
       </c>
       <c r="F27" s="85" t="s">
@@ -3680,15 +3672,15 @@
       </c>
       <c r="I27" s="62"/>
       <c r="J27" s="59"/>
-      <c r="K27" s="243"/>
+      <c r="K27" s="184"/>
       <c r="L27" s="96"/>
       <c r="M27" s="61"/>
       <c r="N27" s="59"/>
       <c r="O27" s="58"/>
-      <c r="P27" s="250"/>
+      <c r="P27" s="190"/>
       <c r="Q27" s="79"/>
       <c r="R27" s="79"/>
-      <c r="S27" s="198"/>
+      <c r="S27" s="143"/>
       <c r="T27" s="96"/>
       <c r="U27" s="79"/>
       <c r="V27" s="79"/>
@@ -3696,7 +3688,7 @@
     </row>
     <row r="28" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D28" s="49"/>
-      <c r="E28" s="179"/>
+      <c r="E28" s="293"/>
       <c r="F28" s="86" t="s">
         <v>68</v>
       </c>
@@ -3712,7 +3704,7 @@
       <c r="P28" s="54"/>
       <c r="Q28" s="65"/>
       <c r="R28" s="65"/>
-      <c r="S28" s="199"/>
+      <c r="S28" s="144"/>
       <c r="T28" s="97"/>
       <c r="U28" s="65"/>
       <c r="V28" s="65"/>
@@ -3720,7 +3712,7 @@
     </row>
     <row r="29" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D29" s="49"/>
-      <c r="E29" s="179"/>
+      <c r="E29" s="293"/>
       <c r="F29" s="86" t="s">
         <v>69</v>
       </c>
@@ -3736,7 +3728,7 @@
       <c r="P29" s="54"/>
       <c r="Q29" s="65"/>
       <c r="R29" s="65"/>
-      <c r="S29" s="199"/>
+      <c r="S29" s="144"/>
       <c r="T29" s="97"/>
       <c r="U29" s="65"/>
       <c r="V29" s="65"/>
@@ -3744,7 +3736,7 @@
     </row>
     <row r="30" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D30" s="49"/>
-      <c r="E30" s="179"/>
+      <c r="E30" s="293"/>
       <c r="F30" s="86" t="s">
         <v>70</v>
       </c>
@@ -3760,7 +3752,7 @@
       <c r="P30" s="54"/>
       <c r="Q30" s="65"/>
       <c r="R30" s="65"/>
-      <c r="S30" s="199"/>
+      <c r="S30" s="144"/>
       <c r="T30" s="97"/>
       <c r="U30" s="65"/>
       <c r="V30" s="65"/>
@@ -3768,7 +3760,7 @@
     </row>
     <row r="31" spans="4:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D31" s="49"/>
-      <c r="E31" s="179"/>
+      <c r="E31" s="293"/>
       <c r="F31" s="86" t="s">
         <v>81</v>
       </c>
@@ -3784,7 +3776,7 @@
       <c r="P31" s="54"/>
       <c r="Q31" s="65"/>
       <c r="R31" s="65"/>
-      <c r="S31" s="199"/>
+      <c r="S31" s="144"/>
       <c r="T31" s="97"/>
       <c r="U31" s="65"/>
       <c r="V31" s="65"/>
@@ -3792,17 +3784,17 @@
     </row>
     <row r="32" spans="4:23" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D32" s="49"/>
-      <c r="E32" s="179"/>
+      <c r="E32" s="293"/>
       <c r="F32" s="87" t="s">
         <v>114</v>
       </c>
       <c r="G32" s="94"/>
       <c r="H32" s="63"/>
-      <c r="I32" s="167" t="s">
+      <c r="I32" s="286" t="s">
         <v>67</v>
       </c>
-      <c r="J32" s="168"/>
-      <c r="K32" s="290"/>
+      <c r="J32" s="288"/>
+      <c r="K32" s="228"/>
       <c r="L32" s="97"/>
       <c r="M32" s="67"/>
       <c r="N32" s="64"/>
@@ -3810,7 +3802,7 @@
       <c r="P32" s="54"/>
       <c r="Q32" s="65"/>
       <c r="R32" s="65"/>
-      <c r="S32" s="199"/>
+      <c r="S32" s="144"/>
       <c r="T32" s="97"/>
       <c r="U32" s="65"/>
       <c r="V32" s="65"/>
@@ -3818,7 +3810,7 @@
     </row>
     <row r="33" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D33" s="49"/>
-      <c r="E33" s="179"/>
+      <c r="E33" s="293"/>
       <c r="F33" s="86" t="s">
         <v>77</v>
       </c>
@@ -3826,7 +3818,7 @@
       <c r="H33" s="113"/>
       <c r="I33" s="119"/>
       <c r="J33" s="69"/>
-      <c r="K33" s="290"/>
+      <c r="K33" s="228"/>
       <c r="L33" s="97"/>
       <c r="M33" s="67"/>
       <c r="N33" s="64"/>
@@ -3834,7 +3826,7 @@
       <c r="P33" s="54"/>
       <c r="Q33" s="65"/>
       <c r="R33" s="65"/>
-      <c r="S33" s="199"/>
+      <c r="S33" s="144"/>
       <c r="T33" s="97"/>
       <c r="U33" s="65"/>
       <c r="V33" s="65"/>
@@ -3842,7 +3834,7 @@
     </row>
     <row r="34" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D34" s="49"/>
-      <c r="E34" s="179"/>
+      <c r="E34" s="293"/>
       <c r="F34" s="86" t="s">
         <v>75</v>
       </c>
@@ -3850,7 +3842,7 @@
       <c r="H34" s="113"/>
       <c r="I34" s="94"/>
       <c r="J34" s="120"/>
-      <c r="K34" s="290"/>
+      <c r="K34" s="228"/>
       <c r="L34" s="97"/>
       <c r="M34" s="67"/>
       <c r="N34" s="64"/>
@@ -3858,7 +3850,7 @@
       <c r="P34" s="54"/>
       <c r="Q34" s="65"/>
       <c r="R34" s="65"/>
-      <c r="S34" s="199"/>
+      <c r="S34" s="144"/>
       <c r="T34" s="97"/>
       <c r="U34" s="65"/>
       <c r="V34" s="65"/>
@@ -3866,7 +3858,7 @@
     </row>
     <row r="35" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D35" s="49"/>
-      <c r="E35" s="179"/>
+      <c r="E35" s="293"/>
       <c r="F35" s="86" t="s">
         <v>80</v>
       </c>
@@ -3874,7 +3866,7 @@
       <c r="H35" s="113"/>
       <c r="I35" s="94"/>
       <c r="J35" s="120"/>
-      <c r="K35" s="186"/>
+      <c r="K35" s="137"/>
       <c r="L35" s="97"/>
       <c r="M35" s="67"/>
       <c r="N35" s="64"/>
@@ -3882,7 +3874,7 @@
       <c r="P35" s="54"/>
       <c r="Q35" s="65"/>
       <c r="R35" s="65"/>
-      <c r="S35" s="199"/>
+      <c r="S35" s="144"/>
       <c r="T35" s="97"/>
       <c r="U35" s="65"/>
       <c r="V35" s="65"/>
@@ -3890,25 +3882,25 @@
     </row>
     <row r="36" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D36" s="49"/>
-      <c r="E36" s="179"/>
-      <c r="F36" s="181" t="s">
+      <c r="E36" s="293"/>
+      <c r="F36" s="132" t="s">
         <v>76</v>
       </c>
       <c r="G36" s="94"/>
       <c r="H36" s="113"/>
       <c r="I36" s="95"/>
       <c r="J36" s="121"/>
-      <c r="K36" s="291" t="s">
+      <c r="K36" s="229" t="s">
         <v>95</v>
       </c>
-      <c r="L36" s="253"/>
+      <c r="L36" s="192"/>
       <c r="M36" s="67"/>
       <c r="N36" s="64"/>
       <c r="O36" s="69"/>
       <c r="P36" s="54"/>
       <c r="Q36" s="65"/>
       <c r="R36" s="65"/>
-      <c r="S36" s="199"/>
+      <c r="S36" s="144"/>
       <c r="T36" s="97"/>
       <c r="U36" s="65"/>
       <c r="V36" s="65"/>
@@ -3916,23 +3908,23 @@
     </row>
     <row r="37" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D37" s="49"/>
-      <c r="E37" s="180"/>
-      <c r="F37" s="213" t="s">
+      <c r="E37" s="294"/>
+      <c r="F37" s="158" t="s">
         <v>111</v>
       </c>
       <c r="G37" s="95"/>
       <c r="H37" s="70"/>
-      <c r="I37" s="212"/>
-      <c r="J37" s="207"/>
+      <c r="I37" s="157"/>
+      <c r="J37" s="152"/>
       <c r="K37" s="111"/>
-      <c r="L37" s="254"/>
+      <c r="L37" s="193"/>
       <c r="M37" s="80"/>
       <c r="N37" s="70"/>
       <c r="O37" s="73"/>
-      <c r="P37" s="208"/>
+      <c r="P37" s="153"/>
       <c r="Q37" s="72"/>
       <c r="R37" s="72"/>
-      <c r="S37" s="248"/>
+      <c r="S37" s="188"/>
       <c r="T37" s="98"/>
       <c r="U37" s="72"/>
       <c r="V37" s="72"/>
@@ -3940,7 +3932,7 @@
     </row>
     <row r="38" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D38" s="49"/>
-      <c r="E38" s="169" t="s">
+      <c r="E38" s="295" t="s">
         <v>47</v>
       </c>
       <c r="F38" s="85" t="s">
@@ -3953,14 +3945,14 @@
       <c r="K38" s="115" t="s">
         <v>47</v>
       </c>
-      <c r="L38" s="252"/>
+      <c r="L38" s="191"/>
       <c r="M38" s="61"/>
       <c r="N38" s="59"/>
       <c r="O38" s="58"/>
-      <c r="P38" s="250"/>
+      <c r="P38" s="190"/>
       <c r="Q38" s="79"/>
       <c r="R38" s="79"/>
-      <c r="S38" s="198"/>
+      <c r="S38" s="143"/>
       <c r="T38" s="96"/>
       <c r="U38" s="79"/>
       <c r="V38" s="79"/>
@@ -3968,7 +3960,7 @@
     </row>
     <row r="39" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D39" s="49"/>
-      <c r="E39" s="170"/>
+      <c r="E39" s="296"/>
       <c r="F39" s="86" t="s">
         <v>79</v>
       </c>
@@ -3976,15 +3968,15 @@
       <c r="H39" s="64"/>
       <c r="I39" s="64"/>
       <c r="J39" s="113"/>
-      <c r="K39" s="215"/>
-      <c r="L39" s="253"/>
+      <c r="K39" s="160"/>
+      <c r="L39" s="192"/>
       <c r="M39" s="67"/>
       <c r="N39" s="64"/>
       <c r="O39" s="69"/>
       <c r="P39" s="54"/>
       <c r="Q39" s="65"/>
       <c r="R39" s="65"/>
-      <c r="S39" s="199"/>
+      <c r="S39" s="144"/>
       <c r="T39" s="97"/>
       <c r="U39" s="65"/>
       <c r="V39" s="65"/>
@@ -3992,7 +3984,7 @@
     </row>
     <row r="40" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D40" s="49"/>
-      <c r="E40" s="171"/>
+      <c r="E40" s="297"/>
       <c r="F40" s="90" t="s">
         <v>78</v>
       </c>
@@ -4000,15 +3992,15 @@
       <c r="H40" s="70"/>
       <c r="I40" s="70"/>
       <c r="J40" s="114"/>
-      <c r="K40" s="216"/>
-      <c r="L40" s="276"/>
+      <c r="K40" s="161"/>
+      <c r="L40" s="215"/>
       <c r="M40" s="80"/>
       <c r="N40" s="70"/>
       <c r="O40" s="73"/>
-      <c r="P40" s="208"/>
+      <c r="P40" s="153"/>
       <c r="Q40" s="72"/>
       <c r="R40" s="72"/>
-      <c r="S40" s="248"/>
+      <c r="S40" s="188"/>
       <c r="T40" s="98"/>
       <c r="U40" s="72"/>
       <c r="V40" s="72"/>
@@ -4016,7 +4008,7 @@
     </row>
     <row r="41" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D41" s="49"/>
-      <c r="E41" s="169" t="s">
+      <c r="E41" s="295" t="s">
         <v>82</v>
       </c>
       <c r="F41" s="85" t="s">
@@ -4026,17 +4018,17 @@
       <c r="H41" s="59"/>
       <c r="I41" s="59"/>
       <c r="J41" s="59"/>
-      <c r="K41" s="243"/>
+      <c r="K41" s="184"/>
       <c r="L41" s="115" t="s">
         <v>106</v>
       </c>
       <c r="M41" s="116"/>
       <c r="N41" s="59"/>
       <c r="O41" s="58"/>
-      <c r="P41" s="250"/>
+      <c r="P41" s="190"/>
       <c r="Q41" s="79"/>
       <c r="R41" s="79"/>
-      <c r="S41" s="198"/>
+      <c r="S41" s="143"/>
       <c r="T41" s="96"/>
       <c r="U41" s="79"/>
       <c r="V41" s="79"/>
@@ -4044,7 +4036,7 @@
     </row>
     <row r="42" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D42" s="49"/>
-      <c r="E42" s="170"/>
+      <c r="E42" s="296"/>
       <c r="F42" s="86" t="s">
         <v>85</v>
       </c>
@@ -4053,16 +4045,16 @@
       <c r="I42" s="64"/>
       <c r="J42" s="64"/>
       <c r="K42" s="113"/>
-      <c r="L42" s="283" t="s">
+      <c r="L42" s="221" t="s">
         <v>105</v>
       </c>
-      <c r="M42" s="289"/>
+      <c r="M42" s="227"/>
       <c r="N42" s="64"/>
       <c r="O42" s="69"/>
       <c r="P42" s="54"/>
       <c r="Q42" s="65"/>
       <c r="R42" s="65"/>
-      <c r="S42" s="199"/>
+      <c r="S42" s="144"/>
       <c r="T42" s="97"/>
       <c r="U42" s="65"/>
       <c r="V42" s="65"/>
@@ -4070,7 +4062,7 @@
     </row>
     <row r="43" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D43" s="49"/>
-      <c r="E43" s="170"/>
+      <c r="E43" s="296"/>
       <c r="F43" s="86" t="s">
         <v>88</v>
       </c>
@@ -4079,16 +4071,16 @@
       <c r="I43" s="64"/>
       <c r="J43" s="64"/>
       <c r="K43" s="113"/>
-      <c r="L43" s="192" t="s">
+      <c r="L43" s="140" t="s">
         <v>104</v>
       </c>
-      <c r="M43" s="289"/>
+      <c r="M43" s="227"/>
       <c r="N43" s="64"/>
       <c r="O43" s="69"/>
       <c r="P43" s="54"/>
       <c r="Q43" s="65"/>
       <c r="R43" s="65"/>
-      <c r="S43" s="199"/>
+      <c r="S43" s="144"/>
       <c r="T43" s="97"/>
       <c r="U43" s="65"/>
       <c r="V43" s="65"/>
@@ -4099,7 +4091,7 @@
     </row>
     <row r="44" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D44" s="49"/>
-      <c r="E44" s="171"/>
+      <c r="E44" s="297"/>
       <c r="F44" s="90" t="s">
         <v>89</v>
       </c>
@@ -4108,50 +4100,50 @@
       <c r="I44" s="70"/>
       <c r="J44" s="70"/>
       <c r="K44" s="114"/>
-      <c r="L44" s="206"/>
+      <c r="L44" s="151"/>
       <c r="M44" s="71"/>
       <c r="N44" s="72"/>
       <c r="O44" s="73"/>
-      <c r="P44" s="208"/>
+      <c r="P44" s="153"/>
       <c r="Q44" s="72"/>
       <c r="R44" s="72"/>
-      <c r="S44" s="248"/>
+      <c r="S44" s="188"/>
       <c r="T44" s="98"/>
       <c r="U44" s="72"/>
       <c r="V44" s="72"/>
       <c r="W44" s="83"/>
-      <c r="X44" s="192" t="s">
+      <c r="X44" s="140" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="45" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D45" s="122"/>
       <c r="F45" s="123"/>
-      <c r="G45" s="240" t="s">
+      <c r="G45" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="H45" s="241"/>
-      <c r="I45" s="241"/>
-      <c r="J45" s="241"/>
-      <c r="K45" s="244"/>
-      <c r="L45" s="240" t="s">
+      <c r="H45" s="299"/>
+      <c r="I45" s="299"/>
+      <c r="J45" s="299"/>
+      <c r="K45" s="300"/>
+      <c r="L45" s="298" t="s">
         <v>1</v>
       </c>
-      <c r="M45" s="241"/>
-      <c r="N45" s="241"/>
-      <c r="O45" s="242"/>
-      <c r="P45" s="251" t="s">
+      <c r="M45" s="299"/>
+      <c r="N45" s="299"/>
+      <c r="O45" s="301"/>
+      <c r="P45" s="302" t="s">
         <v>12</v>
       </c>
-      <c r="Q45" s="241"/>
-      <c r="R45" s="241"/>
-      <c r="S45" s="244"/>
-      <c r="T45" s="194" t="s">
+      <c r="Q45" s="299"/>
+      <c r="R45" s="299"/>
+      <c r="S45" s="300"/>
+      <c r="T45" s="303" t="s">
         <v>13</v>
       </c>
-      <c r="U45" s="195"/>
-      <c r="V45" s="195"/>
-      <c r="W45" s="196"/>
+      <c r="U45" s="304"/>
+      <c r="V45" s="304"/>
+      <c r="W45" s="305"/>
     </row>
     <row r="46" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D46" s="63"/>
@@ -4171,7 +4163,7 @@
       <c r="J46" s="127" t="s">
         <v>5</v>
       </c>
-      <c r="K46" s="201" t="s">
+      <c r="K46" s="146" t="s">
         <v>6</v>
       </c>
       <c r="L46" s="126" t="s">
@@ -4186,7 +4178,7 @@
       <c r="O46" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P46" s="209" t="s">
+      <c r="P46" s="154" t="s">
         <v>2</v>
       </c>
       <c r="Q46" s="127" t="s">
@@ -4195,143 +4187,143 @@
       <c r="R46" s="127" t="s">
         <v>4</v>
       </c>
-      <c r="S46" s="201" t="s">
+      <c r="S46" s="146" t="s">
         <v>5</v>
       </c>
-      <c r="T46" s="262" t="s">
+      <c r="T46" s="201" t="s">
         <v>2</v>
       </c>
-      <c r="U46" s="233" t="s">
+      <c r="U46" s="178" t="s">
         <v>3</v>
       </c>
-      <c r="V46" s="233" t="s">
+      <c r="V46" s="178" t="s">
         <v>4</v>
       </c>
-      <c r="W46" s="263" t="s">
+      <c r="W46" s="202" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="47" spans="4:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E47" s="188" t="s">
+      <c r="E47" s="306" t="s">
         <v>94</v>
       </c>
       <c r="F47" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="G47" s="235"/>
-      <c r="H47" s="236"/>
-      <c r="I47" s="236"/>
-      <c r="J47" s="236"/>
-      <c r="K47" s="245"/>
+      <c r="G47" s="179"/>
+      <c r="H47" s="180"/>
+      <c r="I47" s="180"/>
+      <c r="J47" s="180"/>
+      <c r="K47" s="185"/>
       <c r="L47" s="57" t="s">
         <v>129</v>
       </c>
-      <c r="M47" s="285"/>
-      <c r="N47" s="236"/>
-      <c r="O47" s="256"/>
-      <c r="P47" s="252"/>
+      <c r="M47" s="223"/>
+      <c r="N47" s="180"/>
+      <c r="O47" s="195"/>
+      <c r="P47" s="191"/>
       <c r="Q47" s="79"/>
       <c r="R47" s="79"/>
-      <c r="S47" s="198"/>
+      <c r="S47" s="143"/>
       <c r="T47" s="96"/>
       <c r="U47" s="79"/>
       <c r="V47" s="79"/>
       <c r="W47" s="82"/>
     </row>
     <row r="48" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E48" s="189"/>
-      <c r="F48" s="187" t="s">
+      <c r="E48" s="307"/>
+      <c r="F48" s="138" t="s">
         <v>100</v>
       </c>
-      <c r="G48" s="237"/>
-      <c r="H48" s="226"/>
-      <c r="I48" s="226"/>
-      <c r="J48" s="226"/>
-      <c r="K48" s="246"/>
+      <c r="G48" s="181"/>
+      <c r="H48" s="171"/>
+      <c r="I48" s="171"/>
+      <c r="J48" s="171"/>
+      <c r="K48" s="186"/>
       <c r="L48" s="99"/>
-      <c r="M48" s="286"/>
-      <c r="N48" s="226"/>
-      <c r="O48" s="257"/>
-      <c r="P48" s="253"/>
+      <c r="M48" s="224"/>
+      <c r="N48" s="171"/>
+      <c r="O48" s="196"/>
+      <c r="P48" s="192"/>
       <c r="Q48" s="65"/>
       <c r="R48" s="65"/>
-      <c r="S48" s="199"/>
+      <c r="S48" s="144"/>
       <c r="T48" s="97"/>
       <c r="U48" s="65"/>
       <c r="V48" s="65"/>
       <c r="W48" s="68"/>
     </row>
     <row r="49" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E49" s="189"/>
-      <c r="F49" s="187" t="s">
+      <c r="E49" s="307"/>
+      <c r="F49" s="138" t="s">
         <v>103</v>
       </c>
-      <c r="G49" s="237"/>
-      <c r="H49" s="226"/>
-      <c r="I49" s="226"/>
-      <c r="J49" s="226"/>
-      <c r="K49" s="246"/>
+      <c r="G49" s="181"/>
+      <c r="H49" s="171"/>
+      <c r="I49" s="171"/>
+      <c r="J49" s="171"/>
+      <c r="K49" s="186"/>
       <c r="L49" s="99"/>
-      <c r="M49" s="286"/>
-      <c r="N49" s="226"/>
-      <c r="O49" s="257"/>
-      <c r="P49" s="253"/>
+      <c r="M49" s="224"/>
+      <c r="N49" s="171"/>
+      <c r="O49" s="196"/>
+      <c r="P49" s="192"/>
       <c r="Q49" s="65"/>
       <c r="R49" s="65"/>
-      <c r="S49" s="199"/>
+      <c r="S49" s="144"/>
       <c r="T49" s="97"/>
       <c r="U49" s="65"/>
       <c r="V49" s="65"/>
       <c r="W49" s="68"/>
     </row>
     <row r="50" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E50" s="189"/>
-      <c r="F50" s="187" t="s">
+      <c r="E50" s="307"/>
+      <c r="F50" s="138" t="s">
         <v>99</v>
       </c>
-      <c r="G50" s="237"/>
-      <c r="H50" s="226"/>
-      <c r="I50" s="226"/>
-      <c r="J50" s="226"/>
-      <c r="K50" s="246"/>
+      <c r="G50" s="181"/>
+      <c r="H50" s="171"/>
+      <c r="I50" s="171"/>
+      <c r="J50" s="171"/>
+      <c r="K50" s="186"/>
       <c r="L50" s="100"/>
-      <c r="M50" s="286"/>
-      <c r="N50" s="226"/>
-      <c r="O50" s="257"/>
-      <c r="P50" s="253"/>
+      <c r="M50" s="224"/>
+      <c r="N50" s="171"/>
+      <c r="O50" s="196"/>
+      <c r="P50" s="192"/>
       <c r="Q50" s="65"/>
       <c r="R50" s="65"/>
-      <c r="S50" s="199"/>
+      <c r="S50" s="144"/>
       <c r="T50" s="97"/>
       <c r="U50" s="65"/>
       <c r="V50" s="65"/>
       <c r="W50" s="68"/>
     </row>
     <row r="51" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E51" s="190"/>
+      <c r="E51" s="308"/>
       <c r="F51" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="G51" s="238"/>
-      <c r="H51" s="239"/>
-      <c r="I51" s="239"/>
-      <c r="J51" s="239"/>
-      <c r="K51" s="247"/>
-      <c r="L51" s="193"/>
-      <c r="M51" s="287"/>
-      <c r="N51" s="230"/>
-      <c r="O51" s="278"/>
-      <c r="P51" s="254"/>
+      <c r="G51" s="182"/>
+      <c r="H51" s="183"/>
+      <c r="I51" s="183"/>
+      <c r="J51" s="183"/>
+      <c r="K51" s="187"/>
+      <c r="L51" s="141"/>
+      <c r="M51" s="225"/>
+      <c r="N51" s="175"/>
+      <c r="O51" s="217"/>
+      <c r="P51" s="193"/>
       <c r="Q51" s="72"/>
       <c r="R51" s="72"/>
-      <c r="S51" s="248"/>
-      <c r="T51" s="182"/>
-      <c r="U51" s="183"/>
-      <c r="V51" s="183"/>
-      <c r="W51" s="184"/>
+      <c r="S51" s="188"/>
+      <c r="T51" s="133"/>
+      <c r="U51" s="134"/>
+      <c r="V51" s="134"/>
+      <c r="W51" s="135"/>
     </row>
     <row r="52" spans="5:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E52" s="178" t="s">
+      <c r="E52" s="292" t="s">
         <v>62</v>
       </c>
       <c r="F52" s="85" t="s">
@@ -4341,24 +4333,24 @@
       <c r="H52" s="79"/>
       <c r="I52" s="79"/>
       <c r="J52" s="79"/>
-      <c r="K52" s="198"/>
+      <c r="K52" s="143"/>
       <c r="L52" s="96"/>
-      <c r="M52" s="264"/>
-      <c r="N52" s="167" t="s">
+      <c r="M52" s="203"/>
+      <c r="N52" s="286" t="s">
         <v>17</v>
       </c>
-      <c r="O52" s="168"/>
-      <c r="P52" s="211"/>
+      <c r="O52" s="288"/>
+      <c r="P52" s="156"/>
       <c r="Q52" s="79"/>
       <c r="R52" s="79"/>
-      <c r="S52" s="198"/>
+      <c r="S52" s="143"/>
       <c r="T52" s="96"/>
       <c r="U52" s="79"/>
       <c r="V52" s="79"/>
       <c r="W52" s="82"/>
     </row>
     <row r="53" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E53" s="179"/>
+      <c r="E53" s="293"/>
       <c r="F53" s="86" t="s">
         <v>119</v>
       </c>
@@ -4366,260 +4358,260 @@
       <c r="H53" s="65"/>
       <c r="I53" s="65"/>
       <c r="J53" s="65"/>
-      <c r="K53" s="199"/>
+      <c r="K53" s="144"/>
       <c r="L53" s="97"/>
-      <c r="M53" s="265"/>
+      <c r="M53" s="204"/>
       <c r="N53" s="104"/>
       <c r="O53" s="68"/>
-      <c r="P53" s="253"/>
+      <c r="P53" s="192"/>
       <c r="Q53" s="65"/>
       <c r="R53" s="65"/>
-      <c r="S53" s="199"/>
+      <c r="S53" s="144"/>
       <c r="T53" s="97"/>
       <c r="U53" s="65"/>
       <c r="V53" s="65"/>
       <c r="W53" s="68"/>
     </row>
     <row r="54" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E54" s="179"/>
-      <c r="F54" s="181" t="s">
+      <c r="E54" s="293"/>
+      <c r="F54" s="132" t="s">
         <v>120</v>
       </c>
       <c r="G54" s="97"/>
       <c r="H54" s="65"/>
       <c r="I54" s="65"/>
       <c r="J54" s="65"/>
-      <c r="K54" s="199"/>
+      <c r="K54" s="144"/>
       <c r="L54" s="97"/>
-      <c r="M54" s="265"/>
+      <c r="M54" s="204"/>
       <c r="N54" s="98"/>
-      <c r="O54" s="284"/>
-      <c r="P54" s="276"/>
-      <c r="Q54" s="183"/>
+      <c r="O54" s="222"/>
+      <c r="P54" s="215"/>
+      <c r="Q54" s="134"/>
       <c r="R54" s="65"/>
-      <c r="S54" s="199"/>
+      <c r="S54" s="144"/>
       <c r="T54" s="97"/>
       <c r="U54" s="65"/>
       <c r="V54" s="65"/>
       <c r="W54" s="68"/>
     </row>
     <row r="55" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E55" s="179"/>
-      <c r="F55" s="220" t="s">
+      <c r="E55" s="293"/>
+      <c r="F55" s="165" t="s">
         <v>93</v>
       </c>
       <c r="G55" s="97"/>
       <c r="H55" s="65"/>
       <c r="I55" s="65"/>
       <c r="J55" s="65"/>
-      <c r="K55" s="199"/>
+      <c r="K55" s="144"/>
       <c r="L55" s="97"/>
       <c r="M55" s="66"/>
-      <c r="N55" s="232"/>
-      <c r="O55" s="282"/>
-      <c r="P55" s="167" t="s">
+      <c r="N55" s="177"/>
+      <c r="O55" s="219"/>
+      <c r="P55" s="286" t="s">
         <v>17</v>
       </c>
-      <c r="Q55" s="168"/>
-      <c r="R55" s="253"/>
-      <c r="S55" s="199"/>
+      <c r="Q55" s="288"/>
+      <c r="R55" s="192"/>
+      <c r="S55" s="144"/>
       <c r="T55" s="97"/>
       <c r="U55" s="65"/>
       <c r="V55" s="65"/>
       <c r="W55" s="68"/>
     </row>
     <row r="56" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E56" s="179"/>
-      <c r="F56" s="219" t="s">
+      <c r="E56" s="293"/>
+      <c r="F56" s="164" t="s">
         <v>109</v>
       </c>
       <c r="G56" s="97"/>
       <c r="H56" s="65"/>
       <c r="I56" s="65"/>
       <c r="J56" s="65"/>
-      <c r="K56" s="199"/>
+      <c r="K56" s="144"/>
       <c r="L56" s="97"/>
       <c r="M56" s="66"/>
       <c r="N56" s="65"/>
-      <c r="O56" s="271"/>
+      <c r="O56" s="210"/>
       <c r="P56" s="104"/>
       <c r="Q56" s="68"/>
-      <c r="R56" s="253"/>
-      <c r="S56" s="199"/>
+      <c r="R56" s="192"/>
+      <c r="S56" s="144"/>
       <c r="T56" s="97"/>
       <c r="U56" s="65"/>
       <c r="V56" s="65"/>
       <c r="W56" s="68"/>
     </row>
     <row r="57" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E57" s="180"/>
-      <c r="F57" s="213" t="s">
+      <c r="E57" s="294"/>
+      <c r="F57" s="158" t="s">
         <v>111</v>
       </c>
       <c r="G57" s="98"/>
       <c r="H57" s="72"/>
       <c r="I57" s="72"/>
       <c r="J57" s="72"/>
-      <c r="K57" s="248"/>
+      <c r="K57" s="188"/>
       <c r="L57" s="98"/>
       <c r="M57" s="71"/>
-      <c r="N57" s="183"/>
-      <c r="O57" s="277"/>
+      <c r="N57" s="134"/>
+      <c r="O57" s="216"/>
       <c r="P57" s="98"/>
-      <c r="Q57" s="284"/>
-      <c r="R57" s="254"/>
-      <c r="S57" s="248"/>
+      <c r="Q57" s="222"/>
+      <c r="R57" s="193"/>
+      <c r="S57" s="188"/>
       <c r="T57" s="98"/>
       <c r="U57" s="72"/>
       <c r="V57" s="72"/>
       <c r="W57" s="83"/>
     </row>
     <row r="58" spans="5:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E58" s="178" t="s">
+      <c r="E58" s="292" t="s">
         <v>91</v>
       </c>
-      <c r="F58" s="221" t="s">
+      <c r="F58" s="166" t="s">
         <v>71</v>
       </c>
       <c r="G58" s="96"/>
       <c r="H58" s="79"/>
       <c r="I58" s="79"/>
       <c r="J58" s="79"/>
-      <c r="K58" s="198"/>
+      <c r="K58" s="143"/>
       <c r="L58" s="96"/>
-      <c r="M58" s="264"/>
-      <c r="N58" s="167" t="s">
+      <c r="M58" s="203"/>
+      <c r="N58" s="286" t="s">
         <v>51</v>
       </c>
-      <c r="O58" s="168"/>
-      <c r="P58" s="281"/>
-      <c r="Q58" s="228"/>
+      <c r="O58" s="288"/>
+      <c r="P58" s="220"/>
+      <c r="Q58" s="173"/>
       <c r="R58" s="79"/>
-      <c r="S58" s="198"/>
+      <c r="S58" s="143"/>
       <c r="T58" s="96"/>
       <c r="U58" s="79"/>
       <c r="V58" s="79"/>
       <c r="W58" s="82"/>
     </row>
     <row r="59" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E59" s="179"/>
-      <c r="F59" s="222" t="s">
+      <c r="E59" s="293"/>
+      <c r="F59" s="167" t="s">
         <v>101</v>
       </c>
       <c r="G59" s="97"/>
       <c r="H59" s="65"/>
       <c r="I59" s="65"/>
       <c r="J59" s="65"/>
-      <c r="K59" s="199"/>
+      <c r="K59" s="144"/>
       <c r="L59" s="97"/>
-      <c r="M59" s="265"/>
+      <c r="M59" s="204"/>
       <c r="N59" s="106"/>
       <c r="O59" s="68"/>
-      <c r="P59" s="276"/>
-      <c r="Q59" s="183"/>
+      <c r="P59" s="215"/>
+      <c r="Q59" s="134"/>
       <c r="R59" s="65"/>
-      <c r="S59" s="199"/>
+      <c r="S59" s="144"/>
       <c r="T59" s="97"/>
       <c r="U59" s="65"/>
       <c r="V59" s="65"/>
       <c r="W59" s="68"/>
     </row>
     <row r="60" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E60" s="179"/>
-      <c r="F60" s="222" t="s">
+      <c r="E60" s="293"/>
+      <c r="F60" s="167" t="s">
         <v>102</v>
       </c>
       <c r="G60" s="97"/>
       <c r="H60" s="65"/>
       <c r="I60" s="65"/>
       <c r="J60" s="65"/>
-      <c r="K60" s="199"/>
+      <c r="K60" s="144"/>
       <c r="L60" s="97"/>
-      <c r="M60" s="265"/>
+      <c r="M60" s="204"/>
       <c r="N60" s="98"/>
       <c r="O60" s="107"/>
-      <c r="P60" s="167" t="s">
+      <c r="P60" s="286" t="s">
         <v>51</v>
       </c>
-      <c r="Q60" s="168"/>
-      <c r="R60" s="253"/>
-      <c r="S60" s="199"/>
+      <c r="Q60" s="288"/>
+      <c r="R60" s="192"/>
+      <c r="S60" s="144"/>
       <c r="T60" s="97"/>
       <c r="U60" s="65"/>
       <c r="V60" s="65"/>
       <c r="W60" s="68"/>
     </row>
     <row r="61" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E61" s="179"/>
-      <c r="F61" s="181" t="s">
+      <c r="E61" s="293"/>
+      <c r="F61" s="132" t="s">
         <v>125</v>
       </c>
       <c r="G61" s="97"/>
       <c r="H61" s="65"/>
       <c r="I61" s="65"/>
       <c r="J61" s="65"/>
-      <c r="K61" s="199"/>
+      <c r="K61" s="144"/>
       <c r="L61" s="97"/>
-      <c r="M61" s="265"/>
-      <c r="N61" s="295"/>
-      <c r="O61" s="280"/>
+      <c r="M61" s="204"/>
+      <c r="N61" s="233"/>
+      <c r="O61" s="219"/>
       <c r="P61" s="106"/>
-      <c r="Q61" s="294"/>
-      <c r="R61" s="253"/>
-      <c r="S61" s="199"/>
+      <c r="Q61" s="232"/>
+      <c r="R61" s="192"/>
+      <c r="S61" s="144"/>
       <c r="T61" s="97"/>
       <c r="U61" s="65"/>
       <c r="V61" s="65"/>
       <c r="W61" s="68"/>
     </row>
     <row r="62" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E62" s="179"/>
-      <c r="F62" s="219" t="s">
+      <c r="E62" s="293"/>
+      <c r="F62" s="164" t="s">
         <v>108</v>
       </c>
       <c r="G62" s="97"/>
       <c r="H62" s="65"/>
       <c r="I62" s="65"/>
       <c r="J62" s="65"/>
-      <c r="K62" s="199"/>
+      <c r="K62" s="144"/>
       <c r="L62" s="97"/>
       <c r="M62" s="66"/>
-      <c r="N62" s="228"/>
+      <c r="N62" s="173"/>
       <c r="O62" s="63"/>
       <c r="P62" s="106"/>
       <c r="Q62" s="68"/>
-      <c r="R62" s="253"/>
-      <c r="S62" s="199"/>
+      <c r="R62" s="192"/>
+      <c r="S62" s="144"/>
       <c r="T62" s="97"/>
       <c r="U62" s="65"/>
       <c r="V62" s="65"/>
       <c r="W62" s="68"/>
     </row>
     <row r="63" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E63" s="180"/>
-      <c r="F63" s="213" t="s">
+      <c r="E63" s="294"/>
+      <c r="F63" s="158" t="s">
         <v>111</v>
       </c>
       <c r="G63" s="98"/>
       <c r="H63" s="72"/>
       <c r="I63" s="72"/>
       <c r="J63" s="72"/>
-      <c r="K63" s="248"/>
+      <c r="K63" s="188"/>
       <c r="L63" s="98"/>
       <c r="M63" s="71"/>
-      <c r="N63" s="183"/>
-      <c r="O63" s="200"/>
+      <c r="N63" s="134"/>
+      <c r="O63" s="145"/>
       <c r="P63" s="98"/>
       <c r="Q63" s="107"/>
-      <c r="R63" s="254"/>
-      <c r="S63" s="248"/>
+      <c r="R63" s="193"/>
+      <c r="S63" s="188"/>
       <c r="T63" s="98"/>
       <c r="U63" s="72"/>
       <c r="V63" s="72"/>
       <c r="W63" s="83"/>
     </row>
     <row r="64" spans="5:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E64" s="178" t="s">
+      <c r="E64" s="292" t="s">
         <v>92</v>
       </c>
       <c r="F64" s="85" t="s">
@@ -4631,22 +4623,22 @@
       <c r="J64" s="59"/>
       <c r="K64" s="112"/>
       <c r="L64" s="60"/>
-      <c r="M64" s="264"/>
-      <c r="N64" s="167" t="s">
+      <c r="M64" s="203"/>
+      <c r="N64" s="286" t="s">
         <v>52</v>
       </c>
-      <c r="O64" s="168"/>
-      <c r="P64" s="281"/>
-      <c r="Q64" s="228"/>
+      <c r="O64" s="288"/>
+      <c r="P64" s="220"/>
+      <c r="Q64" s="173"/>
       <c r="R64" s="79"/>
-      <c r="S64" s="198"/>
+      <c r="S64" s="143"/>
       <c r="T64" s="96"/>
       <c r="U64" s="79"/>
       <c r="V64" s="79"/>
       <c r="W64" s="82"/>
     </row>
     <row r="65" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E65" s="179"/>
+      <c r="E65" s="293"/>
       <c r="F65" s="86" t="s">
         <v>117</v>
       </c>
@@ -4656,20 +4648,20 @@
       <c r="J65" s="64"/>
       <c r="K65" s="113"/>
       <c r="L65" s="94"/>
-      <c r="M65" s="265"/>
+      <c r="M65" s="204"/>
       <c r="N65" s="108"/>
       <c r="O65" s="68"/>
-      <c r="P65" s="253"/>
+      <c r="P65" s="192"/>
       <c r="Q65" s="65"/>
       <c r="R65" s="65"/>
-      <c r="S65" s="199"/>
+      <c r="S65" s="144"/>
       <c r="T65" s="97"/>
       <c r="U65" s="65"/>
       <c r="V65" s="65"/>
       <c r="W65" s="68"/>
     </row>
     <row r="66" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E66" s="179"/>
+      <c r="E66" s="293"/>
       <c r="F66" s="86" t="s">
         <v>118</v>
       </c>
@@ -4677,22 +4669,22 @@
       <c r="H66" s="65"/>
       <c r="I66" s="65"/>
       <c r="J66" s="64"/>
-      <c r="K66" s="199"/>
+      <c r="K66" s="144"/>
       <c r="L66" s="94"/>
-      <c r="M66" s="265"/>
+      <c r="M66" s="204"/>
       <c r="N66" s="98"/>
       <c r="O66" s="109"/>
-      <c r="P66" s="276"/>
-      <c r="Q66" s="183"/>
+      <c r="P66" s="215"/>
+      <c r="Q66" s="134"/>
       <c r="R66" s="65"/>
-      <c r="S66" s="199"/>
+      <c r="S66" s="144"/>
       <c r="T66" s="97"/>
       <c r="U66" s="65"/>
       <c r="V66" s="65"/>
       <c r="W66" s="68"/>
     </row>
     <row r="67" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E67" s="179"/>
+      <c r="E67" s="293"/>
       <c r="F67" s="87" t="s">
         <v>110</v>
       </c>
@@ -4700,93 +4692,93 @@
       <c r="H67" s="65"/>
       <c r="I67" s="65"/>
       <c r="J67" s="64"/>
-      <c r="K67" s="199"/>
+      <c r="K67" s="144"/>
       <c r="L67" s="94"/>
       <c r="M67" s="66"/>
-      <c r="N67" s="228"/>
-      <c r="O67" s="280"/>
-      <c r="P67" s="167" t="s">
+      <c r="N67" s="173"/>
+      <c r="O67" s="219"/>
+      <c r="P67" s="286" t="s">
         <v>52</v>
       </c>
-      <c r="Q67" s="168"/>
-      <c r="R67" s="253"/>
-      <c r="S67" s="199"/>
+      <c r="Q67" s="288"/>
+      <c r="R67" s="192"/>
+      <c r="S67" s="144"/>
       <c r="T67" s="97"/>
       <c r="U67" s="65"/>
       <c r="V67" s="65"/>
       <c r="W67" s="68"/>
     </row>
     <row r="68" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E68" s="179"/>
-      <c r="F68" s="181" t="s">
+      <c r="E68" s="293"/>
+      <c r="F68" s="132" t="s">
         <v>125</v>
       </c>
       <c r="G68" s="94"/>
       <c r="H68" s="65"/>
       <c r="I68" s="65"/>
       <c r="J68" s="64"/>
-      <c r="K68" s="199"/>
+      <c r="K68" s="144"/>
       <c r="L68" s="94"/>
       <c r="M68" s="66"/>
-      <c r="N68" s="228"/>
-      <c r="O68" s="280"/>
+      <c r="N68" s="173"/>
+      <c r="O68" s="219"/>
       <c r="P68" s="108"/>
-      <c r="Q68" s="294"/>
-      <c r="R68" s="253"/>
-      <c r="S68" s="199"/>
+      <c r="Q68" s="232"/>
+      <c r="R68" s="192"/>
+      <c r="S68" s="144"/>
       <c r="T68" s="97"/>
       <c r="U68" s="65"/>
       <c r="V68" s="65"/>
       <c r="W68" s="68"/>
     </row>
     <row r="69" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E69" s="179"/>
-      <c r="F69" s="181" t="s">
+      <c r="E69" s="293"/>
+      <c r="F69" s="132" t="s">
         <v>122</v>
       </c>
       <c r="G69" s="94"/>
       <c r="H69" s="65"/>
       <c r="I69" s="65"/>
       <c r="J69" s="64"/>
-      <c r="K69" s="199"/>
+      <c r="K69" s="144"/>
       <c r="L69" s="94"/>
       <c r="M69" s="66"/>
       <c r="N69" s="64"/>
-      <c r="O69" s="266"/>
+      <c r="O69" s="205"/>
       <c r="P69" s="108"/>
       <c r="Q69" s="68"/>
-      <c r="R69" s="253"/>
-      <c r="S69" s="199"/>
+      <c r="R69" s="192"/>
+      <c r="S69" s="144"/>
       <c r="T69" s="97"/>
       <c r="U69" s="65"/>
       <c r="V69" s="65"/>
       <c r="W69" s="68"/>
     </row>
     <row r="70" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E70" s="179"/>
-      <c r="F70" s="213" t="s">
+      <c r="E70" s="293"/>
+      <c r="F70" s="158" t="s">
         <v>111</v>
       </c>
       <c r="G70" s="95"/>
       <c r="H70" s="72"/>
       <c r="I70" s="72"/>
       <c r="J70" s="70"/>
-      <c r="K70" s="248"/>
+      <c r="K70" s="188"/>
       <c r="L70" s="95"/>
       <c r="M70" s="71"/>
       <c r="N70" s="74"/>
-      <c r="O70" s="275"/>
+      <c r="O70" s="214"/>
       <c r="P70" s="98"/>
       <c r="Q70" s="109"/>
-      <c r="R70" s="254"/>
-      <c r="S70" s="248"/>
+      <c r="R70" s="193"/>
+      <c r="S70" s="188"/>
       <c r="T70" s="98"/>
       <c r="U70" s="72"/>
       <c r="V70" s="72"/>
       <c r="W70" s="83"/>
     </row>
     <row r="71" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E71" s="178" t="s">
+      <c r="E71" s="292" t="s">
         <v>113</v>
       </c>
       <c r="F71" s="85" t="s">
@@ -4796,24 +4788,24 @@
       <c r="H71" s="79"/>
       <c r="I71" s="79"/>
       <c r="J71" s="59"/>
-      <c r="K71" s="198"/>
+      <c r="K71" s="143"/>
       <c r="L71" s="60"/>
-      <c r="M71" s="264"/>
-      <c r="N71" s="167" t="s">
+      <c r="M71" s="203"/>
+      <c r="N71" s="286" t="s">
         <v>67</v>
       </c>
-      <c r="O71" s="168"/>
-      <c r="P71" s="272"/>
-      <c r="Q71" s="228"/>
+      <c r="O71" s="288"/>
+      <c r="P71" s="211"/>
+      <c r="Q71" s="173"/>
       <c r="R71" s="79"/>
-      <c r="S71" s="198"/>
+      <c r="S71" s="143"/>
       <c r="T71" s="96"/>
       <c r="U71" s="79"/>
       <c r="V71" s="79"/>
       <c r="W71" s="82"/>
     </row>
     <row r="72" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E72" s="179"/>
+      <c r="E72" s="293"/>
       <c r="F72" s="86" t="s">
         <v>107</v>
       </c>
@@ -4821,22 +4813,22 @@
       <c r="H72" s="65"/>
       <c r="I72" s="65"/>
       <c r="J72" s="64"/>
-      <c r="K72" s="199"/>
+      <c r="K72" s="144"/>
       <c r="L72" s="94"/>
-      <c r="M72" s="265"/>
-      <c r="N72" s="217"/>
+      <c r="M72" s="204"/>
+      <c r="N72" s="162"/>
       <c r="O72" s="68"/>
-      <c r="P72" s="253"/>
+      <c r="P72" s="192"/>
       <c r="Q72" s="65"/>
       <c r="R72" s="65"/>
-      <c r="S72" s="199"/>
+      <c r="S72" s="144"/>
       <c r="T72" s="97"/>
       <c r="U72" s="65"/>
       <c r="V72" s="65"/>
       <c r="W72" s="68"/>
     </row>
     <row r="73" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E73" s="179"/>
+      <c r="E73" s="293"/>
       <c r="F73" s="86" t="s">
         <v>121</v>
       </c>
@@ -4844,22 +4836,22 @@
       <c r="H73" s="65"/>
       <c r="I73" s="65"/>
       <c r="J73" s="64"/>
-      <c r="K73" s="199"/>
+      <c r="K73" s="144"/>
       <c r="L73" s="94"/>
-      <c r="M73" s="265"/>
+      <c r="M73" s="204"/>
       <c r="N73" s="98"/>
-      <c r="O73" s="218"/>
-      <c r="P73" s="276"/>
-      <c r="Q73" s="183"/>
+      <c r="O73" s="163"/>
+      <c r="P73" s="215"/>
+      <c r="Q73" s="134"/>
       <c r="R73" s="65"/>
-      <c r="S73" s="199"/>
+      <c r="S73" s="144"/>
       <c r="T73" s="97"/>
       <c r="U73" s="65"/>
       <c r="V73" s="65"/>
       <c r="W73" s="68"/>
     </row>
     <row r="74" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E74" s="179"/>
+      <c r="E74" s="293"/>
       <c r="F74" s="87" t="s">
         <v>110</v>
       </c>
@@ -4867,112 +4859,112 @@
       <c r="H74" s="65"/>
       <c r="I74" s="65"/>
       <c r="J74" s="64"/>
-      <c r="K74" s="199"/>
+      <c r="K74" s="144"/>
       <c r="L74" s="94"/>
       <c r="M74" s="66"/>
-      <c r="N74" s="227"/>
-      <c r="O74" s="279"/>
-      <c r="P74" s="167" t="s">
+      <c r="N74" s="172"/>
+      <c r="O74" s="218"/>
+      <c r="P74" s="286" t="s">
         <v>124</v>
       </c>
-      <c r="Q74" s="168"/>
-      <c r="R74" s="253"/>
-      <c r="S74" s="199"/>
+      <c r="Q74" s="288"/>
+      <c r="R74" s="192"/>
+      <c r="S74" s="144"/>
       <c r="T74" s="97"/>
       <c r="U74" s="65"/>
       <c r="V74" s="65"/>
       <c r="W74" s="68"/>
     </row>
     <row r="75" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E75" s="179"/>
-      <c r="F75" s="181" t="s">
+      <c r="E75" s="293"/>
+      <c r="F75" s="132" t="s">
         <v>125</v>
       </c>
       <c r="G75" s="94"/>
       <c r="H75" s="65"/>
       <c r="I75" s="65"/>
       <c r="J75" s="64"/>
-      <c r="K75" s="199"/>
+      <c r="K75" s="144"/>
       <c r="L75" s="94"/>
       <c r="M75" s="66"/>
-      <c r="N75" s="227"/>
-      <c r="O75" s="279"/>
-      <c r="P75" s="217"/>
-      <c r="Q75" s="294"/>
-      <c r="R75" s="253"/>
-      <c r="S75" s="199"/>
+      <c r="N75" s="172"/>
+      <c r="O75" s="218"/>
+      <c r="P75" s="162"/>
+      <c r="Q75" s="232"/>
+      <c r="R75" s="192"/>
+      <c r="S75" s="144"/>
       <c r="T75" s="97"/>
       <c r="U75" s="65"/>
       <c r="V75" s="65"/>
       <c r="W75" s="68"/>
     </row>
     <row r="76" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E76" s="179"/>
-      <c r="F76" s="181" t="s">
+      <c r="E76" s="293"/>
+      <c r="F76" s="132" t="s">
         <v>123</v>
       </c>
       <c r="G76" s="94"/>
       <c r="H76" s="65"/>
       <c r="I76" s="65"/>
       <c r="J76" s="64"/>
-      <c r="K76" s="199"/>
+      <c r="K76" s="144"/>
       <c r="L76" s="94"/>
       <c r="M76" s="66"/>
       <c r="N76" s="64"/>
-      <c r="O76" s="266"/>
-      <c r="P76" s="217"/>
+      <c r="O76" s="205"/>
+      <c r="P76" s="162"/>
       <c r="Q76" s="68"/>
-      <c r="R76" s="253"/>
-      <c r="S76" s="199"/>
+      <c r="R76" s="192"/>
+      <c r="S76" s="144"/>
       <c r="T76" s="97"/>
       <c r="U76" s="65"/>
       <c r="V76" s="65"/>
       <c r="W76" s="68"/>
     </row>
     <row r="77" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E77" s="180"/>
-      <c r="F77" s="214" t="s">
+      <c r="E77" s="294"/>
+      <c r="F77" s="159" t="s">
         <v>111</v>
       </c>
       <c r="G77" s="95"/>
       <c r="H77" s="72"/>
       <c r="I77" s="72"/>
       <c r="J77" s="70"/>
-      <c r="K77" s="248"/>
+      <c r="K77" s="188"/>
       <c r="L77" s="95"/>
       <c r="M77" s="71"/>
       <c r="N77" s="70"/>
-      <c r="O77" s="267"/>
+      <c r="O77" s="206"/>
       <c r="P77" s="98"/>
-      <c r="Q77" s="218"/>
-      <c r="R77" s="254"/>
-      <c r="S77" s="248"/>
+      <c r="Q77" s="163"/>
+      <c r="R77" s="193"/>
+      <c r="S77" s="188"/>
       <c r="T77" s="98"/>
       <c r="U77" s="72"/>
       <c r="V77" s="72"/>
       <c r="W77" s="83"/>
     </row>
     <row r="78" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E78" s="169" t="s">
+      <c r="E78" s="295" t="s">
         <v>47</v>
       </c>
       <c r="F78" s="85" t="s">
         <v>83</v>
       </c>
       <c r="G78" s="56"/>
-      <c r="H78" s="227"/>
-      <c r="I78" s="227"/>
-      <c r="J78" s="227"/>
-      <c r="K78" s="243"/>
-      <c r="L78" s="261"/>
-      <c r="M78" s="229"/>
-      <c r="N78" s="227"/>
-      <c r="O78" s="255"/>
-      <c r="P78" s="268"/>
+      <c r="H78" s="172"/>
+      <c r="I78" s="172"/>
+      <c r="J78" s="172"/>
+      <c r="K78" s="184"/>
+      <c r="L78" s="200"/>
+      <c r="M78" s="174"/>
+      <c r="N78" s="172"/>
+      <c r="O78" s="194"/>
+      <c r="P78" s="207"/>
       <c r="Q78" s="115" t="s">
         <v>47</v>
       </c>
-      <c r="R78" s="272"/>
+      <c r="R78" s="211"/>
       <c r="S78" s="63"/>
       <c r="T78" s="96"/>
       <c r="U78" s="79"/>
@@ -4980,7 +4972,7 @@
       <c r="W78" s="82"/>
     </row>
     <row r="79" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E79" s="170"/>
+      <c r="E79" s="296"/>
       <c r="F79" s="86" t="s">
         <v>79</v>
       </c>
@@ -4993,17 +4985,17 @@
       <c r="M79" s="67"/>
       <c r="N79" s="64"/>
       <c r="O79" s="69"/>
-      <c r="P79" s="269"/>
-      <c r="Q79" s="215"/>
-      <c r="R79" s="253"/>
-      <c r="S79" s="199"/>
+      <c r="P79" s="208"/>
+      <c r="Q79" s="160"/>
+      <c r="R79" s="192"/>
+      <c r="S79" s="144"/>
       <c r="T79" s="97"/>
       <c r="U79" s="65"/>
       <c r="V79" s="65"/>
       <c r="W79" s="68"/>
     </row>
     <row r="80" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E80" s="171"/>
+      <c r="E80" s="297"/>
       <c r="F80" s="90" t="s">
         <v>78</v>
       </c>
@@ -5016,17 +5008,17 @@
       <c r="M80" s="80"/>
       <c r="N80" s="70"/>
       <c r="O80" s="73"/>
-      <c r="P80" s="270"/>
-      <c r="Q80" s="216"/>
-      <c r="R80" s="276"/>
-      <c r="S80" s="248"/>
+      <c r="P80" s="209"/>
+      <c r="Q80" s="161"/>
+      <c r="R80" s="215"/>
+      <c r="S80" s="188"/>
       <c r="T80" s="98"/>
       <c r="U80" s="72"/>
       <c r="V80" s="72"/>
       <c r="W80" s="83"/>
     </row>
     <row r="81" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E81" s="169" t="s">
+      <c r="E81" s="295" t="s">
         <v>82</v>
       </c>
       <c r="F81" s="85" t="s">
@@ -5041,19 +5033,19 @@
       <c r="M81" s="61"/>
       <c r="N81" s="59"/>
       <c r="O81" s="58"/>
-      <c r="P81" s="250"/>
+      <c r="P81" s="190"/>
       <c r="Q81" s="63"/>
       <c r="R81" s="115" t="s">
         <v>106</v>
       </c>
-      <c r="S81" s="273"/>
+      <c r="S81" s="212"/>
       <c r="T81" s="96"/>
       <c r="U81" s="79"/>
       <c r="V81" s="79"/>
       <c r="W81" s="82"/>
     </row>
     <row r="82" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E82" s="170"/>
+      <c r="E82" s="296"/>
       <c r="F82" s="86" t="s">
         <v>85</v>
       </c>
@@ -5067,18 +5059,18 @@
       <c r="N82" s="64"/>
       <c r="O82" s="69"/>
       <c r="P82" s="54"/>
-      <c r="Q82" s="199"/>
-      <c r="R82" s="283" t="s">
+      <c r="Q82" s="144"/>
+      <c r="R82" s="221" t="s">
         <v>105</v>
       </c>
-      <c r="S82" s="274"/>
+      <c r="S82" s="213"/>
       <c r="T82" s="97"/>
       <c r="U82" s="65"/>
       <c r="V82" s="65"/>
       <c r="W82" s="68"/>
     </row>
     <row r="83" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E83" s="170"/>
+      <c r="E83" s="296"/>
       <c r="F83" s="86" t="s">
         <v>88</v>
       </c>
@@ -5092,11 +5084,11 @@
       <c r="N83" s="64"/>
       <c r="O83" s="69"/>
       <c r="P83" s="54"/>
-      <c r="Q83" s="199"/>
-      <c r="R83" s="192" t="s">
+      <c r="Q83" s="144"/>
+      <c r="R83" s="140" t="s">
         <v>104</v>
       </c>
-      <c r="S83" s="274"/>
+      <c r="S83" s="213"/>
       <c r="T83" s="97"/>
       <c r="U83" s="65"/>
       <c r="V83" s="65"/>
@@ -5106,7 +5098,7 @@
       </c>
     </row>
     <row r="84" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E84" s="171"/>
+      <c r="E84" s="297"/>
       <c r="F84" s="90" t="s">
         <v>89</v>
       </c>
@@ -5119,45 +5111,45 @@
       <c r="M84" s="71"/>
       <c r="N84" s="72"/>
       <c r="O84" s="73"/>
-      <c r="P84" s="208"/>
+      <c r="P84" s="153"/>
       <c r="Q84" s="72"/>
       <c r="R84" s="117"/>
-      <c r="S84" s="248"/>
+      <c r="S84" s="188"/>
       <c r="T84" s="98"/>
       <c r="U84" s="72"/>
       <c r="V84" s="72"/>
       <c r="W84" s="83"/>
-      <c r="X84" s="192" t="s">
+      <c r="X84" s="140" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="85" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F85" s="123"/>
-      <c r="G85" s="240" t="s">
+      <c r="G85" s="298" t="s">
         <v>0</v>
       </c>
-      <c r="H85" s="241"/>
-      <c r="I85" s="241"/>
-      <c r="J85" s="241"/>
-      <c r="K85" s="244"/>
-      <c r="L85" s="240" t="s">
+      <c r="H85" s="299"/>
+      <c r="I85" s="299"/>
+      <c r="J85" s="299"/>
+      <c r="K85" s="300"/>
+      <c r="L85" s="298" t="s">
         <v>1</v>
       </c>
-      <c r="M85" s="241"/>
-      <c r="N85" s="241"/>
-      <c r="O85" s="242"/>
-      <c r="P85" s="251" t="s">
+      <c r="M85" s="299"/>
+      <c r="N85" s="299"/>
+      <c r="O85" s="301"/>
+      <c r="P85" s="302" t="s">
         <v>12</v>
       </c>
-      <c r="Q85" s="241"/>
-      <c r="R85" s="241"/>
-      <c r="S85" s="244"/>
-      <c r="T85" s="194" t="s">
+      <c r="Q85" s="299"/>
+      <c r="R85" s="299"/>
+      <c r="S85" s="300"/>
+      <c r="T85" s="303" t="s">
         <v>13</v>
       </c>
-      <c r="U85" s="195"/>
-      <c r="V85" s="195"/>
-      <c r="W85" s="196"/>
+      <c r="U85" s="304"/>
+      <c r="V85" s="304"/>
+      <c r="W85" s="305"/>
     </row>
     <row r="86" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E86" s="124"/>
@@ -5176,7 +5168,7 @@
       <c r="J86" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="K86" s="197" t="s">
+      <c r="K86" s="142" t="s">
         <v>6</v>
       </c>
       <c r="L86" s="93" t="s">
@@ -5191,7 +5183,7 @@
       <c r="O86" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="P86" s="249" t="s">
+      <c r="P86" s="189" t="s">
         <v>2</v>
       </c>
       <c r="Q86" s="76" t="s">
@@ -5200,167 +5192,167 @@
       <c r="R86" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="S86" s="197" t="s">
+      <c r="S86" s="142" t="s">
         <v>5</v>
       </c>
-      <c r="T86" s="262" t="s">
+      <c r="T86" s="201" t="s">
         <v>2</v>
       </c>
-      <c r="U86" s="233" t="s">
+      <c r="U86" s="178" t="s">
         <v>3</v>
       </c>
-      <c r="V86" s="233" t="s">
+      <c r="V86" s="178" t="s">
         <v>4</v>
       </c>
-      <c r="W86" s="263" t="s">
+      <c r="W86" s="202" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="87" spans="4:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E87" s="188" t="s">
+      <c r="E87" s="306" t="s">
         <v>94</v>
       </c>
       <c r="F87" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="G87" s="298"/>
-      <c r="H87" s="299"/>
-      <c r="I87" s="299"/>
-      <c r="J87" s="299"/>
-      <c r="K87" s="300"/>
-      <c r="L87" s="298"/>
-      <c r="M87" s="317"/>
-      <c r="N87" s="299"/>
-      <c r="O87" s="300"/>
-      <c r="P87" s="298"/>
-      <c r="Q87" s="312"/>
+      <c r="G87" s="236"/>
+      <c r="H87" s="237"/>
+      <c r="I87" s="237"/>
+      <c r="J87" s="237"/>
+      <c r="K87" s="238"/>
+      <c r="L87" s="236"/>
+      <c r="M87" s="255"/>
+      <c r="N87" s="237"/>
+      <c r="O87" s="238"/>
+      <c r="P87" s="236"/>
+      <c r="Q87" s="250"/>
       <c r="R87" s="57" t="s">
         <v>130</v>
       </c>
-      <c r="S87" s="315"/>
-      <c r="T87" s="320"/>
-      <c r="U87" s="299"/>
-      <c r="V87" s="299"/>
-      <c r="W87" s="300"/>
+      <c r="S87" s="253"/>
+      <c r="T87" s="258"/>
+      <c r="U87" s="237"/>
+      <c r="V87" s="237"/>
+      <c r="W87" s="238"/>
     </row>
     <row r="88" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E88" s="189"/>
+      <c r="E88" s="307"/>
       <c r="F88" s="88" t="s">
         <v>134</v>
       </c>
-      <c r="G88" s="301"/>
-      <c r="H88" s="297"/>
-      <c r="I88" s="297"/>
-      <c r="J88" s="297"/>
-      <c r="K88" s="302"/>
-      <c r="L88" s="301"/>
-      <c r="M88" s="318"/>
-      <c r="N88" s="297"/>
-      <c r="O88" s="302"/>
-      <c r="P88" s="301"/>
-      <c r="Q88" s="313"/>
+      <c r="G88" s="239"/>
+      <c r="H88" s="235"/>
+      <c r="I88" s="235"/>
+      <c r="J88" s="235"/>
+      <c r="K88" s="240"/>
+      <c r="L88" s="239"/>
+      <c r="M88" s="256"/>
+      <c r="N88" s="235"/>
+      <c r="O88" s="240"/>
+      <c r="P88" s="239"/>
+      <c r="Q88" s="251"/>
       <c r="R88" s="99"/>
-      <c r="S88" s="316"/>
-      <c r="T88" s="321"/>
-      <c r="U88" s="297"/>
-      <c r="V88" s="297"/>
-      <c r="W88" s="302"/>
+      <c r="S88" s="254"/>
+      <c r="T88" s="259"/>
+      <c r="U88" s="235"/>
+      <c r="V88" s="235"/>
+      <c r="W88" s="240"/>
     </row>
     <row r="89" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E89" s="189"/>
+      <c r="E89" s="307"/>
       <c r="F89" s="88" t="s">
         <v>53</v>
       </c>
-      <c r="G89" s="301"/>
-      <c r="H89" s="297"/>
-      <c r="I89" s="297"/>
-      <c r="J89" s="297"/>
-      <c r="K89" s="302"/>
-      <c r="L89" s="301"/>
-      <c r="M89" s="318"/>
-      <c r="N89" s="297"/>
-      <c r="O89" s="302"/>
-      <c r="P89" s="301"/>
-      <c r="Q89" s="313"/>
+      <c r="G89" s="239"/>
+      <c r="H89" s="235"/>
+      <c r="I89" s="235"/>
+      <c r="J89" s="235"/>
+      <c r="K89" s="240"/>
+      <c r="L89" s="239"/>
+      <c r="M89" s="256"/>
+      <c r="N89" s="235"/>
+      <c r="O89" s="240"/>
+      <c r="P89" s="239"/>
+      <c r="Q89" s="251"/>
       <c r="R89" s="99"/>
-      <c r="S89" s="316"/>
-      <c r="T89" s="321"/>
-      <c r="U89" s="297"/>
-      <c r="V89" s="297"/>
-      <c r="W89" s="302"/>
+      <c r="S89" s="254"/>
+      <c r="T89" s="259"/>
+      <c r="U89" s="235"/>
+      <c r="V89" s="235"/>
+      <c r="W89" s="240"/>
     </row>
     <row r="90" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E90" s="189"/>
+      <c r="E90" s="307"/>
       <c r="F90" s="88" t="s">
         <v>135</v>
       </c>
-      <c r="G90" s="301"/>
-      <c r="H90" s="297"/>
-      <c r="I90" s="297"/>
-      <c r="J90" s="297"/>
-      <c r="K90" s="302"/>
-      <c r="L90" s="301"/>
-      <c r="M90" s="318"/>
-      <c r="N90" s="297"/>
-      <c r="O90" s="302"/>
-      <c r="P90" s="301"/>
-      <c r="Q90" s="313"/>
+      <c r="G90" s="239"/>
+      <c r="H90" s="235"/>
+      <c r="I90" s="235"/>
+      <c r="J90" s="235"/>
+      <c r="K90" s="240"/>
+      <c r="L90" s="239"/>
+      <c r="M90" s="256"/>
+      <c r="N90" s="235"/>
+      <c r="O90" s="240"/>
+      <c r="P90" s="239"/>
+      <c r="Q90" s="251"/>
       <c r="R90" s="99"/>
-      <c r="S90" s="316"/>
-      <c r="T90" s="321"/>
-      <c r="U90" s="297"/>
-      <c r="V90" s="297"/>
-      <c r="W90" s="302"/>
+      <c r="S90" s="254"/>
+      <c r="T90" s="259"/>
+      <c r="U90" s="235"/>
+      <c r="V90" s="235"/>
+      <c r="W90" s="240"/>
     </row>
     <row r="91" spans="4:24" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E91" s="189"/>
+      <c r="E91" s="307"/>
       <c r="F91" s="88" t="s">
         <v>131</v>
       </c>
-      <c r="G91" s="305"/>
-      <c r="H91" s="303"/>
-      <c r="I91" s="303"/>
-      <c r="J91" s="303"/>
-      <c r="K91" s="304"/>
-      <c r="L91" s="305"/>
-      <c r="M91" s="331"/>
-      <c r="N91" s="303"/>
-      <c r="O91" s="304"/>
-      <c r="P91" s="305"/>
-      <c r="Q91" s="335"/>
-      <c r="R91" s="332"/>
-      <c r="S91" s="336"/>
-      <c r="T91" s="333"/>
-      <c r="U91" s="303"/>
-      <c r="V91" s="303"/>
-      <c r="W91" s="304"/>
+      <c r="G91" s="243"/>
+      <c r="H91" s="241"/>
+      <c r="I91" s="241"/>
+      <c r="J91" s="241"/>
+      <c r="K91" s="242"/>
+      <c r="L91" s="243"/>
+      <c r="M91" s="269"/>
+      <c r="N91" s="241"/>
+      <c r="O91" s="242"/>
+      <c r="P91" s="243"/>
+      <c r="Q91" s="273"/>
+      <c r="R91" s="270"/>
+      <c r="S91" s="274"/>
+      <c r="T91" s="271"/>
+      <c r="U91" s="241"/>
+      <c r="V91" s="241"/>
+      <c r="W91" s="242"/>
     </row>
     <row r="92" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E92" s="190"/>
-      <c r="F92" s="191" t="s">
+      <c r="E92" s="308"/>
+      <c r="F92" s="139" t="s">
         <v>133</v>
       </c>
-      <c r="G92" s="323"/>
-      <c r="H92" s="324"/>
-      <c r="I92" s="324"/>
-      <c r="J92" s="324"/>
-      <c r="K92" s="330"/>
-      <c r="L92" s="323"/>
-      <c r="M92" s="326"/>
-      <c r="N92" s="324"/>
-      <c r="O92" s="325"/>
-      <c r="P92" s="338"/>
-      <c r="Q92" s="339"/>
-      <c r="R92" s="337"/>
-      <c r="S92" s="296"/>
+      <c r="G92" s="261"/>
+      <c r="H92" s="262"/>
+      <c r="I92" s="262"/>
+      <c r="J92" s="262"/>
+      <c r="K92" s="268"/>
+      <c r="L92" s="261"/>
+      <c r="M92" s="264"/>
+      <c r="N92" s="262"/>
+      <c r="O92" s="263"/>
+      <c r="P92" s="276"/>
+      <c r="Q92" s="277"/>
+      <c r="R92" s="275"/>
+      <c r="S92" s="234"/>
       <c r="T92" s="98"/>
       <c r="U92" s="72"/>
-      <c r="V92" s="324"/>
-      <c r="W92" s="325"/>
+      <c r="V92" s="262"/>
+      <c r="W92" s="263"/>
     </row>
     <row r="93" spans="4:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D93" s="49"/>
-      <c r="E93" s="178" t="s">
+      <c r="E93" s="292" t="s">
         <v>62</v>
       </c>
       <c r="F93" s="85" t="s">
@@ -5375,20 +5367,20 @@
       <c r="M93" s="81"/>
       <c r="N93" s="79"/>
       <c r="O93" s="82"/>
-      <c r="P93" s="250"/>
+      <c r="P93" s="190"/>
       <c r="Q93" s="79"/>
-      <c r="R93" s="198"/>
+      <c r="R93" s="143"/>
       <c r="S93" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="T93" s="329"/>
-      <c r="U93" s="306"/>
+      <c r="T93" s="267"/>
+      <c r="U93" s="244"/>
       <c r="V93" s="79"/>
       <c r="W93" s="82"/>
     </row>
     <row r="94" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D94" s="49"/>
-      <c r="E94" s="179"/>
+      <c r="E94" s="293"/>
       <c r="F94" s="86" t="s">
         <v>64</v>
       </c>
@@ -5397,23 +5389,23 @@
       <c r="I94" s="64"/>
       <c r="J94" s="64"/>
       <c r="K94" s="113"/>
-      <c r="L94" s="301"/>
+      <c r="L94" s="239"/>
       <c r="M94" s="66"/>
       <c r="N94" s="65"/>
       <c r="O94" s="68"/>
       <c r="P94" s="54"/>
       <c r="Q94" s="65"/>
-      <c r="R94" s="199"/>
-      <c r="S94" s="340"/>
-      <c r="T94" s="329"/>
-      <c r="U94" s="306"/>
+      <c r="R94" s="144"/>
+      <c r="S94" s="278"/>
+      <c r="T94" s="267"/>
+      <c r="U94" s="244"/>
       <c r="V94" s="65"/>
-      <c r="W94" s="302"/>
+      <c r="W94" s="240"/>
     </row>
     <row r="95" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D95" s="49"/>
-      <c r="E95" s="179"/>
-      <c r="F95" s="219" t="s">
+      <c r="E95" s="293"/>
+      <c r="F95" s="164" t="s">
         <v>132</v>
       </c>
       <c r="G95" s="94"/>
@@ -5421,24 +5413,24 @@
       <c r="I95" s="64"/>
       <c r="J95" s="64"/>
       <c r="K95" s="113"/>
-      <c r="L95" s="301"/>
+      <c r="L95" s="239"/>
       <c r="M95" s="66"/>
       <c r="N95" s="65"/>
       <c r="O95" s="68"/>
       <c r="P95" s="54"/>
       <c r="Q95" s="65"/>
-      <c r="R95" s="199"/>
-      <c r="S95" s="293"/>
-      <c r="T95" s="321"/>
-      <c r="U95" s="297"/>
-      <c r="W95" s="291" t="s">
+      <c r="R95" s="144"/>
+      <c r="S95" s="231"/>
+      <c r="T95" s="259"/>
+      <c r="U95" s="235"/>
+      <c r="W95" s="229" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="96" spans="4:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D96" s="49"/>
-      <c r="E96" s="180"/>
-      <c r="F96" s="214" t="s">
+      <c r="E96" s="294"/>
+      <c r="F96" s="159" t="s">
         <v>111</v>
       </c>
       <c r="G96" s="95"/>
@@ -5446,261 +5438,261 @@
       <c r="I96" s="70"/>
       <c r="J96" s="70"/>
       <c r="K96" s="114"/>
-      <c r="L96" s="311"/>
+      <c r="L96" s="249"/>
       <c r="M96" s="71"/>
       <c r="N96" s="72"/>
       <c r="O96" s="83"/>
-      <c r="P96" s="208"/>
+      <c r="P96" s="153"/>
       <c r="Q96" s="72"/>
       <c r="R96" s="72"/>
-      <c r="S96" s="200"/>
-      <c r="T96" s="182"/>
-      <c r="U96" s="183"/>
-      <c r="V96" s="183"/>
-      <c r="W96" s="293"/>
+      <c r="S96" s="145"/>
+      <c r="T96" s="133"/>
+      <c r="U96" s="134"/>
+      <c r="V96" s="134"/>
+      <c r="W96" s="231"/>
     </row>
     <row r="97" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E97" s="179" t="s">
+      <c r="E97" s="293" t="s">
         <v>91</v>
       </c>
       <c r="F97" s="85" t="s">
         <v>150</v>
       </c>
-      <c r="G97" s="308"/>
-      <c r="H97" s="306"/>
-      <c r="I97" s="306"/>
-      <c r="J97" s="306"/>
-      <c r="K97" s="307"/>
-      <c r="L97" s="308"/>
-      <c r="M97" s="328"/>
-      <c r="N97" s="306"/>
-      <c r="O97" s="307"/>
-      <c r="P97" s="308"/>
-      <c r="Q97" s="306"/>
-      <c r="R97" s="341"/>
-      <c r="S97" s="167" t="s">
+      <c r="G97" s="246"/>
+      <c r="H97" s="244"/>
+      <c r="I97" s="244"/>
+      <c r="J97" s="244"/>
+      <c r="K97" s="245"/>
+      <c r="L97" s="246"/>
+      <c r="M97" s="266"/>
+      <c r="N97" s="244"/>
+      <c r="O97" s="245"/>
+      <c r="P97" s="246"/>
+      <c r="Q97" s="244"/>
+      <c r="R97" s="279"/>
+      <c r="S97" s="286" t="s">
         <v>51</v>
       </c>
-      <c r="T97" s="234"/>
-      <c r="U97" s="234"/>
-      <c r="V97" s="168"/>
-      <c r="W97" s="342"/>
+      <c r="T97" s="287"/>
+      <c r="U97" s="287"/>
+      <c r="V97" s="288"/>
+      <c r="W97" s="280"/>
     </row>
     <row r="98" spans="5:23" x14ac:dyDescent="0.3">
-      <c r="E98" s="179"/>
-      <c r="F98" s="334" t="s">
+      <c r="E98" s="293"/>
+      <c r="F98" s="272" t="s">
         <v>151</v>
       </c>
-      <c r="G98" s="308"/>
-      <c r="H98" s="306"/>
-      <c r="I98" s="306"/>
-      <c r="J98" s="306"/>
-      <c r="K98" s="307"/>
-      <c r="L98" s="308"/>
-      <c r="M98" s="328"/>
-      <c r="N98" s="306"/>
-      <c r="O98" s="307"/>
-      <c r="P98" s="308"/>
-      <c r="Q98" s="306"/>
-      <c r="R98" s="341"/>
+      <c r="G98" s="246"/>
+      <c r="H98" s="244"/>
+      <c r="I98" s="244"/>
+      <c r="J98" s="244"/>
+      <c r="K98" s="245"/>
+      <c r="L98" s="246"/>
+      <c r="M98" s="266"/>
+      <c r="N98" s="244"/>
+      <c r="O98" s="245"/>
+      <c r="P98" s="246"/>
+      <c r="Q98" s="244"/>
+      <c r="R98" s="279"/>
       <c r="S98" s="106"/>
       <c r="T98" s="65"/>
       <c r="U98" s="65"/>
-      <c r="V98" s="302"/>
-      <c r="W98" s="342"/>
+      <c r="V98" s="240"/>
+      <c r="W98" s="280"/>
     </row>
     <row r="99" spans="5:23" x14ac:dyDescent="0.3">
-      <c r="E99" s="179"/>
+      <c r="E99" s="293"/>
       <c r="F99" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="G99" s="301"/>
-      <c r="H99" s="297"/>
-      <c r="I99" s="297"/>
-      <c r="J99" s="297"/>
-      <c r="K99" s="302"/>
-      <c r="L99" s="301"/>
-      <c r="M99" s="318"/>
-      <c r="N99" s="297"/>
-      <c r="O99" s="302"/>
-      <c r="P99" s="301"/>
-      <c r="Q99" s="297"/>
-      <c r="R99" s="313"/>
+      <c r="G99" s="239"/>
+      <c r="H99" s="235"/>
+      <c r="I99" s="235"/>
+      <c r="J99" s="235"/>
+      <c r="K99" s="240"/>
+      <c r="L99" s="239"/>
+      <c r="M99" s="256"/>
+      <c r="N99" s="235"/>
+      <c r="O99" s="240"/>
+      <c r="P99" s="239"/>
+      <c r="Q99" s="235"/>
+      <c r="R99" s="251"/>
       <c r="S99" s="106"/>
       <c r="T99" s="65"/>
       <c r="U99" s="65"/>
-      <c r="V99" s="302"/>
-      <c r="W99" s="316"/>
+      <c r="V99" s="240"/>
+      <c r="W99" s="254"/>
     </row>
     <row r="100" spans="5:23" x14ac:dyDescent="0.3">
-      <c r="E100" s="179"/>
+      <c r="E100" s="293"/>
       <c r="F100" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="G100" s="301"/>
-      <c r="H100" s="297"/>
-      <c r="I100" s="297"/>
-      <c r="J100" s="297"/>
-      <c r="K100" s="302"/>
-      <c r="L100" s="301"/>
-      <c r="M100" s="318"/>
-      <c r="N100" s="297"/>
-      <c r="O100" s="302"/>
-      <c r="P100" s="301"/>
-      <c r="Q100" s="297"/>
-      <c r="R100" s="313"/>
+      <c r="G100" s="239"/>
+      <c r="H100" s="235"/>
+      <c r="I100" s="235"/>
+      <c r="J100" s="235"/>
+      <c r="K100" s="240"/>
+      <c r="L100" s="239"/>
+      <c r="M100" s="256"/>
+      <c r="N100" s="235"/>
+      <c r="O100" s="240"/>
+      <c r="P100" s="239"/>
+      <c r="Q100" s="235"/>
+      <c r="R100" s="251"/>
       <c r="S100" s="97"/>
-      <c r="T100" s="223"/>
+      <c r="T100" s="168"/>
       <c r="U100" s="65"/>
-      <c r="V100" s="302"/>
-      <c r="W100" s="316"/>
+      <c r="V100" s="240"/>
+      <c r="W100" s="254"/>
     </row>
     <row r="101" spans="5:23" x14ac:dyDescent="0.3">
-      <c r="E101" s="179"/>
+      <c r="E101" s="293"/>
       <c r="F101" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="G101" s="301"/>
-      <c r="H101" s="297"/>
-      <c r="I101" s="297"/>
-      <c r="J101" s="297"/>
-      <c r="K101" s="302"/>
-      <c r="L101" s="301"/>
-      <c r="M101" s="318"/>
-      <c r="N101" s="297"/>
-      <c r="O101" s="302"/>
-      <c r="P101" s="301"/>
-      <c r="Q101" s="297"/>
-      <c r="R101" s="313"/>
-      <c r="S101" s="301"/>
-      <c r="T101" s="297"/>
-      <c r="U101" s="223"/>
-      <c r="V101" s="302"/>
-      <c r="W101" s="316"/>
+      <c r="G101" s="239"/>
+      <c r="H101" s="235"/>
+      <c r="I101" s="235"/>
+      <c r="J101" s="235"/>
+      <c r="K101" s="240"/>
+      <c r="L101" s="239"/>
+      <c r="M101" s="256"/>
+      <c r="N101" s="235"/>
+      <c r="O101" s="240"/>
+      <c r="P101" s="239"/>
+      <c r="Q101" s="235"/>
+      <c r="R101" s="251"/>
+      <c r="S101" s="239"/>
+      <c r="T101" s="235"/>
+      <c r="U101" s="168"/>
+      <c r="V101" s="240"/>
+      <c r="W101" s="254"/>
     </row>
     <row r="102" spans="5:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E102" s="179"/>
+      <c r="E102" s="293"/>
       <c r="F102" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="G102" s="301"/>
-      <c r="H102" s="297"/>
-      <c r="I102" s="297"/>
-      <c r="J102" s="297"/>
-      <c r="K102" s="302"/>
-      <c r="L102" s="301"/>
-      <c r="M102" s="318"/>
-      <c r="N102" s="297"/>
-      <c r="O102" s="302"/>
-      <c r="P102" s="301"/>
-      <c r="Q102" s="297"/>
-      <c r="R102" s="313"/>
-      <c r="S102" s="301"/>
-      <c r="T102" s="297"/>
-      <c r="U102" s="297"/>
-      <c r="V102" s="258"/>
-      <c r="W102" s="316"/>
+      <c r="G102" s="239"/>
+      <c r="H102" s="235"/>
+      <c r="I102" s="235"/>
+      <c r="J102" s="235"/>
+      <c r="K102" s="240"/>
+      <c r="L102" s="239"/>
+      <c r="M102" s="256"/>
+      <c r="N102" s="235"/>
+      <c r="O102" s="240"/>
+      <c r="P102" s="239"/>
+      <c r="Q102" s="235"/>
+      <c r="R102" s="251"/>
+      <c r="S102" s="239"/>
+      <c r="T102" s="235"/>
+      <c r="U102" s="235"/>
+      <c r="V102" s="197"/>
+      <c r="W102" s="254"/>
     </row>
     <row r="103" spans="5:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E103" s="179"/>
+      <c r="E103" s="293"/>
       <c r="F103" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="G103" s="301"/>
-      <c r="H103" s="297"/>
-      <c r="I103" s="297"/>
-      <c r="J103" s="297"/>
-      <c r="K103" s="302"/>
-      <c r="L103" s="301"/>
-      <c r="M103" s="318"/>
-      <c r="N103" s="297"/>
-      <c r="O103" s="302"/>
-      <c r="P103" s="301"/>
-      <c r="Q103" s="297"/>
-      <c r="R103" s="313"/>
-      <c r="S103" s="311"/>
-      <c r="T103" s="309"/>
-      <c r="U103" s="309"/>
+      <c r="G103" s="239"/>
+      <c r="H103" s="235"/>
+      <c r="I103" s="235"/>
+      <c r="J103" s="235"/>
+      <c r="K103" s="240"/>
+      <c r="L103" s="239"/>
+      <c r="M103" s="256"/>
+      <c r="N103" s="235"/>
+      <c r="O103" s="240"/>
+      <c r="P103" s="239"/>
+      <c r="Q103" s="235"/>
+      <c r="R103" s="251"/>
+      <c r="S103" s="249"/>
+      <c r="T103" s="247"/>
+      <c r="U103" s="247"/>
       <c r="V103" s="107"/>
-      <c r="W103" s="343" t="s">
+      <c r="W103" s="281" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="104" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E104" s="180"/>
-      <c r="F104" s="214" t="s">
+      <c r="E104" s="294"/>
+      <c r="F104" s="159" t="s">
         <v>111</v>
       </c>
-      <c r="G104" s="311"/>
-      <c r="H104" s="309"/>
-      <c r="I104" s="309"/>
-      <c r="J104" s="309"/>
-      <c r="K104" s="310"/>
-      <c r="L104" s="311"/>
-      <c r="M104" s="319"/>
-      <c r="N104" s="309"/>
-      <c r="O104" s="310"/>
-      <c r="P104" s="311"/>
-      <c r="Q104" s="309"/>
-      <c r="R104" s="309"/>
-      <c r="S104" s="330"/>
-      <c r="T104" s="327"/>
-      <c r="U104" s="324"/>
-      <c r="V104" s="177"/>
-      <c r="W104" s="205"/>
+      <c r="G104" s="249"/>
+      <c r="H104" s="247"/>
+      <c r="I104" s="247"/>
+      <c r="J104" s="247"/>
+      <c r="K104" s="248"/>
+      <c r="L104" s="249"/>
+      <c r="M104" s="257"/>
+      <c r="N104" s="247"/>
+      <c r="O104" s="248"/>
+      <c r="P104" s="249"/>
+      <c r="Q104" s="247"/>
+      <c r="R104" s="247"/>
+      <c r="S104" s="268"/>
+      <c r="T104" s="265"/>
+      <c r="U104" s="262"/>
+      <c r="V104" s="131"/>
+      <c r="W104" s="150"/>
     </row>
     <row r="105" spans="5:23" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E105" s="178" t="s">
+      <c r="E105" s="292" t="s">
         <v>92</v>
       </c>
       <c r="F105" s="85" t="s">
         <v>138</v>
       </c>
-      <c r="G105" s="298"/>
-      <c r="H105" s="299"/>
-      <c r="I105" s="299"/>
-      <c r="J105" s="299"/>
-      <c r="K105" s="300"/>
-      <c r="L105" s="298"/>
-      <c r="M105" s="317"/>
-      <c r="N105" s="299"/>
-      <c r="O105" s="300"/>
-      <c r="P105" s="298"/>
-      <c r="Q105" s="299"/>
-      <c r="R105" s="312"/>
-      <c r="S105" s="167" t="s">
+      <c r="G105" s="236"/>
+      <c r="H105" s="237"/>
+      <c r="I105" s="237"/>
+      <c r="J105" s="237"/>
+      <c r="K105" s="238"/>
+      <c r="L105" s="236"/>
+      <c r="M105" s="255"/>
+      <c r="N105" s="237"/>
+      <c r="O105" s="238"/>
+      <c r="P105" s="236"/>
+      <c r="Q105" s="237"/>
+      <c r="R105" s="250"/>
+      <c r="S105" s="286" t="s">
         <v>52</v>
       </c>
-      <c r="T105" s="234"/>
-      <c r="U105" s="234"/>
-      <c r="V105" s="168"/>
-      <c r="W105" s="315"/>
+      <c r="T105" s="287"/>
+      <c r="U105" s="287"/>
+      <c r="V105" s="288"/>
+      <c r="W105" s="253"/>
     </row>
     <row r="106" spans="5:23" x14ac:dyDescent="0.3">
-      <c r="E106" s="179"/>
-      <c r="F106" s="334" t="s">
+      <c r="E106" s="293"/>
+      <c r="F106" s="272" t="s">
         <v>148</v>
       </c>
-      <c r="G106" s="301"/>
-      <c r="H106" s="297"/>
-      <c r="I106" s="297"/>
-      <c r="J106" s="297"/>
-      <c r="K106" s="302"/>
-      <c r="L106" s="301"/>
-      <c r="M106" s="318"/>
-      <c r="N106" s="297"/>
-      <c r="O106" s="302"/>
-      <c r="P106" s="301"/>
-      <c r="Q106" s="297"/>
-      <c r="R106" s="313"/>
+      <c r="G106" s="239"/>
+      <c r="H106" s="235"/>
+      <c r="I106" s="235"/>
+      <c r="J106" s="235"/>
+      <c r="K106" s="240"/>
+      <c r="L106" s="239"/>
+      <c r="M106" s="256"/>
+      <c r="N106" s="235"/>
+      <c r="O106" s="240"/>
+      <c r="P106" s="239"/>
+      <c r="Q106" s="235"/>
+      <c r="R106" s="251"/>
       <c r="S106" s="108"/>
       <c r="T106" s="65"/>
-      <c r="U106" s="297"/>
-      <c r="V106" s="302"/>
-      <c r="W106" s="316"/>
+      <c r="U106" s="235"/>
+      <c r="V106" s="240"/>
+      <c r="W106" s="254"/>
     </row>
     <row r="107" spans="5:23" x14ac:dyDescent="0.3">
-      <c r="E107" s="179"/>
+      <c r="E107" s="293"/>
       <c r="F107" s="4" t="s">
         <v>149</v>
       </c>
@@ -5715,15 +5707,15 @@
       <c r="O107" s="68"/>
       <c r="P107" s="97"/>
       <c r="Q107" s="65"/>
-      <c r="R107" s="199"/>
+      <c r="R107" s="144"/>
       <c r="S107" s="108"/>
       <c r="T107" s="65"/>
-      <c r="U107" s="297"/>
-      <c r="V107" s="302"/>
-      <c r="W107" s="316"/>
+      <c r="U107" s="235"/>
+      <c r="V107" s="240"/>
+      <c r="W107" s="254"/>
     </row>
     <row r="108" spans="5:23" x14ac:dyDescent="0.3">
-      <c r="E108" s="179"/>
+      <c r="E108" s="293"/>
       <c r="F108" s="4" t="s">
         <v>157</v>
       </c>
@@ -5738,15 +5730,15 @@
       <c r="O108" s="68"/>
       <c r="P108" s="97"/>
       <c r="Q108" s="65"/>
-      <c r="R108" s="199"/>
+      <c r="R108" s="144"/>
       <c r="S108" s="97"/>
-      <c r="T108" s="224"/>
-      <c r="U108" s="297"/>
-      <c r="V108" s="302"/>
-      <c r="W108" s="316"/>
+      <c r="T108" s="169"/>
+      <c r="U108" s="235"/>
+      <c r="V108" s="240"/>
+      <c r="W108" s="254"/>
     </row>
     <row r="109" spans="5:23" x14ac:dyDescent="0.3">
-      <c r="E109" s="179"/>
+      <c r="E109" s="293"/>
       <c r="F109" s="4" t="s">
         <v>154</v>
       </c>
@@ -5761,15 +5753,15 @@
       <c r="O109" s="68"/>
       <c r="P109" s="97"/>
       <c r="Q109" s="65"/>
-      <c r="R109" s="199"/>
+      <c r="R109" s="144"/>
       <c r="S109" s="97"/>
-      <c r="T109" s="297"/>
-      <c r="U109" s="224"/>
-      <c r="V109" s="302"/>
-      <c r="W109" s="316"/>
+      <c r="T109" s="235"/>
+      <c r="U109" s="169"/>
+      <c r="V109" s="240"/>
+      <c r="W109" s="254"/>
     </row>
     <row r="110" spans="5:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E110" s="179"/>
+      <c r="E110" s="293"/>
       <c r="F110" s="4" t="s">
         <v>142</v>
       </c>
@@ -5784,15 +5776,15 @@
       <c r="O110" s="68"/>
       <c r="P110" s="97"/>
       <c r="Q110" s="65"/>
-      <c r="R110" s="199"/>
+      <c r="R110" s="144"/>
       <c r="S110" s="97"/>
       <c r="T110" s="65"/>
       <c r="U110" s="65"/>
-      <c r="V110" s="259"/>
-      <c r="W110" s="316"/>
+      <c r="V110" s="198"/>
+      <c r="W110" s="254"/>
     </row>
     <row r="111" spans="5:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E111" s="179"/>
+      <c r="E111" s="293"/>
       <c r="F111" s="4" t="s">
         <v>143</v>
       </c>
@@ -5807,18 +5799,18 @@
       <c r="O111" s="68"/>
       <c r="P111" s="97"/>
       <c r="Q111" s="65"/>
-      <c r="R111" s="199"/>
+      <c r="R111" s="144"/>
       <c r="S111" s="98"/>
-      <c r="T111" s="309"/>
-      <c r="U111" s="309"/>
+      <c r="T111" s="247"/>
+      <c r="U111" s="247"/>
       <c r="V111" s="109"/>
-      <c r="W111" s="343" t="s">
+      <c r="W111" s="281" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="112" spans="5:23" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E112" s="179"/>
-      <c r="F112" s="214" t="s">
+      <c r="E112" s="293"/>
+      <c r="F112" s="159" t="s">
         <v>111</v>
       </c>
       <c r="G112" s="98"/>
@@ -5833,14 +5825,14 @@
       <c r="P112" s="98"/>
       <c r="Q112" s="72"/>
       <c r="R112" s="72"/>
-      <c r="S112" s="210"/>
-      <c r="T112" s="344"/>
-      <c r="U112" s="345"/>
+      <c r="S112" s="155"/>
+      <c r="T112" s="282"/>
+      <c r="U112" s="283"/>
       <c r="V112" s="117"/>
-      <c r="W112" s="292"/>
+      <c r="W112" s="230"/>
     </row>
     <row r="113" spans="5:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E113" s="178" t="s">
+      <c r="E113" s="292" t="s">
         <v>113</v>
       </c>
       <c r="F113" s="85" t="s">
@@ -5857,17 +5849,17 @@
       <c r="O113" s="82"/>
       <c r="P113" s="96"/>
       <c r="Q113" s="79"/>
-      <c r="R113" s="198"/>
-      <c r="S113" s="150" t="s">
+      <c r="R113" s="143"/>
+      <c r="S113" s="289" t="s">
         <v>67</v>
       </c>
-      <c r="T113" s="151"/>
-      <c r="U113" s="151"/>
-      <c r="V113" s="152"/>
-      <c r="W113" s="315"/>
+      <c r="T113" s="290"/>
+      <c r="U113" s="290"/>
+      <c r="V113" s="291"/>
+      <c r="W113" s="253"/>
     </row>
     <row r="114" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E114" s="179"/>
+      <c r="E114" s="293"/>
       <c r="F114" s="4" t="s">
         <v>139</v>
       </c>
@@ -5882,16 +5874,16 @@
       <c r="O114" s="68"/>
       <c r="P114" s="97"/>
       <c r="Q114" s="65"/>
-      <c r="R114" s="199"/>
-      <c r="S114" s="347"/>
+      <c r="R114" s="144"/>
+      <c r="S114" s="285"/>
       <c r="T114" s="59"/>
-      <c r="U114" s="299"/>
-      <c r="V114" s="300"/>
-      <c r="W114" s="316"/>
+      <c r="U114" s="237"/>
+      <c r="V114" s="238"/>
+      <c r="W114" s="254"/>
     </row>
     <row r="115" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E115" s="179"/>
-      <c r="F115" s="334" t="s">
+      <c r="E115" s="293"/>
+      <c r="F115" s="272" t="s">
         <v>147</v>
       </c>
       <c r="G115" s="97"/>
@@ -5905,15 +5897,15 @@
       <c r="O115" s="68"/>
       <c r="P115" s="97"/>
       <c r="Q115" s="65"/>
-      <c r="R115" s="199"/>
+      <c r="R115" s="144"/>
       <c r="S115" s="119"/>
       <c r="T115" s="65"/>
-      <c r="U115" s="297"/>
-      <c r="V115" s="302"/>
-      <c r="W115" s="316"/>
+      <c r="U115" s="235"/>
+      <c r="V115" s="240"/>
+      <c r="W115" s="254"/>
     </row>
     <row r="116" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E116" s="179"/>
+      <c r="E116" s="293"/>
       <c r="F116" s="4" t="s">
         <v>146</v>
       </c>
@@ -5928,15 +5920,15 @@
       <c r="O116" s="68"/>
       <c r="P116" s="97"/>
       <c r="Q116" s="65"/>
-      <c r="R116" s="199"/>
+      <c r="R116" s="144"/>
       <c r="S116" s="119"/>
-      <c r="T116" s="297"/>
-      <c r="U116" s="297"/>
-      <c r="V116" s="302"/>
-      <c r="W116" s="316"/>
+      <c r="T116" s="235"/>
+      <c r="U116" s="235"/>
+      <c r="V116" s="240"/>
+      <c r="W116" s="254"/>
     </row>
     <row r="117" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E117" s="179"/>
+      <c r="E117" s="293"/>
       <c r="F117" s="4" t="s">
         <v>158</v>
       </c>
@@ -5951,15 +5943,15 @@
       <c r="O117" s="68"/>
       <c r="P117" s="97"/>
       <c r="Q117" s="65"/>
-      <c r="R117" s="199"/>
+      <c r="R117" s="144"/>
       <c r="S117" s="97"/>
-      <c r="T117" s="225"/>
-      <c r="U117" s="297"/>
-      <c r="V117" s="302"/>
-      <c r="W117" s="316"/>
+      <c r="T117" s="170"/>
+      <c r="U117" s="235"/>
+      <c r="V117" s="240"/>
+      <c r="W117" s="254"/>
     </row>
     <row r="118" spans="5:24" x14ac:dyDescent="0.3">
-      <c r="E118" s="179"/>
+      <c r="E118" s="293"/>
       <c r="F118" s="4" t="s">
         <v>155</v>
       </c>
@@ -5974,15 +5966,15 @@
       <c r="O118" s="68"/>
       <c r="P118" s="97"/>
       <c r="Q118" s="65"/>
-      <c r="R118" s="199"/>
+      <c r="R118" s="144"/>
       <c r="S118" s="97"/>
-      <c r="T118" s="297"/>
-      <c r="U118" s="225"/>
-      <c r="V118" s="302"/>
-      <c r="W118" s="316"/>
+      <c r="T118" s="235"/>
+      <c r="U118" s="170"/>
+      <c r="V118" s="240"/>
+      <c r="W118" s="254"/>
     </row>
     <row r="119" spans="5:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E119" s="179"/>
+      <c r="E119" s="293"/>
       <c r="F119" s="4" t="s">
         <v>144</v>
       </c>
@@ -5997,15 +5989,15 @@
       <c r="O119" s="68"/>
       <c r="P119" s="97"/>
       <c r="Q119" s="65"/>
-      <c r="R119" s="199"/>
+      <c r="R119" s="144"/>
       <c r="S119" s="97"/>
       <c r="T119" s="65"/>
       <c r="U119" s="65"/>
-      <c r="V119" s="260"/>
-      <c r="W119" s="316"/>
+      <c r="V119" s="199"/>
+      <c r="W119" s="254"/>
     </row>
     <row r="120" spans="5:24" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E120" s="179"/>
+      <c r="E120" s="293"/>
       <c r="F120" s="4" t="s">
         <v>145</v>
       </c>
@@ -6020,18 +6012,18 @@
       <c r="O120" s="68"/>
       <c r="P120" s="97"/>
       <c r="Q120" s="65"/>
-      <c r="R120" s="199"/>
+      <c r="R120" s="144"/>
       <c r="S120" s="98"/>
-      <c r="T120" s="309"/>
-      <c r="U120" s="309"/>
+      <c r="T120" s="247"/>
+      <c r="U120" s="247"/>
       <c r="V120" s="121"/>
-      <c r="W120" s="343" t="s">
+      <c r="W120" s="281" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="121" spans="5:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E121" s="180"/>
-      <c r="F121" s="214" t="s">
+      <c r="E121" s="294"/>
+      <c r="F121" s="159" t="s">
         <v>111</v>
       </c>
       <c r="G121" s="98"/>
@@ -6046,13 +6038,13 @@
       <c r="P121" s="98"/>
       <c r="Q121" s="72"/>
       <c r="R121" s="72"/>
-      <c r="S121" s="346"/>
-      <c r="T121" s="344"/>
-      <c r="U121" s="345"/>
+      <c r="S121" s="284"/>
+      <c r="T121" s="282"/>
+      <c r="U121" s="283"/>
       <c r="W121" s="111"/>
     </row>
     <row r="122" spans="5:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E122" s="169" t="s">
+      <c r="E122" s="295" t="s">
         <v>47</v>
       </c>
       <c r="F122" s="85" t="s">
@@ -6071,15 +6063,15 @@
       <c r="Q122" s="79"/>
       <c r="R122" s="79"/>
       <c r="S122" s="82"/>
-      <c r="T122" s="320"/>
-      <c r="U122" s="312"/>
-      <c r="V122" s="198"/>
+      <c r="T122" s="258"/>
+      <c r="U122" s="250"/>
+      <c r="V122" s="143"/>
       <c r="W122" s="115" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="123" spans="5:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E123" s="170"/>
+      <c r="E123" s="296"/>
       <c r="F123" s="86" t="s">
         <v>79</v>
       </c>
@@ -6096,12 +6088,12 @@
       <c r="Q123" s="65"/>
       <c r="R123" s="65"/>
       <c r="S123" s="68"/>
-      <c r="T123" s="321"/>
-      <c r="U123" s="313"/>
-      <c r="W123" s="215"/>
+      <c r="T123" s="259"/>
+      <c r="U123" s="251"/>
+      <c r="W123" s="160"/>
     </row>
     <row r="124" spans="5:24" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E124" s="171"/>
+      <c r="E124" s="297"/>
       <c r="F124" s="90" t="s">
         <v>78</v>
       </c>
@@ -6118,12 +6110,12 @@
       <c r="Q124" s="72"/>
       <c r="R124" s="72"/>
       <c r="S124" s="83"/>
-      <c r="T124" s="322"/>
-      <c r="U124" s="314"/>
-      <c r="W124" s="216"/>
+      <c r="T124" s="260"/>
+      <c r="U124" s="252"/>
+      <c r="W124" s="161"/>
     </row>
     <row r="125" spans="5:24" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E125" s="169" t="s">
+      <c r="E125" s="295" t="s">
         <v>82</v>
       </c>
       <c r="F125" s="85" t="s">
@@ -6138,20 +6130,20 @@
       <c r="M125" s="61"/>
       <c r="N125" s="59"/>
       <c r="O125" s="58"/>
-      <c r="P125" s="203"/>
+      <c r="P125" s="148"/>
       <c r="Q125" s="79"/>
       <c r="R125" s="79"/>
       <c r="S125" s="82"/>
       <c r="T125" s="96"/>
       <c r="U125" s="79"/>
-      <c r="V125" s="198"/>
+      <c r="V125" s="143"/>
       <c r="W125" s="82"/>
       <c r="X125" s="115" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="126" spans="5:24" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="E126" s="170"/>
+      <c r="E126" s="296"/>
       <c r="F126" s="86" t="s">
         <v>127</v>
       </c>
@@ -6164,20 +6156,20 @@
       <c r="M126" s="67"/>
       <c r="N126" s="64"/>
       <c r="O126" s="69"/>
-      <c r="P126" s="202"/>
+      <c r="P126" s="147"/>
       <c r="Q126" s="65"/>
       <c r="R126" s="65"/>
       <c r="S126" s="68"/>
       <c r="T126" s="97"/>
       <c r="U126" s="65"/>
-      <c r="V126" s="199"/>
+      <c r="V126" s="144"/>
       <c r="W126" s="68"/>
-      <c r="X126" s="283" t="s">
+      <c r="X126" s="221" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="127" spans="5:24" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="E127" s="171"/>
+      <c r="E127" s="297"/>
       <c r="F127" s="90" t="s">
         <v>128</v>
       </c>
@@ -6190,57 +6182,21 @@
       <c r="M127" s="80"/>
       <c r="N127" s="70"/>
       <c r="O127" s="73"/>
-      <c r="P127" s="204"/>
+      <c r="P127" s="149"/>
       <c r="Q127" s="72"/>
       <c r="R127" s="72"/>
       <c r="S127" s="83"/>
       <c r="T127" s="98"/>
       <c r="U127" s="72"/>
-      <c r="V127" s="248"/>
+      <c r="V127" s="188"/>
       <c r="W127" s="83"/>
-      <c r="X127" s="192" t="s">
+      <c r="X127" s="140" t="s">
         <v>104</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="S105:V105"/>
-    <mergeCell ref="S113:V113"/>
-    <mergeCell ref="S97:V97"/>
-    <mergeCell ref="E113:E121"/>
-    <mergeCell ref="E122:E124"/>
-    <mergeCell ref="E125:E127"/>
-    <mergeCell ref="E93:E96"/>
-    <mergeCell ref="G85:K85"/>
-    <mergeCell ref="L85:O85"/>
-    <mergeCell ref="P85:S85"/>
-    <mergeCell ref="T85:W85"/>
-    <mergeCell ref="E97:E104"/>
-    <mergeCell ref="E105:E112"/>
-    <mergeCell ref="E87:E92"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="T4:W4"/>
-    <mergeCell ref="T45:W45"/>
-    <mergeCell ref="E81:E84"/>
-    <mergeCell ref="N64:O64"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="E52:E57"/>
-    <mergeCell ref="E58:E63"/>
-    <mergeCell ref="E64:E70"/>
-    <mergeCell ref="E71:E77"/>
-    <mergeCell ref="N71:O71"/>
-    <mergeCell ref="E78:E80"/>
-    <mergeCell ref="P4:S4"/>
-    <mergeCell ref="P45:S45"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="E27:E37"/>
-    <mergeCell ref="E15:E18"/>
-    <mergeCell ref="E19:E22"/>
-    <mergeCell ref="E23:E26"/>
-    <mergeCell ref="E47:E51"/>
+    <mergeCell ref="E6:E14"/>
     <mergeCell ref="G45:K45"/>
     <mergeCell ref="L45:O45"/>
     <mergeCell ref="G4:K4"/>
@@ -6248,19 +6204,55 @@
     <mergeCell ref="H15:I15"/>
     <mergeCell ref="H23:I23"/>
     <mergeCell ref="H19:I19"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="E27:E37"/>
+    <mergeCell ref="E15:E18"/>
+    <mergeCell ref="E19:E22"/>
+    <mergeCell ref="E23:E26"/>
+    <mergeCell ref="E47:E51"/>
     <mergeCell ref="E38:E40"/>
     <mergeCell ref="E41:E44"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="E6:E14"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="E52:E57"/>
+    <mergeCell ref="E58:E63"/>
+    <mergeCell ref="E64:E70"/>
+    <mergeCell ref="E71:E77"/>
+    <mergeCell ref="N71:O71"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="T4:W4"/>
+    <mergeCell ref="T45:W45"/>
+    <mergeCell ref="P4:S4"/>
+    <mergeCell ref="P45:S45"/>
+    <mergeCell ref="T85:W85"/>
+    <mergeCell ref="E97:E104"/>
+    <mergeCell ref="E105:E112"/>
+    <mergeCell ref="E87:E92"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="E81:E84"/>
+    <mergeCell ref="N64:O64"/>
+    <mergeCell ref="E78:E80"/>
+    <mergeCell ref="E125:E127"/>
+    <mergeCell ref="E93:E96"/>
+    <mergeCell ref="G85:K85"/>
+    <mergeCell ref="L85:O85"/>
+    <mergeCell ref="P85:S85"/>
+    <mergeCell ref="S105:V105"/>
+    <mergeCell ref="S113:V113"/>
+    <mergeCell ref="S97:V97"/>
+    <mergeCell ref="E113:E121"/>
+    <mergeCell ref="E122:E124"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="22" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:W61"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6270,136 +6262,136 @@
   <sheetData>
     <row r="3" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F4" s="130" t="s">
+      <c r="F4" s="328" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="131"/>
-      <c r="H4" s="131"/>
-      <c r="I4" s="131"/>
-      <c r="J4" s="131"/>
-      <c r="K4" s="131"/>
-      <c r="L4" s="131"/>
-      <c r="M4" s="131"/>
-      <c r="N4" s="131"/>
-      <c r="O4" s="131"/>
-      <c r="P4" s="131"/>
-      <c r="Q4" s="131"/>
-      <c r="R4" s="131"/>
-      <c r="S4" s="131"/>
-      <c r="T4" s="131"/>
-      <c r="U4" s="131"/>
-      <c r="V4" s="131"/>
-      <c r="W4" s="132"/>
+      <c r="G4" s="329"/>
+      <c r="H4" s="329"/>
+      <c r="I4" s="329"/>
+      <c r="J4" s="329"/>
+      <c r="K4" s="329"/>
+      <c r="L4" s="329"/>
+      <c r="M4" s="329"/>
+      <c r="N4" s="329"/>
+      <c r="O4" s="329"/>
+      <c r="P4" s="329"/>
+      <c r="Q4" s="329"/>
+      <c r="R4" s="329"/>
+      <c r="S4" s="329"/>
+      <c r="T4" s="329"/>
+      <c r="U4" s="329"/>
+      <c r="V4" s="329"/>
+      <c r="W4" s="330"/>
     </row>
     <row r="5" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F5" s="133"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
-      <c r="K5" s="134"/>
-      <c r="L5" s="134"/>
-      <c r="M5" s="134"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="134"/>
-      <c r="S5" s="134"/>
-      <c r="T5" s="134"/>
-      <c r="U5" s="134"/>
-      <c r="V5" s="134"/>
-      <c r="W5" s="135"/>
+      <c r="F5" s="331"/>
+      <c r="G5" s="332"/>
+      <c r="H5" s="332"/>
+      <c r="I5" s="332"/>
+      <c r="J5" s="332"/>
+      <c r="K5" s="332"/>
+      <c r="L5" s="332"/>
+      <c r="M5" s="332"/>
+      <c r="N5" s="332"/>
+      <c r="O5" s="332"/>
+      <c r="P5" s="332"/>
+      <c r="Q5" s="332"/>
+      <c r="R5" s="332"/>
+      <c r="S5" s="332"/>
+      <c r="T5" s="332"/>
+      <c r="U5" s="332"/>
+      <c r="V5" s="332"/>
+      <c r="W5" s="333"/>
     </row>
     <row r="6" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F6" s="136"/>
-      <c r="G6" s="137"/>
-      <c r="H6" s="137"/>
-      <c r="I6" s="137"/>
-      <c r="J6" s="137"/>
-      <c r="K6" s="137"/>
-      <c r="L6" s="137"/>
-      <c r="M6" s="137"/>
-      <c r="N6" s="137"/>
-      <c r="O6" s="137"/>
-      <c r="P6" s="137"/>
-      <c r="Q6" s="137"/>
-      <c r="R6" s="137"/>
-      <c r="S6" s="137"/>
-      <c r="T6" s="137"/>
-      <c r="U6" s="137"/>
-      <c r="V6" s="137"/>
-      <c r="W6" s="138"/>
+      <c r="F6" s="334"/>
+      <c r="G6" s="335"/>
+      <c r="H6" s="335"/>
+      <c r="I6" s="335"/>
+      <c r="J6" s="335"/>
+      <c r="K6" s="335"/>
+      <c r="L6" s="335"/>
+      <c r="M6" s="335"/>
+      <c r="N6" s="335"/>
+      <c r="O6" s="335"/>
+      <c r="P6" s="335"/>
+      <c r="Q6" s="335"/>
+      <c r="R6" s="335"/>
+      <c r="S6" s="335"/>
+      <c r="T6" s="335"/>
+      <c r="U6" s="335"/>
+      <c r="V6" s="335"/>
+      <c r="W6" s="336"/>
     </row>
     <row r="7" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F7" s="139" t="s">
+      <c r="F7" s="337" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="140"/>
-      <c r="H7" s="140"/>
-      <c r="I7" s="140"/>
-      <c r="J7" s="140"/>
-      <c r="K7" s="140"/>
-      <c r="L7" s="140"/>
-      <c r="M7" s="140"/>
-      <c r="N7" s="140"/>
-      <c r="O7" s="140"/>
-      <c r="P7" s="140"/>
-      <c r="Q7" s="140"/>
-      <c r="R7" s="140"/>
-      <c r="S7" s="140"/>
-      <c r="T7" s="140"/>
-      <c r="U7" s="140"/>
-      <c r="V7" s="140"/>
-      <c r="W7" s="141"/>
+      <c r="G7" s="338"/>
+      <c r="H7" s="338"/>
+      <c r="I7" s="338"/>
+      <c r="J7" s="338"/>
+      <c r="K7" s="338"/>
+      <c r="L7" s="338"/>
+      <c r="M7" s="338"/>
+      <c r="N7" s="338"/>
+      <c r="O7" s="338"/>
+      <c r="P7" s="338"/>
+      <c r="Q7" s="338"/>
+      <c r="R7" s="338"/>
+      <c r="S7" s="338"/>
+      <c r="T7" s="338"/>
+      <c r="U7" s="338"/>
+      <c r="V7" s="338"/>
+      <c r="W7" s="339"/>
     </row>
     <row r="8" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F8" s="142"/>
-      <c r="G8" s="143"/>
-      <c r="H8" s="143"/>
-      <c r="I8" s="143"/>
-      <c r="J8" s="143"/>
-      <c r="K8" s="143"/>
-      <c r="L8" s="143"/>
-      <c r="M8" s="143"/>
-      <c r="N8" s="143"/>
-      <c r="O8" s="143"/>
-      <c r="P8" s="143"/>
-      <c r="Q8" s="143"/>
-      <c r="R8" s="143"/>
-      <c r="S8" s="143"/>
-      <c r="T8" s="143"/>
-      <c r="U8" s="143"/>
-      <c r="V8" s="143"/>
-      <c r="W8" s="144"/>
+      <c r="F8" s="340"/>
+      <c r="G8" s="341"/>
+      <c r="H8" s="341"/>
+      <c r="I8" s="341"/>
+      <c r="J8" s="341"/>
+      <c r="K8" s="341"/>
+      <c r="L8" s="341"/>
+      <c r="M8" s="341"/>
+      <c r="N8" s="341"/>
+      <c r="O8" s="341"/>
+      <c r="P8" s="341"/>
+      <c r="Q8" s="341"/>
+      <c r="R8" s="341"/>
+      <c r="S8" s="341"/>
+      <c r="T8" s="341"/>
+      <c r="U8" s="341"/>
+      <c r="V8" s="341"/>
+      <c r="W8" s="342"/>
     </row>
     <row r="9" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F9" s="145" t="s">
+      <c r="F9" s="316" t="s">
         <v>0</v>
       </c>
-      <c r="G9" s="146"/>
-      <c r="H9" s="146"/>
-      <c r="I9" s="146"/>
-      <c r="J9" s="146"/>
-      <c r="K9" s="145" t="s">
+      <c r="G9" s="317"/>
+      <c r="H9" s="317"/>
+      <c r="I9" s="317"/>
+      <c r="J9" s="317"/>
+      <c r="K9" s="316" t="s">
         <v>1</v>
       </c>
-      <c r="L9" s="146"/>
-      <c r="M9" s="146"/>
-      <c r="N9" s="147"/>
-      <c r="O9" s="145" t="s">
+      <c r="L9" s="317"/>
+      <c r="M9" s="317"/>
+      <c r="N9" s="318"/>
+      <c r="O9" s="316" t="s">
         <v>12</v>
       </c>
-      <c r="P9" s="146"/>
-      <c r="Q9" s="146"/>
-      <c r="R9" s="147"/>
-      <c r="S9" s="145" t="s">
+      <c r="P9" s="317"/>
+      <c r="Q9" s="317"/>
+      <c r="R9" s="318"/>
+      <c r="S9" s="316" t="s">
         <v>13</v>
       </c>
-      <c r="T9" s="146"/>
-      <c r="U9" s="146"/>
-      <c r="V9" s="146"/>
-      <c r="W9" s="147"/>
+      <c r="T9" s="317"/>
+      <c r="U9" s="317"/>
+      <c r="V9" s="317"/>
+      <c r="W9" s="318"/>
     </row>
     <row r="10" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F10" s="3" t="s">
@@ -6488,11 +6480,11 @@
       <c r="F13" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="153" t="s">
+      <c r="G13" s="319" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="154"/>
-      <c r="I13" s="155"/>
+      <c r="H13" s="320"/>
+      <c r="I13" s="321"/>
       <c r="K13" s="4"/>
       <c r="L13" s="17"/>
       <c r="N13" s="7"/>
@@ -6751,74 +6743,74 @@
       <c r="W29" s="14"/>
     </row>
     <row r="30" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F30" s="156" t="s">
+      <c r="F30" s="322" t="s">
         <v>11</v>
       </c>
-      <c r="G30" s="157"/>
-      <c r="H30" s="157"/>
-      <c r="I30" s="157"/>
-      <c r="J30" s="157"/>
-      <c r="K30" s="157"/>
-      <c r="L30" s="157"/>
-      <c r="M30" s="157"/>
-      <c r="N30" s="157"/>
-      <c r="O30" s="157"/>
-      <c r="P30" s="157"/>
-      <c r="Q30" s="157"/>
-      <c r="R30" s="157"/>
-      <c r="S30" s="157"/>
-      <c r="T30" s="157"/>
-      <c r="U30" s="157"/>
-      <c r="V30" s="157"/>
-      <c r="W30" s="158"/>
+      <c r="G30" s="323"/>
+      <c r="H30" s="323"/>
+      <c r="I30" s="323"/>
+      <c r="J30" s="323"/>
+      <c r="K30" s="323"/>
+      <c r="L30" s="323"/>
+      <c r="M30" s="323"/>
+      <c r="N30" s="323"/>
+      <c r="O30" s="323"/>
+      <c r="P30" s="323"/>
+      <c r="Q30" s="323"/>
+      <c r="R30" s="323"/>
+      <c r="S30" s="323"/>
+      <c r="T30" s="323"/>
+      <c r="U30" s="323"/>
+      <c r="V30" s="323"/>
+      <c r="W30" s="324"/>
     </row>
     <row r="31" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F31" s="159"/>
-      <c r="G31" s="160"/>
-      <c r="H31" s="160"/>
-      <c r="I31" s="160"/>
-      <c r="J31" s="160"/>
-      <c r="K31" s="160"/>
-      <c r="L31" s="160"/>
-      <c r="M31" s="160"/>
-      <c r="N31" s="160"/>
-      <c r="O31" s="160"/>
-      <c r="P31" s="160"/>
-      <c r="Q31" s="160"/>
-      <c r="R31" s="160"/>
-      <c r="S31" s="160"/>
-      <c r="T31" s="160"/>
-      <c r="U31" s="160"/>
-      <c r="V31" s="160"/>
-      <c r="W31" s="161"/>
+      <c r="F31" s="325"/>
+      <c r="G31" s="326"/>
+      <c r="H31" s="326"/>
+      <c r="I31" s="326"/>
+      <c r="J31" s="326"/>
+      <c r="K31" s="326"/>
+      <c r="L31" s="326"/>
+      <c r="M31" s="326"/>
+      <c r="N31" s="326"/>
+      <c r="O31" s="326"/>
+      <c r="P31" s="326"/>
+      <c r="Q31" s="326"/>
+      <c r="R31" s="326"/>
+      <c r="S31" s="326"/>
+      <c r="T31" s="326"/>
+      <c r="U31" s="326"/>
+      <c r="V31" s="326"/>
+      <c r="W31" s="327"/>
     </row>
     <row r="32" spans="2:23" x14ac:dyDescent="0.3">
-      <c r="F32" s="145" t="s">
+      <c r="F32" s="316" t="s">
         <v>0</v>
       </c>
-      <c r="G32" s="146"/>
-      <c r="H32" s="146"/>
-      <c r="I32" s="146"/>
-      <c r="J32" s="146"/>
-      <c r="K32" s="145" t="s">
+      <c r="G32" s="317"/>
+      <c r="H32" s="317"/>
+      <c r="I32" s="317"/>
+      <c r="J32" s="317"/>
+      <c r="K32" s="316" t="s">
         <v>1</v>
       </c>
-      <c r="L32" s="146"/>
-      <c r="M32" s="146"/>
-      <c r="N32" s="147"/>
-      <c r="O32" s="145" t="s">
+      <c r="L32" s="317"/>
+      <c r="M32" s="317"/>
+      <c r="N32" s="318"/>
+      <c r="O32" s="316" t="s">
         <v>12</v>
       </c>
-      <c r="P32" s="146"/>
-      <c r="Q32" s="146"/>
-      <c r="R32" s="147"/>
-      <c r="S32" s="145" t="s">
+      <c r="P32" s="317"/>
+      <c r="Q32" s="317"/>
+      <c r="R32" s="318"/>
+      <c r="S32" s="316" t="s">
         <v>13</v>
       </c>
-      <c r="T32" s="146"/>
-      <c r="U32" s="146"/>
-      <c r="V32" s="146"/>
-      <c r="W32" s="147"/>
+      <c r="T32" s="317"/>
+      <c r="U32" s="317"/>
+      <c r="V32" s="317"/>
+      <c r="W32" s="318"/>
     </row>
     <row r="33" spans="2:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F33" s="3" t="s">
@@ -7107,74 +7099,74 @@
       <c r="W49" s="14"/>
     </row>
     <row r="50" spans="6:23" x14ac:dyDescent="0.3">
-      <c r="F50" s="156" t="s">
+      <c r="F50" s="322" t="s">
         <v>20</v>
       </c>
-      <c r="G50" s="157"/>
-      <c r="H50" s="157"/>
-      <c r="I50" s="157"/>
-      <c r="J50" s="157"/>
-      <c r="K50" s="157"/>
-      <c r="L50" s="157"/>
-      <c r="M50" s="157"/>
-      <c r="N50" s="157"/>
-      <c r="O50" s="157"/>
-      <c r="P50" s="157"/>
-      <c r="Q50" s="157"/>
-      <c r="R50" s="157"/>
-      <c r="S50" s="157"/>
-      <c r="T50" s="157"/>
-      <c r="U50" s="157"/>
-      <c r="V50" s="157"/>
-      <c r="W50" s="158"/>
+      <c r="G50" s="323"/>
+      <c r="H50" s="323"/>
+      <c r="I50" s="323"/>
+      <c r="J50" s="323"/>
+      <c r="K50" s="323"/>
+      <c r="L50" s="323"/>
+      <c r="M50" s="323"/>
+      <c r="N50" s="323"/>
+      <c r="O50" s="323"/>
+      <c r="P50" s="323"/>
+      <c r="Q50" s="323"/>
+      <c r="R50" s="323"/>
+      <c r="S50" s="323"/>
+      <c r="T50" s="323"/>
+      <c r="U50" s="323"/>
+      <c r="V50" s="323"/>
+      <c r="W50" s="324"/>
     </row>
     <row r="51" spans="6:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F51" s="159"/>
-      <c r="G51" s="160"/>
-      <c r="H51" s="160"/>
-      <c r="I51" s="160"/>
-      <c r="J51" s="160"/>
-      <c r="K51" s="160"/>
-      <c r="L51" s="160"/>
-      <c r="M51" s="160"/>
-      <c r="N51" s="160"/>
-      <c r="O51" s="160"/>
-      <c r="P51" s="160"/>
-      <c r="Q51" s="160"/>
-      <c r="R51" s="160"/>
-      <c r="S51" s="160"/>
-      <c r="T51" s="160"/>
-      <c r="U51" s="160"/>
-      <c r="V51" s="160"/>
-      <c r="W51" s="161"/>
+      <c r="F51" s="325"/>
+      <c r="G51" s="326"/>
+      <c r="H51" s="326"/>
+      <c r="I51" s="326"/>
+      <c r="J51" s="326"/>
+      <c r="K51" s="326"/>
+      <c r="L51" s="326"/>
+      <c r="M51" s="326"/>
+      <c r="N51" s="326"/>
+      <c r="O51" s="326"/>
+      <c r="P51" s="326"/>
+      <c r="Q51" s="326"/>
+      <c r="R51" s="326"/>
+      <c r="S51" s="326"/>
+      <c r="T51" s="326"/>
+      <c r="U51" s="326"/>
+      <c r="V51" s="326"/>
+      <c r="W51" s="327"/>
     </row>
     <row r="52" spans="6:23" x14ac:dyDescent="0.3">
-      <c r="F52" s="145" t="s">
+      <c r="F52" s="316" t="s">
         <v>0</v>
       </c>
-      <c r="G52" s="146"/>
-      <c r="H52" s="146"/>
-      <c r="I52" s="146"/>
-      <c r="J52" s="146"/>
-      <c r="K52" s="145" t="s">
+      <c r="G52" s="317"/>
+      <c r="H52" s="317"/>
+      <c r="I52" s="317"/>
+      <c r="J52" s="317"/>
+      <c r="K52" s="316" t="s">
         <v>1</v>
       </c>
-      <c r="L52" s="146"/>
-      <c r="M52" s="146"/>
-      <c r="N52" s="147"/>
-      <c r="O52" s="145" t="s">
+      <c r="L52" s="317"/>
+      <c r="M52" s="317"/>
+      <c r="N52" s="318"/>
+      <c r="O52" s="316" t="s">
         <v>12</v>
       </c>
-      <c r="P52" s="146"/>
-      <c r="Q52" s="146"/>
-      <c r="R52" s="147"/>
-      <c r="S52" s="145" t="s">
+      <c r="P52" s="317"/>
+      <c r="Q52" s="317"/>
+      <c r="R52" s="318"/>
+      <c r="S52" s="316" t="s">
         <v>13</v>
       </c>
-      <c r="T52" s="146"/>
-      <c r="U52" s="146"/>
-      <c r="V52" s="146"/>
-      <c r="W52" s="147"/>
+      <c r="T52" s="317"/>
+      <c r="U52" s="317"/>
+      <c r="V52" s="317"/>
+      <c r="W52" s="318"/>
     </row>
     <row r="53" spans="6:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="F53" s="3" t="s">
@@ -7270,12 +7262,12 @@
       <c r="L56" s="17"/>
       <c r="N56" s="7"/>
       <c r="O56" s="4"/>
-      <c r="P56" s="150" t="s">
+      <c r="P56" s="289" t="s">
         <v>16</v>
       </c>
-      <c r="Q56" s="151"/>
-      <c r="R56" s="151"/>
-      <c r="S56" s="152"/>
+      <c r="Q56" s="290"/>
+      <c r="R56" s="290"/>
+      <c r="S56" s="291"/>
       <c r="W56" s="7"/>
     </row>
     <row r="57" spans="6:23" x14ac:dyDescent="0.3">
@@ -7322,10 +7314,10 @@
       <c r="O59" s="4"/>
       <c r="R59" s="7"/>
       <c r="S59" s="4"/>
-      <c r="T59" s="148" t="s">
+      <c r="T59" s="314" t="s">
         <v>23</v>
       </c>
-      <c r="U59" s="149"/>
+      <c r="U59" s="315"/>
       <c r="W59" s="7"/>
     </row>
     <row r="60" spans="6:23" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -7363,6 +7355,12 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="F4:W6"/>
+    <mergeCell ref="F7:W8"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="S9:W9"/>
     <mergeCell ref="T59:U59"/>
     <mergeCell ref="S52:W52"/>
     <mergeCell ref="P56:S56"/>
@@ -7376,12 +7374,6 @@
     <mergeCell ref="K32:N32"/>
     <mergeCell ref="O32:R32"/>
     <mergeCell ref="S32:W32"/>
-    <mergeCell ref="F4:W6"/>
-    <mergeCell ref="F7:W8"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="S9:W9"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7390,7 +7382,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B3:U17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7399,50 +7391,50 @@
   <sheetData>
     <row r="3" spans="2:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B4" s="139" t="s">
+      <c r="B4" s="337" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="140"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="140"/>
-      <c r="F4" s="140"/>
-      <c r="G4" s="140"/>
-      <c r="H4" s="140"/>
-      <c r="I4" s="140"/>
-      <c r="J4" s="140"/>
-      <c r="K4" s="140"/>
-      <c r="L4" s="140"/>
-      <c r="M4" s="140"/>
-      <c r="N4" s="140"/>
-      <c r="O4" s="140"/>
-      <c r="P4" s="140"/>
-      <c r="Q4" s="140"/>
-      <c r="R4" s="140"/>
-      <c r="S4" s="141"/>
+      <c r="C4" s="338"/>
+      <c r="D4" s="338"/>
+      <c r="E4" s="338"/>
+      <c r="F4" s="338"/>
+      <c r="G4" s="338"/>
+      <c r="H4" s="338"/>
+      <c r="I4" s="338"/>
+      <c r="J4" s="338"/>
+      <c r="K4" s="338"/>
+      <c r="L4" s="338"/>
+      <c r="M4" s="338"/>
+      <c r="N4" s="338"/>
+      <c r="O4" s="338"/>
+      <c r="P4" s="338"/>
+      <c r="Q4" s="338"/>
+      <c r="R4" s="338"/>
+      <c r="S4" s="339"/>
     </row>
     <row r="5" spans="2:21" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="142"/>
-      <c r="C5" s="143"/>
-      <c r="D5" s="143"/>
-      <c r="E5" s="143"/>
-      <c r="F5" s="143"/>
-      <c r="G5" s="143"/>
-      <c r="H5" s="143"/>
-      <c r="I5" s="143"/>
-      <c r="J5" s="143"/>
-      <c r="K5" s="143"/>
-      <c r="L5" s="143"/>
-      <c r="M5" s="143"/>
-      <c r="N5" s="143"/>
-      <c r="O5" s="143"/>
-      <c r="P5" s="143"/>
-      <c r="Q5" s="143"/>
-      <c r="R5" s="143"/>
-      <c r="S5" s="144"/>
+      <c r="B5" s="340"/>
+      <c r="C5" s="341"/>
+      <c r="D5" s="341"/>
+      <c r="E5" s="341"/>
+      <c r="F5" s="341"/>
+      <c r="G5" s="341"/>
+      <c r="H5" s="341"/>
+      <c r="I5" s="341"/>
+      <c r="J5" s="341"/>
+      <c r="K5" s="341"/>
+      <c r="L5" s="341"/>
+      <c r="M5" s="341"/>
+      <c r="N5" s="341"/>
+      <c r="O5" s="341"/>
+      <c r="P5" s="341"/>
+      <c r="Q5" s="341"/>
+      <c r="R5" s="341"/>
+      <c r="S5" s="342"/>
     </row>
     <row r="6" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="172"/>
-      <c r="C6" s="175" t="s">
+      <c r="B6" s="343"/>
+      <c r="C6" s="346" t="s">
         <v>24</v>
       </c>
       <c r="D6" t="s">
@@ -7465,8 +7457,8 @@
       <c r="S6" s="32"/>
     </row>
     <row r="7" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="173"/>
-      <c r="C7" s="174"/>
+      <c r="B7" s="344"/>
+      <c r="C7" s="345"/>
       <c r="D7" t="s">
         <v>26</v>
       </c>
@@ -7475,8 +7467,8 @@
       </c>
     </row>
     <row r="8" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="173"/>
-      <c r="C8" s="174"/>
+      <c r="B8" s="344"/>
+      <c r="C8" s="345"/>
       <c r="D8" t="s">
         <v>28</v>
       </c>
@@ -7485,7 +7477,7 @@
       </c>
     </row>
     <row r="9" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="173"/>
+      <c r="B9" s="344"/>
       <c r="C9" s="10" t="s">
         <v>19</v>
       </c>
@@ -7497,8 +7489,8 @@
       </c>
     </row>
     <row r="10" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="173"/>
-      <c r="C10" s="174" t="s">
+      <c r="B10" s="344"/>
+      <c r="C10" s="345" t="s">
         <v>17</v>
       </c>
       <c r="D10" t="s">
@@ -7506,15 +7498,15 @@
       </c>
     </row>
     <row r="11" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="173"/>
-      <c r="C11" s="174"/>
+      <c r="B11" s="344"/>
+      <c r="C11" s="345"/>
       <c r="D11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="173"/>
-      <c r="C12" s="174" t="s">
+      <c r="B12" s="344"/>
+      <c r="C12" s="345" t="s">
         <v>18</v>
       </c>
       <c r="D12" t="s">
@@ -7525,8 +7517,8 @@
       </c>
     </row>
     <row r="13" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="173"/>
-      <c r="C13" s="174"/>
+      <c r="B13" s="344"/>
+      <c r="C13" s="345"/>
       <c r="D13" t="s">
         <v>30</v>
       </c>
@@ -7535,8 +7527,8 @@
       </c>
     </row>
     <row r="14" spans="2:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="173"/>
-      <c r="C14" s="174"/>
+      <c r="B14" s="344"/>
+      <c r="C14" s="345"/>
       <c r="D14" t="s">
         <v>29</v>
       </c>
@@ -7545,8 +7537,8 @@
       </c>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B15" s="173"/>
-      <c r="C15" s="174"/>
+      <c r="B15" s="344"/>
+      <c r="C15" s="345"/>
       <c r="D15" t="s">
         <v>33</v>
       </c>
